--- a/WorldCup2026_Sweepstake.xlsx
+++ b/WorldCup2026_Sweepstake.xlsx
@@ -706,9 +706,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -716,9 +714,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -747,9 +743,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -799,9 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -830,9 +822,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -861,9 +851,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
@@ -913,9 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
@@ -1007,9 +993,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -1052,9 +1036,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
@@ -1090,9 +1072,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
@@ -1154,7 +1134,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3136,11 +3115,11 @@
         </is>
       </c>
       <c r="H5" s="19">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),IF(E5&gt;F5,3,IF(E5=F5,1,0)),"")</f>
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),IF(E5&gt;F5,3,IF(E5=F5,2,0)),"")</f>
         <v/>
       </c>
       <c r="I5" s="19">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),IF(F5&gt;E5,3,IF(E5=F5,1,0)),"")</f>
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),IF(F5&gt;E5,3,IF(E5=F5,2,0)),"")</f>
         <v/>
       </c>
       <c r="J5" s="19">
@@ -3179,11 +3158,11 @@
         </is>
       </c>
       <c r="H6" s="19">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),IF(E6&gt;F6,3,IF(E6=F6,1,0)),"")</f>
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),IF(E6&gt;F6,3,IF(E6=F6,2,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="19">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),IF(F6&gt;E6,3,IF(E6=F6,1,0)),"")</f>
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),IF(F6&gt;E6,3,IF(E6=F6,2,0)),"")</f>
         <v/>
       </c>
       <c r="J6" s="19">
@@ -3222,11 +3201,11 @@
         </is>
       </c>
       <c r="H7" s="21">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),IF(E7&gt;F7,3,IF(E7=F7,1,0)),"")</f>
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),IF(E7&gt;F7,3,IF(E7=F7,2,0)),"")</f>
         <v/>
       </c>
       <c r="I7" s="21">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),IF(F7&gt;E7,3,IF(E7=F7,1,0)),"")</f>
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),IF(F7&gt;E7,3,IF(E7=F7,2,0)),"")</f>
         <v/>
       </c>
       <c r="J7" s="21">
@@ -3265,11 +3244,11 @@
         </is>
       </c>
       <c r="H8" s="23">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),IF(E8&gt;F8,3,IF(E8=F8,1,0)),"")</f>
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),IF(E8&gt;F8,3,IF(E8=F8,2,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="23">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),IF(F8&gt;E8,3,IF(E8=F8,1,0)),"")</f>
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),IF(F8&gt;E8,3,IF(E8=F8,2,0)),"")</f>
         <v/>
       </c>
       <c r="J8" s="23">
@@ -3308,11 +3287,11 @@
         </is>
       </c>
       <c r="H9" s="25">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),IF(E9&gt;F9,3,IF(E9=F9,1,0)),"")</f>
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),IF(E9&gt;F9,3,IF(E9=F9,2,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="25">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),IF(F9&gt;E9,3,IF(E9=F9,1,0)),"")</f>
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),IF(F9&gt;E9,3,IF(E9=F9,2,0)),"")</f>
         <v/>
       </c>
       <c r="J9" s="25">
@@ -3351,11 +3330,11 @@
         </is>
       </c>
       <c r="H10" s="23">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),IF(E10&gt;F10,3,IF(E10=F10,1,0)),"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),IF(E10&gt;F10,3,IF(E10=F10,2,0)),"")</f>
         <v/>
       </c>
       <c r="I10" s="23">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),IF(F10&gt;E10,3,IF(E10=F10,1,0)),"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),IF(F10&gt;E10,3,IF(E10=F10,2,0)),"")</f>
         <v/>
       </c>
       <c r="J10" s="23">
@@ -3394,11 +3373,11 @@
         </is>
       </c>
       <c r="H11" s="25">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),IF(E11&gt;F11,3,IF(E11=F11,1,0)),"")</f>
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),IF(E11&gt;F11,3,IF(E11=F11,2,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="25">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),IF(F11&gt;E11,3,IF(E11=F11,1,0)),"")</f>
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),IF(F11&gt;E11,3,IF(E11=F11,2,0)),"")</f>
         <v/>
       </c>
       <c r="J11" s="25">
@@ -3437,11 +3416,11 @@
         </is>
       </c>
       <c r="H12" s="21">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),IF(E12&gt;F12,3,IF(E12=F12,1,0)),"")</f>
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),IF(E12&gt;F12,3,IF(E12=F12,2,0)),"")</f>
         <v/>
       </c>
       <c r="I12" s="21">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),IF(F12&gt;E12,3,IF(E12=F12,1,0)),"")</f>
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),IF(F12&gt;E12,3,IF(E12=F12,2,0)),"")</f>
         <v/>
       </c>
       <c r="J12" s="21">
@@ -3480,11 +3459,11 @@
         </is>
       </c>
       <c r="H13" s="27">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),IF(E13&gt;F13,3,IF(E13=F13,1,0)),"")</f>
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),IF(E13&gt;F13,3,IF(E13=F13,2,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="27">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),IF(F13&gt;E13,3,IF(E13=F13,1,0)),"")</f>
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),IF(F13&gt;E13,3,IF(E13=F13,2,0)),"")</f>
         <v/>
       </c>
       <c r="J13" s="27">
@@ -3523,11 +3502,11 @@
         </is>
       </c>
       <c r="H14" s="27">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),IF(E14&gt;F14,3,IF(E14=F14,1,0)),"")</f>
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),IF(E14&gt;F14,3,IF(E14=F14,2,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="27">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),IF(F14&gt;E14,3,IF(E14=F14,1,0)),"")</f>
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),IF(F14&gt;E14,3,IF(E14=F14,2,0)),"")</f>
         <v/>
       </c>
       <c r="J14" s="27">
@@ -3566,11 +3545,11 @@
         </is>
       </c>
       <c r="H15" s="29">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),IF(E15&gt;F15,3,IF(E15=F15,1,0)),"")</f>
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),IF(E15&gt;F15,3,IF(E15=F15,2,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="29">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),IF(F15&gt;E15,3,IF(E15=F15,1,0)),"")</f>
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),IF(F15&gt;E15,3,IF(E15=F15,2,0)),"")</f>
         <v/>
       </c>
       <c r="J15" s="29">
@@ -3609,11 +3588,11 @@
         </is>
       </c>
       <c r="H16" s="29">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),IF(E16&gt;F16,3,IF(E16=F16,1,0)),"")</f>
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),IF(E16&gt;F16,3,IF(E16=F16,2,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="29">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),IF(F16&gt;E16,3,IF(E16=F16,1,0)),"")</f>
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),IF(F16&gt;E16,3,IF(E16=F16,2,0)),"")</f>
         <v/>
       </c>
       <c r="J16" s="29">
@@ -3652,11 +3631,11 @@
         </is>
       </c>
       <c r="H17" s="31">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),IF(E17&gt;F17,3,IF(E17=F17,1,0)),"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),IF(E17&gt;F17,3,IF(E17=F17,2,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="31">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),IF(F17&gt;E17,3,IF(E17=F17,1,0)),"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),IF(F17&gt;E17,3,IF(E17=F17,2,0)),"")</f>
         <v/>
       </c>
       <c r="J17" s="31">
@@ -3695,11 +3674,11 @@
         </is>
       </c>
       <c r="H18" s="31">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),IF(E18&gt;F18,3,IF(E18=F18,1,0)),"")</f>
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),IF(E18&gt;F18,3,IF(E18=F18,2,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="31">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),IF(F18&gt;E18,3,IF(E18=F18,1,0)),"")</f>
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),IF(F18&gt;E18,3,IF(E18=F18,2,0)),"")</f>
         <v/>
       </c>
       <c r="J18" s="31">
@@ -3738,11 +3717,11 @@
         </is>
       </c>
       <c r="H19" s="33">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),IF(E19&gt;F19,3,IF(E19=F19,1,0)),"")</f>
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),IF(E19&gt;F19,3,IF(E19=F19,2,0)),"")</f>
         <v/>
       </c>
       <c r="I19" s="33">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),IF(F19&gt;E19,3,IF(E19=F19,1,0)),"")</f>
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),IF(F19&gt;E19,3,IF(E19=F19,2,0)),"")</f>
         <v/>
       </c>
       <c r="J19" s="33">
@@ -3781,11 +3760,11 @@
         </is>
       </c>
       <c r="H20" s="33">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),IF(E20&gt;F20,3,IF(E20=F20,1,0)),"")</f>
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),IF(E20&gt;F20,3,IF(E20=F20,2,0)),"")</f>
         <v/>
       </c>
       <c r="I20" s="33">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),IF(F20&gt;E20,3,IF(E20=F20,1,0)),"")</f>
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),IF(F20&gt;E20,3,IF(E20=F20,2,0)),"")</f>
         <v/>
       </c>
       <c r="J20" s="33">
@@ -3824,11 +3803,11 @@
         </is>
       </c>
       <c r="H21" s="35">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),IF(E21&gt;F21,3,IF(E21=F21,1,0)),"")</f>
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),IF(E21&gt;F21,3,IF(E21=F21,2,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="35">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),IF(F21&gt;E21,3,IF(E21=F21,1,0)),"")</f>
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),IF(F21&gt;E21,3,IF(E21=F21,2,0)),"")</f>
         <v/>
       </c>
       <c r="J21" s="35">
@@ -3867,11 +3846,11 @@
         </is>
       </c>
       <c r="H22" s="35">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),IF(E22&gt;F22,3,IF(E22=F22,1,0)),"")</f>
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),IF(E22&gt;F22,3,IF(E22=F22,2,0)),"")</f>
         <v/>
       </c>
       <c r="I22" s="35">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),IF(F22&gt;E22,3,IF(E22=F22,1,0)),"")</f>
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),IF(F22&gt;E22,3,IF(E22=F22,2,0)),"")</f>
         <v/>
       </c>
       <c r="J22" s="35">
@@ -3910,11 +3889,11 @@
         </is>
       </c>
       <c r="H23" s="37">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),IF(E23&gt;F23,3,IF(E23=F23,1,0)),"")</f>
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),IF(E23&gt;F23,3,IF(E23=F23,2,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="37">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),IF(F23&gt;E23,3,IF(E23=F23,1,0)),"")</f>
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),IF(F23&gt;E23,3,IF(E23=F23,2,0)),"")</f>
         <v/>
       </c>
       <c r="J23" s="37">
@@ -3953,11 +3932,11 @@
         </is>
       </c>
       <c r="H24" s="37">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),IF(E24&gt;F24,3,IF(E24=F24,1,0)),"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),IF(E24&gt;F24,3,IF(E24=F24,2,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="37">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),IF(F24&gt;E24,3,IF(E24=F24,1,0)),"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),IF(F24&gt;E24,3,IF(E24=F24,2,0)),"")</f>
         <v/>
       </c>
       <c r="J24" s="37">
@@ -3996,11 +3975,11 @@
         </is>
       </c>
       <c r="H25" s="39">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),IF(E25&gt;F25,3,IF(E25=F25,1,0)),"")</f>
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),IF(E25&gt;F25,3,IF(E25=F25,2,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="39">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),IF(F25&gt;E25,3,IF(E25=F25,1,0)),"")</f>
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),IF(F25&gt;E25,3,IF(E25=F25,2,0)),"")</f>
         <v/>
       </c>
       <c r="J25" s="39">
@@ -4039,11 +4018,11 @@
         </is>
       </c>
       <c r="H26" s="39">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),IF(E26&gt;F26,3,IF(E26=F26,1,0)),"")</f>
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),IF(E26&gt;F26,3,IF(E26=F26,2,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="39">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),IF(F26&gt;E26,3,IF(E26=F26,1,0)),"")</f>
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),IF(F26&gt;E26,3,IF(E26=F26,2,0)),"")</f>
         <v/>
       </c>
       <c r="J26" s="39">
@@ -4082,11 +4061,11 @@
         </is>
       </c>
       <c r="H27" s="41">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),IF(E27&gt;F27,3,IF(E27=F27,1,0)),"")</f>
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),IF(E27&gt;F27,3,IF(E27=F27,2,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="41">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),IF(F27&gt;E27,3,IF(E27=F27,1,0)),"")</f>
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),IF(F27&gt;E27,3,IF(E27=F27,2,0)),"")</f>
         <v/>
       </c>
       <c r="J27" s="41">
@@ -4125,11 +4104,11 @@
         </is>
       </c>
       <c r="H28" s="41">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),IF(E28&gt;F28,3,IF(E28=F28,1,0)),"")</f>
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),IF(E28&gt;F28,3,IF(E28=F28,2,0)),"")</f>
         <v/>
       </c>
       <c r="I28" s="41">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),IF(F28&gt;E28,3,IF(E28=F28,1,0)),"")</f>
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),IF(F28&gt;E28,3,IF(E28=F28,2,0)),"")</f>
         <v/>
       </c>
       <c r="J28" s="41">
@@ -4168,11 +4147,11 @@
         </is>
       </c>
       <c r="H29" s="19">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),IF(E29&gt;F29,3,IF(E29=F29,1,0)),"")</f>
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),IF(E29&gt;F29,3,IF(E29=F29,2,0)),"")</f>
         <v/>
       </c>
       <c r="I29" s="19">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),IF(F29&gt;E29,3,IF(E29=F29,1,0)),"")</f>
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),IF(F29&gt;E29,3,IF(E29=F29,2,0)),"")</f>
         <v/>
       </c>
       <c r="J29" s="19">
@@ -4211,11 +4190,11 @@
         </is>
       </c>
       <c r="H30" s="21">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),IF(E30&gt;F30,3,IF(E30=F30,1,0)),"")</f>
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),IF(E30&gt;F30,3,IF(E30=F30,2,0)),"")</f>
         <v/>
       </c>
       <c r="I30" s="21">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),IF(F30&gt;E30,3,IF(E30=F30,1,0)),"")</f>
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),IF(F30&gt;E30,3,IF(E30=F30,2,0)),"")</f>
         <v/>
       </c>
       <c r="J30" s="21">
@@ -4254,11 +4233,11 @@
         </is>
       </c>
       <c r="H31" s="21">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),IF(E31&gt;F31,3,IF(E31=F31,1,0)),"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),IF(E31&gt;F31,3,IF(E31=F31,2,0)),"")</f>
         <v/>
       </c>
       <c r="I31" s="21">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),IF(F31&gt;E31,3,IF(E31=F31,1,0)),"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),IF(F31&gt;E31,3,IF(E31=F31,2,0)),"")</f>
         <v/>
       </c>
       <c r="J31" s="21">
@@ -4297,11 +4276,11 @@
         </is>
       </c>
       <c r="H32" s="19">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),IF(E32&gt;F32,3,IF(E32=F32,1,0)),"")</f>
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),IF(E32&gt;F32,3,IF(E32=F32,2,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="19">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),IF(F32&gt;E32,3,IF(E32=F32,1,0)),"")</f>
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),IF(F32&gt;E32,3,IF(E32=F32,2,0)),"")</f>
         <v/>
       </c>
       <c r="J32" s="19">
@@ -4340,11 +4319,11 @@
         </is>
       </c>
       <c r="H33" s="25">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),IF(E33&gt;F33,3,IF(E33=F33,1,0)),"")</f>
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),IF(E33&gt;F33,3,IF(E33=F33,2,0)),"")</f>
         <v/>
       </c>
       <c r="I33" s="25">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),IF(F33&gt;E33,3,IF(E33=F33,1,0)),"")</f>
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),IF(F33&gt;E33,3,IF(E33=F33,2,0)),"")</f>
         <v/>
       </c>
       <c r="J33" s="25">
@@ -4383,11 +4362,11 @@
         </is>
       </c>
       <c r="H34" s="25">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),IF(E34&gt;F34,3,IF(E34=F34,1,0)),"")</f>
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),IF(E34&gt;F34,3,IF(E34=F34,2,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="25">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),IF(F34&gt;E34,3,IF(E34=F34,1,0)),"")</f>
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),IF(F34&gt;E34,3,IF(E34=F34,2,0)),"")</f>
         <v/>
       </c>
       <c r="J34" s="25">
@@ -4426,11 +4405,11 @@
         </is>
       </c>
       <c r="H35" s="23">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),IF(E35&gt;F35,3,IF(E35=F35,1,0)),"")</f>
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),IF(E35&gt;F35,3,IF(E35=F35,2,0)),"")</f>
         <v/>
       </c>
       <c r="I35" s="23">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),IF(F35&gt;E35,3,IF(E35=F35,1,0)),"")</f>
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),IF(F35&gt;E35,3,IF(E35=F35,2,0)),"")</f>
         <v/>
       </c>
       <c r="J35" s="23">
@@ -4469,11 +4448,11 @@
         </is>
       </c>
       <c r="H36" s="23">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),IF(E36&gt;F36,3,IF(E36=F36,1,0)),"")</f>
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),IF(E36&gt;F36,3,IF(E36=F36,2,0)),"")</f>
         <v/>
       </c>
       <c r="I36" s="23">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),IF(F36&gt;E36,3,IF(E36=F36,1,0)),"")</f>
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),IF(F36&gt;E36,3,IF(E36=F36,2,0)),"")</f>
         <v/>
       </c>
       <c r="J36" s="23">
@@ -4512,11 +4491,11 @@
         </is>
       </c>
       <c r="H37" s="27">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),IF(E37&gt;F37,3,IF(E37=F37,1,0)),"")</f>
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),IF(E37&gt;F37,3,IF(E37=F37,2,0)),"")</f>
         <v/>
       </c>
       <c r="I37" s="27">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),IF(F37&gt;E37,3,IF(E37=F37,1,0)),"")</f>
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),IF(F37&gt;E37,3,IF(E37=F37,2,0)),"")</f>
         <v/>
       </c>
       <c r="J37" s="27">
@@ -4555,11 +4534,11 @@
         </is>
       </c>
       <c r="H38" s="27">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),IF(E38&gt;F38,3,IF(E38=F38,1,0)),"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),IF(E38&gt;F38,3,IF(E38=F38,2,0)),"")</f>
         <v/>
       </c>
       <c r="I38" s="27">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),IF(F38&gt;E38,3,IF(E38=F38,1,0)),"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),IF(F38&gt;E38,3,IF(E38=F38,2,0)),"")</f>
         <v/>
       </c>
       <c r="J38" s="27">
@@ -4598,11 +4577,11 @@
         </is>
       </c>
       <c r="H39" s="29">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),IF(E39&gt;F39,3,IF(E39=F39,1,0)),"")</f>
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),IF(E39&gt;F39,3,IF(E39=F39,2,0)),"")</f>
         <v/>
       </c>
       <c r="I39" s="29">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),IF(F39&gt;E39,3,IF(E39=F39,1,0)),"")</f>
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),IF(F39&gt;E39,3,IF(E39=F39,2,0)),"")</f>
         <v/>
       </c>
       <c r="J39" s="29">
@@ -4641,11 +4620,11 @@
         </is>
       </c>
       <c r="H40" s="29">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),IF(E40&gt;F40,3,IF(E40=F40,1,0)),"")</f>
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),IF(E40&gt;F40,3,IF(E40=F40,2,0)),"")</f>
         <v/>
       </c>
       <c r="I40" s="29">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),IF(F40&gt;E40,3,IF(E40=F40,1,0)),"")</f>
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),IF(F40&gt;E40,3,IF(E40=F40,2,0)),"")</f>
         <v/>
       </c>
       <c r="J40" s="29">
@@ -4684,11 +4663,11 @@
         </is>
       </c>
       <c r="H41" s="31">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),IF(E41&gt;F41,3,IF(E41=F41,1,0)),"")</f>
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),IF(E41&gt;F41,3,IF(E41=F41,2,0)),"")</f>
         <v/>
       </c>
       <c r="I41" s="31">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),IF(F41&gt;E41,3,IF(E41=F41,1,0)),"")</f>
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),IF(F41&gt;E41,3,IF(E41=F41,2,0)),"")</f>
         <v/>
       </c>
       <c r="J41" s="31">
@@ -4727,11 +4706,11 @@
         </is>
       </c>
       <c r="H42" s="31">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),IF(E42&gt;F42,3,IF(E42=F42,1,0)),"")</f>
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),IF(E42&gt;F42,3,IF(E42=F42,2,0)),"")</f>
         <v/>
       </c>
       <c r="I42" s="31">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),IF(F42&gt;E42,3,IF(E42=F42,1,0)),"")</f>
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),IF(F42&gt;E42,3,IF(E42=F42,2,0)),"")</f>
         <v/>
       </c>
       <c r="J42" s="31">
@@ -4770,11 +4749,11 @@
         </is>
       </c>
       <c r="H43" s="33">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),IF(E43&gt;F43,3,IF(E43=F43,1,0)),"")</f>
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),IF(E43&gt;F43,3,IF(E43=F43,2,0)),"")</f>
         <v/>
       </c>
       <c r="I43" s="33">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),IF(F43&gt;E43,3,IF(E43=F43,1,0)),"")</f>
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),IF(F43&gt;E43,3,IF(E43=F43,2,0)),"")</f>
         <v/>
       </c>
       <c r="J43" s="33">
@@ -4813,11 +4792,11 @@
         </is>
       </c>
       <c r="H44" s="33">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),IF(E44&gt;F44,3,IF(E44=F44,1,0)),"")</f>
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),IF(E44&gt;F44,3,IF(E44=F44,2,0)),"")</f>
         <v/>
       </c>
       <c r="I44" s="33">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),IF(F44&gt;E44,3,IF(E44=F44,1,0)),"")</f>
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),IF(F44&gt;E44,3,IF(E44=F44,2,0)),"")</f>
         <v/>
       </c>
       <c r="J44" s="33">
@@ -4856,11 +4835,11 @@
         </is>
       </c>
       <c r="H45" s="35">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),IF(E45&gt;F45,3,IF(E45=F45,1,0)),"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),IF(E45&gt;F45,3,IF(E45=F45,2,0)),"")</f>
         <v/>
       </c>
       <c r="I45" s="35">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),IF(F45&gt;E45,3,IF(E45=F45,1,0)),"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),IF(F45&gt;E45,3,IF(E45=F45,2,0)),"")</f>
         <v/>
       </c>
       <c r="J45" s="35">
@@ -4899,11 +4878,11 @@
         </is>
       </c>
       <c r="H46" s="35">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),IF(E46&gt;F46,3,IF(E46=F46,1,0)),"")</f>
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),IF(E46&gt;F46,3,IF(E46=F46,2,0)),"")</f>
         <v/>
       </c>
       <c r="I46" s="35">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),IF(F46&gt;E46,3,IF(E46=F46,1,0)),"")</f>
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),IF(F46&gt;E46,3,IF(E46=F46,2,0)),"")</f>
         <v/>
       </c>
       <c r="J46" s="35">
@@ -4942,11 +4921,11 @@
         </is>
       </c>
       <c r="H47" s="37">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),IF(E47&gt;F47,3,IF(E47=F47,1,0)),"")</f>
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),IF(E47&gt;F47,3,IF(E47=F47,2,0)),"")</f>
         <v/>
       </c>
       <c r="I47" s="37">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),IF(F47&gt;E47,3,IF(E47=F47,1,0)),"")</f>
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),IF(F47&gt;E47,3,IF(E47=F47,2,0)),"")</f>
         <v/>
       </c>
       <c r="J47" s="37">
@@ -4985,11 +4964,11 @@
         </is>
       </c>
       <c r="H48" s="37">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),IF(E48&gt;F48,3,IF(E48=F48,1,0)),"")</f>
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),IF(E48&gt;F48,3,IF(E48=F48,2,0)),"")</f>
         <v/>
       </c>
       <c r="I48" s="37">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),IF(F48&gt;E48,3,IF(E48=F48,1,0)),"")</f>
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),IF(F48&gt;E48,3,IF(E48=F48,2,0)),"")</f>
         <v/>
       </c>
       <c r="J48" s="37">
@@ -5028,11 +5007,11 @@
         </is>
       </c>
       <c r="H49" s="39">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),IF(E49&gt;F49,3,IF(E49=F49,1,0)),"")</f>
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),IF(E49&gt;F49,3,IF(E49=F49,2,0)),"")</f>
         <v/>
       </c>
       <c r="I49" s="39">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),IF(F49&gt;E49,3,IF(E49=F49,1,0)),"")</f>
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),IF(F49&gt;E49,3,IF(E49=F49,2,0)),"")</f>
         <v/>
       </c>
       <c r="J49" s="39">
@@ -5071,11 +5050,11 @@
         </is>
       </c>
       <c r="H50" s="39">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),IF(E50&gt;F50,3,IF(E50=F50,1,0)),"")</f>
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),IF(E50&gt;F50,3,IF(E50=F50,2,0)),"")</f>
         <v/>
       </c>
       <c r="I50" s="39">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),IF(F50&gt;E50,3,IF(E50=F50,1,0)),"")</f>
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),IF(F50&gt;E50,3,IF(E50=F50,2,0)),"")</f>
         <v/>
       </c>
       <c r="J50" s="39">
@@ -5114,11 +5093,11 @@
         </is>
       </c>
       <c r="H51" s="41">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),IF(E51&gt;F51,3,IF(E51=F51,1,0)),"")</f>
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),IF(E51&gt;F51,3,IF(E51=F51,2,0)),"")</f>
         <v/>
       </c>
       <c r="I51" s="41">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),IF(F51&gt;E51,3,IF(E51=F51,1,0)),"")</f>
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),IF(F51&gt;E51,3,IF(E51=F51,2,0)),"")</f>
         <v/>
       </c>
       <c r="J51" s="41">
@@ -5157,11 +5136,11 @@
         </is>
       </c>
       <c r="H52" s="41">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),IF(E52&gt;F52,3,IF(E52=F52,1,0)),"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),IF(E52&gt;F52,3,IF(E52=F52,2,0)),"")</f>
         <v/>
       </c>
       <c r="I52" s="41">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),IF(F52&gt;E52,3,IF(E52=F52,1,0)),"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),IF(F52&gt;E52,3,IF(E52=F52,2,0)),"")</f>
         <v/>
       </c>
       <c r="J52" s="41">
@@ -5200,11 +5179,11 @@
         </is>
       </c>
       <c r="H53" s="25">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),IF(E53&gt;F53,3,IF(E53=F53,1,0)),"")</f>
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),IF(E53&gt;F53,3,IF(E53=F53,2,0)),"")</f>
         <v/>
       </c>
       <c r="I53" s="25">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),IF(F53&gt;E53,3,IF(E53=F53,1,0)),"")</f>
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),IF(F53&gt;E53,3,IF(E53=F53,2,0)),"")</f>
         <v/>
       </c>
       <c r="J53" s="25">
@@ -5243,11 +5222,11 @@
         </is>
       </c>
       <c r="H54" s="25">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),IF(E54&gt;F54,3,IF(E54=F54,1,0)),"")</f>
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),IF(E54&gt;F54,3,IF(E54=F54,2,0)),"")</f>
         <v/>
       </c>
       <c r="I54" s="25">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),IF(F54&gt;E54,3,IF(E54=F54,1,0)),"")</f>
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),IF(F54&gt;E54,3,IF(E54=F54,2,0)),"")</f>
         <v/>
       </c>
       <c r="J54" s="25">
@@ -5286,11 +5265,11 @@
         </is>
       </c>
       <c r="H55" s="21">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),IF(E55&gt;F55,3,IF(E55=F55,1,0)),"")</f>
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),IF(E55&gt;F55,3,IF(E55=F55,2,0)),"")</f>
         <v/>
       </c>
       <c r="I55" s="21">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),IF(F55&gt;E55,3,IF(E55=F55,1,0)),"")</f>
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),IF(F55&gt;E55,3,IF(E55=F55,2,0)),"")</f>
         <v/>
       </c>
       <c r="J55" s="21">
@@ -5329,11 +5308,11 @@
         </is>
       </c>
       <c r="H56" s="21">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),IF(E56&gt;F56,3,IF(E56=F56,1,0)),"")</f>
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),IF(E56&gt;F56,3,IF(E56=F56,2,0)),"")</f>
         <v/>
       </c>
       <c r="I56" s="21">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),IF(F56&gt;E56,3,IF(E56=F56,1,0)),"")</f>
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),IF(F56&gt;E56,3,IF(E56=F56,2,0)),"")</f>
         <v/>
       </c>
       <c r="J56" s="21">
@@ -5372,11 +5351,11 @@
         </is>
       </c>
       <c r="H57" s="19">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),IF(E57&gt;F57,3,IF(E57=F57,1,0)),"")</f>
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),IF(E57&gt;F57,3,IF(E57=F57,2,0)),"")</f>
         <v/>
       </c>
       <c r="I57" s="19">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),IF(F57&gt;E57,3,IF(E57=F57,1,0)),"")</f>
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),IF(F57&gt;E57,3,IF(E57=F57,2,0)),"")</f>
         <v/>
       </c>
       <c r="J57" s="19">
@@ -5415,11 +5394,11 @@
         </is>
       </c>
       <c r="H58" s="19">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),IF(E58&gt;F58,3,IF(E58=F58,1,0)),"")</f>
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),IF(E58&gt;F58,3,IF(E58=F58,2,0)),"")</f>
         <v/>
       </c>
       <c r="I58" s="19">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),IF(F58&gt;E58,3,IF(E58=F58,1,0)),"")</f>
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),IF(F58&gt;E58,3,IF(E58=F58,2,0)),"")</f>
         <v/>
       </c>
       <c r="J58" s="19">
@@ -5458,11 +5437,11 @@
         </is>
       </c>
       <c r="H59" s="27">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),IF(E59&gt;F59,3,IF(E59=F59,1,0)),"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),IF(E59&gt;F59,3,IF(E59=F59,2,0)),"")</f>
         <v/>
       </c>
       <c r="I59" s="27">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),IF(F59&gt;E59,3,IF(E59=F59,1,0)),"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),IF(F59&gt;E59,3,IF(E59=F59,2,0)),"")</f>
         <v/>
       </c>
       <c r="J59" s="27">
@@ -5501,11 +5480,11 @@
         </is>
       </c>
       <c r="H60" s="27">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),IF(E60&gt;F60,3,IF(E60=F60,1,0)),"")</f>
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),IF(E60&gt;F60,3,IF(E60=F60,2,0)),"")</f>
         <v/>
       </c>
       <c r="I60" s="27">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),IF(F60&gt;E60,3,IF(E60=F60,1,0)),"")</f>
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),IF(F60&gt;E60,3,IF(E60=F60,2,0)),"")</f>
         <v/>
       </c>
       <c r="J60" s="27">
@@ -5544,11 +5523,11 @@
         </is>
       </c>
       <c r="H61" s="29">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),IF(E61&gt;F61,3,IF(E61=F61,1,0)),"")</f>
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),IF(E61&gt;F61,3,IF(E61=F61,2,0)),"")</f>
         <v/>
       </c>
       <c r="I61" s="29">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),IF(F61&gt;E61,3,IF(E61=F61,1,0)),"")</f>
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),IF(F61&gt;E61,3,IF(E61=F61,2,0)),"")</f>
         <v/>
       </c>
       <c r="J61" s="29">
@@ -5587,11 +5566,11 @@
         </is>
       </c>
       <c r="H62" s="29">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),IF(E62&gt;F62,3,IF(E62=F62,1,0)),"")</f>
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),IF(E62&gt;F62,3,IF(E62=F62,2,0)),"")</f>
         <v/>
       </c>
       <c r="I62" s="29">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),IF(F62&gt;E62,3,IF(E62=F62,1,0)),"")</f>
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),IF(F62&gt;E62,3,IF(E62=F62,2,0)),"")</f>
         <v/>
       </c>
       <c r="J62" s="29">
@@ -5630,11 +5609,11 @@
         </is>
       </c>
       <c r="H63" s="23">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),IF(E63&gt;F63,3,IF(E63=F63,1,0)),"")</f>
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),IF(E63&gt;F63,3,IF(E63=F63,2,0)),"")</f>
         <v/>
       </c>
       <c r="I63" s="23">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),IF(F63&gt;E63,3,IF(E63=F63,1,0)),"")</f>
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),IF(F63&gt;E63,3,IF(E63=F63,2,0)),"")</f>
         <v/>
       </c>
       <c r="J63" s="23">
@@ -5673,11 +5652,11 @@
         </is>
       </c>
       <c r="H64" s="23">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),IF(E64&gt;F64,3,IF(E64=F64,1,0)),"")</f>
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),IF(E64&gt;F64,3,IF(E64=F64,2,0)),"")</f>
         <v/>
       </c>
       <c r="I64" s="23">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),IF(F64&gt;E64,3,IF(E64=F64,1,0)),"")</f>
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),IF(F64&gt;E64,3,IF(E64=F64,2,0)),"")</f>
         <v/>
       </c>
       <c r="J64" s="23">
@@ -5716,11 +5695,11 @@
         </is>
       </c>
       <c r="H65" s="35">
-        <f>IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),IF(E65&gt;F65,3,IF(E65=F65,1,0)),"")</f>
+        <f>IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),IF(E65&gt;F65,3,IF(E65=F65,2,0)),"")</f>
         <v/>
       </c>
       <c r="I65" s="35">
-        <f>IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),IF(F65&gt;E65,3,IF(E65=F65,1,0)),"")</f>
+        <f>IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),IF(F65&gt;E65,3,IF(E65=F65,2,0)),"")</f>
         <v/>
       </c>
       <c r="J65" s="35">
@@ -5759,11 +5738,11 @@
         </is>
       </c>
       <c r="H66" s="35">
-        <f>IF(AND(E66&lt;&gt;"",F66&lt;&gt;""),IF(E66&gt;F66,3,IF(E66=F66,1,0)),"")</f>
+        <f>IF(AND(E66&lt;&gt;"",F66&lt;&gt;""),IF(E66&gt;F66,3,IF(E66=F66,2,0)),"")</f>
         <v/>
       </c>
       <c r="I66" s="35">
-        <f>IF(AND(E66&lt;&gt;"",F66&lt;&gt;""),IF(F66&gt;E66,3,IF(E66=F66,1,0)),"")</f>
+        <f>IF(AND(E66&lt;&gt;"",F66&lt;&gt;""),IF(F66&gt;E66,3,IF(E66=F66,2,0)),"")</f>
         <v/>
       </c>
       <c r="J66" s="35">
@@ -5802,11 +5781,11 @@
         </is>
       </c>
       <c r="H67" s="33">
-        <f>IF(AND(E67&lt;&gt;"",F67&lt;&gt;""),IF(E67&gt;F67,3,IF(E67=F67,1,0)),"")</f>
+        <f>IF(AND(E67&lt;&gt;"",F67&lt;&gt;""),IF(E67&gt;F67,3,IF(E67=F67,2,0)),"")</f>
         <v/>
       </c>
       <c r="I67" s="33">
-        <f>IF(AND(E67&lt;&gt;"",F67&lt;&gt;""),IF(F67&gt;E67,3,IF(E67=F67,1,0)),"")</f>
+        <f>IF(AND(E67&lt;&gt;"",F67&lt;&gt;""),IF(F67&gt;E67,3,IF(E67=F67,2,0)),"")</f>
         <v/>
       </c>
       <c r="J67" s="33">
@@ -5845,11 +5824,11 @@
         </is>
       </c>
       <c r="H68" s="33">
-        <f>IF(AND(E68&lt;&gt;"",F68&lt;&gt;""),IF(E68&gt;F68,3,IF(E68=F68,1,0)),"")</f>
+        <f>IF(AND(E68&lt;&gt;"",F68&lt;&gt;""),IF(E68&gt;F68,3,IF(E68=F68,2,0)),"")</f>
         <v/>
       </c>
       <c r="I68" s="33">
-        <f>IF(AND(E68&lt;&gt;"",F68&lt;&gt;""),IF(F68&gt;E68,3,IF(E68=F68,1,0)),"")</f>
+        <f>IF(AND(E68&lt;&gt;"",F68&lt;&gt;""),IF(F68&gt;E68,3,IF(E68=F68,2,0)),"")</f>
         <v/>
       </c>
       <c r="J68" s="33">
@@ -5888,11 +5867,11 @@
         </is>
       </c>
       <c r="H69" s="31">
-        <f>IF(AND(E69&lt;&gt;"",F69&lt;&gt;""),IF(E69&gt;F69,3,IF(E69=F69,1,0)),"")</f>
+        <f>IF(AND(E69&lt;&gt;"",F69&lt;&gt;""),IF(E69&gt;F69,3,IF(E69=F69,2,0)),"")</f>
         <v/>
       </c>
       <c r="I69" s="31">
-        <f>IF(AND(E69&lt;&gt;"",F69&lt;&gt;""),IF(F69&gt;E69,3,IF(E69=F69,1,0)),"")</f>
+        <f>IF(AND(E69&lt;&gt;"",F69&lt;&gt;""),IF(F69&gt;E69,3,IF(E69=F69,2,0)),"")</f>
         <v/>
       </c>
       <c r="J69" s="31">
@@ -5931,11 +5910,11 @@
         </is>
       </c>
       <c r="H70" s="31">
-        <f>IF(AND(E70&lt;&gt;"",F70&lt;&gt;""),IF(E70&gt;F70,3,IF(E70=F70,1,0)),"")</f>
+        <f>IF(AND(E70&lt;&gt;"",F70&lt;&gt;""),IF(E70&gt;F70,3,IF(E70=F70,2,0)),"")</f>
         <v/>
       </c>
       <c r="I70" s="31">
-        <f>IF(AND(E70&lt;&gt;"",F70&lt;&gt;""),IF(F70&gt;E70,3,IF(E70=F70,1,0)),"")</f>
+        <f>IF(AND(E70&lt;&gt;"",F70&lt;&gt;""),IF(F70&gt;E70,3,IF(E70=F70,2,0)),"")</f>
         <v/>
       </c>
       <c r="J70" s="31">
@@ -5974,11 +5953,11 @@
         </is>
       </c>
       <c r="H71" s="39">
-        <f>IF(AND(E71&lt;&gt;"",F71&lt;&gt;""),IF(E71&gt;F71,3,IF(E71=F71,1,0)),"")</f>
+        <f>IF(AND(E71&lt;&gt;"",F71&lt;&gt;""),IF(E71&gt;F71,3,IF(E71=F71,2,0)),"")</f>
         <v/>
       </c>
       <c r="I71" s="39">
-        <f>IF(AND(E71&lt;&gt;"",F71&lt;&gt;""),IF(F71&gt;E71,3,IF(E71=F71,1,0)),"")</f>
+        <f>IF(AND(E71&lt;&gt;"",F71&lt;&gt;""),IF(F71&gt;E71,3,IF(E71=F71,2,0)),"")</f>
         <v/>
       </c>
       <c r="J71" s="39">
@@ -6017,11 +5996,11 @@
         </is>
       </c>
       <c r="H72" s="39">
-        <f>IF(AND(E72&lt;&gt;"",F72&lt;&gt;""),IF(E72&gt;F72,3,IF(E72=F72,1,0)),"")</f>
+        <f>IF(AND(E72&lt;&gt;"",F72&lt;&gt;""),IF(E72&gt;F72,3,IF(E72=F72,2,0)),"")</f>
         <v/>
       </c>
       <c r="I72" s="39">
-        <f>IF(AND(E72&lt;&gt;"",F72&lt;&gt;""),IF(F72&gt;E72,3,IF(E72=F72,1,0)),"")</f>
+        <f>IF(AND(E72&lt;&gt;"",F72&lt;&gt;""),IF(F72&gt;E72,3,IF(E72=F72,2,0)),"")</f>
         <v/>
       </c>
       <c r="J72" s="39">
@@ -6060,11 +6039,11 @@
         </is>
       </c>
       <c r="H73" s="37">
-        <f>IF(AND(E73&lt;&gt;"",F73&lt;&gt;""),IF(E73&gt;F73,3,IF(E73=F73,1,0)),"")</f>
+        <f>IF(AND(E73&lt;&gt;"",F73&lt;&gt;""),IF(E73&gt;F73,3,IF(E73=F73,2,0)),"")</f>
         <v/>
       </c>
       <c r="I73" s="37">
-        <f>IF(AND(E73&lt;&gt;"",F73&lt;&gt;""),IF(F73&gt;E73,3,IF(E73=F73,1,0)),"")</f>
+        <f>IF(AND(E73&lt;&gt;"",F73&lt;&gt;""),IF(F73&gt;E73,3,IF(E73=F73,2,0)),"")</f>
         <v/>
       </c>
       <c r="J73" s="37">
@@ -6103,11 +6082,11 @@
         </is>
       </c>
       <c r="H74" s="37">
-        <f>IF(AND(E74&lt;&gt;"",F74&lt;&gt;""),IF(E74&gt;F74,3,IF(E74=F74,1,0)),"")</f>
+        <f>IF(AND(E74&lt;&gt;"",F74&lt;&gt;""),IF(E74&gt;F74,3,IF(E74=F74,2,0)),"")</f>
         <v/>
       </c>
       <c r="I74" s="37">
-        <f>IF(AND(E74&lt;&gt;"",F74&lt;&gt;""),IF(F74&gt;E74,3,IF(E74=F74,1,0)),"")</f>
+        <f>IF(AND(E74&lt;&gt;"",F74&lt;&gt;""),IF(F74&gt;E74,3,IF(E74=F74,2,0)),"")</f>
         <v/>
       </c>
       <c r="J74" s="37">
@@ -6146,11 +6125,11 @@
         </is>
       </c>
       <c r="H75" s="41">
-        <f>IF(AND(E75&lt;&gt;"",F75&lt;&gt;""),IF(E75&gt;F75,3,IF(E75=F75,1,0)),"")</f>
+        <f>IF(AND(E75&lt;&gt;"",F75&lt;&gt;""),IF(E75&gt;F75,3,IF(E75=F75,2,0)),"")</f>
         <v/>
       </c>
       <c r="I75" s="41">
-        <f>IF(AND(E75&lt;&gt;"",F75&lt;&gt;""),IF(F75&gt;E75,3,IF(E75=F75,1,0)),"")</f>
+        <f>IF(AND(E75&lt;&gt;"",F75&lt;&gt;""),IF(F75&gt;E75,3,IF(E75=F75,2,0)),"")</f>
         <v/>
       </c>
       <c r="J75" s="41">
@@ -6189,11 +6168,11 @@
         </is>
       </c>
       <c r="H76" s="41">
-        <f>IF(AND(E76&lt;&gt;"",F76&lt;&gt;""),IF(E76&gt;F76,3,IF(E76=F76,1,0)),"")</f>
+        <f>IF(AND(E76&lt;&gt;"",F76&lt;&gt;""),IF(E76&gt;F76,3,IF(E76=F76,2,0)),"")</f>
         <v/>
       </c>
       <c r="I76" s="41">
-        <f>IF(AND(E76&lt;&gt;"",F76&lt;&gt;""),IF(F76&gt;E76,3,IF(E76=F76,1,0)),"")</f>
+        <f>IF(AND(E76&lt;&gt;"",F76&lt;&gt;""),IF(F76&gt;E76,3,IF(E76=F76,2,0)),"")</f>
         <v/>
       </c>
       <c r="J76" s="41">
@@ -6232,11 +6211,11 @@
         </is>
       </c>
       <c r="H77" s="43">
-        <f>IF(AND(E77&lt;&gt;"",F77&lt;&gt;""),IF(E77&gt;F77,3,IF(E77=F77,1,0)),"")</f>
+        <f>IF(AND(E77&lt;&gt;"",F77&lt;&gt;""),IF(E77&gt;F77,3,IF(E77=F77,2,0)),"")</f>
         <v/>
       </c>
       <c r="I77" s="43">
-        <f>IF(AND(E77&lt;&gt;"",F77&lt;&gt;""),IF(F77&gt;E77,3,IF(E77=F77,1,0)),"")</f>
+        <f>IF(AND(E77&lt;&gt;"",F77&lt;&gt;""),IF(F77&gt;E77,3,IF(E77=F77,2,0)),"")</f>
         <v/>
       </c>
       <c r="J77" s="43">
@@ -6275,11 +6254,11 @@
         </is>
       </c>
       <c r="H78" s="43">
-        <f>IF(AND(E78&lt;&gt;"",F78&lt;&gt;""),IF(E78&gt;F78,3,IF(E78=F78,1,0)),"")</f>
+        <f>IF(AND(E78&lt;&gt;"",F78&lt;&gt;""),IF(E78&gt;F78,3,IF(E78=F78,2,0)),"")</f>
         <v/>
       </c>
       <c r="I78" s="43">
-        <f>IF(AND(E78&lt;&gt;"",F78&lt;&gt;""),IF(F78&gt;E78,3,IF(E78=F78,1,0)),"")</f>
+        <f>IF(AND(E78&lt;&gt;"",F78&lt;&gt;""),IF(F78&gt;E78,3,IF(E78=F78,2,0)),"")</f>
         <v/>
       </c>
       <c r="J78" s="43">
@@ -6318,11 +6297,11 @@
         </is>
       </c>
       <c r="H79" s="43">
-        <f>IF(AND(E79&lt;&gt;"",F79&lt;&gt;""),IF(E79&gt;F79,3,IF(E79=F79,1,0)),"")</f>
+        <f>IF(AND(E79&lt;&gt;"",F79&lt;&gt;""),IF(E79&gt;F79,3,IF(E79=F79,2,0)),"")</f>
         <v/>
       </c>
       <c r="I79" s="43">
-        <f>IF(AND(E79&lt;&gt;"",F79&lt;&gt;""),IF(F79&gt;E79,3,IF(E79=F79,1,0)),"")</f>
+        <f>IF(AND(E79&lt;&gt;"",F79&lt;&gt;""),IF(F79&gt;E79,3,IF(E79=F79,2,0)),"")</f>
         <v/>
       </c>
       <c r="J79" s="43">
@@ -6361,11 +6340,11 @@
         </is>
       </c>
       <c r="H80" s="43">
-        <f>IF(AND(E80&lt;&gt;"",F80&lt;&gt;""),IF(E80&gt;F80,3,IF(E80=F80,1,0)),"")</f>
+        <f>IF(AND(E80&lt;&gt;"",F80&lt;&gt;""),IF(E80&gt;F80,3,IF(E80=F80,2,0)),"")</f>
         <v/>
       </c>
       <c r="I80" s="43">
-        <f>IF(AND(E80&lt;&gt;"",F80&lt;&gt;""),IF(F80&gt;E80,3,IF(E80=F80,1,0)),"")</f>
+        <f>IF(AND(E80&lt;&gt;"",F80&lt;&gt;""),IF(F80&gt;E80,3,IF(E80=F80,2,0)),"")</f>
         <v/>
       </c>
       <c r="J80" s="43">
@@ -6404,11 +6383,11 @@
         </is>
       </c>
       <c r="H81" s="43">
-        <f>IF(AND(E81&lt;&gt;"",F81&lt;&gt;""),IF(E81&gt;F81,3,IF(E81=F81,1,0)),"")</f>
+        <f>IF(AND(E81&lt;&gt;"",F81&lt;&gt;""),IF(E81&gt;F81,3,IF(E81=F81,2,0)),"")</f>
         <v/>
       </c>
       <c r="I81" s="43">
-        <f>IF(AND(E81&lt;&gt;"",F81&lt;&gt;""),IF(F81&gt;E81,3,IF(E81=F81,1,0)),"")</f>
+        <f>IF(AND(E81&lt;&gt;"",F81&lt;&gt;""),IF(F81&gt;E81,3,IF(E81=F81,2,0)),"")</f>
         <v/>
       </c>
       <c r="J81" s="43">
@@ -6447,11 +6426,11 @@
         </is>
       </c>
       <c r="H82" s="43">
-        <f>IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),IF(E82&gt;F82,3,IF(E82=F82,1,0)),"")</f>
+        <f>IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),IF(E82&gt;F82,3,IF(E82=F82,2,0)),"")</f>
         <v/>
       </c>
       <c r="I82" s="43">
-        <f>IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),IF(F82&gt;E82,3,IF(E82=F82,1,0)),"")</f>
+        <f>IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),IF(F82&gt;E82,3,IF(E82=F82,2,0)),"")</f>
         <v/>
       </c>
       <c r="J82" s="43">
@@ -6490,11 +6469,11 @@
         </is>
       </c>
       <c r="H83" s="43">
-        <f>IF(AND(E83&lt;&gt;"",F83&lt;&gt;""),IF(E83&gt;F83,3,IF(E83=F83,1,0)),"")</f>
+        <f>IF(AND(E83&lt;&gt;"",F83&lt;&gt;""),IF(E83&gt;F83,3,IF(E83=F83,2,0)),"")</f>
         <v/>
       </c>
       <c r="I83" s="43">
-        <f>IF(AND(E83&lt;&gt;"",F83&lt;&gt;""),IF(F83&gt;E83,3,IF(E83=F83,1,0)),"")</f>
+        <f>IF(AND(E83&lt;&gt;"",F83&lt;&gt;""),IF(F83&gt;E83,3,IF(E83=F83,2,0)),"")</f>
         <v/>
       </c>
       <c r="J83" s="43">
@@ -6533,11 +6512,11 @@
         </is>
       </c>
       <c r="H84" s="43">
-        <f>IF(AND(E84&lt;&gt;"",F84&lt;&gt;""),IF(E84&gt;F84,3,IF(E84=F84,1,0)),"")</f>
+        <f>IF(AND(E84&lt;&gt;"",F84&lt;&gt;""),IF(E84&gt;F84,3,IF(E84=F84,2,0)),"")</f>
         <v/>
       </c>
       <c r="I84" s="43">
-        <f>IF(AND(E84&lt;&gt;"",F84&lt;&gt;""),IF(F84&gt;E84,3,IF(E84=F84,1,0)),"")</f>
+        <f>IF(AND(E84&lt;&gt;"",F84&lt;&gt;""),IF(F84&gt;E84,3,IF(E84=F84,2,0)),"")</f>
         <v/>
       </c>
       <c r="J84" s="43">
@@ -6576,11 +6555,11 @@
         </is>
       </c>
       <c r="H85" s="43">
-        <f>IF(AND(E85&lt;&gt;"",F85&lt;&gt;""),IF(E85&gt;F85,3,IF(E85=F85,1,0)),"")</f>
+        <f>IF(AND(E85&lt;&gt;"",F85&lt;&gt;""),IF(E85&gt;F85,3,IF(E85=F85,2,0)),"")</f>
         <v/>
       </c>
       <c r="I85" s="43">
-        <f>IF(AND(E85&lt;&gt;"",F85&lt;&gt;""),IF(F85&gt;E85,3,IF(E85=F85,1,0)),"")</f>
+        <f>IF(AND(E85&lt;&gt;"",F85&lt;&gt;""),IF(F85&gt;E85,3,IF(E85=F85,2,0)),"")</f>
         <v/>
       </c>
       <c r="J85" s="43">
@@ -6619,11 +6598,11 @@
         </is>
       </c>
       <c r="H86" s="43">
-        <f>IF(AND(E86&lt;&gt;"",F86&lt;&gt;""),IF(E86&gt;F86,3,IF(E86=F86,1,0)),"")</f>
+        <f>IF(AND(E86&lt;&gt;"",F86&lt;&gt;""),IF(E86&gt;F86,3,IF(E86=F86,2,0)),"")</f>
         <v/>
       </c>
       <c r="I86" s="43">
-        <f>IF(AND(E86&lt;&gt;"",F86&lt;&gt;""),IF(F86&gt;E86,3,IF(E86=F86,1,0)),"")</f>
+        <f>IF(AND(E86&lt;&gt;"",F86&lt;&gt;""),IF(F86&gt;E86,3,IF(E86=F86,2,0)),"")</f>
         <v/>
       </c>
       <c r="J86" s="43">
@@ -6662,11 +6641,11 @@
         </is>
       </c>
       <c r="H87" s="43">
-        <f>IF(AND(E87&lt;&gt;"",F87&lt;&gt;""),IF(E87&gt;F87,3,IF(E87=F87,1,0)),"")</f>
+        <f>IF(AND(E87&lt;&gt;"",F87&lt;&gt;""),IF(E87&gt;F87,3,IF(E87=F87,2,0)),"")</f>
         <v/>
       </c>
       <c r="I87" s="43">
-        <f>IF(AND(E87&lt;&gt;"",F87&lt;&gt;""),IF(F87&gt;E87,3,IF(E87=F87,1,0)),"")</f>
+        <f>IF(AND(E87&lt;&gt;"",F87&lt;&gt;""),IF(F87&gt;E87,3,IF(E87=F87,2,0)),"")</f>
         <v/>
       </c>
       <c r="J87" s="43">
@@ -6705,11 +6684,11 @@
         </is>
       </c>
       <c r="H88" s="43">
-        <f>IF(AND(E88&lt;&gt;"",F88&lt;&gt;""),IF(E88&gt;F88,3,IF(E88=F88,1,0)),"")</f>
+        <f>IF(AND(E88&lt;&gt;"",F88&lt;&gt;""),IF(E88&gt;F88,3,IF(E88=F88,2,0)),"")</f>
         <v/>
       </c>
       <c r="I88" s="43">
-        <f>IF(AND(E88&lt;&gt;"",F88&lt;&gt;""),IF(F88&gt;E88,3,IF(E88=F88,1,0)),"")</f>
+        <f>IF(AND(E88&lt;&gt;"",F88&lt;&gt;""),IF(F88&gt;E88,3,IF(E88=F88,2,0)),"")</f>
         <v/>
       </c>
       <c r="J88" s="43">
@@ -6748,11 +6727,11 @@
         </is>
       </c>
       <c r="H89" s="43">
-        <f>IF(AND(E89&lt;&gt;"",F89&lt;&gt;""),IF(E89&gt;F89,3,IF(E89=F89,1,0)),"")</f>
+        <f>IF(AND(E89&lt;&gt;"",F89&lt;&gt;""),IF(E89&gt;F89,3,IF(E89=F89,2,0)),"")</f>
         <v/>
       </c>
       <c r="I89" s="43">
-        <f>IF(AND(E89&lt;&gt;"",F89&lt;&gt;""),IF(F89&gt;E89,3,IF(E89=F89,1,0)),"")</f>
+        <f>IF(AND(E89&lt;&gt;"",F89&lt;&gt;""),IF(F89&gt;E89,3,IF(E89=F89,2,0)),"")</f>
         <v/>
       </c>
       <c r="J89" s="43">
@@ -6791,11 +6770,11 @@
         </is>
       </c>
       <c r="H90" s="43">
-        <f>IF(AND(E90&lt;&gt;"",F90&lt;&gt;""),IF(E90&gt;F90,3,IF(E90=F90,1,0)),"")</f>
+        <f>IF(AND(E90&lt;&gt;"",F90&lt;&gt;""),IF(E90&gt;F90,3,IF(E90=F90,2,0)),"")</f>
         <v/>
       </c>
       <c r="I90" s="43">
-        <f>IF(AND(E90&lt;&gt;"",F90&lt;&gt;""),IF(F90&gt;E90,3,IF(E90=F90,1,0)),"")</f>
+        <f>IF(AND(E90&lt;&gt;"",F90&lt;&gt;""),IF(F90&gt;E90,3,IF(E90=F90,2,0)),"")</f>
         <v/>
       </c>
       <c r="J90" s="43">
@@ -6834,11 +6813,11 @@
         </is>
       </c>
       <c r="H91" s="43">
-        <f>IF(AND(E91&lt;&gt;"",F91&lt;&gt;""),IF(E91&gt;F91,3,IF(E91=F91,1,0)),"")</f>
+        <f>IF(AND(E91&lt;&gt;"",F91&lt;&gt;""),IF(E91&gt;F91,3,IF(E91=F91,2,0)),"")</f>
         <v/>
       </c>
       <c r="I91" s="43">
-        <f>IF(AND(E91&lt;&gt;"",F91&lt;&gt;""),IF(F91&gt;E91,3,IF(E91=F91,1,0)),"")</f>
+        <f>IF(AND(E91&lt;&gt;"",F91&lt;&gt;""),IF(F91&gt;E91,3,IF(E91=F91,2,0)),"")</f>
         <v/>
       </c>
       <c r="J91" s="43">
@@ -6877,11 +6856,11 @@
         </is>
       </c>
       <c r="H92" s="43">
-        <f>IF(AND(E92&lt;&gt;"",F92&lt;&gt;""),IF(E92&gt;F92,3,IF(E92=F92,1,0)),"")</f>
+        <f>IF(AND(E92&lt;&gt;"",F92&lt;&gt;""),IF(E92&gt;F92,3,IF(E92=F92,2,0)),"")</f>
         <v/>
       </c>
       <c r="I92" s="43">
-        <f>IF(AND(E92&lt;&gt;"",F92&lt;&gt;""),IF(F92&gt;E92,3,IF(E92=F92,1,0)),"")</f>
+        <f>IF(AND(E92&lt;&gt;"",F92&lt;&gt;""),IF(F92&gt;E92,3,IF(E92=F92,2,0)),"")</f>
         <v/>
       </c>
       <c r="J92" s="43">
@@ -6920,11 +6899,11 @@
         </is>
       </c>
       <c r="H93" s="43">
-        <f>IF(AND(E93&lt;&gt;"",F93&lt;&gt;""),IF(E93&gt;F93,3,IF(E93=F93,1,0)),"")</f>
+        <f>IF(AND(E93&lt;&gt;"",F93&lt;&gt;""),IF(E93&gt;F93,3,IF(E93=F93,2,0)),"")</f>
         <v/>
       </c>
       <c r="I93" s="43">
-        <f>IF(AND(E93&lt;&gt;"",F93&lt;&gt;""),IF(F93&gt;E93,3,IF(E93=F93,1,0)),"")</f>
+        <f>IF(AND(E93&lt;&gt;"",F93&lt;&gt;""),IF(F93&gt;E93,3,IF(E93=F93,2,0)),"")</f>
         <v/>
       </c>
       <c r="J93" s="43">
@@ -6963,11 +6942,11 @@
         </is>
       </c>
       <c r="H94" s="43">
-        <f>IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),IF(E94&gt;F94,3,IF(E94=F94,1,0)),"")</f>
+        <f>IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),IF(E94&gt;F94,3,IF(E94=F94,2,0)),"")</f>
         <v/>
       </c>
       <c r="I94" s="43">
-        <f>IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),IF(F94&gt;E94,3,IF(E94=F94,1,0)),"")</f>
+        <f>IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),IF(F94&gt;E94,3,IF(E94=F94,2,0)),"")</f>
         <v/>
       </c>
       <c r="J94" s="43">
@@ -7006,11 +6985,11 @@
         </is>
       </c>
       <c r="H95" s="43">
-        <f>IF(AND(E95&lt;&gt;"",F95&lt;&gt;""),IF(E95&gt;F95,3,IF(E95=F95,1,0)),"")</f>
+        <f>IF(AND(E95&lt;&gt;"",F95&lt;&gt;""),IF(E95&gt;F95,3,IF(E95=F95,2,0)),"")</f>
         <v/>
       </c>
       <c r="I95" s="43">
-        <f>IF(AND(E95&lt;&gt;"",F95&lt;&gt;""),IF(F95&gt;E95,3,IF(E95=F95,1,0)),"")</f>
+        <f>IF(AND(E95&lt;&gt;"",F95&lt;&gt;""),IF(F95&gt;E95,3,IF(E95=F95,2,0)),"")</f>
         <v/>
       </c>
       <c r="J95" s="43">
@@ -7049,11 +7028,11 @@
         </is>
       </c>
       <c r="H96" s="43">
-        <f>IF(AND(E96&lt;&gt;"",F96&lt;&gt;""),IF(E96&gt;F96,3,IF(E96=F96,1,0)),"")</f>
+        <f>IF(AND(E96&lt;&gt;"",F96&lt;&gt;""),IF(E96&gt;F96,3,IF(E96=F96,2,0)),"")</f>
         <v/>
       </c>
       <c r="I96" s="43">
-        <f>IF(AND(E96&lt;&gt;"",F96&lt;&gt;""),IF(F96&gt;E96,3,IF(E96=F96,1,0)),"")</f>
+        <f>IF(AND(E96&lt;&gt;"",F96&lt;&gt;""),IF(F96&gt;E96,3,IF(E96=F96,2,0)),"")</f>
         <v/>
       </c>
       <c r="J96" s="43">
@@ -7092,11 +7071,11 @@
         </is>
       </c>
       <c r="H97" s="43">
-        <f>IF(AND(E97&lt;&gt;"",F97&lt;&gt;""),IF(E97&gt;F97,3,IF(E97=F97,1,0)),"")</f>
+        <f>IF(AND(E97&lt;&gt;"",F97&lt;&gt;""),IF(E97&gt;F97,3,IF(E97=F97,2,0)),"")</f>
         <v/>
       </c>
       <c r="I97" s="43">
-        <f>IF(AND(E97&lt;&gt;"",F97&lt;&gt;""),IF(F97&gt;E97,3,IF(E97=F97,1,0)),"")</f>
+        <f>IF(AND(E97&lt;&gt;"",F97&lt;&gt;""),IF(F97&gt;E97,3,IF(E97=F97,2,0)),"")</f>
         <v/>
       </c>
       <c r="J97" s="43">
@@ -7135,11 +7114,11 @@
         </is>
       </c>
       <c r="H98" s="43">
-        <f>IF(AND(E98&lt;&gt;"",F98&lt;&gt;""),IF(E98&gt;F98,3,IF(E98=F98,1,0)),"")</f>
+        <f>IF(AND(E98&lt;&gt;"",F98&lt;&gt;""),IF(E98&gt;F98,3,IF(E98=F98,2,0)),"")</f>
         <v/>
       </c>
       <c r="I98" s="43">
-        <f>IF(AND(E98&lt;&gt;"",F98&lt;&gt;""),IF(F98&gt;E98,3,IF(E98=F98,1,0)),"")</f>
+        <f>IF(AND(E98&lt;&gt;"",F98&lt;&gt;""),IF(F98&gt;E98,3,IF(E98=F98,2,0)),"")</f>
         <v/>
       </c>
       <c r="J98" s="43">
@@ -7178,11 +7157,11 @@
         </is>
       </c>
       <c r="H99" s="43">
-        <f>IF(AND(E99&lt;&gt;"",F99&lt;&gt;""),IF(E99&gt;F99,3,IF(E99=F99,1,0)),"")</f>
+        <f>IF(AND(E99&lt;&gt;"",F99&lt;&gt;""),IF(E99&gt;F99,3,IF(E99=F99,2,0)),"")</f>
         <v/>
       </c>
       <c r="I99" s="43">
-        <f>IF(AND(E99&lt;&gt;"",F99&lt;&gt;""),IF(F99&gt;E99,3,IF(E99=F99,1,0)),"")</f>
+        <f>IF(AND(E99&lt;&gt;"",F99&lt;&gt;""),IF(F99&gt;E99,3,IF(E99=F99,2,0)),"")</f>
         <v/>
       </c>
       <c r="J99" s="43">
@@ -7221,11 +7200,11 @@
         </is>
       </c>
       <c r="H100" s="43">
-        <f>IF(AND(E100&lt;&gt;"",F100&lt;&gt;""),IF(E100&gt;F100,3,IF(E100=F100,1,0)),"")</f>
+        <f>IF(AND(E100&lt;&gt;"",F100&lt;&gt;""),IF(E100&gt;F100,3,IF(E100=F100,2,0)),"")</f>
         <v/>
       </c>
       <c r="I100" s="43">
-        <f>IF(AND(E100&lt;&gt;"",F100&lt;&gt;""),IF(F100&gt;E100,3,IF(E100=F100,1,0)),"")</f>
+        <f>IF(AND(E100&lt;&gt;"",F100&lt;&gt;""),IF(F100&gt;E100,3,IF(E100=F100,2,0)),"")</f>
         <v/>
       </c>
       <c r="J100" s="43">
@@ -7264,11 +7243,11 @@
         </is>
       </c>
       <c r="H101" s="43">
-        <f>IF(AND(E101&lt;&gt;"",F101&lt;&gt;""),IF(E101&gt;F101,3,IF(E101=F101,1,0)),"")</f>
+        <f>IF(AND(E101&lt;&gt;"",F101&lt;&gt;""),IF(E101&gt;F101,3,IF(E101=F101,2,0)),"")</f>
         <v/>
       </c>
       <c r="I101" s="43">
-        <f>IF(AND(E101&lt;&gt;"",F101&lt;&gt;""),IF(F101&gt;E101,3,IF(E101=F101,1,0)),"")</f>
+        <f>IF(AND(E101&lt;&gt;"",F101&lt;&gt;""),IF(F101&gt;E101,3,IF(E101=F101,2,0)),"")</f>
         <v/>
       </c>
       <c r="J101" s="43">
@@ -7307,11 +7286,11 @@
         </is>
       </c>
       <c r="H102" s="43">
-        <f>IF(AND(E102&lt;&gt;"",F102&lt;&gt;""),IF(E102&gt;F102,3,IF(E102=F102,1,0)),"")</f>
+        <f>IF(AND(E102&lt;&gt;"",F102&lt;&gt;""),IF(E102&gt;F102,3,IF(E102=F102,2,0)),"")</f>
         <v/>
       </c>
       <c r="I102" s="43">
-        <f>IF(AND(E102&lt;&gt;"",F102&lt;&gt;""),IF(F102&gt;E102,3,IF(E102=F102,1,0)),"")</f>
+        <f>IF(AND(E102&lt;&gt;"",F102&lt;&gt;""),IF(F102&gt;E102,3,IF(E102=F102,2,0)),"")</f>
         <v/>
       </c>
       <c r="J102" s="43">
@@ -7350,11 +7329,11 @@
         </is>
       </c>
       <c r="H103" s="43">
-        <f>IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),IF(E103&gt;F103,3,IF(E103=F103,1,0)),"")</f>
+        <f>IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),IF(E103&gt;F103,3,IF(E103=F103,2,0)),"")</f>
         <v/>
       </c>
       <c r="I103" s="43">
-        <f>IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),IF(F103&gt;E103,3,IF(E103=F103,1,0)),"")</f>
+        <f>IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),IF(F103&gt;E103,3,IF(E103=F103,2,0)),"")</f>
         <v/>
       </c>
       <c r="J103" s="43">
@@ -7393,11 +7372,11 @@
         </is>
       </c>
       <c r="H104" s="43">
-        <f>IF(AND(E104&lt;&gt;"",F104&lt;&gt;""),IF(E104&gt;F104,3,IF(E104=F104,1,0)),"")</f>
+        <f>IF(AND(E104&lt;&gt;"",F104&lt;&gt;""),IF(E104&gt;F104,3,IF(E104=F104,2,0)),"")</f>
         <v/>
       </c>
       <c r="I104" s="43">
-        <f>IF(AND(E104&lt;&gt;"",F104&lt;&gt;""),IF(F104&gt;E104,3,IF(E104=F104,1,0)),"")</f>
+        <f>IF(AND(E104&lt;&gt;"",F104&lt;&gt;""),IF(F104&gt;E104,3,IF(E104=F104,2,0)),"")</f>
         <v/>
       </c>
       <c r="J104" s="43">
@@ -7436,11 +7415,11 @@
         </is>
       </c>
       <c r="H105" s="43">
-        <f>IF(AND(E105&lt;&gt;"",F105&lt;&gt;""),IF(E105&gt;F105,3,IF(E105=F105,1,0)),"")</f>
+        <f>IF(AND(E105&lt;&gt;"",F105&lt;&gt;""),IF(E105&gt;F105,3,IF(E105=F105,2,0)),"")</f>
         <v/>
       </c>
       <c r="I105" s="43">
-        <f>IF(AND(E105&lt;&gt;"",F105&lt;&gt;""),IF(F105&gt;E105,3,IF(E105=F105,1,0)),"")</f>
+        <f>IF(AND(E105&lt;&gt;"",F105&lt;&gt;""),IF(F105&gt;E105,3,IF(E105=F105,2,0)),"")</f>
         <v/>
       </c>
       <c r="J105" s="43">
@@ -7479,11 +7458,11 @@
         </is>
       </c>
       <c r="H106" s="43">
-        <f>IF(AND(E106&lt;&gt;"",F106&lt;&gt;""),IF(E106&gt;F106,3,IF(E106=F106,1,0)),"")</f>
+        <f>IF(AND(E106&lt;&gt;"",F106&lt;&gt;""),IF(E106&gt;F106,3,IF(E106=F106,2,0)),"")</f>
         <v/>
       </c>
       <c r="I106" s="43">
-        <f>IF(AND(E106&lt;&gt;"",F106&lt;&gt;""),IF(F106&gt;E106,3,IF(E106=F106,1,0)),"")</f>
+        <f>IF(AND(E106&lt;&gt;"",F106&lt;&gt;""),IF(F106&gt;E106,3,IF(E106=F106,2,0)),"")</f>
         <v/>
       </c>
       <c r="J106" s="43">
@@ -7522,11 +7501,11 @@
         </is>
       </c>
       <c r="H107" s="43">
-        <f>IF(AND(E107&lt;&gt;"",F107&lt;&gt;""),IF(E107&gt;F107,3,IF(E107=F107,1,0)),"")</f>
+        <f>IF(AND(E107&lt;&gt;"",F107&lt;&gt;""),IF(E107&gt;F107,3,IF(E107=F107,2,0)),"")</f>
         <v/>
       </c>
       <c r="I107" s="43">
-        <f>IF(AND(E107&lt;&gt;"",F107&lt;&gt;""),IF(F107&gt;E107,3,IF(E107=F107,1,0)),"")</f>
+        <f>IF(AND(E107&lt;&gt;"",F107&lt;&gt;""),IF(F107&gt;E107,3,IF(E107=F107,2,0)),"")</f>
         <v/>
       </c>
       <c r="J107" s="43">
@@ -7565,11 +7544,11 @@
         </is>
       </c>
       <c r="H108" s="43">
-        <f>IF(AND(E108&lt;&gt;"",F108&lt;&gt;""),IF(E108&gt;F108,3,IF(E108=F108,1,0)),"")</f>
+        <f>IF(AND(E108&lt;&gt;"",F108&lt;&gt;""),IF(E108&gt;F108,3,IF(E108=F108,2,0)),"")</f>
         <v/>
       </c>
       <c r="I108" s="43">
-        <f>IF(AND(E108&lt;&gt;"",F108&lt;&gt;""),IF(F108&gt;E108,3,IF(E108=F108,1,0)),"")</f>
+        <f>IF(AND(E108&lt;&gt;"",F108&lt;&gt;""),IF(F108&gt;E108,3,IF(E108=F108,2,0)),"")</f>
         <v/>
       </c>
       <c r="J108" s="43">

--- a/WorldCup2026_Sweepstake.xlsx
+++ b/WorldCup2026_Sweepstake.xlsx
@@ -706,7 +706,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -714,7 +713,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -743,7 +741,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -793,7 +790,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -822,7 +818,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -851,7 +846,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
@@ -901,7 +895,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
@@ -993,7 +986,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -1036,7 +1028,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
@@ -1072,7 +1063,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
@@ -15386,7 +15376,7 @@
       </c>
       <c r="D4" s="52" t="inlineStr">
         <is>
-          <t>Enter one row per scorer per match</t>
+          <t>Enter one row per goal scorer per match (multiple scorers per match OK)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -15550,7 +15540,7 @@
         <v/>
       </c>
       <c r="S6">
-        <f>IF(OR(B6="",COUNTIF($B$6:$B6,B6)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B6,$B$6:$B$305)=1)*($R$6:$R$305&gt;R6)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B6="",COUNTIF($B$6:$B6,B6)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R6)+(($R$6:$R$305=R6)*(ROW($B$6:$B$305)&lt;ROW(B6)))))+1)</f>
         <v/>
       </c>
       <c r="T6">
@@ -15618,7 +15608,7 @@
         <v/>
       </c>
       <c r="S7">
-        <f>IF(OR(B7="",COUNTIF($B$6:$B7,B7)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B7,$B$6:$B$305)=1)*($R$6:$R$305&gt;R7)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B7="",COUNTIF($B$6:$B7,B7)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R7)+(($R$6:$R$305=R7)*(ROW($B$6:$B$305)&lt;ROW(B7)))))+1)</f>
         <v/>
       </c>
       <c r="T7">
@@ -15686,7 +15676,7 @@
         <v/>
       </c>
       <c r="S8">
-        <f>IF(OR(B8="",COUNTIF($B$6:$B8,B8)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B8,$B$6:$B$305)=1)*($R$6:$R$305&gt;R8)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B8="",COUNTIF($B$6:$B8,B8)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R8)+(($R$6:$R$305=R8)*(ROW($B$6:$B$305)&lt;ROW(B8)))))+1)</f>
         <v/>
       </c>
       <c r="T8">
@@ -15754,7 +15744,7 @@
         <v/>
       </c>
       <c r="S9">
-        <f>IF(OR(B9="",COUNTIF($B$6:$B9,B9)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B9,$B$6:$B$305)=1)*($R$6:$R$305&gt;R9)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B9="",COUNTIF($B$6:$B9,B9)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R9)+(($R$6:$R$305=R9)*(ROW($B$6:$B$305)&lt;ROW(B9)))))+1)</f>
         <v/>
       </c>
       <c r="T9">
@@ -15822,7 +15812,7 @@
         <v/>
       </c>
       <c r="S10">
-        <f>IF(OR(B10="",COUNTIF($B$6:$B10,B10)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B10,$B$6:$B$305)=1)*($R$6:$R$305&gt;R10)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B10="",COUNTIF($B$6:$B10,B10)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R10)+(($R$6:$R$305=R10)*(ROW($B$6:$B$305)&lt;ROW(B10)))))+1)</f>
         <v/>
       </c>
       <c r="T10">
@@ -15890,7 +15880,7 @@
         <v/>
       </c>
       <c r="S11">
-        <f>IF(OR(B11="",COUNTIF($B$6:$B11,B11)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B11,$B$6:$B$305)=1)*($R$6:$R$305&gt;R11)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B11="",COUNTIF($B$6:$B11,B11)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R11)+(($R$6:$R$305=R11)*(ROW($B$6:$B$305)&lt;ROW(B11)))))+1)</f>
         <v/>
       </c>
       <c r="T11">
@@ -15958,7 +15948,7 @@
         <v/>
       </c>
       <c r="S12">
-        <f>IF(OR(B12="",COUNTIF($B$6:$B12,B12)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B12,$B$6:$B$305)=1)*($R$6:$R$305&gt;R12)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B12="",COUNTIF($B$6:$B12,B12)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R12)+(($R$6:$R$305=R12)*(ROW($B$6:$B$305)&lt;ROW(B12)))))+1)</f>
         <v/>
       </c>
       <c r="T12">
@@ -16026,7 +16016,7 @@
         <v/>
       </c>
       <c r="S13">
-        <f>IF(OR(B13="",COUNTIF($B$6:$B13,B13)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B13,$B$6:$B$305)=1)*($R$6:$R$305&gt;R13)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B13="",COUNTIF($B$6:$B13,B13)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R13)+(($R$6:$R$305=R13)*(ROW($B$6:$B$305)&lt;ROW(B13)))))+1)</f>
         <v/>
       </c>
       <c r="T13">
@@ -16094,7 +16084,7 @@
         <v/>
       </c>
       <c r="S14">
-        <f>IF(OR(B14="",COUNTIF($B$6:$B14,B14)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B14,$B$6:$B$305)=1)*($R$6:$R$305&gt;R14)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B14="",COUNTIF($B$6:$B14,B14)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R14)+(($R$6:$R$305=R14)*(ROW($B$6:$B$305)&lt;ROW(B14)))))+1)</f>
         <v/>
       </c>
       <c r="T14">
@@ -16162,7 +16152,7 @@
         <v/>
       </c>
       <c r="S15">
-        <f>IF(OR(B15="",COUNTIF($B$6:$B15,B15)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B15,$B$6:$B$305)=1)*($R$6:$R$305&gt;R15)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B15="",COUNTIF($B$6:$B15,B15)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R15)+(($R$6:$R$305=R15)*(ROW($B$6:$B$305)&lt;ROW(B15)))))+1)</f>
         <v/>
       </c>
       <c r="T15">
@@ -16230,7 +16220,7 @@
         <v/>
       </c>
       <c r="S16">
-        <f>IF(OR(B16="",COUNTIF($B$6:$B16,B16)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B16,$B$6:$B$305)=1)*($R$6:$R$305&gt;R16)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B16="",COUNTIF($B$6:$B16,B16)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R16)+(($R$6:$R$305=R16)*(ROW($B$6:$B$305)&lt;ROW(B16)))))+1)</f>
         <v/>
       </c>
       <c r="T16">
@@ -16298,7 +16288,7 @@
         <v/>
       </c>
       <c r="S17">
-        <f>IF(OR(B17="",COUNTIF($B$6:$B17,B17)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B17,$B$6:$B$305)=1)*($R$6:$R$305&gt;R17)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B17="",COUNTIF($B$6:$B17,B17)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R17)+(($R$6:$R$305=R17)*(ROW($B$6:$B$305)&lt;ROW(B17)))))+1)</f>
         <v/>
       </c>
       <c r="T17">
@@ -16366,7 +16356,7 @@
         <v/>
       </c>
       <c r="S18">
-        <f>IF(OR(B18="",COUNTIF($B$6:$B18,B18)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B18,$B$6:$B$305)=1)*($R$6:$R$305&gt;R18)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B18="",COUNTIF($B$6:$B18,B18)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R18)+(($R$6:$R$305=R18)*(ROW($B$6:$B$305)&lt;ROW(B18)))))+1)</f>
         <v/>
       </c>
       <c r="T18">
@@ -16434,7 +16424,7 @@
         <v/>
       </c>
       <c r="S19">
-        <f>IF(OR(B19="",COUNTIF($B$6:$B19,B19)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B19,$B$6:$B$305)=1)*($R$6:$R$305&gt;R19)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B19="",COUNTIF($B$6:$B19,B19)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R19)+(($R$6:$R$305=R19)*(ROW($B$6:$B$305)&lt;ROW(B19)))))+1)</f>
         <v/>
       </c>
       <c r="T19">
@@ -16502,7 +16492,7 @@
         <v/>
       </c>
       <c r="S20">
-        <f>IF(OR(B20="",COUNTIF($B$6:$B20,B20)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B20,$B$6:$B$305)=1)*($R$6:$R$305&gt;R20)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B20="",COUNTIF($B$6:$B20,B20)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R20)+(($R$6:$R$305=R20)*(ROW($B$6:$B$305)&lt;ROW(B20)))))+1)</f>
         <v/>
       </c>
       <c r="T20">
@@ -16570,7 +16560,7 @@
         <v/>
       </c>
       <c r="S21">
-        <f>IF(OR(B21="",COUNTIF($B$6:$B21,B21)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B21,$B$6:$B$305)=1)*($R$6:$R$305&gt;R21)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B21="",COUNTIF($B$6:$B21,B21)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R21)+(($R$6:$R$305=R21)*(ROW($B$6:$B$305)&lt;ROW(B21)))))+1)</f>
         <v/>
       </c>
       <c r="T21">
@@ -16638,7 +16628,7 @@
         <v/>
       </c>
       <c r="S22">
-        <f>IF(OR(B22="",COUNTIF($B$6:$B22,B22)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B22,$B$6:$B$305)=1)*($R$6:$R$305&gt;R22)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B22="",COUNTIF($B$6:$B22,B22)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R22)+(($R$6:$R$305=R22)*(ROW($B$6:$B$305)&lt;ROW(B22)))))+1)</f>
         <v/>
       </c>
       <c r="T22">
@@ -16706,7 +16696,7 @@
         <v/>
       </c>
       <c r="S23">
-        <f>IF(OR(B23="",COUNTIF($B$6:$B23,B23)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B23,$B$6:$B$305)=1)*($R$6:$R$305&gt;R23)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B23="",COUNTIF($B$6:$B23,B23)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R23)+(($R$6:$R$305=R23)*(ROW($B$6:$B$305)&lt;ROW(B23)))))+1)</f>
         <v/>
       </c>
       <c r="T23">
@@ -16774,7 +16764,7 @@
         <v/>
       </c>
       <c r="S24">
-        <f>IF(OR(B24="",COUNTIF($B$6:$B24,B24)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B24,$B$6:$B$305)=1)*($R$6:$R$305&gt;R24)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B24="",COUNTIF($B$6:$B24,B24)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R24)+(($R$6:$R$305=R24)*(ROW($B$6:$B$305)&lt;ROW(B24)))))+1)</f>
         <v/>
       </c>
       <c r="T24">
@@ -16842,7 +16832,7 @@
         <v/>
       </c>
       <c r="S25">
-        <f>IF(OR(B25="",COUNTIF($B$6:$B25,B25)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B25,$B$6:$B$305)=1)*($R$6:$R$305&gt;R25)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B25="",COUNTIF($B$6:$B25,B25)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R25)+(($R$6:$R$305=R25)*(ROW($B$6:$B$305)&lt;ROW(B25)))))+1)</f>
         <v/>
       </c>
       <c r="T25">
@@ -16910,7 +16900,7 @@
         <v/>
       </c>
       <c r="S26">
-        <f>IF(OR(B26="",COUNTIF($B$6:$B26,B26)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B26,$B$6:$B$305)=1)*($R$6:$R$305&gt;R26)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B26="",COUNTIF($B$6:$B26,B26)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R26)+(($R$6:$R$305=R26)*(ROW($B$6:$B$305)&lt;ROW(B26)))))+1)</f>
         <v/>
       </c>
       <c r="T26">
@@ -16978,7 +16968,7 @@
         <v/>
       </c>
       <c r="S27">
-        <f>IF(OR(B27="",COUNTIF($B$6:$B27,B27)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B27,$B$6:$B$305)=1)*($R$6:$R$305&gt;R27)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B27="",COUNTIF($B$6:$B27,B27)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R27)+(($R$6:$R$305=R27)*(ROW($B$6:$B$305)&lt;ROW(B27)))))+1)</f>
         <v/>
       </c>
       <c r="T27">
@@ -17046,7 +17036,7 @@
         <v/>
       </c>
       <c r="S28">
-        <f>IF(OR(B28="",COUNTIF($B$6:$B28,B28)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B28,$B$6:$B$305)=1)*($R$6:$R$305&gt;R28)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B28="",COUNTIF($B$6:$B28,B28)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R28)+(($R$6:$R$305=R28)*(ROW($B$6:$B$305)&lt;ROW(B28)))))+1)</f>
         <v/>
       </c>
       <c r="T28">
@@ -17114,7 +17104,7 @@
         <v/>
       </c>
       <c r="S29">
-        <f>IF(OR(B29="",COUNTIF($B$6:$B29,B29)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B29,$B$6:$B$305)=1)*($R$6:$R$305&gt;R29)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B29="",COUNTIF($B$6:$B29,B29)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R29)+(($R$6:$R$305=R29)*(ROW($B$6:$B$305)&lt;ROW(B29)))))+1)</f>
         <v/>
       </c>
       <c r="T29">
@@ -17182,7 +17172,7 @@
         <v/>
       </c>
       <c r="S30">
-        <f>IF(OR(B30="",COUNTIF($B$6:$B30,B30)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B30,$B$6:$B$305)=1)*($R$6:$R$305&gt;R30)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B30="",COUNTIF($B$6:$B30,B30)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R30)+(($R$6:$R$305=R30)*(ROW($B$6:$B$305)&lt;ROW(B30)))))+1)</f>
         <v/>
       </c>
       <c r="T30">
@@ -17250,7 +17240,7 @@
         <v/>
       </c>
       <c r="S31">
-        <f>IF(OR(B31="",COUNTIF($B$6:$B31,B31)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B31,$B$6:$B$305)=1)*($R$6:$R$305&gt;R31)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B31="",COUNTIF($B$6:$B31,B31)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R31)+(($R$6:$R$305=R31)*(ROW($B$6:$B$305)&lt;ROW(B31)))))+1)</f>
         <v/>
       </c>
       <c r="T31">
@@ -17318,7 +17308,7 @@
         <v/>
       </c>
       <c r="S32">
-        <f>IF(OR(B32="",COUNTIF($B$6:$B32,B32)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B32,$B$6:$B$305)=1)*($R$6:$R$305&gt;R32)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B32="",COUNTIF($B$6:$B32,B32)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R32)+(($R$6:$R$305=R32)*(ROW($B$6:$B$305)&lt;ROW(B32)))))+1)</f>
         <v/>
       </c>
       <c r="T32">
@@ -17386,7 +17376,7 @@
         <v/>
       </c>
       <c r="S33">
-        <f>IF(OR(B33="",COUNTIF($B$6:$B33,B33)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B33,$B$6:$B$305)=1)*($R$6:$R$305&gt;R33)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B33="",COUNTIF($B$6:$B33,B33)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R33)+(($R$6:$R$305=R33)*(ROW($B$6:$B$305)&lt;ROW(B33)))))+1)</f>
         <v/>
       </c>
       <c r="T33">
@@ -17454,7 +17444,7 @@
         <v/>
       </c>
       <c r="S34">
-        <f>IF(OR(B34="",COUNTIF($B$6:$B34,B34)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B34,$B$6:$B$305)=1)*($R$6:$R$305&gt;R34)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B34="",COUNTIF($B$6:$B34,B34)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R34)+(($R$6:$R$305=R34)*(ROW($B$6:$B$305)&lt;ROW(B34)))))+1)</f>
         <v/>
       </c>
       <c r="T34">
@@ -17522,7 +17512,7 @@
         <v/>
       </c>
       <c r="S35">
-        <f>IF(OR(B35="",COUNTIF($B$6:$B35,B35)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B35,$B$6:$B$305)=1)*($R$6:$R$305&gt;R35)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B35="",COUNTIF($B$6:$B35,B35)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R35)+(($R$6:$R$305=R35)*(ROW($B$6:$B$305)&lt;ROW(B35)))))+1)</f>
         <v/>
       </c>
       <c r="T35">
@@ -17575,7 +17565,7 @@
         <v/>
       </c>
       <c r="S36">
-        <f>IF(OR(B36="",COUNTIF($B$6:$B36,B36)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B36,$B$6:$B$305)=1)*($R$6:$R$305&gt;R36)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B36="",COUNTIF($B$6:$B36,B36)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R36)+(($R$6:$R$305=R36)*(ROW($B$6:$B$305)&lt;ROW(B36)))))+1)</f>
         <v/>
       </c>
       <c r="T36">
@@ -17628,7 +17618,7 @@
         <v/>
       </c>
       <c r="S37">
-        <f>IF(OR(B37="",COUNTIF($B$6:$B37,B37)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B37,$B$6:$B$305)=1)*($R$6:$R$305&gt;R37)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B37="",COUNTIF($B$6:$B37,B37)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R37)+(($R$6:$R$305=R37)*(ROW($B$6:$B$305)&lt;ROW(B37)))))+1)</f>
         <v/>
       </c>
       <c r="T37">
@@ -17681,7 +17671,7 @@
         <v/>
       </c>
       <c r="S38">
-        <f>IF(OR(B38="",COUNTIF($B$6:$B38,B38)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B38,$B$6:$B$305)=1)*($R$6:$R$305&gt;R38)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B38="",COUNTIF($B$6:$B38,B38)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R38)+(($R$6:$R$305=R38)*(ROW($B$6:$B$305)&lt;ROW(B38)))))+1)</f>
         <v/>
       </c>
       <c r="T38">
@@ -17734,7 +17724,7 @@
         <v/>
       </c>
       <c r="S39">
-        <f>IF(OR(B39="",COUNTIF($B$6:$B39,B39)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B39,$B$6:$B$305)=1)*($R$6:$R$305&gt;R39)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B39="",COUNTIF($B$6:$B39,B39)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R39)+(($R$6:$R$305=R39)*(ROW($B$6:$B$305)&lt;ROW(B39)))))+1)</f>
         <v/>
       </c>
       <c r="T39">
@@ -17787,7 +17777,7 @@
         <v/>
       </c>
       <c r="S40">
-        <f>IF(OR(B40="",COUNTIF($B$6:$B40,B40)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B40,$B$6:$B$305)=1)*($R$6:$R$305&gt;R40)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B40="",COUNTIF($B$6:$B40,B40)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R40)+(($R$6:$R$305=R40)*(ROW($B$6:$B$305)&lt;ROW(B40)))))+1)</f>
         <v/>
       </c>
       <c r="T40">
@@ -17840,7 +17830,7 @@
         <v/>
       </c>
       <c r="S41">
-        <f>IF(OR(B41="",COUNTIF($B$6:$B41,B41)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B41,$B$6:$B$305)=1)*($R$6:$R$305&gt;R41)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B41="",COUNTIF($B$6:$B41,B41)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R41)+(($R$6:$R$305=R41)*(ROW($B$6:$B$305)&lt;ROW(B41)))))+1)</f>
         <v/>
       </c>
       <c r="T41">
@@ -17893,7 +17883,7 @@
         <v/>
       </c>
       <c r="S42">
-        <f>IF(OR(B42="",COUNTIF($B$6:$B42,B42)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B42,$B$6:$B$305)=1)*($R$6:$R$305&gt;R42)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B42="",COUNTIF($B$6:$B42,B42)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R42)+(($R$6:$R$305=R42)*(ROW($B$6:$B$305)&lt;ROW(B42)))))+1)</f>
         <v/>
       </c>
       <c r="T42">
@@ -17946,7 +17936,7 @@
         <v/>
       </c>
       <c r="S43">
-        <f>IF(OR(B43="",COUNTIF($B$6:$B43,B43)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B43,$B$6:$B$305)=1)*($R$6:$R$305&gt;R43)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B43="",COUNTIF($B$6:$B43,B43)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R43)+(($R$6:$R$305=R43)*(ROW($B$6:$B$305)&lt;ROW(B43)))))+1)</f>
         <v/>
       </c>
       <c r="T43">
@@ -17999,7 +17989,7 @@
         <v/>
       </c>
       <c r="S44">
-        <f>IF(OR(B44="",COUNTIF($B$6:$B44,B44)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B44,$B$6:$B$305)=1)*($R$6:$R$305&gt;R44)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B44="",COUNTIF($B$6:$B44,B44)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R44)+(($R$6:$R$305=R44)*(ROW($B$6:$B$305)&lt;ROW(B44)))))+1)</f>
         <v/>
       </c>
       <c r="T44">
@@ -18052,7 +18042,7 @@
         <v/>
       </c>
       <c r="S45">
-        <f>IF(OR(B45="",COUNTIF($B$6:$B45,B45)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B45,$B$6:$B$305)=1)*($R$6:$R$305&gt;R45)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B45="",COUNTIF($B$6:$B45,B45)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R45)+(($R$6:$R$305=R45)*(ROW($B$6:$B$305)&lt;ROW(B45)))))+1)</f>
         <v/>
       </c>
       <c r="T45">
@@ -18105,7 +18095,7 @@
         <v/>
       </c>
       <c r="S46">
-        <f>IF(OR(B46="",COUNTIF($B$6:$B46,B46)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B46,$B$6:$B$305)=1)*($R$6:$R$305&gt;R46)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B46="",COUNTIF($B$6:$B46,B46)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R46)+(($R$6:$R$305=R46)*(ROW($B$6:$B$305)&lt;ROW(B46)))))+1)</f>
         <v/>
       </c>
       <c r="T46">
@@ -18158,7 +18148,7 @@
         <v/>
       </c>
       <c r="S47">
-        <f>IF(OR(B47="",COUNTIF($B$6:$B47,B47)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B47,$B$6:$B$305)=1)*($R$6:$R$305&gt;R47)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B47="",COUNTIF($B$6:$B47,B47)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R47)+(($R$6:$R$305=R47)*(ROW($B$6:$B$305)&lt;ROW(B47)))))+1)</f>
         <v/>
       </c>
       <c r="T47">
@@ -18211,7 +18201,7 @@
         <v/>
       </c>
       <c r="S48">
-        <f>IF(OR(B48="",COUNTIF($B$6:$B48,B48)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B48,$B$6:$B$305)=1)*($R$6:$R$305&gt;R48)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B48="",COUNTIF($B$6:$B48,B48)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R48)+(($R$6:$R$305=R48)*(ROW($B$6:$B$305)&lt;ROW(B48)))))+1)</f>
         <v/>
       </c>
       <c r="T48">
@@ -18264,7 +18254,7 @@
         <v/>
       </c>
       <c r="S49">
-        <f>IF(OR(B49="",COUNTIF($B$6:$B49,B49)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B49,$B$6:$B$305)=1)*($R$6:$R$305&gt;R49)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B49="",COUNTIF($B$6:$B49,B49)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R49)+(($R$6:$R$305=R49)*(ROW($B$6:$B$305)&lt;ROW(B49)))))+1)</f>
         <v/>
       </c>
       <c r="T49">
@@ -18317,7 +18307,7 @@
         <v/>
       </c>
       <c r="S50">
-        <f>IF(OR(B50="",COUNTIF($B$6:$B50,B50)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B50,$B$6:$B$305)=1)*($R$6:$R$305&gt;R50)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B50="",COUNTIF($B$6:$B50,B50)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R50)+(($R$6:$R$305=R50)*(ROW($B$6:$B$305)&lt;ROW(B50)))))+1)</f>
         <v/>
       </c>
       <c r="T50">
@@ -18370,7 +18360,7 @@
         <v/>
       </c>
       <c r="S51">
-        <f>IF(OR(B51="",COUNTIF($B$6:$B51,B51)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B51,$B$6:$B$305)=1)*($R$6:$R$305&gt;R51)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B51="",COUNTIF($B$6:$B51,B51)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R51)+(($R$6:$R$305=R51)*(ROW($B$6:$B$305)&lt;ROW(B51)))))+1)</f>
         <v/>
       </c>
       <c r="T51">
@@ -18423,7 +18413,7 @@
         <v/>
       </c>
       <c r="S52">
-        <f>IF(OR(B52="",COUNTIF($B$6:$B52,B52)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B52,$B$6:$B$305)=1)*($R$6:$R$305&gt;R52)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B52="",COUNTIF($B$6:$B52,B52)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R52)+(($R$6:$R$305=R52)*(ROW($B$6:$B$305)&lt;ROW(B52)))))+1)</f>
         <v/>
       </c>
       <c r="T52">
@@ -18476,7 +18466,7 @@
         <v/>
       </c>
       <c r="S53">
-        <f>IF(OR(B53="",COUNTIF($B$6:$B53,B53)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B53,$B$6:$B$305)=1)*($R$6:$R$305&gt;R53)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B53="",COUNTIF($B$6:$B53,B53)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R53)+(($R$6:$R$305=R53)*(ROW($B$6:$B$305)&lt;ROW(B53)))))+1)</f>
         <v/>
       </c>
       <c r="T53">
@@ -18529,7 +18519,7 @@
         <v/>
       </c>
       <c r="S54">
-        <f>IF(OR(B54="",COUNTIF($B$6:$B54,B54)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B54,$B$6:$B$305)=1)*($R$6:$R$305&gt;R54)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B54="",COUNTIF($B$6:$B54,B54)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R54)+(($R$6:$R$305=R54)*(ROW($B$6:$B$305)&lt;ROW(B54)))))+1)</f>
         <v/>
       </c>
       <c r="T54">
@@ -18582,7 +18572,7 @@
         <v/>
       </c>
       <c r="S55">
-        <f>IF(OR(B55="",COUNTIF($B$6:$B55,B55)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B55,$B$6:$B$305)=1)*($R$6:$R$305&gt;R55)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B55="",COUNTIF($B$6:$B55,B55)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R55)+(($R$6:$R$305=R55)*(ROW($B$6:$B$305)&lt;ROW(B55)))))+1)</f>
         <v/>
       </c>
       <c r="T55">
@@ -18620,7 +18610,7 @@
         <v/>
       </c>
       <c r="S56">
-        <f>IF(OR(B56="",COUNTIF($B$6:$B56,B56)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B56,$B$6:$B$305)=1)*($R$6:$R$305&gt;R56)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B56="",COUNTIF($B$6:$B56,B56)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R56)+(($R$6:$R$305=R56)*(ROW($B$6:$B$305)&lt;ROW(B56)))))+1)</f>
         <v/>
       </c>
       <c r="T56">
@@ -18658,7 +18648,7 @@
         <v/>
       </c>
       <c r="S57">
-        <f>IF(OR(B57="",COUNTIF($B$6:$B57,B57)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B57,$B$6:$B$305)=1)*($R$6:$R$305&gt;R57)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B57="",COUNTIF($B$6:$B57,B57)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R57)+(($R$6:$R$305=R57)*(ROW($B$6:$B$305)&lt;ROW(B57)))))+1)</f>
         <v/>
       </c>
       <c r="T57">
@@ -18696,7 +18686,7 @@
         <v/>
       </c>
       <c r="S58">
-        <f>IF(OR(B58="",COUNTIF($B$6:$B58,B58)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B58,$B$6:$B$305)=1)*($R$6:$R$305&gt;R58)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B58="",COUNTIF($B$6:$B58,B58)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R58)+(($R$6:$R$305=R58)*(ROW($B$6:$B$305)&lt;ROW(B58)))))+1)</f>
         <v/>
       </c>
       <c r="T58">
@@ -18734,7 +18724,7 @@
         <v/>
       </c>
       <c r="S59">
-        <f>IF(OR(B59="",COUNTIF($B$6:$B59,B59)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B59,$B$6:$B$305)=1)*($R$6:$R$305&gt;R59)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B59="",COUNTIF($B$6:$B59,B59)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R59)+(($R$6:$R$305=R59)*(ROW($B$6:$B$305)&lt;ROW(B59)))))+1)</f>
         <v/>
       </c>
       <c r="T59">
@@ -18772,7 +18762,7 @@
         <v/>
       </c>
       <c r="S60">
-        <f>IF(OR(B60="",COUNTIF($B$6:$B60,B60)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B60,$B$6:$B$305)=1)*($R$6:$R$305&gt;R60)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B60="",COUNTIF($B$6:$B60,B60)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R60)+(($R$6:$R$305=R60)*(ROW($B$6:$B$305)&lt;ROW(B60)))))+1)</f>
         <v/>
       </c>
       <c r="T60">
@@ -18810,7 +18800,7 @@
         <v/>
       </c>
       <c r="S61">
-        <f>IF(OR(B61="",COUNTIF($B$6:$B61,B61)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B61,$B$6:$B$305)=1)*($R$6:$R$305&gt;R61)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B61="",COUNTIF($B$6:$B61,B61)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R61)+(($R$6:$R$305=R61)*(ROW($B$6:$B$305)&lt;ROW(B61)))))+1)</f>
         <v/>
       </c>
       <c r="T61">
@@ -18848,7 +18838,7 @@
         <v/>
       </c>
       <c r="S62">
-        <f>IF(OR(B62="",COUNTIF($B$6:$B62,B62)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B62,$B$6:$B$305)=1)*($R$6:$R$305&gt;R62)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B62="",COUNTIF($B$6:$B62,B62)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R62)+(($R$6:$R$305=R62)*(ROW($B$6:$B$305)&lt;ROW(B62)))))+1)</f>
         <v/>
       </c>
       <c r="T62">
@@ -18886,7 +18876,7 @@
         <v/>
       </c>
       <c r="S63">
-        <f>IF(OR(B63="",COUNTIF($B$6:$B63,B63)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B63,$B$6:$B$305)=1)*($R$6:$R$305&gt;R63)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B63="",COUNTIF($B$6:$B63,B63)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R63)+(($R$6:$R$305=R63)*(ROW($B$6:$B$305)&lt;ROW(B63)))))+1)</f>
         <v/>
       </c>
       <c r="T63">
@@ -18924,7 +18914,7 @@
         <v/>
       </c>
       <c r="S64">
-        <f>IF(OR(B64="",COUNTIF($B$6:$B64,B64)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B64,$B$6:$B$305)=1)*($R$6:$R$305&gt;R64)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B64="",COUNTIF($B$6:$B64,B64)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R64)+(($R$6:$R$305=R64)*(ROW($B$6:$B$305)&lt;ROW(B64)))))+1)</f>
         <v/>
       </c>
       <c r="T64">
@@ -18962,7 +18952,7 @@
         <v/>
       </c>
       <c r="S65">
-        <f>IF(OR(B65="",COUNTIF($B$6:$B65,B65)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B65,$B$6:$B$305)=1)*($R$6:$R$305&gt;R65)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B65="",COUNTIF($B$6:$B65,B65)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R65)+(($R$6:$R$305=R65)*(ROW($B$6:$B$305)&lt;ROW(B65)))))+1)</f>
         <v/>
       </c>
       <c r="T65">
@@ -19000,7 +18990,7 @@
         <v/>
       </c>
       <c r="S66">
-        <f>IF(OR(B66="",COUNTIF($B$6:$B66,B66)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B66,$B$6:$B$305)=1)*($R$6:$R$305&gt;R66)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B66="",COUNTIF($B$6:$B66,B66)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R66)+(($R$6:$R$305=R66)*(ROW($B$6:$B$305)&lt;ROW(B66)))))+1)</f>
         <v/>
       </c>
       <c r="T66">
@@ -19038,7 +19028,7 @@
         <v/>
       </c>
       <c r="S67">
-        <f>IF(OR(B67="",COUNTIF($B$6:$B67,B67)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B67,$B$6:$B$305)=1)*($R$6:$R$305&gt;R67)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B67="",COUNTIF($B$6:$B67,B67)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R67)+(($R$6:$R$305=R67)*(ROW($B$6:$B$305)&lt;ROW(B67)))))+1)</f>
         <v/>
       </c>
       <c r="T67">
@@ -19076,7 +19066,7 @@
         <v/>
       </c>
       <c r="S68">
-        <f>IF(OR(B68="",COUNTIF($B$6:$B68,B68)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B68,$B$6:$B$305)=1)*($R$6:$R$305&gt;R68)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B68="",COUNTIF($B$6:$B68,B68)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R68)+(($R$6:$R$305=R68)*(ROW($B$6:$B$305)&lt;ROW(B68)))))+1)</f>
         <v/>
       </c>
       <c r="T68">
@@ -19114,7 +19104,7 @@
         <v/>
       </c>
       <c r="S69">
-        <f>IF(OR(B69="",COUNTIF($B$6:$B69,B69)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B69,$B$6:$B$305)=1)*($R$6:$R$305&gt;R69)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B69="",COUNTIF($B$6:$B69,B69)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R69)+(($R$6:$R$305=R69)*(ROW($B$6:$B$305)&lt;ROW(B69)))))+1)</f>
         <v/>
       </c>
       <c r="T69">
@@ -19152,7 +19142,7 @@
         <v/>
       </c>
       <c r="S70">
-        <f>IF(OR(B70="",COUNTIF($B$6:$B70,B70)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B70,$B$6:$B$305)=1)*($R$6:$R$305&gt;R70)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B70="",COUNTIF($B$6:$B70,B70)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R70)+(($R$6:$R$305=R70)*(ROW($B$6:$B$305)&lt;ROW(B70)))))+1)</f>
         <v/>
       </c>
       <c r="T70">
@@ -19190,7 +19180,7 @@
         <v/>
       </c>
       <c r="S71">
-        <f>IF(OR(B71="",COUNTIF($B$6:$B71,B71)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B71,$B$6:$B$305)=1)*($R$6:$R$305&gt;R71)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B71="",COUNTIF($B$6:$B71,B71)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R71)+(($R$6:$R$305=R71)*(ROW($B$6:$B$305)&lt;ROW(B71)))))+1)</f>
         <v/>
       </c>
       <c r="T71">
@@ -19228,7 +19218,7 @@
         <v/>
       </c>
       <c r="S72">
-        <f>IF(OR(B72="",COUNTIF($B$6:$B72,B72)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B72,$B$6:$B$305)=1)*($R$6:$R$305&gt;R72)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B72="",COUNTIF($B$6:$B72,B72)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R72)+(($R$6:$R$305=R72)*(ROW($B$6:$B$305)&lt;ROW(B72)))))+1)</f>
         <v/>
       </c>
       <c r="T72">
@@ -19266,7 +19256,7 @@
         <v/>
       </c>
       <c r="S73">
-        <f>IF(OR(B73="",COUNTIF($B$6:$B73,B73)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B73,$B$6:$B$305)=1)*($R$6:$R$305&gt;R73)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B73="",COUNTIF($B$6:$B73,B73)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R73)+(($R$6:$R$305=R73)*(ROW($B$6:$B$305)&lt;ROW(B73)))))+1)</f>
         <v/>
       </c>
       <c r="T73">
@@ -19304,7 +19294,7 @@
         <v/>
       </c>
       <c r="S74">
-        <f>IF(OR(B74="",COUNTIF($B$6:$B74,B74)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B74,$B$6:$B$305)=1)*($R$6:$R$305&gt;R74)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B74="",COUNTIF($B$6:$B74,B74)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R74)+(($R$6:$R$305=R74)*(ROW($B$6:$B$305)&lt;ROW(B74)))))+1)</f>
         <v/>
       </c>
       <c r="T74">
@@ -19342,7 +19332,7 @@
         <v/>
       </c>
       <c r="S75">
-        <f>IF(OR(B75="",COUNTIF($B$6:$B75,B75)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B75,$B$6:$B$305)=1)*($R$6:$R$305&gt;R75)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B75="",COUNTIF($B$6:$B75,B75)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R75)+(($R$6:$R$305=R75)*(ROW($B$6:$B$305)&lt;ROW(B75)))))+1)</f>
         <v/>
       </c>
       <c r="T75">
@@ -19380,7 +19370,7 @@
         <v/>
       </c>
       <c r="S76">
-        <f>IF(OR(B76="",COUNTIF($B$6:$B76,B76)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B76,$B$6:$B$305)=1)*($R$6:$R$305&gt;R76)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B76="",COUNTIF($B$6:$B76,B76)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R76)+(($R$6:$R$305=R76)*(ROW($B$6:$B$305)&lt;ROW(B76)))))+1)</f>
         <v/>
       </c>
       <c r="T76">
@@ -19418,7 +19408,7 @@
         <v/>
       </c>
       <c r="S77">
-        <f>IF(OR(B77="",COUNTIF($B$6:$B77,B77)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B77,$B$6:$B$305)=1)*($R$6:$R$305&gt;R77)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B77="",COUNTIF($B$6:$B77,B77)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R77)+(($R$6:$R$305=R77)*(ROW($B$6:$B$305)&lt;ROW(B77)))))+1)</f>
         <v/>
       </c>
       <c r="T77">
@@ -19456,7 +19446,7 @@
         <v/>
       </c>
       <c r="S78">
-        <f>IF(OR(B78="",COUNTIF($B$6:$B78,B78)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B78,$B$6:$B$305)=1)*($R$6:$R$305&gt;R78)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B78="",COUNTIF($B$6:$B78,B78)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R78)+(($R$6:$R$305=R78)*(ROW($B$6:$B$305)&lt;ROW(B78)))))+1)</f>
         <v/>
       </c>
       <c r="T78">
@@ -19494,7 +19484,7 @@
         <v/>
       </c>
       <c r="S79">
-        <f>IF(OR(B79="",COUNTIF($B$6:$B79,B79)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B79,$B$6:$B$305)=1)*($R$6:$R$305&gt;R79)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B79="",COUNTIF($B$6:$B79,B79)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R79)+(($R$6:$R$305=R79)*(ROW($B$6:$B$305)&lt;ROW(B79)))))+1)</f>
         <v/>
       </c>
       <c r="T79">
@@ -19532,7 +19522,7 @@
         <v/>
       </c>
       <c r="S80">
-        <f>IF(OR(B80="",COUNTIF($B$6:$B80,B80)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B80,$B$6:$B$305)=1)*($R$6:$R$305&gt;R80)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B80="",COUNTIF($B$6:$B80,B80)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R80)+(($R$6:$R$305=R80)*(ROW($B$6:$B$305)&lt;ROW(B80)))))+1)</f>
         <v/>
       </c>
       <c r="T80">
@@ -19570,7 +19560,7 @@
         <v/>
       </c>
       <c r="S81">
-        <f>IF(OR(B81="",COUNTIF($B$6:$B81,B81)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B81,$B$6:$B$305)=1)*($R$6:$R$305&gt;R81)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B81="",COUNTIF($B$6:$B81,B81)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R81)+(($R$6:$R$305=R81)*(ROW($B$6:$B$305)&lt;ROW(B81)))))+1)</f>
         <v/>
       </c>
       <c r="T81">
@@ -19608,7 +19598,7 @@
         <v/>
       </c>
       <c r="S82">
-        <f>IF(OR(B82="",COUNTIF($B$6:$B82,B82)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B82,$B$6:$B$305)=1)*($R$6:$R$305&gt;R82)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B82="",COUNTIF($B$6:$B82,B82)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R82)+(($R$6:$R$305=R82)*(ROW($B$6:$B$305)&lt;ROW(B82)))))+1)</f>
         <v/>
       </c>
       <c r="T82">
@@ -19646,7 +19636,7 @@
         <v/>
       </c>
       <c r="S83">
-        <f>IF(OR(B83="",COUNTIF($B$6:$B83,B83)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B83,$B$6:$B$305)=1)*($R$6:$R$305&gt;R83)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B83="",COUNTIF($B$6:$B83,B83)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R83)+(($R$6:$R$305=R83)*(ROW($B$6:$B$305)&lt;ROW(B83)))))+1)</f>
         <v/>
       </c>
       <c r="T83">
@@ -19684,7 +19674,7 @@
         <v/>
       </c>
       <c r="S84">
-        <f>IF(OR(B84="",COUNTIF($B$6:$B84,B84)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B84,$B$6:$B$305)=1)*($R$6:$R$305&gt;R84)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B84="",COUNTIF($B$6:$B84,B84)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R84)+(($R$6:$R$305=R84)*(ROW($B$6:$B$305)&lt;ROW(B84)))))+1)</f>
         <v/>
       </c>
       <c r="T84">
@@ -19722,7 +19712,7 @@
         <v/>
       </c>
       <c r="S85">
-        <f>IF(OR(B85="",COUNTIF($B$6:$B85,B85)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B85,$B$6:$B$305)=1)*($R$6:$R$305&gt;R85)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B85="",COUNTIF($B$6:$B85,B85)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R85)+(($R$6:$R$305=R85)*(ROW($B$6:$B$305)&lt;ROW(B85)))))+1)</f>
         <v/>
       </c>
       <c r="T85">
@@ -19760,7 +19750,7 @@
         <v/>
       </c>
       <c r="S86">
-        <f>IF(OR(B86="",COUNTIF($B$6:$B86,B86)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B86,$B$6:$B$305)=1)*($R$6:$R$305&gt;R86)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B86="",COUNTIF($B$6:$B86,B86)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R86)+(($R$6:$R$305=R86)*(ROW($B$6:$B$305)&lt;ROW(B86)))))+1)</f>
         <v/>
       </c>
       <c r="T86">
@@ -19798,7 +19788,7 @@
         <v/>
       </c>
       <c r="S87">
-        <f>IF(OR(B87="",COUNTIF($B$6:$B87,B87)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B87,$B$6:$B$305)=1)*($R$6:$R$305&gt;R87)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B87="",COUNTIF($B$6:$B87,B87)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R87)+(($R$6:$R$305=R87)*(ROW($B$6:$B$305)&lt;ROW(B87)))))+1)</f>
         <v/>
       </c>
       <c r="T87">
@@ -19836,7 +19826,7 @@
         <v/>
       </c>
       <c r="S88">
-        <f>IF(OR(B88="",COUNTIF($B$6:$B88,B88)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B88,$B$6:$B$305)=1)*($R$6:$R$305&gt;R88)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B88="",COUNTIF($B$6:$B88,B88)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R88)+(($R$6:$R$305=R88)*(ROW($B$6:$B$305)&lt;ROW(B88)))))+1)</f>
         <v/>
       </c>
       <c r="T88">
@@ -19874,7 +19864,7 @@
         <v/>
       </c>
       <c r="S89">
-        <f>IF(OR(B89="",COUNTIF($B$6:$B89,B89)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B89,$B$6:$B$305)=1)*($R$6:$R$305&gt;R89)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B89="",COUNTIF($B$6:$B89,B89)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R89)+(($R$6:$R$305=R89)*(ROW($B$6:$B$305)&lt;ROW(B89)))))+1)</f>
         <v/>
       </c>
       <c r="T89">
@@ -19912,7 +19902,7 @@
         <v/>
       </c>
       <c r="S90">
-        <f>IF(OR(B90="",COUNTIF($B$6:$B90,B90)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B90,$B$6:$B$305)=1)*($R$6:$R$305&gt;R90)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B90="",COUNTIF($B$6:$B90,B90)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R90)+(($R$6:$R$305=R90)*(ROW($B$6:$B$305)&lt;ROW(B90)))))+1)</f>
         <v/>
       </c>
       <c r="T90">
@@ -19950,7 +19940,7 @@
         <v/>
       </c>
       <c r="S91">
-        <f>IF(OR(B91="",COUNTIF($B$6:$B91,B91)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B91,$B$6:$B$305)=1)*($R$6:$R$305&gt;R91)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B91="",COUNTIF($B$6:$B91,B91)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R91)+(($R$6:$R$305=R91)*(ROW($B$6:$B$305)&lt;ROW(B91)))))+1)</f>
         <v/>
       </c>
       <c r="T91">
@@ -19988,7 +19978,7 @@
         <v/>
       </c>
       <c r="S92">
-        <f>IF(OR(B92="",COUNTIF($B$6:$B92,B92)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B92,$B$6:$B$305)=1)*($R$6:$R$305&gt;R92)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B92="",COUNTIF($B$6:$B92,B92)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R92)+(($R$6:$R$305=R92)*(ROW($B$6:$B$305)&lt;ROW(B92)))))+1)</f>
         <v/>
       </c>
       <c r="T92">
@@ -20026,7 +20016,7 @@
         <v/>
       </c>
       <c r="S93">
-        <f>IF(OR(B93="",COUNTIF($B$6:$B93,B93)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B93,$B$6:$B$305)=1)*($R$6:$R$305&gt;R93)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B93="",COUNTIF($B$6:$B93,B93)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R93)+(($R$6:$R$305=R93)*(ROW($B$6:$B$305)&lt;ROW(B93)))))+1)</f>
         <v/>
       </c>
       <c r="T93">
@@ -20064,7 +20054,7 @@
         <v/>
       </c>
       <c r="S94">
-        <f>IF(OR(B94="",COUNTIF($B$6:$B94,B94)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B94,$B$6:$B$305)=1)*($R$6:$R$305&gt;R94)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B94="",COUNTIF($B$6:$B94,B94)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R94)+(($R$6:$R$305=R94)*(ROW($B$6:$B$305)&lt;ROW(B94)))))+1)</f>
         <v/>
       </c>
       <c r="T94">
@@ -20102,7 +20092,7 @@
         <v/>
       </c>
       <c r="S95">
-        <f>IF(OR(B95="",COUNTIF($B$6:$B95,B95)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B95,$B$6:$B$305)=1)*($R$6:$R$305&gt;R95)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B95="",COUNTIF($B$6:$B95,B95)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R95)+(($R$6:$R$305=R95)*(ROW($B$6:$B$305)&lt;ROW(B95)))))+1)</f>
         <v/>
       </c>
       <c r="T95">
@@ -20140,7 +20130,7 @@
         <v/>
       </c>
       <c r="S96">
-        <f>IF(OR(B96="",COUNTIF($B$6:$B96,B96)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B96,$B$6:$B$305)=1)*($R$6:$R$305&gt;R96)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B96="",COUNTIF($B$6:$B96,B96)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R96)+(($R$6:$R$305=R96)*(ROW($B$6:$B$305)&lt;ROW(B96)))))+1)</f>
         <v/>
       </c>
       <c r="T96">
@@ -20178,7 +20168,7 @@
         <v/>
       </c>
       <c r="S97">
-        <f>IF(OR(B97="",COUNTIF($B$6:$B97,B97)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B97,$B$6:$B$305)=1)*($R$6:$R$305&gt;R97)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B97="",COUNTIF($B$6:$B97,B97)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R97)+(($R$6:$R$305=R97)*(ROW($B$6:$B$305)&lt;ROW(B97)))))+1)</f>
         <v/>
       </c>
       <c r="T97">
@@ -20216,7 +20206,7 @@
         <v/>
       </c>
       <c r="S98">
-        <f>IF(OR(B98="",COUNTIF($B$6:$B98,B98)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B98,$B$6:$B$305)=1)*($R$6:$R$305&gt;R98)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B98="",COUNTIF($B$6:$B98,B98)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R98)+(($R$6:$R$305=R98)*(ROW($B$6:$B$305)&lt;ROW(B98)))))+1)</f>
         <v/>
       </c>
       <c r="T98">
@@ -20254,7 +20244,7 @@
         <v/>
       </c>
       <c r="S99">
-        <f>IF(OR(B99="",COUNTIF($B$6:$B99,B99)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B99,$B$6:$B$305)=1)*($R$6:$R$305&gt;R99)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B99="",COUNTIF($B$6:$B99,B99)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R99)+(($R$6:$R$305=R99)*(ROW($B$6:$B$305)&lt;ROW(B99)))))+1)</f>
         <v/>
       </c>
       <c r="T99">
@@ -20292,7 +20282,7 @@
         <v/>
       </c>
       <c r="S100">
-        <f>IF(OR(B100="",COUNTIF($B$6:$B100,B100)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B100,$B$6:$B$305)=1)*($R$6:$R$305&gt;R100)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B100="",COUNTIF($B$6:$B100,B100)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R100)+(($R$6:$R$305=R100)*(ROW($B$6:$B$305)&lt;ROW(B100)))))+1)</f>
         <v/>
       </c>
       <c r="T100">
@@ -20330,7 +20320,7 @@
         <v/>
       </c>
       <c r="S101">
-        <f>IF(OR(B101="",COUNTIF($B$6:$B101,B101)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B101,$B$6:$B$305)=1)*($R$6:$R$305&gt;R101)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B101="",COUNTIF($B$6:$B101,B101)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R101)+(($R$6:$R$305=R101)*(ROW($B$6:$B$305)&lt;ROW(B101)))))+1)</f>
         <v/>
       </c>
       <c r="T101">
@@ -20368,7 +20358,7 @@
         <v/>
       </c>
       <c r="S102">
-        <f>IF(OR(B102="",COUNTIF($B$6:$B102,B102)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B102,$B$6:$B$305)=1)*($R$6:$R$305&gt;R102)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B102="",COUNTIF($B$6:$B102,B102)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R102)+(($R$6:$R$305=R102)*(ROW($B$6:$B$305)&lt;ROW(B102)))))+1)</f>
         <v/>
       </c>
       <c r="T102">
@@ -20406,7 +20396,7 @@
         <v/>
       </c>
       <c r="S103">
-        <f>IF(OR(B103="",COUNTIF($B$6:$B103,B103)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B103,$B$6:$B$305)=1)*($R$6:$R$305&gt;R103)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B103="",COUNTIF($B$6:$B103,B103)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R103)+(($R$6:$R$305=R103)*(ROW($B$6:$B$305)&lt;ROW(B103)))))+1)</f>
         <v/>
       </c>
       <c r="T103">
@@ -20444,7 +20434,7 @@
         <v/>
       </c>
       <c r="S104">
-        <f>IF(OR(B104="",COUNTIF($B$6:$B104,B104)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B104,$B$6:$B$305)=1)*($R$6:$R$305&gt;R104)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B104="",COUNTIF($B$6:$B104,B104)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R104)+(($R$6:$R$305=R104)*(ROW($B$6:$B$305)&lt;ROW(B104)))))+1)</f>
         <v/>
       </c>
       <c r="T104">
@@ -20482,7 +20472,7 @@
         <v/>
       </c>
       <c r="S105">
-        <f>IF(OR(B105="",COUNTIF($B$6:$B105,B105)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B105,$B$6:$B$305)=1)*($R$6:$R$305&gt;R105)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B105="",COUNTIF($B$6:$B105,B105)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R105)+(($R$6:$R$305=R105)*(ROW($B$6:$B$305)&lt;ROW(B105)))))+1)</f>
         <v/>
       </c>
       <c r="T105">
@@ -20520,7 +20510,7 @@
         <v/>
       </c>
       <c r="S106">
-        <f>IF(OR(B106="",COUNTIF($B$6:$B106,B106)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B106,$B$6:$B$305)=1)*($R$6:$R$305&gt;R106)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B106="",COUNTIF($B$6:$B106,B106)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R106)+(($R$6:$R$305=R106)*(ROW($B$6:$B$305)&lt;ROW(B106)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20542,7 +20532,7 @@
         <v/>
       </c>
       <c r="S107">
-        <f>IF(OR(B107="",COUNTIF($B$6:$B107,B107)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B107,$B$6:$B$305)=1)*($R$6:$R$305&gt;R107)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B107="",COUNTIF($B$6:$B107,B107)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R107)+(($R$6:$R$305=R107)*(ROW($B$6:$B$305)&lt;ROW(B107)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20564,7 +20554,7 @@
         <v/>
       </c>
       <c r="S108">
-        <f>IF(OR(B108="",COUNTIF($B$6:$B108,B108)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B108,$B$6:$B$305)=1)*($R$6:$R$305&gt;R108)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B108="",COUNTIF($B$6:$B108,B108)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R108)+(($R$6:$R$305=R108)*(ROW($B$6:$B$305)&lt;ROW(B108)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20586,7 +20576,7 @@
         <v/>
       </c>
       <c r="S109">
-        <f>IF(OR(B109="",COUNTIF($B$6:$B109,B109)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B109,$B$6:$B$305)=1)*($R$6:$R$305&gt;R109)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B109="",COUNTIF($B$6:$B109,B109)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R109)+(($R$6:$R$305=R109)*(ROW($B$6:$B$305)&lt;ROW(B109)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20608,7 +20598,7 @@
         <v/>
       </c>
       <c r="S110">
-        <f>IF(OR(B110="",COUNTIF($B$6:$B110,B110)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B110,$B$6:$B$305)=1)*($R$6:$R$305&gt;R110)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B110="",COUNTIF($B$6:$B110,B110)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R110)+(($R$6:$R$305=R110)*(ROW($B$6:$B$305)&lt;ROW(B110)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20630,7 +20620,7 @@
         <v/>
       </c>
       <c r="S111">
-        <f>IF(OR(B111="",COUNTIF($B$6:$B111,B111)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B111,$B$6:$B$305)=1)*($R$6:$R$305&gt;R111)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B111="",COUNTIF($B$6:$B111,B111)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R111)+(($R$6:$R$305=R111)*(ROW($B$6:$B$305)&lt;ROW(B111)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20652,7 +20642,7 @@
         <v/>
       </c>
       <c r="S112">
-        <f>IF(OR(B112="",COUNTIF($B$6:$B112,B112)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B112,$B$6:$B$305)=1)*($R$6:$R$305&gt;R112)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B112="",COUNTIF($B$6:$B112,B112)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R112)+(($R$6:$R$305=R112)*(ROW($B$6:$B$305)&lt;ROW(B112)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20674,7 +20664,7 @@
         <v/>
       </c>
       <c r="S113">
-        <f>IF(OR(B113="",COUNTIF($B$6:$B113,B113)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B113,$B$6:$B$305)=1)*($R$6:$R$305&gt;R113)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B113="",COUNTIF($B$6:$B113,B113)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R113)+(($R$6:$R$305=R113)*(ROW($B$6:$B$305)&lt;ROW(B113)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20696,7 +20686,7 @@
         <v/>
       </c>
       <c r="S114">
-        <f>IF(OR(B114="",COUNTIF($B$6:$B114,B114)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B114,$B$6:$B$305)=1)*($R$6:$R$305&gt;R114)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B114="",COUNTIF($B$6:$B114,B114)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R114)+(($R$6:$R$305=R114)*(ROW($B$6:$B$305)&lt;ROW(B114)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20718,7 +20708,7 @@
         <v/>
       </c>
       <c r="S115">
-        <f>IF(OR(B115="",COUNTIF($B$6:$B115,B115)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B115,$B$6:$B$305)=1)*($R$6:$R$305&gt;R115)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B115="",COUNTIF($B$6:$B115,B115)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R115)+(($R$6:$R$305=R115)*(ROW($B$6:$B$305)&lt;ROW(B115)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20740,7 +20730,7 @@
         <v/>
       </c>
       <c r="S116">
-        <f>IF(OR(B116="",COUNTIF($B$6:$B116,B116)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B116,$B$6:$B$305)=1)*($R$6:$R$305&gt;R116)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B116="",COUNTIF($B$6:$B116,B116)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R116)+(($R$6:$R$305=R116)*(ROW($B$6:$B$305)&lt;ROW(B116)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20762,7 +20752,7 @@
         <v/>
       </c>
       <c r="S117">
-        <f>IF(OR(B117="",COUNTIF($B$6:$B117,B117)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B117,$B$6:$B$305)=1)*($R$6:$R$305&gt;R117)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B117="",COUNTIF($B$6:$B117,B117)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R117)+(($R$6:$R$305=R117)*(ROW($B$6:$B$305)&lt;ROW(B117)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20784,7 +20774,7 @@
         <v/>
       </c>
       <c r="S118">
-        <f>IF(OR(B118="",COUNTIF($B$6:$B118,B118)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B118,$B$6:$B$305)=1)*($R$6:$R$305&gt;R118)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B118="",COUNTIF($B$6:$B118,B118)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R118)+(($R$6:$R$305=R118)*(ROW($B$6:$B$305)&lt;ROW(B118)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20806,7 +20796,7 @@
         <v/>
       </c>
       <c r="S119">
-        <f>IF(OR(B119="",COUNTIF($B$6:$B119,B119)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B119,$B$6:$B$305)=1)*($R$6:$R$305&gt;R119)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B119="",COUNTIF($B$6:$B119,B119)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R119)+(($R$6:$R$305=R119)*(ROW($B$6:$B$305)&lt;ROW(B119)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20828,7 +20818,7 @@
         <v/>
       </c>
       <c r="S120">
-        <f>IF(OR(B120="",COUNTIF($B$6:$B120,B120)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B120,$B$6:$B$305)=1)*($R$6:$R$305&gt;R120)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B120="",COUNTIF($B$6:$B120,B120)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R120)+(($R$6:$R$305=R120)*(ROW($B$6:$B$305)&lt;ROW(B120)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20850,7 +20840,7 @@
         <v/>
       </c>
       <c r="S121">
-        <f>IF(OR(B121="",COUNTIF($B$6:$B121,B121)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B121,$B$6:$B$305)=1)*($R$6:$R$305&gt;R121)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B121="",COUNTIF($B$6:$B121,B121)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R121)+(($R$6:$R$305=R121)*(ROW($B$6:$B$305)&lt;ROW(B121)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20872,7 +20862,7 @@
         <v/>
       </c>
       <c r="S122">
-        <f>IF(OR(B122="",COUNTIF($B$6:$B122,B122)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B122,$B$6:$B$305)=1)*($R$6:$R$305&gt;R122)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B122="",COUNTIF($B$6:$B122,B122)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R122)+(($R$6:$R$305=R122)*(ROW($B$6:$B$305)&lt;ROW(B122)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20894,7 +20884,7 @@
         <v/>
       </c>
       <c r="S123">
-        <f>IF(OR(B123="",COUNTIF($B$6:$B123,B123)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B123,$B$6:$B$305)=1)*($R$6:$R$305&gt;R123)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B123="",COUNTIF($B$6:$B123,B123)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R123)+(($R$6:$R$305=R123)*(ROW($B$6:$B$305)&lt;ROW(B123)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20916,7 +20906,7 @@
         <v/>
       </c>
       <c r="S124">
-        <f>IF(OR(B124="",COUNTIF($B$6:$B124,B124)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B124,$B$6:$B$305)=1)*($R$6:$R$305&gt;R124)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B124="",COUNTIF($B$6:$B124,B124)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R124)+(($R$6:$R$305=R124)*(ROW($B$6:$B$305)&lt;ROW(B124)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20938,7 +20928,7 @@
         <v/>
       </c>
       <c r="S125">
-        <f>IF(OR(B125="",COUNTIF($B$6:$B125,B125)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B125,$B$6:$B$305)=1)*($R$6:$R$305&gt;R125)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B125="",COUNTIF($B$6:$B125,B125)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R125)+(($R$6:$R$305=R125)*(ROW($B$6:$B$305)&lt;ROW(B125)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20960,7 +20950,7 @@
         <v/>
       </c>
       <c r="S126">
-        <f>IF(OR(B126="",COUNTIF($B$6:$B126,B126)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B126,$B$6:$B$305)=1)*($R$6:$R$305&gt;R126)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B126="",COUNTIF($B$6:$B126,B126)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R126)+(($R$6:$R$305=R126)*(ROW($B$6:$B$305)&lt;ROW(B126)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -20982,7 +20972,7 @@
         <v/>
       </c>
       <c r="S127">
-        <f>IF(OR(B127="",COUNTIF($B$6:$B127,B127)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B127,$B$6:$B$305)=1)*($R$6:$R$305&gt;R127)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B127="",COUNTIF($B$6:$B127,B127)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R127)+(($R$6:$R$305=R127)*(ROW($B$6:$B$305)&lt;ROW(B127)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21004,7 +20994,7 @@
         <v/>
       </c>
       <c r="S128">
-        <f>IF(OR(B128="",COUNTIF($B$6:$B128,B128)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B128,$B$6:$B$305)=1)*($R$6:$R$305&gt;R128)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B128="",COUNTIF($B$6:$B128,B128)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R128)+(($R$6:$R$305=R128)*(ROW($B$6:$B$305)&lt;ROW(B128)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21026,7 +21016,7 @@
         <v/>
       </c>
       <c r="S129">
-        <f>IF(OR(B129="",COUNTIF($B$6:$B129,B129)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B129,$B$6:$B$305)=1)*($R$6:$R$305&gt;R129)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B129="",COUNTIF($B$6:$B129,B129)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R129)+(($R$6:$R$305=R129)*(ROW($B$6:$B$305)&lt;ROW(B129)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21048,7 +21038,7 @@
         <v/>
       </c>
       <c r="S130">
-        <f>IF(OR(B130="",COUNTIF($B$6:$B130,B130)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B130,$B$6:$B$305)=1)*($R$6:$R$305&gt;R130)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B130="",COUNTIF($B$6:$B130,B130)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R130)+(($R$6:$R$305=R130)*(ROW($B$6:$B$305)&lt;ROW(B130)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21070,7 +21060,7 @@
         <v/>
       </c>
       <c r="S131">
-        <f>IF(OR(B131="",COUNTIF($B$6:$B131,B131)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B131,$B$6:$B$305)=1)*($R$6:$R$305&gt;R131)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B131="",COUNTIF($B$6:$B131,B131)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R131)+(($R$6:$R$305=R131)*(ROW($B$6:$B$305)&lt;ROW(B131)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21092,7 +21082,7 @@
         <v/>
       </c>
       <c r="S132">
-        <f>IF(OR(B132="",COUNTIF($B$6:$B132,B132)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B132,$B$6:$B$305)=1)*($R$6:$R$305&gt;R132)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B132="",COUNTIF($B$6:$B132,B132)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R132)+(($R$6:$R$305=R132)*(ROW($B$6:$B$305)&lt;ROW(B132)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21114,7 +21104,7 @@
         <v/>
       </c>
       <c r="S133">
-        <f>IF(OR(B133="",COUNTIF($B$6:$B133,B133)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B133,$B$6:$B$305)=1)*($R$6:$R$305&gt;R133)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B133="",COUNTIF($B$6:$B133,B133)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R133)+(($R$6:$R$305=R133)*(ROW($B$6:$B$305)&lt;ROW(B133)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21136,7 +21126,7 @@
         <v/>
       </c>
       <c r="S134">
-        <f>IF(OR(B134="",COUNTIF($B$6:$B134,B134)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B134,$B$6:$B$305)=1)*($R$6:$R$305&gt;R134)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B134="",COUNTIF($B$6:$B134,B134)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R134)+(($R$6:$R$305=R134)*(ROW($B$6:$B$305)&lt;ROW(B134)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21158,7 +21148,7 @@
         <v/>
       </c>
       <c r="S135">
-        <f>IF(OR(B135="",COUNTIF($B$6:$B135,B135)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B135,$B$6:$B$305)=1)*($R$6:$R$305&gt;R135)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B135="",COUNTIF($B$6:$B135,B135)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R135)+(($R$6:$R$305=R135)*(ROW($B$6:$B$305)&lt;ROW(B135)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21180,7 +21170,7 @@
         <v/>
       </c>
       <c r="S136">
-        <f>IF(OR(B136="",COUNTIF($B$6:$B136,B136)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B136,$B$6:$B$305)=1)*($R$6:$R$305&gt;R136)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B136="",COUNTIF($B$6:$B136,B136)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R136)+(($R$6:$R$305=R136)*(ROW($B$6:$B$305)&lt;ROW(B136)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21202,7 +21192,7 @@
         <v/>
       </c>
       <c r="S137">
-        <f>IF(OR(B137="",COUNTIF($B$6:$B137,B137)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B137,$B$6:$B$305)=1)*($R$6:$R$305&gt;R137)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B137="",COUNTIF($B$6:$B137,B137)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R137)+(($R$6:$R$305=R137)*(ROW($B$6:$B$305)&lt;ROW(B137)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21224,7 +21214,7 @@
         <v/>
       </c>
       <c r="S138">
-        <f>IF(OR(B138="",COUNTIF($B$6:$B138,B138)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B138,$B$6:$B$305)=1)*($R$6:$R$305&gt;R138)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B138="",COUNTIF($B$6:$B138,B138)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R138)+(($R$6:$R$305=R138)*(ROW($B$6:$B$305)&lt;ROW(B138)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21246,7 +21236,7 @@
         <v/>
       </c>
       <c r="S139">
-        <f>IF(OR(B139="",COUNTIF($B$6:$B139,B139)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B139,$B$6:$B$305)=1)*($R$6:$R$305&gt;R139)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B139="",COUNTIF($B$6:$B139,B139)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R139)+(($R$6:$R$305=R139)*(ROW($B$6:$B$305)&lt;ROW(B139)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21268,7 +21258,7 @@
         <v/>
       </c>
       <c r="S140">
-        <f>IF(OR(B140="",COUNTIF($B$6:$B140,B140)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B140,$B$6:$B$305)=1)*($R$6:$R$305&gt;R140)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B140="",COUNTIF($B$6:$B140,B140)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R140)+(($R$6:$R$305=R140)*(ROW($B$6:$B$305)&lt;ROW(B140)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21290,7 +21280,7 @@
         <v/>
       </c>
       <c r="S141">
-        <f>IF(OR(B141="",COUNTIF($B$6:$B141,B141)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B141,$B$6:$B$305)=1)*($R$6:$R$305&gt;R141)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B141="",COUNTIF($B$6:$B141,B141)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R141)+(($R$6:$R$305=R141)*(ROW($B$6:$B$305)&lt;ROW(B141)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21312,7 +21302,7 @@
         <v/>
       </c>
       <c r="S142">
-        <f>IF(OR(B142="",COUNTIF($B$6:$B142,B142)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B142,$B$6:$B$305)=1)*($R$6:$R$305&gt;R142)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B142="",COUNTIF($B$6:$B142,B142)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R142)+(($R$6:$R$305=R142)*(ROW($B$6:$B$305)&lt;ROW(B142)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21334,7 +21324,7 @@
         <v/>
       </c>
       <c r="S143">
-        <f>IF(OR(B143="",COUNTIF($B$6:$B143,B143)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B143,$B$6:$B$305)=1)*($R$6:$R$305&gt;R143)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B143="",COUNTIF($B$6:$B143,B143)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R143)+(($R$6:$R$305=R143)*(ROW($B$6:$B$305)&lt;ROW(B143)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21356,7 +21346,7 @@
         <v/>
       </c>
       <c r="S144">
-        <f>IF(OR(B144="",COUNTIF($B$6:$B144,B144)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B144,$B$6:$B$305)=1)*($R$6:$R$305&gt;R144)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B144="",COUNTIF($B$6:$B144,B144)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R144)+(($R$6:$R$305=R144)*(ROW($B$6:$B$305)&lt;ROW(B144)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21378,7 +21368,7 @@
         <v/>
       </c>
       <c r="S145">
-        <f>IF(OR(B145="",COUNTIF($B$6:$B145,B145)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B145,$B$6:$B$305)=1)*($R$6:$R$305&gt;R145)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B145="",COUNTIF($B$6:$B145,B145)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R145)+(($R$6:$R$305=R145)*(ROW($B$6:$B$305)&lt;ROW(B145)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21400,7 +21390,7 @@
         <v/>
       </c>
       <c r="S146">
-        <f>IF(OR(B146="",COUNTIF($B$6:$B146,B146)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B146,$B$6:$B$305)=1)*($R$6:$R$305&gt;R146)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B146="",COUNTIF($B$6:$B146,B146)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R146)+(($R$6:$R$305=R146)*(ROW($B$6:$B$305)&lt;ROW(B146)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21422,7 +21412,7 @@
         <v/>
       </c>
       <c r="S147">
-        <f>IF(OR(B147="",COUNTIF($B$6:$B147,B147)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B147,$B$6:$B$305)=1)*($R$6:$R$305&gt;R147)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B147="",COUNTIF($B$6:$B147,B147)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R147)+(($R$6:$R$305=R147)*(ROW($B$6:$B$305)&lt;ROW(B147)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21444,7 +21434,7 @@
         <v/>
       </c>
       <c r="S148">
-        <f>IF(OR(B148="",COUNTIF($B$6:$B148,B148)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B148,$B$6:$B$305)=1)*($R$6:$R$305&gt;R148)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B148="",COUNTIF($B$6:$B148,B148)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R148)+(($R$6:$R$305=R148)*(ROW($B$6:$B$305)&lt;ROW(B148)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21466,7 +21456,7 @@
         <v/>
       </c>
       <c r="S149">
-        <f>IF(OR(B149="",COUNTIF($B$6:$B149,B149)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B149,$B$6:$B$305)=1)*($R$6:$R$305&gt;R149)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B149="",COUNTIF($B$6:$B149,B149)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R149)+(($R$6:$R$305=R149)*(ROW($B$6:$B$305)&lt;ROW(B149)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21488,7 +21478,7 @@
         <v/>
       </c>
       <c r="S150">
-        <f>IF(OR(B150="",COUNTIF($B$6:$B150,B150)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B150,$B$6:$B$305)=1)*($R$6:$R$305&gt;R150)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B150="",COUNTIF($B$6:$B150,B150)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R150)+(($R$6:$R$305=R150)*(ROW($B$6:$B$305)&lt;ROW(B150)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21510,7 +21500,7 @@
         <v/>
       </c>
       <c r="S151">
-        <f>IF(OR(B151="",COUNTIF($B$6:$B151,B151)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B151,$B$6:$B$305)=1)*($R$6:$R$305&gt;R151)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B151="",COUNTIF($B$6:$B151,B151)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R151)+(($R$6:$R$305=R151)*(ROW($B$6:$B$305)&lt;ROW(B151)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21532,7 +21522,7 @@
         <v/>
       </c>
       <c r="S152">
-        <f>IF(OR(B152="",COUNTIF($B$6:$B152,B152)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B152,$B$6:$B$305)=1)*($R$6:$R$305&gt;R152)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B152="",COUNTIF($B$6:$B152,B152)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R152)+(($R$6:$R$305=R152)*(ROW($B$6:$B$305)&lt;ROW(B152)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21554,7 +21544,7 @@
         <v/>
       </c>
       <c r="S153">
-        <f>IF(OR(B153="",COUNTIF($B$6:$B153,B153)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B153,$B$6:$B$305)=1)*($R$6:$R$305&gt;R153)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B153="",COUNTIF($B$6:$B153,B153)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R153)+(($R$6:$R$305=R153)*(ROW($B$6:$B$305)&lt;ROW(B153)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21576,7 +21566,7 @@
         <v/>
       </c>
       <c r="S154">
-        <f>IF(OR(B154="",COUNTIF($B$6:$B154,B154)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B154,$B$6:$B$305)=1)*($R$6:$R$305&gt;R154)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B154="",COUNTIF($B$6:$B154,B154)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R154)+(($R$6:$R$305=R154)*(ROW($B$6:$B$305)&lt;ROW(B154)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21598,7 +21588,7 @@
         <v/>
       </c>
       <c r="S155">
-        <f>IF(OR(B155="",COUNTIF($B$6:$B155,B155)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B155,$B$6:$B$305)=1)*($R$6:$R$305&gt;R155)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B155="",COUNTIF($B$6:$B155,B155)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R155)+(($R$6:$R$305=R155)*(ROW($B$6:$B$305)&lt;ROW(B155)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21620,7 +21610,7 @@
         <v/>
       </c>
       <c r="S156">
-        <f>IF(OR(B156="",COUNTIF($B$6:$B156,B156)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B156,$B$6:$B$305)=1)*($R$6:$R$305&gt;R156)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B156="",COUNTIF($B$6:$B156,B156)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R156)+(($R$6:$R$305=R156)*(ROW($B$6:$B$305)&lt;ROW(B156)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21642,7 +21632,7 @@
         <v/>
       </c>
       <c r="S157">
-        <f>IF(OR(B157="",COUNTIF($B$6:$B157,B157)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B157,$B$6:$B$305)=1)*($R$6:$R$305&gt;R157)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B157="",COUNTIF($B$6:$B157,B157)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R157)+(($R$6:$R$305=R157)*(ROW($B$6:$B$305)&lt;ROW(B157)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21664,7 +21654,7 @@
         <v/>
       </c>
       <c r="S158">
-        <f>IF(OR(B158="",COUNTIF($B$6:$B158,B158)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B158,$B$6:$B$305)=1)*($R$6:$R$305&gt;R158)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B158="",COUNTIF($B$6:$B158,B158)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R158)+(($R$6:$R$305=R158)*(ROW($B$6:$B$305)&lt;ROW(B158)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21686,7 +21676,7 @@
         <v/>
       </c>
       <c r="S159">
-        <f>IF(OR(B159="",COUNTIF($B$6:$B159,B159)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B159,$B$6:$B$305)=1)*($R$6:$R$305&gt;R159)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B159="",COUNTIF($B$6:$B159,B159)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R159)+(($R$6:$R$305=R159)*(ROW($B$6:$B$305)&lt;ROW(B159)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21708,7 +21698,7 @@
         <v/>
       </c>
       <c r="S160">
-        <f>IF(OR(B160="",COUNTIF($B$6:$B160,B160)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B160,$B$6:$B$305)=1)*($R$6:$R$305&gt;R160)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B160="",COUNTIF($B$6:$B160,B160)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R160)+(($R$6:$R$305=R160)*(ROW($B$6:$B$305)&lt;ROW(B160)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21730,7 +21720,7 @@
         <v/>
       </c>
       <c r="S161">
-        <f>IF(OR(B161="",COUNTIF($B$6:$B161,B161)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B161,$B$6:$B$305)=1)*($R$6:$R$305&gt;R161)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B161="",COUNTIF($B$6:$B161,B161)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R161)+(($R$6:$R$305=R161)*(ROW($B$6:$B$305)&lt;ROW(B161)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21752,7 +21742,7 @@
         <v/>
       </c>
       <c r="S162">
-        <f>IF(OR(B162="",COUNTIF($B$6:$B162,B162)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B162,$B$6:$B$305)=1)*($R$6:$R$305&gt;R162)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B162="",COUNTIF($B$6:$B162,B162)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R162)+(($R$6:$R$305=R162)*(ROW($B$6:$B$305)&lt;ROW(B162)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21774,7 +21764,7 @@
         <v/>
       </c>
       <c r="S163">
-        <f>IF(OR(B163="",COUNTIF($B$6:$B163,B163)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B163,$B$6:$B$305)=1)*($R$6:$R$305&gt;R163)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B163="",COUNTIF($B$6:$B163,B163)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R163)+(($R$6:$R$305=R163)*(ROW($B$6:$B$305)&lt;ROW(B163)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21796,7 +21786,7 @@
         <v/>
       </c>
       <c r="S164">
-        <f>IF(OR(B164="",COUNTIF($B$6:$B164,B164)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B164,$B$6:$B$305)=1)*($R$6:$R$305&gt;R164)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B164="",COUNTIF($B$6:$B164,B164)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R164)+(($R$6:$R$305=R164)*(ROW($B$6:$B$305)&lt;ROW(B164)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21818,7 +21808,7 @@
         <v/>
       </c>
       <c r="S165">
-        <f>IF(OR(B165="",COUNTIF($B$6:$B165,B165)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B165,$B$6:$B$305)=1)*($R$6:$R$305&gt;R165)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B165="",COUNTIF($B$6:$B165,B165)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R165)+(($R$6:$R$305=R165)*(ROW($B$6:$B$305)&lt;ROW(B165)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21840,7 +21830,7 @@
         <v/>
       </c>
       <c r="S166">
-        <f>IF(OR(B166="",COUNTIF($B$6:$B166,B166)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B166,$B$6:$B$305)=1)*($R$6:$R$305&gt;R166)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B166="",COUNTIF($B$6:$B166,B166)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R166)+(($R$6:$R$305=R166)*(ROW($B$6:$B$305)&lt;ROW(B166)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21862,7 +21852,7 @@
         <v/>
       </c>
       <c r="S167">
-        <f>IF(OR(B167="",COUNTIF($B$6:$B167,B167)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B167,$B$6:$B$305)=1)*($R$6:$R$305&gt;R167)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B167="",COUNTIF($B$6:$B167,B167)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R167)+(($R$6:$R$305=R167)*(ROW($B$6:$B$305)&lt;ROW(B167)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21884,7 +21874,7 @@
         <v/>
       </c>
       <c r="S168">
-        <f>IF(OR(B168="",COUNTIF($B$6:$B168,B168)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B168,$B$6:$B$305)=1)*($R$6:$R$305&gt;R168)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B168="",COUNTIF($B$6:$B168,B168)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R168)+(($R$6:$R$305=R168)*(ROW($B$6:$B$305)&lt;ROW(B168)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21906,7 +21896,7 @@
         <v/>
       </c>
       <c r="S169">
-        <f>IF(OR(B169="",COUNTIF($B$6:$B169,B169)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B169,$B$6:$B$305)=1)*($R$6:$R$305&gt;R169)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B169="",COUNTIF($B$6:$B169,B169)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R169)+(($R$6:$R$305=R169)*(ROW($B$6:$B$305)&lt;ROW(B169)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21928,7 +21918,7 @@
         <v/>
       </c>
       <c r="S170">
-        <f>IF(OR(B170="",COUNTIF($B$6:$B170,B170)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B170,$B$6:$B$305)=1)*($R$6:$R$305&gt;R170)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B170="",COUNTIF($B$6:$B170,B170)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R170)+(($R$6:$R$305=R170)*(ROW($B$6:$B$305)&lt;ROW(B170)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21950,7 +21940,7 @@
         <v/>
       </c>
       <c r="S171">
-        <f>IF(OR(B171="",COUNTIF($B$6:$B171,B171)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B171,$B$6:$B$305)=1)*($R$6:$R$305&gt;R171)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B171="",COUNTIF($B$6:$B171,B171)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R171)+(($R$6:$R$305=R171)*(ROW($B$6:$B$305)&lt;ROW(B171)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21972,7 +21962,7 @@
         <v/>
       </c>
       <c r="S172">
-        <f>IF(OR(B172="",COUNTIF($B$6:$B172,B172)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B172,$B$6:$B$305)=1)*($R$6:$R$305&gt;R172)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B172="",COUNTIF($B$6:$B172,B172)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R172)+(($R$6:$R$305=R172)*(ROW($B$6:$B$305)&lt;ROW(B172)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -21994,7 +21984,7 @@
         <v/>
       </c>
       <c r="S173">
-        <f>IF(OR(B173="",COUNTIF($B$6:$B173,B173)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B173,$B$6:$B$305)=1)*($R$6:$R$305&gt;R173)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B173="",COUNTIF($B$6:$B173,B173)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R173)+(($R$6:$R$305=R173)*(ROW($B$6:$B$305)&lt;ROW(B173)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22016,7 +22006,7 @@
         <v/>
       </c>
       <c r="S174">
-        <f>IF(OR(B174="",COUNTIF($B$6:$B174,B174)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B174,$B$6:$B$305)=1)*($R$6:$R$305&gt;R174)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B174="",COUNTIF($B$6:$B174,B174)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R174)+(($R$6:$R$305=R174)*(ROW($B$6:$B$305)&lt;ROW(B174)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22038,7 +22028,7 @@
         <v/>
       </c>
       <c r="S175">
-        <f>IF(OR(B175="",COUNTIF($B$6:$B175,B175)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B175,$B$6:$B$305)=1)*($R$6:$R$305&gt;R175)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B175="",COUNTIF($B$6:$B175,B175)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R175)+(($R$6:$R$305=R175)*(ROW($B$6:$B$305)&lt;ROW(B175)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22060,7 +22050,7 @@
         <v/>
       </c>
       <c r="S176">
-        <f>IF(OR(B176="",COUNTIF($B$6:$B176,B176)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B176,$B$6:$B$305)=1)*($R$6:$R$305&gt;R176)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B176="",COUNTIF($B$6:$B176,B176)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R176)+(($R$6:$R$305=R176)*(ROW($B$6:$B$305)&lt;ROW(B176)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22082,7 +22072,7 @@
         <v/>
       </c>
       <c r="S177">
-        <f>IF(OR(B177="",COUNTIF($B$6:$B177,B177)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B177,$B$6:$B$305)=1)*($R$6:$R$305&gt;R177)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B177="",COUNTIF($B$6:$B177,B177)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R177)+(($R$6:$R$305=R177)*(ROW($B$6:$B$305)&lt;ROW(B177)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22104,7 +22094,7 @@
         <v/>
       </c>
       <c r="S178">
-        <f>IF(OR(B178="",COUNTIF($B$6:$B178,B178)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B178,$B$6:$B$305)=1)*($R$6:$R$305&gt;R178)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B178="",COUNTIF($B$6:$B178,B178)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R178)+(($R$6:$R$305=R178)*(ROW($B$6:$B$305)&lt;ROW(B178)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22126,7 +22116,7 @@
         <v/>
       </c>
       <c r="S179">
-        <f>IF(OR(B179="",COUNTIF($B$6:$B179,B179)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B179,$B$6:$B$305)=1)*($R$6:$R$305&gt;R179)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B179="",COUNTIF($B$6:$B179,B179)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R179)+(($R$6:$R$305=R179)*(ROW($B$6:$B$305)&lt;ROW(B179)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22148,7 +22138,7 @@
         <v/>
       </c>
       <c r="S180">
-        <f>IF(OR(B180="",COUNTIF($B$6:$B180,B180)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B180,$B$6:$B$305)=1)*($R$6:$R$305&gt;R180)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B180="",COUNTIF($B$6:$B180,B180)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R180)+(($R$6:$R$305=R180)*(ROW($B$6:$B$305)&lt;ROW(B180)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22170,7 +22160,7 @@
         <v/>
       </c>
       <c r="S181">
-        <f>IF(OR(B181="",COUNTIF($B$6:$B181,B181)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B181,$B$6:$B$305)=1)*($R$6:$R$305&gt;R181)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B181="",COUNTIF($B$6:$B181,B181)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R181)+(($R$6:$R$305=R181)*(ROW($B$6:$B$305)&lt;ROW(B181)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22192,7 +22182,7 @@
         <v/>
       </c>
       <c r="S182">
-        <f>IF(OR(B182="",COUNTIF($B$6:$B182,B182)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B182,$B$6:$B$305)=1)*($R$6:$R$305&gt;R182)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B182="",COUNTIF($B$6:$B182,B182)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R182)+(($R$6:$R$305=R182)*(ROW($B$6:$B$305)&lt;ROW(B182)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22214,7 +22204,7 @@
         <v/>
       </c>
       <c r="S183">
-        <f>IF(OR(B183="",COUNTIF($B$6:$B183,B183)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B183,$B$6:$B$305)=1)*($R$6:$R$305&gt;R183)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B183="",COUNTIF($B$6:$B183,B183)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R183)+(($R$6:$R$305=R183)*(ROW($B$6:$B$305)&lt;ROW(B183)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22236,7 +22226,7 @@
         <v/>
       </c>
       <c r="S184">
-        <f>IF(OR(B184="",COUNTIF($B$6:$B184,B184)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B184,$B$6:$B$305)=1)*($R$6:$R$305&gt;R184)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B184="",COUNTIF($B$6:$B184,B184)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R184)+(($R$6:$R$305=R184)*(ROW($B$6:$B$305)&lt;ROW(B184)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22258,7 +22248,7 @@
         <v/>
       </c>
       <c r="S185">
-        <f>IF(OR(B185="",COUNTIF($B$6:$B185,B185)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B185,$B$6:$B$305)=1)*($R$6:$R$305&gt;R185)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B185="",COUNTIF($B$6:$B185,B185)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R185)+(($R$6:$R$305=R185)*(ROW($B$6:$B$305)&lt;ROW(B185)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22280,7 +22270,7 @@
         <v/>
       </c>
       <c r="S186">
-        <f>IF(OR(B186="",COUNTIF($B$6:$B186,B186)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B186,$B$6:$B$305)=1)*($R$6:$R$305&gt;R186)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B186="",COUNTIF($B$6:$B186,B186)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R186)+(($R$6:$R$305=R186)*(ROW($B$6:$B$305)&lt;ROW(B186)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22302,7 +22292,7 @@
         <v/>
       </c>
       <c r="S187">
-        <f>IF(OR(B187="",COUNTIF($B$6:$B187,B187)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B187,$B$6:$B$305)=1)*($R$6:$R$305&gt;R187)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B187="",COUNTIF($B$6:$B187,B187)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R187)+(($R$6:$R$305=R187)*(ROW($B$6:$B$305)&lt;ROW(B187)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22324,7 +22314,7 @@
         <v/>
       </c>
       <c r="S188">
-        <f>IF(OR(B188="",COUNTIF($B$6:$B188,B188)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B188,$B$6:$B$305)=1)*($R$6:$R$305&gt;R188)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B188="",COUNTIF($B$6:$B188,B188)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R188)+(($R$6:$R$305=R188)*(ROW($B$6:$B$305)&lt;ROW(B188)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22346,7 +22336,7 @@
         <v/>
       </c>
       <c r="S189">
-        <f>IF(OR(B189="",COUNTIF($B$6:$B189,B189)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B189,$B$6:$B$305)=1)*($R$6:$R$305&gt;R189)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B189="",COUNTIF($B$6:$B189,B189)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R189)+(($R$6:$R$305=R189)*(ROW($B$6:$B$305)&lt;ROW(B189)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22368,7 +22358,7 @@
         <v/>
       </c>
       <c r="S190">
-        <f>IF(OR(B190="",COUNTIF($B$6:$B190,B190)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B190,$B$6:$B$305)=1)*($R$6:$R$305&gt;R190)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B190="",COUNTIF($B$6:$B190,B190)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R190)+(($R$6:$R$305=R190)*(ROW($B$6:$B$305)&lt;ROW(B190)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22390,7 +22380,7 @@
         <v/>
       </c>
       <c r="S191">
-        <f>IF(OR(B191="",COUNTIF($B$6:$B191,B191)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B191,$B$6:$B$305)=1)*($R$6:$R$305&gt;R191)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B191="",COUNTIF($B$6:$B191,B191)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R191)+(($R$6:$R$305=R191)*(ROW($B$6:$B$305)&lt;ROW(B191)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22412,7 +22402,7 @@
         <v/>
       </c>
       <c r="S192">
-        <f>IF(OR(B192="",COUNTIF($B$6:$B192,B192)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B192,$B$6:$B$305)=1)*($R$6:$R$305&gt;R192)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B192="",COUNTIF($B$6:$B192,B192)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R192)+(($R$6:$R$305=R192)*(ROW($B$6:$B$305)&lt;ROW(B192)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22434,7 +22424,7 @@
         <v/>
       </c>
       <c r="S193">
-        <f>IF(OR(B193="",COUNTIF($B$6:$B193,B193)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B193,$B$6:$B$305)=1)*($R$6:$R$305&gt;R193)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B193="",COUNTIF($B$6:$B193,B193)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R193)+(($R$6:$R$305=R193)*(ROW($B$6:$B$305)&lt;ROW(B193)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22456,7 +22446,7 @@
         <v/>
       </c>
       <c r="S194">
-        <f>IF(OR(B194="",COUNTIF($B$6:$B194,B194)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B194,$B$6:$B$305)=1)*($R$6:$R$305&gt;R194)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B194="",COUNTIF($B$6:$B194,B194)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R194)+(($R$6:$R$305=R194)*(ROW($B$6:$B$305)&lt;ROW(B194)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22478,7 +22468,7 @@
         <v/>
       </c>
       <c r="S195">
-        <f>IF(OR(B195="",COUNTIF($B$6:$B195,B195)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B195,$B$6:$B$305)=1)*($R$6:$R$305&gt;R195)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B195="",COUNTIF($B$6:$B195,B195)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R195)+(($R$6:$R$305=R195)*(ROW($B$6:$B$305)&lt;ROW(B195)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22500,7 +22490,7 @@
         <v/>
       </c>
       <c r="S196">
-        <f>IF(OR(B196="",COUNTIF($B$6:$B196,B196)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B196,$B$6:$B$305)=1)*($R$6:$R$305&gt;R196)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B196="",COUNTIF($B$6:$B196,B196)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R196)+(($R$6:$R$305=R196)*(ROW($B$6:$B$305)&lt;ROW(B196)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22522,7 +22512,7 @@
         <v/>
       </c>
       <c r="S197">
-        <f>IF(OR(B197="",COUNTIF($B$6:$B197,B197)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B197,$B$6:$B$305)=1)*($R$6:$R$305&gt;R197)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B197="",COUNTIF($B$6:$B197,B197)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R197)+(($R$6:$R$305=R197)*(ROW($B$6:$B$305)&lt;ROW(B197)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22544,7 +22534,7 @@
         <v/>
       </c>
       <c r="S198">
-        <f>IF(OR(B198="",COUNTIF($B$6:$B198,B198)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B198,$B$6:$B$305)=1)*($R$6:$R$305&gt;R198)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B198="",COUNTIF($B$6:$B198,B198)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R198)+(($R$6:$R$305=R198)*(ROW($B$6:$B$305)&lt;ROW(B198)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22566,7 +22556,7 @@
         <v/>
       </c>
       <c r="S199">
-        <f>IF(OR(B199="",COUNTIF($B$6:$B199,B199)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B199,$B$6:$B$305)=1)*($R$6:$R$305&gt;R199)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B199="",COUNTIF($B$6:$B199,B199)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R199)+(($R$6:$R$305=R199)*(ROW($B$6:$B$305)&lt;ROW(B199)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22588,7 +22578,7 @@
         <v/>
       </c>
       <c r="S200">
-        <f>IF(OR(B200="",COUNTIF($B$6:$B200,B200)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B200,$B$6:$B$305)=1)*($R$6:$R$305&gt;R200)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B200="",COUNTIF($B$6:$B200,B200)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R200)+(($R$6:$R$305=R200)*(ROW($B$6:$B$305)&lt;ROW(B200)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22610,7 +22600,7 @@
         <v/>
       </c>
       <c r="S201">
-        <f>IF(OR(B201="",COUNTIF($B$6:$B201,B201)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B201,$B$6:$B$305)=1)*($R$6:$R$305&gt;R201)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B201="",COUNTIF($B$6:$B201,B201)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R201)+(($R$6:$R$305=R201)*(ROW($B$6:$B$305)&lt;ROW(B201)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22632,7 +22622,7 @@
         <v/>
       </c>
       <c r="S202">
-        <f>IF(OR(B202="",COUNTIF($B$6:$B202,B202)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B202,$B$6:$B$305)=1)*($R$6:$R$305&gt;R202)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B202="",COUNTIF($B$6:$B202,B202)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R202)+(($R$6:$R$305=R202)*(ROW($B$6:$B$305)&lt;ROW(B202)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22654,7 +22644,7 @@
         <v/>
       </c>
       <c r="S203">
-        <f>IF(OR(B203="",COUNTIF($B$6:$B203,B203)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B203,$B$6:$B$305)=1)*($R$6:$R$305&gt;R203)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B203="",COUNTIF($B$6:$B203,B203)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R203)+(($R$6:$R$305=R203)*(ROW($B$6:$B$305)&lt;ROW(B203)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22676,7 +22666,7 @@
         <v/>
       </c>
       <c r="S204">
-        <f>IF(OR(B204="",COUNTIF($B$6:$B204,B204)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B204,$B$6:$B$305)=1)*($R$6:$R$305&gt;R204)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B204="",COUNTIF($B$6:$B204,B204)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R204)+(($R$6:$R$305=R204)*(ROW($B$6:$B$305)&lt;ROW(B204)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22698,7 +22688,7 @@
         <v/>
       </c>
       <c r="S205">
-        <f>IF(OR(B205="",COUNTIF($B$6:$B205,B205)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B205,$B$6:$B$305)=1)*($R$6:$R$305&gt;R205)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B205="",COUNTIF($B$6:$B205,B205)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R205)+(($R$6:$R$305=R205)*(ROW($B$6:$B$305)&lt;ROW(B205)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22720,7 +22710,7 @@
         <v/>
       </c>
       <c r="S206">
-        <f>IF(OR(B206="",COUNTIF($B$6:$B206,B206)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B206,$B$6:$B$305)=1)*($R$6:$R$305&gt;R206)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B206="",COUNTIF($B$6:$B206,B206)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R206)+(($R$6:$R$305=R206)*(ROW($B$6:$B$305)&lt;ROW(B206)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22742,7 +22732,7 @@
         <v/>
       </c>
       <c r="S207">
-        <f>IF(OR(B207="",COUNTIF($B$6:$B207,B207)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B207,$B$6:$B$305)=1)*($R$6:$R$305&gt;R207)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B207="",COUNTIF($B$6:$B207,B207)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R207)+(($R$6:$R$305=R207)*(ROW($B$6:$B$305)&lt;ROW(B207)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22764,7 +22754,7 @@
         <v/>
       </c>
       <c r="S208">
-        <f>IF(OR(B208="",COUNTIF($B$6:$B208,B208)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B208,$B$6:$B$305)=1)*($R$6:$R$305&gt;R208)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B208="",COUNTIF($B$6:$B208,B208)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R208)+(($R$6:$R$305=R208)*(ROW($B$6:$B$305)&lt;ROW(B208)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22786,7 +22776,7 @@
         <v/>
       </c>
       <c r="S209">
-        <f>IF(OR(B209="",COUNTIF($B$6:$B209,B209)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B209,$B$6:$B$305)=1)*($R$6:$R$305&gt;R209)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B209="",COUNTIF($B$6:$B209,B209)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R209)+(($R$6:$R$305=R209)*(ROW($B$6:$B$305)&lt;ROW(B209)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22808,7 +22798,7 @@
         <v/>
       </c>
       <c r="S210">
-        <f>IF(OR(B210="",COUNTIF($B$6:$B210,B210)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B210,$B$6:$B$305)=1)*($R$6:$R$305&gt;R210)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B210="",COUNTIF($B$6:$B210,B210)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R210)+(($R$6:$R$305=R210)*(ROW($B$6:$B$305)&lt;ROW(B210)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22830,7 +22820,7 @@
         <v/>
       </c>
       <c r="S211">
-        <f>IF(OR(B211="",COUNTIF($B$6:$B211,B211)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B211,$B$6:$B$305)=1)*($R$6:$R$305&gt;R211)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B211="",COUNTIF($B$6:$B211,B211)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R211)+(($R$6:$R$305=R211)*(ROW($B$6:$B$305)&lt;ROW(B211)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22852,7 +22842,7 @@
         <v/>
       </c>
       <c r="S212">
-        <f>IF(OR(B212="",COUNTIF($B$6:$B212,B212)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B212,$B$6:$B$305)=1)*($R$6:$R$305&gt;R212)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B212="",COUNTIF($B$6:$B212,B212)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R212)+(($R$6:$R$305=R212)*(ROW($B$6:$B$305)&lt;ROW(B212)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22874,7 +22864,7 @@
         <v/>
       </c>
       <c r="S213">
-        <f>IF(OR(B213="",COUNTIF($B$6:$B213,B213)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B213,$B$6:$B$305)=1)*($R$6:$R$305&gt;R213)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B213="",COUNTIF($B$6:$B213,B213)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R213)+(($R$6:$R$305=R213)*(ROW($B$6:$B$305)&lt;ROW(B213)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22896,7 +22886,7 @@
         <v/>
       </c>
       <c r="S214">
-        <f>IF(OR(B214="",COUNTIF($B$6:$B214,B214)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B214,$B$6:$B$305)=1)*($R$6:$R$305&gt;R214)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B214="",COUNTIF($B$6:$B214,B214)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R214)+(($R$6:$R$305=R214)*(ROW($B$6:$B$305)&lt;ROW(B214)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22918,7 +22908,7 @@
         <v/>
       </c>
       <c r="S215">
-        <f>IF(OR(B215="",COUNTIF($B$6:$B215,B215)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B215,$B$6:$B$305)=1)*($R$6:$R$305&gt;R215)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B215="",COUNTIF($B$6:$B215,B215)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R215)+(($R$6:$R$305=R215)*(ROW($B$6:$B$305)&lt;ROW(B215)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22940,7 +22930,7 @@
         <v/>
       </c>
       <c r="S216">
-        <f>IF(OR(B216="",COUNTIF($B$6:$B216,B216)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B216,$B$6:$B$305)=1)*($R$6:$R$305&gt;R216)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B216="",COUNTIF($B$6:$B216,B216)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R216)+(($R$6:$R$305=R216)*(ROW($B$6:$B$305)&lt;ROW(B216)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22962,7 +22952,7 @@
         <v/>
       </c>
       <c r="S217">
-        <f>IF(OR(B217="",COUNTIF($B$6:$B217,B217)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B217,$B$6:$B$305)=1)*($R$6:$R$305&gt;R217)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B217="",COUNTIF($B$6:$B217,B217)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R217)+(($R$6:$R$305=R217)*(ROW($B$6:$B$305)&lt;ROW(B217)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -22984,7 +22974,7 @@
         <v/>
       </c>
       <c r="S218">
-        <f>IF(OR(B218="",COUNTIF($B$6:$B218,B218)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B218,$B$6:$B$305)=1)*($R$6:$R$305&gt;R218)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B218="",COUNTIF($B$6:$B218,B218)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R218)+(($R$6:$R$305=R218)*(ROW($B$6:$B$305)&lt;ROW(B218)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23006,7 +22996,7 @@
         <v/>
       </c>
       <c r="S219">
-        <f>IF(OR(B219="",COUNTIF($B$6:$B219,B219)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B219,$B$6:$B$305)=1)*($R$6:$R$305&gt;R219)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B219="",COUNTIF($B$6:$B219,B219)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R219)+(($R$6:$R$305=R219)*(ROW($B$6:$B$305)&lt;ROW(B219)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23028,7 +23018,7 @@
         <v/>
       </c>
       <c r="S220">
-        <f>IF(OR(B220="",COUNTIF($B$6:$B220,B220)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B220,$B$6:$B$305)=1)*($R$6:$R$305&gt;R220)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B220="",COUNTIF($B$6:$B220,B220)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R220)+(($R$6:$R$305=R220)*(ROW($B$6:$B$305)&lt;ROW(B220)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23050,7 +23040,7 @@
         <v/>
       </c>
       <c r="S221">
-        <f>IF(OR(B221="",COUNTIF($B$6:$B221,B221)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B221,$B$6:$B$305)=1)*($R$6:$R$305&gt;R221)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B221="",COUNTIF($B$6:$B221,B221)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R221)+(($R$6:$R$305=R221)*(ROW($B$6:$B$305)&lt;ROW(B221)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23072,7 +23062,7 @@
         <v/>
       </c>
       <c r="S222">
-        <f>IF(OR(B222="",COUNTIF($B$6:$B222,B222)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B222,$B$6:$B$305)=1)*($R$6:$R$305&gt;R222)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B222="",COUNTIF($B$6:$B222,B222)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R222)+(($R$6:$R$305=R222)*(ROW($B$6:$B$305)&lt;ROW(B222)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23094,7 +23084,7 @@
         <v/>
       </c>
       <c r="S223">
-        <f>IF(OR(B223="",COUNTIF($B$6:$B223,B223)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B223,$B$6:$B$305)=1)*($R$6:$R$305&gt;R223)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B223="",COUNTIF($B$6:$B223,B223)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R223)+(($R$6:$R$305=R223)*(ROW($B$6:$B$305)&lt;ROW(B223)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23116,7 +23106,7 @@
         <v/>
       </c>
       <c r="S224">
-        <f>IF(OR(B224="",COUNTIF($B$6:$B224,B224)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B224,$B$6:$B$305)=1)*($R$6:$R$305&gt;R224)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B224="",COUNTIF($B$6:$B224,B224)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R224)+(($R$6:$R$305=R224)*(ROW($B$6:$B$305)&lt;ROW(B224)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23138,7 +23128,7 @@
         <v/>
       </c>
       <c r="S225">
-        <f>IF(OR(B225="",COUNTIF($B$6:$B225,B225)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B225,$B$6:$B$305)=1)*($R$6:$R$305&gt;R225)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B225="",COUNTIF($B$6:$B225,B225)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R225)+(($R$6:$R$305=R225)*(ROW($B$6:$B$305)&lt;ROW(B225)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23160,7 +23150,7 @@
         <v/>
       </c>
       <c r="S226">
-        <f>IF(OR(B226="",COUNTIF($B$6:$B226,B226)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B226,$B$6:$B$305)=1)*($R$6:$R$305&gt;R226)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B226="",COUNTIF($B$6:$B226,B226)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R226)+(($R$6:$R$305=R226)*(ROW($B$6:$B$305)&lt;ROW(B226)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23182,7 +23172,7 @@
         <v/>
       </c>
       <c r="S227">
-        <f>IF(OR(B227="",COUNTIF($B$6:$B227,B227)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B227,$B$6:$B$305)=1)*($R$6:$R$305&gt;R227)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B227="",COUNTIF($B$6:$B227,B227)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R227)+(($R$6:$R$305=R227)*(ROW($B$6:$B$305)&lt;ROW(B227)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23204,7 +23194,7 @@
         <v/>
       </c>
       <c r="S228">
-        <f>IF(OR(B228="",COUNTIF($B$6:$B228,B228)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B228,$B$6:$B$305)=1)*($R$6:$R$305&gt;R228)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B228="",COUNTIF($B$6:$B228,B228)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R228)+(($R$6:$R$305=R228)*(ROW($B$6:$B$305)&lt;ROW(B228)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23226,7 +23216,7 @@
         <v/>
       </c>
       <c r="S229">
-        <f>IF(OR(B229="",COUNTIF($B$6:$B229,B229)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B229,$B$6:$B$305)=1)*($R$6:$R$305&gt;R229)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B229="",COUNTIF($B$6:$B229,B229)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R229)+(($R$6:$R$305=R229)*(ROW($B$6:$B$305)&lt;ROW(B229)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23248,7 +23238,7 @@
         <v/>
       </c>
       <c r="S230">
-        <f>IF(OR(B230="",COUNTIF($B$6:$B230,B230)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B230,$B$6:$B$305)=1)*($R$6:$R$305&gt;R230)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B230="",COUNTIF($B$6:$B230,B230)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R230)+(($R$6:$R$305=R230)*(ROW($B$6:$B$305)&lt;ROW(B230)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23270,7 +23260,7 @@
         <v/>
       </c>
       <c r="S231">
-        <f>IF(OR(B231="",COUNTIF($B$6:$B231,B231)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B231,$B$6:$B$305)=1)*($R$6:$R$305&gt;R231)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B231="",COUNTIF($B$6:$B231,B231)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R231)+(($R$6:$R$305=R231)*(ROW($B$6:$B$305)&lt;ROW(B231)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23292,7 +23282,7 @@
         <v/>
       </c>
       <c r="S232">
-        <f>IF(OR(B232="",COUNTIF($B$6:$B232,B232)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B232,$B$6:$B$305)=1)*($R$6:$R$305&gt;R232)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B232="",COUNTIF($B$6:$B232,B232)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R232)+(($R$6:$R$305=R232)*(ROW($B$6:$B$305)&lt;ROW(B232)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23314,7 +23304,7 @@
         <v/>
       </c>
       <c r="S233">
-        <f>IF(OR(B233="",COUNTIF($B$6:$B233,B233)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B233,$B$6:$B$305)=1)*($R$6:$R$305&gt;R233)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B233="",COUNTIF($B$6:$B233,B233)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R233)+(($R$6:$R$305=R233)*(ROW($B$6:$B$305)&lt;ROW(B233)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23336,7 +23326,7 @@
         <v/>
       </c>
       <c r="S234">
-        <f>IF(OR(B234="",COUNTIF($B$6:$B234,B234)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B234,$B$6:$B$305)=1)*($R$6:$R$305&gt;R234)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B234="",COUNTIF($B$6:$B234,B234)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R234)+(($R$6:$R$305=R234)*(ROW($B$6:$B$305)&lt;ROW(B234)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23358,7 +23348,7 @@
         <v/>
       </c>
       <c r="S235">
-        <f>IF(OR(B235="",COUNTIF($B$6:$B235,B235)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B235,$B$6:$B$305)=1)*($R$6:$R$305&gt;R235)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B235="",COUNTIF($B$6:$B235,B235)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R235)+(($R$6:$R$305=R235)*(ROW($B$6:$B$305)&lt;ROW(B235)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23380,7 +23370,7 @@
         <v/>
       </c>
       <c r="S236">
-        <f>IF(OR(B236="",COUNTIF($B$6:$B236,B236)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B236,$B$6:$B$305)=1)*($R$6:$R$305&gt;R236)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B236="",COUNTIF($B$6:$B236,B236)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R236)+(($R$6:$R$305=R236)*(ROW($B$6:$B$305)&lt;ROW(B236)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23402,7 +23392,7 @@
         <v/>
       </c>
       <c r="S237">
-        <f>IF(OR(B237="",COUNTIF($B$6:$B237,B237)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B237,$B$6:$B$305)=1)*($R$6:$R$305&gt;R237)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B237="",COUNTIF($B$6:$B237,B237)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R237)+(($R$6:$R$305=R237)*(ROW($B$6:$B$305)&lt;ROW(B237)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23424,7 +23414,7 @@
         <v/>
       </c>
       <c r="S238">
-        <f>IF(OR(B238="",COUNTIF($B$6:$B238,B238)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B238,$B$6:$B$305)=1)*($R$6:$R$305&gt;R238)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B238="",COUNTIF($B$6:$B238,B238)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R238)+(($R$6:$R$305=R238)*(ROW($B$6:$B$305)&lt;ROW(B238)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23446,7 +23436,7 @@
         <v/>
       </c>
       <c r="S239">
-        <f>IF(OR(B239="",COUNTIF($B$6:$B239,B239)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B239,$B$6:$B$305)=1)*($R$6:$R$305&gt;R239)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B239="",COUNTIF($B$6:$B239,B239)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R239)+(($R$6:$R$305=R239)*(ROW($B$6:$B$305)&lt;ROW(B239)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23468,7 +23458,7 @@
         <v/>
       </c>
       <c r="S240">
-        <f>IF(OR(B240="",COUNTIF($B$6:$B240,B240)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B240,$B$6:$B$305)=1)*($R$6:$R$305&gt;R240)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B240="",COUNTIF($B$6:$B240,B240)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R240)+(($R$6:$R$305=R240)*(ROW($B$6:$B$305)&lt;ROW(B240)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23490,7 +23480,7 @@
         <v/>
       </c>
       <c r="S241">
-        <f>IF(OR(B241="",COUNTIF($B$6:$B241,B241)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B241,$B$6:$B$305)=1)*($R$6:$R$305&gt;R241)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B241="",COUNTIF($B$6:$B241,B241)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R241)+(($R$6:$R$305=R241)*(ROW($B$6:$B$305)&lt;ROW(B241)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23512,7 +23502,7 @@
         <v/>
       </c>
       <c r="S242">
-        <f>IF(OR(B242="",COUNTIF($B$6:$B242,B242)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B242,$B$6:$B$305)=1)*($R$6:$R$305&gt;R242)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B242="",COUNTIF($B$6:$B242,B242)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R242)+(($R$6:$R$305=R242)*(ROW($B$6:$B$305)&lt;ROW(B242)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23534,7 +23524,7 @@
         <v/>
       </c>
       <c r="S243">
-        <f>IF(OR(B243="",COUNTIF($B$6:$B243,B243)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B243,$B$6:$B$305)=1)*($R$6:$R$305&gt;R243)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B243="",COUNTIF($B$6:$B243,B243)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R243)+(($R$6:$R$305=R243)*(ROW($B$6:$B$305)&lt;ROW(B243)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23556,7 +23546,7 @@
         <v/>
       </c>
       <c r="S244">
-        <f>IF(OR(B244="",COUNTIF($B$6:$B244,B244)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B244,$B$6:$B$305)=1)*($R$6:$R$305&gt;R244)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B244="",COUNTIF($B$6:$B244,B244)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R244)+(($R$6:$R$305=R244)*(ROW($B$6:$B$305)&lt;ROW(B244)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23578,7 +23568,7 @@
         <v/>
       </c>
       <c r="S245">
-        <f>IF(OR(B245="",COUNTIF($B$6:$B245,B245)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B245,$B$6:$B$305)=1)*($R$6:$R$305&gt;R245)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B245="",COUNTIF($B$6:$B245,B245)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R245)+(($R$6:$R$305=R245)*(ROW($B$6:$B$305)&lt;ROW(B245)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23600,7 +23590,7 @@
         <v/>
       </c>
       <c r="S246">
-        <f>IF(OR(B246="",COUNTIF($B$6:$B246,B246)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B246,$B$6:$B$305)=1)*($R$6:$R$305&gt;R246)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B246="",COUNTIF($B$6:$B246,B246)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R246)+(($R$6:$R$305=R246)*(ROW($B$6:$B$305)&lt;ROW(B246)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23622,7 +23612,7 @@
         <v/>
       </c>
       <c r="S247">
-        <f>IF(OR(B247="",COUNTIF($B$6:$B247,B247)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B247,$B$6:$B$305)=1)*($R$6:$R$305&gt;R247)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B247="",COUNTIF($B$6:$B247,B247)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R247)+(($R$6:$R$305=R247)*(ROW($B$6:$B$305)&lt;ROW(B247)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23644,7 +23634,7 @@
         <v/>
       </c>
       <c r="S248">
-        <f>IF(OR(B248="",COUNTIF($B$6:$B248,B248)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B248,$B$6:$B$305)=1)*($R$6:$R$305&gt;R248)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B248="",COUNTIF($B$6:$B248,B248)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R248)+(($R$6:$R$305=R248)*(ROW($B$6:$B$305)&lt;ROW(B248)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23666,7 +23656,7 @@
         <v/>
       </c>
       <c r="S249">
-        <f>IF(OR(B249="",COUNTIF($B$6:$B249,B249)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B249,$B$6:$B$305)=1)*($R$6:$R$305&gt;R249)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B249="",COUNTIF($B$6:$B249,B249)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R249)+(($R$6:$R$305=R249)*(ROW($B$6:$B$305)&lt;ROW(B249)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23688,7 +23678,7 @@
         <v/>
       </c>
       <c r="S250">
-        <f>IF(OR(B250="",COUNTIF($B$6:$B250,B250)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B250,$B$6:$B$305)=1)*($R$6:$R$305&gt;R250)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B250="",COUNTIF($B$6:$B250,B250)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R250)+(($R$6:$R$305=R250)*(ROW($B$6:$B$305)&lt;ROW(B250)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23710,7 +23700,7 @@
         <v/>
       </c>
       <c r="S251">
-        <f>IF(OR(B251="",COUNTIF($B$6:$B251,B251)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B251,$B$6:$B$305)=1)*($R$6:$R$305&gt;R251)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B251="",COUNTIF($B$6:$B251,B251)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R251)+(($R$6:$R$305=R251)*(ROW($B$6:$B$305)&lt;ROW(B251)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23732,7 +23722,7 @@
         <v/>
       </c>
       <c r="S252">
-        <f>IF(OR(B252="",COUNTIF($B$6:$B252,B252)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B252,$B$6:$B$305)=1)*($R$6:$R$305&gt;R252)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B252="",COUNTIF($B$6:$B252,B252)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R252)+(($R$6:$R$305=R252)*(ROW($B$6:$B$305)&lt;ROW(B252)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23754,7 +23744,7 @@
         <v/>
       </c>
       <c r="S253">
-        <f>IF(OR(B253="",COUNTIF($B$6:$B253,B253)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B253,$B$6:$B$305)=1)*($R$6:$R$305&gt;R253)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B253="",COUNTIF($B$6:$B253,B253)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R253)+(($R$6:$R$305=R253)*(ROW($B$6:$B$305)&lt;ROW(B253)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23776,7 +23766,7 @@
         <v/>
       </c>
       <c r="S254">
-        <f>IF(OR(B254="",COUNTIF($B$6:$B254,B254)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B254,$B$6:$B$305)=1)*($R$6:$R$305&gt;R254)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B254="",COUNTIF($B$6:$B254,B254)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R254)+(($R$6:$R$305=R254)*(ROW($B$6:$B$305)&lt;ROW(B254)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23798,7 +23788,7 @@
         <v/>
       </c>
       <c r="S255">
-        <f>IF(OR(B255="",COUNTIF($B$6:$B255,B255)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B255,$B$6:$B$305)=1)*($R$6:$R$305&gt;R255)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B255="",COUNTIF($B$6:$B255,B255)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R255)+(($R$6:$R$305=R255)*(ROW($B$6:$B$305)&lt;ROW(B255)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23820,7 +23810,7 @@
         <v/>
       </c>
       <c r="S256">
-        <f>IF(OR(B256="",COUNTIF($B$6:$B256,B256)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B256,$B$6:$B$305)=1)*($R$6:$R$305&gt;R256)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B256="",COUNTIF($B$6:$B256,B256)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R256)+(($R$6:$R$305=R256)*(ROW($B$6:$B$305)&lt;ROW(B256)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23842,7 +23832,7 @@
         <v/>
       </c>
       <c r="S257">
-        <f>IF(OR(B257="",COUNTIF($B$6:$B257,B257)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B257,$B$6:$B$305)=1)*($R$6:$R$305&gt;R257)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B257="",COUNTIF($B$6:$B257,B257)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R257)+(($R$6:$R$305=R257)*(ROW($B$6:$B$305)&lt;ROW(B257)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23864,7 +23854,7 @@
         <v/>
       </c>
       <c r="S258">
-        <f>IF(OR(B258="",COUNTIF($B$6:$B258,B258)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B258,$B$6:$B$305)=1)*($R$6:$R$305&gt;R258)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B258="",COUNTIF($B$6:$B258,B258)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R258)+(($R$6:$R$305=R258)*(ROW($B$6:$B$305)&lt;ROW(B258)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23886,7 +23876,7 @@
         <v/>
       </c>
       <c r="S259">
-        <f>IF(OR(B259="",COUNTIF($B$6:$B259,B259)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B259,$B$6:$B$305)=1)*($R$6:$R$305&gt;R259)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B259="",COUNTIF($B$6:$B259,B259)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R259)+(($R$6:$R$305=R259)*(ROW($B$6:$B$305)&lt;ROW(B259)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23908,7 +23898,7 @@
         <v/>
       </c>
       <c r="S260">
-        <f>IF(OR(B260="",COUNTIF($B$6:$B260,B260)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B260,$B$6:$B$305)=1)*($R$6:$R$305&gt;R260)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B260="",COUNTIF($B$6:$B260,B260)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R260)+(($R$6:$R$305=R260)*(ROW($B$6:$B$305)&lt;ROW(B260)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23930,7 +23920,7 @@
         <v/>
       </c>
       <c r="S261">
-        <f>IF(OR(B261="",COUNTIF($B$6:$B261,B261)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B261,$B$6:$B$305)=1)*($R$6:$R$305&gt;R261)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B261="",COUNTIF($B$6:$B261,B261)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R261)+(($R$6:$R$305=R261)*(ROW($B$6:$B$305)&lt;ROW(B261)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23952,7 +23942,7 @@
         <v/>
       </c>
       <c r="S262">
-        <f>IF(OR(B262="",COUNTIF($B$6:$B262,B262)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B262,$B$6:$B$305)=1)*($R$6:$R$305&gt;R262)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B262="",COUNTIF($B$6:$B262,B262)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R262)+(($R$6:$R$305=R262)*(ROW($B$6:$B$305)&lt;ROW(B262)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23974,7 +23964,7 @@
         <v/>
       </c>
       <c r="S263">
-        <f>IF(OR(B263="",COUNTIF($B$6:$B263,B263)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B263,$B$6:$B$305)=1)*($R$6:$R$305&gt;R263)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B263="",COUNTIF($B$6:$B263,B263)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R263)+(($R$6:$R$305=R263)*(ROW($B$6:$B$305)&lt;ROW(B263)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -23996,7 +23986,7 @@
         <v/>
       </c>
       <c r="S264">
-        <f>IF(OR(B264="",COUNTIF($B$6:$B264,B264)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B264,$B$6:$B$305)=1)*($R$6:$R$305&gt;R264)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B264="",COUNTIF($B$6:$B264,B264)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R264)+(($R$6:$R$305=R264)*(ROW($B$6:$B$305)&lt;ROW(B264)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24018,7 +24008,7 @@
         <v/>
       </c>
       <c r="S265">
-        <f>IF(OR(B265="",COUNTIF($B$6:$B265,B265)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B265,$B$6:$B$305)=1)*($R$6:$R$305&gt;R265)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B265="",COUNTIF($B$6:$B265,B265)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R265)+(($R$6:$R$305=R265)*(ROW($B$6:$B$305)&lt;ROW(B265)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24040,7 +24030,7 @@
         <v/>
       </c>
       <c r="S266">
-        <f>IF(OR(B266="",COUNTIF($B$6:$B266,B266)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B266,$B$6:$B$305)=1)*($R$6:$R$305&gt;R266)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B266="",COUNTIF($B$6:$B266,B266)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R266)+(($R$6:$R$305=R266)*(ROW($B$6:$B$305)&lt;ROW(B266)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24062,7 +24052,7 @@
         <v/>
       </c>
       <c r="S267">
-        <f>IF(OR(B267="",COUNTIF($B$6:$B267,B267)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B267,$B$6:$B$305)=1)*($R$6:$R$305&gt;R267)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B267="",COUNTIF($B$6:$B267,B267)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R267)+(($R$6:$R$305=R267)*(ROW($B$6:$B$305)&lt;ROW(B267)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24084,7 +24074,7 @@
         <v/>
       </c>
       <c r="S268">
-        <f>IF(OR(B268="",COUNTIF($B$6:$B268,B268)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B268,$B$6:$B$305)=1)*($R$6:$R$305&gt;R268)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B268="",COUNTIF($B$6:$B268,B268)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R268)+(($R$6:$R$305=R268)*(ROW($B$6:$B$305)&lt;ROW(B268)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24106,7 +24096,7 @@
         <v/>
       </c>
       <c r="S269">
-        <f>IF(OR(B269="",COUNTIF($B$6:$B269,B269)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B269,$B$6:$B$305)=1)*($R$6:$R$305&gt;R269)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B269="",COUNTIF($B$6:$B269,B269)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R269)+(($R$6:$R$305=R269)*(ROW($B$6:$B$305)&lt;ROW(B269)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24128,7 +24118,7 @@
         <v/>
       </c>
       <c r="S270">
-        <f>IF(OR(B270="",COUNTIF($B$6:$B270,B270)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B270,$B$6:$B$305)=1)*($R$6:$R$305&gt;R270)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B270="",COUNTIF($B$6:$B270,B270)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R270)+(($R$6:$R$305=R270)*(ROW($B$6:$B$305)&lt;ROW(B270)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24150,7 +24140,7 @@
         <v/>
       </c>
       <c r="S271">
-        <f>IF(OR(B271="",COUNTIF($B$6:$B271,B271)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B271,$B$6:$B$305)=1)*($R$6:$R$305&gt;R271)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B271="",COUNTIF($B$6:$B271,B271)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R271)+(($R$6:$R$305=R271)*(ROW($B$6:$B$305)&lt;ROW(B271)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24172,7 +24162,7 @@
         <v/>
       </c>
       <c r="S272">
-        <f>IF(OR(B272="",COUNTIF($B$6:$B272,B272)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B272,$B$6:$B$305)=1)*($R$6:$R$305&gt;R272)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B272="",COUNTIF($B$6:$B272,B272)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R272)+(($R$6:$R$305=R272)*(ROW($B$6:$B$305)&lt;ROW(B272)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24194,7 +24184,7 @@
         <v/>
       </c>
       <c r="S273">
-        <f>IF(OR(B273="",COUNTIF($B$6:$B273,B273)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B273,$B$6:$B$305)=1)*($R$6:$R$305&gt;R273)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B273="",COUNTIF($B$6:$B273,B273)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R273)+(($R$6:$R$305=R273)*(ROW($B$6:$B$305)&lt;ROW(B273)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24216,7 +24206,7 @@
         <v/>
       </c>
       <c r="S274">
-        <f>IF(OR(B274="",COUNTIF($B$6:$B274,B274)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B274,$B$6:$B$305)=1)*($R$6:$R$305&gt;R274)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B274="",COUNTIF($B$6:$B274,B274)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R274)+(($R$6:$R$305=R274)*(ROW($B$6:$B$305)&lt;ROW(B274)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24238,7 +24228,7 @@
         <v/>
       </c>
       <c r="S275">
-        <f>IF(OR(B275="",COUNTIF($B$6:$B275,B275)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B275,$B$6:$B$305)=1)*($R$6:$R$305&gt;R275)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B275="",COUNTIF($B$6:$B275,B275)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R275)+(($R$6:$R$305=R275)*(ROW($B$6:$B$305)&lt;ROW(B275)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24260,7 +24250,7 @@
         <v/>
       </c>
       <c r="S276">
-        <f>IF(OR(B276="",COUNTIF($B$6:$B276,B276)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B276,$B$6:$B$305)=1)*($R$6:$R$305&gt;R276)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B276="",COUNTIF($B$6:$B276,B276)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R276)+(($R$6:$R$305=R276)*(ROW($B$6:$B$305)&lt;ROW(B276)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24282,7 +24272,7 @@
         <v/>
       </c>
       <c r="S277">
-        <f>IF(OR(B277="",COUNTIF($B$6:$B277,B277)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B277,$B$6:$B$305)=1)*($R$6:$R$305&gt;R277)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B277="",COUNTIF($B$6:$B277,B277)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R277)+(($R$6:$R$305=R277)*(ROW($B$6:$B$305)&lt;ROW(B277)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24304,7 +24294,7 @@
         <v/>
       </c>
       <c r="S278">
-        <f>IF(OR(B278="",COUNTIF($B$6:$B278,B278)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B278,$B$6:$B$305)=1)*($R$6:$R$305&gt;R278)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B278="",COUNTIF($B$6:$B278,B278)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R278)+(($R$6:$R$305=R278)*(ROW($B$6:$B$305)&lt;ROW(B278)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24326,7 +24316,7 @@
         <v/>
       </c>
       <c r="S279">
-        <f>IF(OR(B279="",COUNTIF($B$6:$B279,B279)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B279,$B$6:$B$305)=1)*($R$6:$R$305&gt;R279)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B279="",COUNTIF($B$6:$B279,B279)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R279)+(($R$6:$R$305=R279)*(ROW($B$6:$B$305)&lt;ROW(B279)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24348,7 +24338,7 @@
         <v/>
       </c>
       <c r="S280">
-        <f>IF(OR(B280="",COUNTIF($B$6:$B280,B280)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B280,$B$6:$B$305)=1)*($R$6:$R$305&gt;R280)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B280="",COUNTIF($B$6:$B280,B280)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R280)+(($R$6:$R$305=R280)*(ROW($B$6:$B$305)&lt;ROW(B280)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24370,7 +24360,7 @@
         <v/>
       </c>
       <c r="S281">
-        <f>IF(OR(B281="",COUNTIF($B$6:$B281,B281)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B281,$B$6:$B$305)=1)*($R$6:$R$305&gt;R281)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B281="",COUNTIF($B$6:$B281,B281)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R281)+(($R$6:$R$305=R281)*(ROW($B$6:$B$305)&lt;ROW(B281)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24392,7 +24382,7 @@
         <v/>
       </c>
       <c r="S282">
-        <f>IF(OR(B282="",COUNTIF($B$6:$B282,B282)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B282,$B$6:$B$305)=1)*($R$6:$R$305&gt;R282)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B282="",COUNTIF($B$6:$B282,B282)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R282)+(($R$6:$R$305=R282)*(ROW($B$6:$B$305)&lt;ROW(B282)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24414,7 +24404,7 @@
         <v/>
       </c>
       <c r="S283">
-        <f>IF(OR(B283="",COUNTIF($B$6:$B283,B283)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B283,$B$6:$B$305)=1)*($R$6:$R$305&gt;R283)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B283="",COUNTIF($B$6:$B283,B283)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R283)+(($R$6:$R$305=R283)*(ROW($B$6:$B$305)&lt;ROW(B283)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24436,7 +24426,7 @@
         <v/>
       </c>
       <c r="S284">
-        <f>IF(OR(B284="",COUNTIF($B$6:$B284,B284)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B284,$B$6:$B$305)=1)*($R$6:$R$305&gt;R284)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B284="",COUNTIF($B$6:$B284,B284)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R284)+(($R$6:$R$305=R284)*(ROW($B$6:$B$305)&lt;ROW(B284)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24458,7 +24448,7 @@
         <v/>
       </c>
       <c r="S285">
-        <f>IF(OR(B285="",COUNTIF($B$6:$B285,B285)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B285,$B$6:$B$305)=1)*($R$6:$R$305&gt;R285)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B285="",COUNTIF($B$6:$B285,B285)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R285)+(($R$6:$R$305=R285)*(ROW($B$6:$B$305)&lt;ROW(B285)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24480,7 +24470,7 @@
         <v/>
       </c>
       <c r="S286">
-        <f>IF(OR(B286="",COUNTIF($B$6:$B286,B286)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B286,$B$6:$B$305)=1)*($R$6:$R$305&gt;R286)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B286="",COUNTIF($B$6:$B286,B286)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R286)+(($R$6:$R$305=R286)*(ROW($B$6:$B$305)&lt;ROW(B286)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24502,7 +24492,7 @@
         <v/>
       </c>
       <c r="S287">
-        <f>IF(OR(B287="",COUNTIF($B$6:$B287,B287)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B287,$B$6:$B$305)=1)*($R$6:$R$305&gt;R287)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B287="",COUNTIF($B$6:$B287,B287)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R287)+(($R$6:$R$305=R287)*(ROW($B$6:$B$305)&lt;ROW(B287)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24524,7 +24514,7 @@
         <v/>
       </c>
       <c r="S288">
-        <f>IF(OR(B288="",COUNTIF($B$6:$B288,B288)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B288,$B$6:$B$305)=1)*($R$6:$R$305&gt;R288)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B288="",COUNTIF($B$6:$B288,B288)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R288)+(($R$6:$R$305=R288)*(ROW($B$6:$B$305)&lt;ROW(B288)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24546,7 +24536,7 @@
         <v/>
       </c>
       <c r="S289">
-        <f>IF(OR(B289="",COUNTIF($B$6:$B289,B289)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B289,$B$6:$B$305)=1)*($R$6:$R$305&gt;R289)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B289="",COUNTIF($B$6:$B289,B289)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R289)+(($R$6:$R$305=R289)*(ROW($B$6:$B$305)&lt;ROW(B289)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24568,7 +24558,7 @@
         <v/>
       </c>
       <c r="S290">
-        <f>IF(OR(B290="",COUNTIF($B$6:$B290,B290)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B290,$B$6:$B$305)=1)*($R$6:$R$305&gt;R290)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B290="",COUNTIF($B$6:$B290,B290)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R290)+(($R$6:$R$305=R290)*(ROW($B$6:$B$305)&lt;ROW(B290)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24590,7 +24580,7 @@
         <v/>
       </c>
       <c r="S291">
-        <f>IF(OR(B291="",COUNTIF($B$6:$B291,B291)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B291,$B$6:$B$305)=1)*($R$6:$R$305&gt;R291)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B291="",COUNTIF($B$6:$B291,B291)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R291)+(($R$6:$R$305=R291)*(ROW($B$6:$B$305)&lt;ROW(B291)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24612,7 +24602,7 @@
         <v/>
       </c>
       <c r="S292">
-        <f>IF(OR(B292="",COUNTIF($B$6:$B292,B292)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B292,$B$6:$B$305)=1)*($R$6:$R$305&gt;R292)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B292="",COUNTIF($B$6:$B292,B292)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R292)+(($R$6:$R$305=R292)*(ROW($B$6:$B$305)&lt;ROW(B292)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24634,7 +24624,7 @@
         <v/>
       </c>
       <c r="S293">
-        <f>IF(OR(B293="",COUNTIF($B$6:$B293,B293)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B293,$B$6:$B$305)=1)*($R$6:$R$305&gt;R293)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B293="",COUNTIF($B$6:$B293,B293)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R293)+(($R$6:$R$305=R293)*(ROW($B$6:$B$305)&lt;ROW(B293)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24656,7 +24646,7 @@
         <v/>
       </c>
       <c r="S294">
-        <f>IF(OR(B294="",COUNTIF($B$6:$B294,B294)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B294,$B$6:$B$305)=1)*($R$6:$R$305&gt;R294)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B294="",COUNTIF($B$6:$B294,B294)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R294)+(($R$6:$R$305=R294)*(ROW($B$6:$B$305)&lt;ROW(B294)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24678,7 +24668,7 @@
         <v/>
       </c>
       <c r="S295">
-        <f>IF(OR(B295="",COUNTIF($B$6:$B295,B295)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B295,$B$6:$B$305)=1)*($R$6:$R$305&gt;R295)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B295="",COUNTIF($B$6:$B295,B295)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R295)+(($R$6:$R$305=R295)*(ROW($B$6:$B$305)&lt;ROW(B295)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24700,7 +24690,7 @@
         <v/>
       </c>
       <c r="S296">
-        <f>IF(OR(B296="",COUNTIF($B$6:$B296,B296)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B296,$B$6:$B$305)=1)*($R$6:$R$305&gt;R296)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B296="",COUNTIF($B$6:$B296,B296)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R296)+(($R$6:$R$305=R296)*(ROW($B$6:$B$305)&lt;ROW(B296)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24722,7 +24712,7 @@
         <v/>
       </c>
       <c r="S297">
-        <f>IF(OR(B297="",COUNTIF($B$6:$B297,B297)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B297,$B$6:$B$305)=1)*($R$6:$R$305&gt;R297)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B297="",COUNTIF($B$6:$B297,B297)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R297)+(($R$6:$R$305=R297)*(ROW($B$6:$B$305)&lt;ROW(B297)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24744,7 +24734,7 @@
         <v/>
       </c>
       <c r="S298">
-        <f>IF(OR(B298="",COUNTIF($B$6:$B298,B298)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B298,$B$6:$B$305)=1)*($R$6:$R$305&gt;R298)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B298="",COUNTIF($B$6:$B298,B298)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R298)+(($R$6:$R$305=R298)*(ROW($B$6:$B$305)&lt;ROW(B298)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24766,7 +24756,7 @@
         <v/>
       </c>
       <c r="S299">
-        <f>IF(OR(B299="",COUNTIF($B$6:$B299,B299)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B299,$B$6:$B$305)=1)*($R$6:$R$305&gt;R299)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B299="",COUNTIF($B$6:$B299,B299)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R299)+(($R$6:$R$305=R299)*(ROW($B$6:$B$305)&lt;ROW(B299)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24788,7 +24778,7 @@
         <v/>
       </c>
       <c r="S300">
-        <f>IF(OR(B300="",COUNTIF($B$6:$B300,B300)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B300,$B$6:$B$305)=1)*($R$6:$R$305&gt;R300)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B300="",COUNTIF($B$6:$B300,B300)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R300)+(($R$6:$R$305=R300)*(ROW($B$6:$B$305)&lt;ROW(B300)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24810,7 +24800,7 @@
         <v/>
       </c>
       <c r="S301">
-        <f>IF(OR(B301="",COUNTIF($B$6:$B301,B301)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B301,$B$6:$B$305)=1)*($R$6:$R$305&gt;R301)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B301="",COUNTIF($B$6:$B301,B301)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R301)+(($R$6:$R$305=R301)*(ROW($B$6:$B$305)&lt;ROW(B301)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24832,7 +24822,7 @@
         <v/>
       </c>
       <c r="S302">
-        <f>IF(OR(B302="",COUNTIF($B$6:$B302,B302)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B302,$B$6:$B$305)=1)*($R$6:$R$305&gt;R302)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B302="",COUNTIF($B$6:$B302,B302)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R302)+(($R$6:$R$305=R302)*(ROW($B$6:$B$305)&lt;ROW(B302)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24854,7 +24844,7 @@
         <v/>
       </c>
       <c r="S303">
-        <f>IF(OR(B303="",COUNTIF($B$6:$B303,B303)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B303,$B$6:$B$305)=1)*($R$6:$R$305&gt;R303)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B303="",COUNTIF($B$6:$B303,B303)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R303)+(($R$6:$R$305=R303)*(ROW($B$6:$B$305)&lt;ROW(B303)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24876,7 +24866,7 @@
         <v/>
       </c>
       <c r="S304">
-        <f>IF(OR(B304="",COUNTIF($B$6:$B304,B304)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B304,$B$6:$B$305)=1)*($R$6:$R$305&gt;R304)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B304="",COUNTIF($B$6:$B304,B304)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R304)+(($R$6:$R$305=R304)*(ROW($B$6:$B$305)&lt;ROW(B304)))))+1)</f>
         <v/>
       </c>
     </row>
@@ -24898,7 +24888,7 @@
         <v/>
       </c>
       <c r="S305">
-        <f>IF(OR(B305="",COUNTIF($B$6:$B305,B305)&gt;1),"",SUMPRODUCT((COUNTIF($B$5:B305,$B$6:$B$305)=1)*($R$6:$R$305&gt;R305)*($B$6:$B$305&lt;&gt;""))+1)</f>
+        <f>IF(OR(B305="",COUNTIF($B$6:$B305,B305)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R305)+(($R$6:$R$305=R305)*(ROW($B$6:$B$305)&lt;ROW(B305)))))+1)</f>
         <v/>
       </c>
     </row>

--- a/WorldCup2026_Sweepstake.xlsx
+++ b/WorldCup2026_Sweepstake.xlsx
@@ -15540,7 +15540,7 @@
         <v/>
       </c>
       <c r="S6">
-        <f>IF(OR(B6="",COUNTIF($B$6:$B6,B6)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R6)+(($R$6:$R$305=R6)*(ROW($B$6:$B$305)&lt;ROW(B6)))))+1)</f>
+        <f>IF(OR(B6="",COUNTIF($B$6:$B6,B6)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R6)+(($R$6:$R$305=R6)*($B$6:$B$305&lt;B6)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T6">
@@ -15608,7 +15608,7 @@
         <v/>
       </c>
       <c r="S7">
-        <f>IF(OR(B7="",COUNTIF($B$6:$B7,B7)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R7)+(($R$6:$R$305=R7)*(ROW($B$6:$B$305)&lt;ROW(B7)))))+1)</f>
+        <f>IF(OR(B7="",COUNTIF($B$6:$B7,B7)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R7)+(($R$6:$R$305=R7)*($B$6:$B$305&lt;B7)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T7">
@@ -15676,7 +15676,7 @@
         <v/>
       </c>
       <c r="S8">
-        <f>IF(OR(B8="",COUNTIF($B$6:$B8,B8)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R8)+(($R$6:$R$305=R8)*(ROW($B$6:$B$305)&lt;ROW(B8)))))+1)</f>
+        <f>IF(OR(B8="",COUNTIF($B$6:$B8,B8)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R8)+(($R$6:$R$305=R8)*($B$6:$B$305&lt;B8)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T8">
@@ -15744,7 +15744,7 @@
         <v/>
       </c>
       <c r="S9">
-        <f>IF(OR(B9="",COUNTIF($B$6:$B9,B9)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R9)+(($R$6:$R$305=R9)*(ROW($B$6:$B$305)&lt;ROW(B9)))))+1)</f>
+        <f>IF(OR(B9="",COUNTIF($B$6:$B9,B9)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R9)+(($R$6:$R$305=R9)*($B$6:$B$305&lt;B9)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T9">
@@ -15812,7 +15812,7 @@
         <v/>
       </c>
       <c r="S10">
-        <f>IF(OR(B10="",COUNTIF($B$6:$B10,B10)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R10)+(($R$6:$R$305=R10)*(ROW($B$6:$B$305)&lt;ROW(B10)))))+1)</f>
+        <f>IF(OR(B10="",COUNTIF($B$6:$B10,B10)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R10)+(($R$6:$R$305=R10)*($B$6:$B$305&lt;B10)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T10">
@@ -15880,7 +15880,7 @@
         <v/>
       </c>
       <c r="S11">
-        <f>IF(OR(B11="",COUNTIF($B$6:$B11,B11)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R11)+(($R$6:$R$305=R11)*(ROW($B$6:$B$305)&lt;ROW(B11)))))+1)</f>
+        <f>IF(OR(B11="",COUNTIF($B$6:$B11,B11)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R11)+(($R$6:$R$305=R11)*($B$6:$B$305&lt;B11)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T11">
@@ -15948,7 +15948,7 @@
         <v/>
       </c>
       <c r="S12">
-        <f>IF(OR(B12="",COUNTIF($B$6:$B12,B12)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R12)+(($R$6:$R$305=R12)*(ROW($B$6:$B$305)&lt;ROW(B12)))))+1)</f>
+        <f>IF(OR(B12="",COUNTIF($B$6:$B12,B12)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R12)+(($R$6:$R$305=R12)*($B$6:$B$305&lt;B12)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T12">
@@ -16016,7 +16016,7 @@
         <v/>
       </c>
       <c r="S13">
-        <f>IF(OR(B13="",COUNTIF($B$6:$B13,B13)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R13)+(($R$6:$R$305=R13)*(ROW($B$6:$B$305)&lt;ROW(B13)))))+1)</f>
+        <f>IF(OR(B13="",COUNTIF($B$6:$B13,B13)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R13)+(($R$6:$R$305=R13)*($B$6:$B$305&lt;B13)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T13">
@@ -16084,7 +16084,7 @@
         <v/>
       </c>
       <c r="S14">
-        <f>IF(OR(B14="",COUNTIF($B$6:$B14,B14)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R14)+(($R$6:$R$305=R14)*(ROW($B$6:$B$305)&lt;ROW(B14)))))+1)</f>
+        <f>IF(OR(B14="",COUNTIF($B$6:$B14,B14)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R14)+(($R$6:$R$305=R14)*($B$6:$B$305&lt;B14)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T14">
@@ -16152,7 +16152,7 @@
         <v/>
       </c>
       <c r="S15">
-        <f>IF(OR(B15="",COUNTIF($B$6:$B15,B15)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R15)+(($R$6:$R$305=R15)*(ROW($B$6:$B$305)&lt;ROW(B15)))))+1)</f>
+        <f>IF(OR(B15="",COUNTIF($B$6:$B15,B15)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R15)+(($R$6:$R$305=R15)*($B$6:$B$305&lt;B15)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T15">
@@ -16220,7 +16220,7 @@
         <v/>
       </c>
       <c r="S16">
-        <f>IF(OR(B16="",COUNTIF($B$6:$B16,B16)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R16)+(($R$6:$R$305=R16)*(ROW($B$6:$B$305)&lt;ROW(B16)))))+1)</f>
+        <f>IF(OR(B16="",COUNTIF($B$6:$B16,B16)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R16)+(($R$6:$R$305=R16)*($B$6:$B$305&lt;B16)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T16">
@@ -16288,7 +16288,7 @@
         <v/>
       </c>
       <c r="S17">
-        <f>IF(OR(B17="",COUNTIF($B$6:$B17,B17)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R17)+(($R$6:$R$305=R17)*(ROW($B$6:$B$305)&lt;ROW(B17)))))+1)</f>
+        <f>IF(OR(B17="",COUNTIF($B$6:$B17,B17)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R17)+(($R$6:$R$305=R17)*($B$6:$B$305&lt;B17)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T17">
@@ -16356,7 +16356,7 @@
         <v/>
       </c>
       <c r="S18">
-        <f>IF(OR(B18="",COUNTIF($B$6:$B18,B18)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R18)+(($R$6:$R$305=R18)*(ROW($B$6:$B$305)&lt;ROW(B18)))))+1)</f>
+        <f>IF(OR(B18="",COUNTIF($B$6:$B18,B18)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R18)+(($R$6:$R$305=R18)*($B$6:$B$305&lt;B18)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T18">
@@ -16424,7 +16424,7 @@
         <v/>
       </c>
       <c r="S19">
-        <f>IF(OR(B19="",COUNTIF($B$6:$B19,B19)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R19)+(($R$6:$R$305=R19)*(ROW($B$6:$B$305)&lt;ROW(B19)))))+1)</f>
+        <f>IF(OR(B19="",COUNTIF($B$6:$B19,B19)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R19)+(($R$6:$R$305=R19)*($B$6:$B$305&lt;B19)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T19">
@@ -16492,7 +16492,7 @@
         <v/>
       </c>
       <c r="S20">
-        <f>IF(OR(B20="",COUNTIF($B$6:$B20,B20)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R20)+(($R$6:$R$305=R20)*(ROW($B$6:$B$305)&lt;ROW(B20)))))+1)</f>
+        <f>IF(OR(B20="",COUNTIF($B$6:$B20,B20)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R20)+(($R$6:$R$305=R20)*($B$6:$B$305&lt;B20)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T20">
@@ -16560,7 +16560,7 @@
         <v/>
       </c>
       <c r="S21">
-        <f>IF(OR(B21="",COUNTIF($B$6:$B21,B21)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R21)+(($R$6:$R$305=R21)*(ROW($B$6:$B$305)&lt;ROW(B21)))))+1)</f>
+        <f>IF(OR(B21="",COUNTIF($B$6:$B21,B21)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R21)+(($R$6:$R$305=R21)*($B$6:$B$305&lt;B21)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T21">
@@ -16628,7 +16628,7 @@
         <v/>
       </c>
       <c r="S22">
-        <f>IF(OR(B22="",COUNTIF($B$6:$B22,B22)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R22)+(($R$6:$R$305=R22)*(ROW($B$6:$B$305)&lt;ROW(B22)))))+1)</f>
+        <f>IF(OR(B22="",COUNTIF($B$6:$B22,B22)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R22)+(($R$6:$R$305=R22)*($B$6:$B$305&lt;B22)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T22">
@@ -16696,7 +16696,7 @@
         <v/>
       </c>
       <c r="S23">
-        <f>IF(OR(B23="",COUNTIF($B$6:$B23,B23)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R23)+(($R$6:$R$305=R23)*(ROW($B$6:$B$305)&lt;ROW(B23)))))+1)</f>
+        <f>IF(OR(B23="",COUNTIF($B$6:$B23,B23)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R23)+(($R$6:$R$305=R23)*($B$6:$B$305&lt;B23)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T23">
@@ -16764,7 +16764,7 @@
         <v/>
       </c>
       <c r="S24">
-        <f>IF(OR(B24="",COUNTIF($B$6:$B24,B24)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R24)+(($R$6:$R$305=R24)*(ROW($B$6:$B$305)&lt;ROW(B24)))))+1)</f>
+        <f>IF(OR(B24="",COUNTIF($B$6:$B24,B24)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R24)+(($R$6:$R$305=R24)*($B$6:$B$305&lt;B24)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T24">
@@ -16832,7 +16832,7 @@
         <v/>
       </c>
       <c r="S25">
-        <f>IF(OR(B25="",COUNTIF($B$6:$B25,B25)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R25)+(($R$6:$R$305=R25)*(ROW($B$6:$B$305)&lt;ROW(B25)))))+1)</f>
+        <f>IF(OR(B25="",COUNTIF($B$6:$B25,B25)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R25)+(($R$6:$R$305=R25)*($B$6:$B$305&lt;B25)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T25">
@@ -16900,7 +16900,7 @@
         <v/>
       </c>
       <c r="S26">
-        <f>IF(OR(B26="",COUNTIF($B$6:$B26,B26)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R26)+(($R$6:$R$305=R26)*(ROW($B$6:$B$305)&lt;ROW(B26)))))+1)</f>
+        <f>IF(OR(B26="",COUNTIF($B$6:$B26,B26)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R26)+(($R$6:$R$305=R26)*($B$6:$B$305&lt;B26)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T26">
@@ -16968,7 +16968,7 @@
         <v/>
       </c>
       <c r="S27">
-        <f>IF(OR(B27="",COUNTIF($B$6:$B27,B27)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R27)+(($R$6:$R$305=R27)*(ROW($B$6:$B$305)&lt;ROW(B27)))))+1)</f>
+        <f>IF(OR(B27="",COUNTIF($B$6:$B27,B27)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R27)+(($R$6:$R$305=R27)*($B$6:$B$305&lt;B27)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T27">
@@ -17036,7 +17036,7 @@
         <v/>
       </c>
       <c r="S28">
-        <f>IF(OR(B28="",COUNTIF($B$6:$B28,B28)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R28)+(($R$6:$R$305=R28)*(ROW($B$6:$B$305)&lt;ROW(B28)))))+1)</f>
+        <f>IF(OR(B28="",COUNTIF($B$6:$B28,B28)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R28)+(($R$6:$R$305=R28)*($B$6:$B$305&lt;B28)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T28">
@@ -17104,7 +17104,7 @@
         <v/>
       </c>
       <c r="S29">
-        <f>IF(OR(B29="",COUNTIF($B$6:$B29,B29)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R29)+(($R$6:$R$305=R29)*(ROW($B$6:$B$305)&lt;ROW(B29)))))+1)</f>
+        <f>IF(OR(B29="",COUNTIF($B$6:$B29,B29)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R29)+(($R$6:$R$305=R29)*($B$6:$B$305&lt;B29)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T29">
@@ -17172,7 +17172,7 @@
         <v/>
       </c>
       <c r="S30">
-        <f>IF(OR(B30="",COUNTIF($B$6:$B30,B30)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R30)+(($R$6:$R$305=R30)*(ROW($B$6:$B$305)&lt;ROW(B30)))))+1)</f>
+        <f>IF(OR(B30="",COUNTIF($B$6:$B30,B30)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R30)+(($R$6:$R$305=R30)*($B$6:$B$305&lt;B30)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T30">
@@ -17240,7 +17240,7 @@
         <v/>
       </c>
       <c r="S31">
-        <f>IF(OR(B31="",COUNTIF($B$6:$B31,B31)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R31)+(($R$6:$R$305=R31)*(ROW($B$6:$B$305)&lt;ROW(B31)))))+1)</f>
+        <f>IF(OR(B31="",COUNTIF($B$6:$B31,B31)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R31)+(($R$6:$R$305=R31)*($B$6:$B$305&lt;B31)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T31">
@@ -17308,7 +17308,7 @@
         <v/>
       </c>
       <c r="S32">
-        <f>IF(OR(B32="",COUNTIF($B$6:$B32,B32)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R32)+(($R$6:$R$305=R32)*(ROW($B$6:$B$305)&lt;ROW(B32)))))+1)</f>
+        <f>IF(OR(B32="",COUNTIF($B$6:$B32,B32)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R32)+(($R$6:$R$305=R32)*($B$6:$B$305&lt;B32)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T32">
@@ -17376,7 +17376,7 @@
         <v/>
       </c>
       <c r="S33">
-        <f>IF(OR(B33="",COUNTIF($B$6:$B33,B33)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R33)+(($R$6:$R$305=R33)*(ROW($B$6:$B$305)&lt;ROW(B33)))))+1)</f>
+        <f>IF(OR(B33="",COUNTIF($B$6:$B33,B33)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R33)+(($R$6:$R$305=R33)*($B$6:$B$305&lt;B33)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T33">
@@ -17444,7 +17444,7 @@
         <v/>
       </c>
       <c r="S34">
-        <f>IF(OR(B34="",COUNTIF($B$6:$B34,B34)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R34)+(($R$6:$R$305=R34)*(ROW($B$6:$B$305)&lt;ROW(B34)))))+1)</f>
+        <f>IF(OR(B34="",COUNTIF($B$6:$B34,B34)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R34)+(($R$6:$R$305=R34)*($B$6:$B$305&lt;B34)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T34">
@@ -17512,7 +17512,7 @@
         <v/>
       </c>
       <c r="S35">
-        <f>IF(OR(B35="",COUNTIF($B$6:$B35,B35)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R35)+(($R$6:$R$305=R35)*(ROW($B$6:$B$305)&lt;ROW(B35)))))+1)</f>
+        <f>IF(OR(B35="",COUNTIF($B$6:$B35,B35)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R35)+(($R$6:$R$305=R35)*($B$6:$B$305&lt;B35)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T35">
@@ -17565,7 +17565,7 @@
         <v/>
       </c>
       <c r="S36">
-        <f>IF(OR(B36="",COUNTIF($B$6:$B36,B36)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R36)+(($R$6:$R$305=R36)*(ROW($B$6:$B$305)&lt;ROW(B36)))))+1)</f>
+        <f>IF(OR(B36="",COUNTIF($B$6:$B36,B36)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R36)+(($R$6:$R$305=R36)*($B$6:$B$305&lt;B36)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T36">
@@ -17618,7 +17618,7 @@
         <v/>
       </c>
       <c r="S37">
-        <f>IF(OR(B37="",COUNTIF($B$6:$B37,B37)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R37)+(($R$6:$R$305=R37)*(ROW($B$6:$B$305)&lt;ROW(B37)))))+1)</f>
+        <f>IF(OR(B37="",COUNTIF($B$6:$B37,B37)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R37)+(($R$6:$R$305=R37)*($B$6:$B$305&lt;B37)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T37">
@@ -17671,7 +17671,7 @@
         <v/>
       </c>
       <c r="S38">
-        <f>IF(OR(B38="",COUNTIF($B$6:$B38,B38)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R38)+(($R$6:$R$305=R38)*(ROW($B$6:$B$305)&lt;ROW(B38)))))+1)</f>
+        <f>IF(OR(B38="",COUNTIF($B$6:$B38,B38)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R38)+(($R$6:$R$305=R38)*($B$6:$B$305&lt;B38)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T38">
@@ -17724,7 +17724,7 @@
         <v/>
       </c>
       <c r="S39">
-        <f>IF(OR(B39="",COUNTIF($B$6:$B39,B39)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R39)+(($R$6:$R$305=R39)*(ROW($B$6:$B$305)&lt;ROW(B39)))))+1)</f>
+        <f>IF(OR(B39="",COUNTIF($B$6:$B39,B39)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R39)+(($R$6:$R$305=R39)*($B$6:$B$305&lt;B39)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T39">
@@ -17777,7 +17777,7 @@
         <v/>
       </c>
       <c r="S40">
-        <f>IF(OR(B40="",COUNTIF($B$6:$B40,B40)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R40)+(($R$6:$R$305=R40)*(ROW($B$6:$B$305)&lt;ROW(B40)))))+1)</f>
+        <f>IF(OR(B40="",COUNTIF($B$6:$B40,B40)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R40)+(($R$6:$R$305=R40)*($B$6:$B$305&lt;B40)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T40">
@@ -17830,7 +17830,7 @@
         <v/>
       </c>
       <c r="S41">
-        <f>IF(OR(B41="",COUNTIF($B$6:$B41,B41)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R41)+(($R$6:$R$305=R41)*(ROW($B$6:$B$305)&lt;ROW(B41)))))+1)</f>
+        <f>IF(OR(B41="",COUNTIF($B$6:$B41,B41)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R41)+(($R$6:$R$305=R41)*($B$6:$B$305&lt;B41)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T41">
@@ -17883,7 +17883,7 @@
         <v/>
       </c>
       <c r="S42">
-        <f>IF(OR(B42="",COUNTIF($B$6:$B42,B42)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R42)+(($R$6:$R$305=R42)*(ROW($B$6:$B$305)&lt;ROW(B42)))))+1)</f>
+        <f>IF(OR(B42="",COUNTIF($B$6:$B42,B42)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R42)+(($R$6:$R$305=R42)*($B$6:$B$305&lt;B42)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T42">
@@ -17936,7 +17936,7 @@
         <v/>
       </c>
       <c r="S43">
-        <f>IF(OR(B43="",COUNTIF($B$6:$B43,B43)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R43)+(($R$6:$R$305=R43)*(ROW($B$6:$B$305)&lt;ROW(B43)))))+1)</f>
+        <f>IF(OR(B43="",COUNTIF($B$6:$B43,B43)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R43)+(($R$6:$R$305=R43)*($B$6:$B$305&lt;B43)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T43">
@@ -17989,7 +17989,7 @@
         <v/>
       </c>
       <c r="S44">
-        <f>IF(OR(B44="",COUNTIF($B$6:$B44,B44)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R44)+(($R$6:$R$305=R44)*(ROW($B$6:$B$305)&lt;ROW(B44)))))+1)</f>
+        <f>IF(OR(B44="",COUNTIF($B$6:$B44,B44)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R44)+(($R$6:$R$305=R44)*($B$6:$B$305&lt;B44)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T44">
@@ -18042,7 +18042,7 @@
         <v/>
       </c>
       <c r="S45">
-        <f>IF(OR(B45="",COUNTIF($B$6:$B45,B45)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R45)+(($R$6:$R$305=R45)*(ROW($B$6:$B$305)&lt;ROW(B45)))))+1)</f>
+        <f>IF(OR(B45="",COUNTIF($B$6:$B45,B45)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R45)+(($R$6:$R$305=R45)*($B$6:$B$305&lt;B45)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T45">
@@ -18095,7 +18095,7 @@
         <v/>
       </c>
       <c r="S46">
-        <f>IF(OR(B46="",COUNTIF($B$6:$B46,B46)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R46)+(($R$6:$R$305=R46)*(ROW($B$6:$B$305)&lt;ROW(B46)))))+1)</f>
+        <f>IF(OR(B46="",COUNTIF($B$6:$B46,B46)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R46)+(($R$6:$R$305=R46)*($B$6:$B$305&lt;B46)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T46">
@@ -18148,7 +18148,7 @@
         <v/>
       </c>
       <c r="S47">
-        <f>IF(OR(B47="",COUNTIF($B$6:$B47,B47)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R47)+(($R$6:$R$305=R47)*(ROW($B$6:$B$305)&lt;ROW(B47)))))+1)</f>
+        <f>IF(OR(B47="",COUNTIF($B$6:$B47,B47)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R47)+(($R$6:$R$305=R47)*($B$6:$B$305&lt;B47)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T47">
@@ -18201,7 +18201,7 @@
         <v/>
       </c>
       <c r="S48">
-        <f>IF(OR(B48="",COUNTIF($B$6:$B48,B48)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R48)+(($R$6:$R$305=R48)*(ROW($B$6:$B$305)&lt;ROW(B48)))))+1)</f>
+        <f>IF(OR(B48="",COUNTIF($B$6:$B48,B48)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R48)+(($R$6:$R$305=R48)*($B$6:$B$305&lt;B48)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T48">
@@ -18254,7 +18254,7 @@
         <v/>
       </c>
       <c r="S49">
-        <f>IF(OR(B49="",COUNTIF($B$6:$B49,B49)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R49)+(($R$6:$R$305=R49)*(ROW($B$6:$B$305)&lt;ROW(B49)))))+1)</f>
+        <f>IF(OR(B49="",COUNTIF($B$6:$B49,B49)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R49)+(($R$6:$R$305=R49)*($B$6:$B$305&lt;B49)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T49">
@@ -18307,7 +18307,7 @@
         <v/>
       </c>
       <c r="S50">
-        <f>IF(OR(B50="",COUNTIF($B$6:$B50,B50)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R50)+(($R$6:$R$305=R50)*(ROW($B$6:$B$305)&lt;ROW(B50)))))+1)</f>
+        <f>IF(OR(B50="",COUNTIF($B$6:$B50,B50)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R50)+(($R$6:$R$305=R50)*($B$6:$B$305&lt;B50)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T50">
@@ -18360,7 +18360,7 @@
         <v/>
       </c>
       <c r="S51">
-        <f>IF(OR(B51="",COUNTIF($B$6:$B51,B51)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R51)+(($R$6:$R$305=R51)*(ROW($B$6:$B$305)&lt;ROW(B51)))))+1)</f>
+        <f>IF(OR(B51="",COUNTIF($B$6:$B51,B51)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R51)+(($R$6:$R$305=R51)*($B$6:$B$305&lt;B51)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T51">
@@ -18413,7 +18413,7 @@
         <v/>
       </c>
       <c r="S52">
-        <f>IF(OR(B52="",COUNTIF($B$6:$B52,B52)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R52)+(($R$6:$R$305=R52)*(ROW($B$6:$B$305)&lt;ROW(B52)))))+1)</f>
+        <f>IF(OR(B52="",COUNTIF($B$6:$B52,B52)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R52)+(($R$6:$R$305=R52)*($B$6:$B$305&lt;B52)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T52">
@@ -18466,7 +18466,7 @@
         <v/>
       </c>
       <c r="S53">
-        <f>IF(OR(B53="",COUNTIF($B$6:$B53,B53)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R53)+(($R$6:$R$305=R53)*(ROW($B$6:$B$305)&lt;ROW(B53)))))+1)</f>
+        <f>IF(OR(B53="",COUNTIF($B$6:$B53,B53)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R53)+(($R$6:$R$305=R53)*($B$6:$B$305&lt;B53)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T53">
@@ -18519,7 +18519,7 @@
         <v/>
       </c>
       <c r="S54">
-        <f>IF(OR(B54="",COUNTIF($B$6:$B54,B54)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R54)+(($R$6:$R$305=R54)*(ROW($B$6:$B$305)&lt;ROW(B54)))))+1)</f>
+        <f>IF(OR(B54="",COUNTIF($B$6:$B54,B54)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R54)+(($R$6:$R$305=R54)*($B$6:$B$305&lt;B54)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T54">
@@ -18572,7 +18572,7 @@
         <v/>
       </c>
       <c r="S55">
-        <f>IF(OR(B55="",COUNTIF($B$6:$B55,B55)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R55)+(($R$6:$R$305=R55)*(ROW($B$6:$B$305)&lt;ROW(B55)))))+1)</f>
+        <f>IF(OR(B55="",COUNTIF($B$6:$B55,B55)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R55)+(($R$6:$R$305=R55)*($B$6:$B$305&lt;B55)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T55">
@@ -18610,7 +18610,7 @@
         <v/>
       </c>
       <c r="S56">
-        <f>IF(OR(B56="",COUNTIF($B$6:$B56,B56)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R56)+(($R$6:$R$305=R56)*(ROW($B$6:$B$305)&lt;ROW(B56)))))+1)</f>
+        <f>IF(OR(B56="",COUNTIF($B$6:$B56,B56)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R56)+(($R$6:$R$305=R56)*($B$6:$B$305&lt;B56)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T56">
@@ -18648,7 +18648,7 @@
         <v/>
       </c>
       <c r="S57">
-        <f>IF(OR(B57="",COUNTIF($B$6:$B57,B57)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R57)+(($R$6:$R$305=R57)*(ROW($B$6:$B$305)&lt;ROW(B57)))))+1)</f>
+        <f>IF(OR(B57="",COUNTIF($B$6:$B57,B57)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R57)+(($R$6:$R$305=R57)*($B$6:$B$305&lt;B57)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T57">
@@ -18686,7 +18686,7 @@
         <v/>
       </c>
       <c r="S58">
-        <f>IF(OR(B58="",COUNTIF($B$6:$B58,B58)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R58)+(($R$6:$R$305=R58)*(ROW($B$6:$B$305)&lt;ROW(B58)))))+1)</f>
+        <f>IF(OR(B58="",COUNTIF($B$6:$B58,B58)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R58)+(($R$6:$R$305=R58)*($B$6:$B$305&lt;B58)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T58">
@@ -18724,7 +18724,7 @@
         <v/>
       </c>
       <c r="S59">
-        <f>IF(OR(B59="",COUNTIF($B$6:$B59,B59)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R59)+(($R$6:$R$305=R59)*(ROW($B$6:$B$305)&lt;ROW(B59)))))+1)</f>
+        <f>IF(OR(B59="",COUNTIF($B$6:$B59,B59)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R59)+(($R$6:$R$305=R59)*($B$6:$B$305&lt;B59)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T59">
@@ -18762,7 +18762,7 @@
         <v/>
       </c>
       <c r="S60">
-        <f>IF(OR(B60="",COUNTIF($B$6:$B60,B60)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R60)+(($R$6:$R$305=R60)*(ROW($B$6:$B$305)&lt;ROW(B60)))))+1)</f>
+        <f>IF(OR(B60="",COUNTIF($B$6:$B60,B60)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R60)+(($R$6:$R$305=R60)*($B$6:$B$305&lt;B60)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T60">
@@ -18800,7 +18800,7 @@
         <v/>
       </c>
       <c r="S61">
-        <f>IF(OR(B61="",COUNTIF($B$6:$B61,B61)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R61)+(($R$6:$R$305=R61)*(ROW($B$6:$B$305)&lt;ROW(B61)))))+1)</f>
+        <f>IF(OR(B61="",COUNTIF($B$6:$B61,B61)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R61)+(($R$6:$R$305=R61)*($B$6:$B$305&lt;B61)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T61">
@@ -18838,7 +18838,7 @@
         <v/>
       </c>
       <c r="S62">
-        <f>IF(OR(B62="",COUNTIF($B$6:$B62,B62)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R62)+(($R$6:$R$305=R62)*(ROW($B$6:$B$305)&lt;ROW(B62)))))+1)</f>
+        <f>IF(OR(B62="",COUNTIF($B$6:$B62,B62)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R62)+(($R$6:$R$305=R62)*($B$6:$B$305&lt;B62)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T62">
@@ -18876,7 +18876,7 @@
         <v/>
       </c>
       <c r="S63">
-        <f>IF(OR(B63="",COUNTIF($B$6:$B63,B63)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R63)+(($R$6:$R$305=R63)*(ROW($B$6:$B$305)&lt;ROW(B63)))))+1)</f>
+        <f>IF(OR(B63="",COUNTIF($B$6:$B63,B63)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R63)+(($R$6:$R$305=R63)*($B$6:$B$305&lt;B63)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T63">
@@ -18914,7 +18914,7 @@
         <v/>
       </c>
       <c r="S64">
-        <f>IF(OR(B64="",COUNTIF($B$6:$B64,B64)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R64)+(($R$6:$R$305=R64)*(ROW($B$6:$B$305)&lt;ROW(B64)))))+1)</f>
+        <f>IF(OR(B64="",COUNTIF($B$6:$B64,B64)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R64)+(($R$6:$R$305=R64)*($B$6:$B$305&lt;B64)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T64">
@@ -18952,7 +18952,7 @@
         <v/>
       </c>
       <c r="S65">
-        <f>IF(OR(B65="",COUNTIF($B$6:$B65,B65)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R65)+(($R$6:$R$305=R65)*(ROW($B$6:$B$305)&lt;ROW(B65)))))+1)</f>
+        <f>IF(OR(B65="",COUNTIF($B$6:$B65,B65)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R65)+(($R$6:$R$305=R65)*($B$6:$B$305&lt;B65)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T65">
@@ -18990,7 +18990,7 @@
         <v/>
       </c>
       <c r="S66">
-        <f>IF(OR(B66="",COUNTIF($B$6:$B66,B66)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R66)+(($R$6:$R$305=R66)*(ROW($B$6:$B$305)&lt;ROW(B66)))))+1)</f>
+        <f>IF(OR(B66="",COUNTIF($B$6:$B66,B66)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R66)+(($R$6:$R$305=R66)*($B$6:$B$305&lt;B66)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T66">
@@ -19028,7 +19028,7 @@
         <v/>
       </c>
       <c r="S67">
-        <f>IF(OR(B67="",COUNTIF($B$6:$B67,B67)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R67)+(($R$6:$R$305=R67)*(ROW($B$6:$B$305)&lt;ROW(B67)))))+1)</f>
+        <f>IF(OR(B67="",COUNTIF($B$6:$B67,B67)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R67)+(($R$6:$R$305=R67)*($B$6:$B$305&lt;B67)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T67">
@@ -19066,7 +19066,7 @@
         <v/>
       </c>
       <c r="S68">
-        <f>IF(OR(B68="",COUNTIF($B$6:$B68,B68)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R68)+(($R$6:$R$305=R68)*(ROW($B$6:$B$305)&lt;ROW(B68)))))+1)</f>
+        <f>IF(OR(B68="",COUNTIF($B$6:$B68,B68)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R68)+(($R$6:$R$305=R68)*($B$6:$B$305&lt;B68)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T68">
@@ -19104,7 +19104,7 @@
         <v/>
       </c>
       <c r="S69">
-        <f>IF(OR(B69="",COUNTIF($B$6:$B69,B69)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R69)+(($R$6:$R$305=R69)*(ROW($B$6:$B$305)&lt;ROW(B69)))))+1)</f>
+        <f>IF(OR(B69="",COUNTIF($B$6:$B69,B69)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R69)+(($R$6:$R$305=R69)*($B$6:$B$305&lt;B69)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T69">
@@ -19142,7 +19142,7 @@
         <v/>
       </c>
       <c r="S70">
-        <f>IF(OR(B70="",COUNTIF($B$6:$B70,B70)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R70)+(($R$6:$R$305=R70)*(ROW($B$6:$B$305)&lt;ROW(B70)))))+1)</f>
+        <f>IF(OR(B70="",COUNTIF($B$6:$B70,B70)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R70)+(($R$6:$R$305=R70)*($B$6:$B$305&lt;B70)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T70">
@@ -19180,7 +19180,7 @@
         <v/>
       </c>
       <c r="S71">
-        <f>IF(OR(B71="",COUNTIF($B$6:$B71,B71)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R71)+(($R$6:$R$305=R71)*(ROW($B$6:$B$305)&lt;ROW(B71)))))+1)</f>
+        <f>IF(OR(B71="",COUNTIF($B$6:$B71,B71)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R71)+(($R$6:$R$305=R71)*($B$6:$B$305&lt;B71)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T71">
@@ -19218,7 +19218,7 @@
         <v/>
       </c>
       <c r="S72">
-        <f>IF(OR(B72="",COUNTIF($B$6:$B72,B72)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R72)+(($R$6:$R$305=R72)*(ROW($B$6:$B$305)&lt;ROW(B72)))))+1)</f>
+        <f>IF(OR(B72="",COUNTIF($B$6:$B72,B72)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R72)+(($R$6:$R$305=R72)*($B$6:$B$305&lt;B72)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T72">
@@ -19256,7 +19256,7 @@
         <v/>
       </c>
       <c r="S73">
-        <f>IF(OR(B73="",COUNTIF($B$6:$B73,B73)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R73)+(($R$6:$R$305=R73)*(ROW($B$6:$B$305)&lt;ROW(B73)))))+1)</f>
+        <f>IF(OR(B73="",COUNTIF($B$6:$B73,B73)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R73)+(($R$6:$R$305=R73)*($B$6:$B$305&lt;B73)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T73">
@@ -19294,7 +19294,7 @@
         <v/>
       </c>
       <c r="S74">
-        <f>IF(OR(B74="",COUNTIF($B$6:$B74,B74)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R74)+(($R$6:$R$305=R74)*(ROW($B$6:$B$305)&lt;ROW(B74)))))+1)</f>
+        <f>IF(OR(B74="",COUNTIF($B$6:$B74,B74)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R74)+(($R$6:$R$305=R74)*($B$6:$B$305&lt;B74)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T74">
@@ -19332,7 +19332,7 @@
         <v/>
       </c>
       <c r="S75">
-        <f>IF(OR(B75="",COUNTIF($B$6:$B75,B75)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R75)+(($R$6:$R$305=R75)*(ROW($B$6:$B$305)&lt;ROW(B75)))))+1)</f>
+        <f>IF(OR(B75="",COUNTIF($B$6:$B75,B75)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R75)+(($R$6:$R$305=R75)*($B$6:$B$305&lt;B75)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T75">
@@ -19370,7 +19370,7 @@
         <v/>
       </c>
       <c r="S76">
-        <f>IF(OR(B76="",COUNTIF($B$6:$B76,B76)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R76)+(($R$6:$R$305=R76)*(ROW($B$6:$B$305)&lt;ROW(B76)))))+1)</f>
+        <f>IF(OR(B76="",COUNTIF($B$6:$B76,B76)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R76)+(($R$6:$R$305=R76)*($B$6:$B$305&lt;B76)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T76">
@@ -19408,7 +19408,7 @@
         <v/>
       </c>
       <c r="S77">
-        <f>IF(OR(B77="",COUNTIF($B$6:$B77,B77)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R77)+(($R$6:$R$305=R77)*(ROW($B$6:$B$305)&lt;ROW(B77)))))+1)</f>
+        <f>IF(OR(B77="",COUNTIF($B$6:$B77,B77)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R77)+(($R$6:$R$305=R77)*($B$6:$B$305&lt;B77)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T77">
@@ -19446,7 +19446,7 @@
         <v/>
       </c>
       <c r="S78">
-        <f>IF(OR(B78="",COUNTIF($B$6:$B78,B78)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R78)+(($R$6:$R$305=R78)*(ROW($B$6:$B$305)&lt;ROW(B78)))))+1)</f>
+        <f>IF(OR(B78="",COUNTIF($B$6:$B78,B78)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R78)+(($R$6:$R$305=R78)*($B$6:$B$305&lt;B78)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T78">
@@ -19484,7 +19484,7 @@
         <v/>
       </c>
       <c r="S79">
-        <f>IF(OR(B79="",COUNTIF($B$6:$B79,B79)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R79)+(($R$6:$R$305=R79)*(ROW($B$6:$B$305)&lt;ROW(B79)))))+1)</f>
+        <f>IF(OR(B79="",COUNTIF($B$6:$B79,B79)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R79)+(($R$6:$R$305=R79)*($B$6:$B$305&lt;B79)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T79">
@@ -19522,7 +19522,7 @@
         <v/>
       </c>
       <c r="S80">
-        <f>IF(OR(B80="",COUNTIF($B$6:$B80,B80)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R80)+(($R$6:$R$305=R80)*(ROW($B$6:$B$305)&lt;ROW(B80)))))+1)</f>
+        <f>IF(OR(B80="",COUNTIF($B$6:$B80,B80)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R80)+(($R$6:$R$305=R80)*($B$6:$B$305&lt;B80)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T80">
@@ -19560,7 +19560,7 @@
         <v/>
       </c>
       <c r="S81">
-        <f>IF(OR(B81="",COUNTIF($B$6:$B81,B81)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R81)+(($R$6:$R$305=R81)*(ROW($B$6:$B$305)&lt;ROW(B81)))))+1)</f>
+        <f>IF(OR(B81="",COUNTIF($B$6:$B81,B81)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R81)+(($R$6:$R$305=R81)*($B$6:$B$305&lt;B81)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T81">
@@ -19598,7 +19598,7 @@
         <v/>
       </c>
       <c r="S82">
-        <f>IF(OR(B82="",COUNTIF($B$6:$B82,B82)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R82)+(($R$6:$R$305=R82)*(ROW($B$6:$B$305)&lt;ROW(B82)))))+1)</f>
+        <f>IF(OR(B82="",COUNTIF($B$6:$B82,B82)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R82)+(($R$6:$R$305=R82)*($B$6:$B$305&lt;B82)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T82">
@@ -19636,7 +19636,7 @@
         <v/>
       </c>
       <c r="S83">
-        <f>IF(OR(B83="",COUNTIF($B$6:$B83,B83)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R83)+(($R$6:$R$305=R83)*(ROW($B$6:$B$305)&lt;ROW(B83)))))+1)</f>
+        <f>IF(OR(B83="",COUNTIF($B$6:$B83,B83)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R83)+(($R$6:$R$305=R83)*($B$6:$B$305&lt;B83)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T83">
@@ -19674,7 +19674,7 @@
         <v/>
       </c>
       <c r="S84">
-        <f>IF(OR(B84="",COUNTIF($B$6:$B84,B84)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R84)+(($R$6:$R$305=R84)*(ROW($B$6:$B$305)&lt;ROW(B84)))))+1)</f>
+        <f>IF(OR(B84="",COUNTIF($B$6:$B84,B84)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R84)+(($R$6:$R$305=R84)*($B$6:$B$305&lt;B84)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T84">
@@ -19712,7 +19712,7 @@
         <v/>
       </c>
       <c r="S85">
-        <f>IF(OR(B85="",COUNTIF($B$6:$B85,B85)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R85)+(($R$6:$R$305=R85)*(ROW($B$6:$B$305)&lt;ROW(B85)))))+1)</f>
+        <f>IF(OR(B85="",COUNTIF($B$6:$B85,B85)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R85)+(($R$6:$R$305=R85)*($B$6:$B$305&lt;B85)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T85">
@@ -19750,7 +19750,7 @@
         <v/>
       </c>
       <c r="S86">
-        <f>IF(OR(B86="",COUNTIF($B$6:$B86,B86)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R86)+(($R$6:$R$305=R86)*(ROW($B$6:$B$305)&lt;ROW(B86)))))+1)</f>
+        <f>IF(OR(B86="",COUNTIF($B$6:$B86,B86)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R86)+(($R$6:$R$305=R86)*($B$6:$B$305&lt;B86)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T86">
@@ -19788,7 +19788,7 @@
         <v/>
       </c>
       <c r="S87">
-        <f>IF(OR(B87="",COUNTIF($B$6:$B87,B87)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R87)+(($R$6:$R$305=R87)*(ROW($B$6:$B$305)&lt;ROW(B87)))))+1)</f>
+        <f>IF(OR(B87="",COUNTIF($B$6:$B87,B87)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R87)+(($R$6:$R$305=R87)*($B$6:$B$305&lt;B87)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T87">
@@ -19826,7 +19826,7 @@
         <v/>
       </c>
       <c r="S88">
-        <f>IF(OR(B88="",COUNTIF($B$6:$B88,B88)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R88)+(($R$6:$R$305=R88)*(ROW($B$6:$B$305)&lt;ROW(B88)))))+1)</f>
+        <f>IF(OR(B88="",COUNTIF($B$6:$B88,B88)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R88)+(($R$6:$R$305=R88)*($B$6:$B$305&lt;B88)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T88">
@@ -19864,7 +19864,7 @@
         <v/>
       </c>
       <c r="S89">
-        <f>IF(OR(B89="",COUNTIF($B$6:$B89,B89)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R89)+(($R$6:$R$305=R89)*(ROW($B$6:$B$305)&lt;ROW(B89)))))+1)</f>
+        <f>IF(OR(B89="",COUNTIF($B$6:$B89,B89)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R89)+(($R$6:$R$305=R89)*($B$6:$B$305&lt;B89)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T89">
@@ -19902,7 +19902,7 @@
         <v/>
       </c>
       <c r="S90">
-        <f>IF(OR(B90="",COUNTIF($B$6:$B90,B90)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R90)+(($R$6:$R$305=R90)*(ROW($B$6:$B$305)&lt;ROW(B90)))))+1)</f>
+        <f>IF(OR(B90="",COUNTIF($B$6:$B90,B90)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R90)+(($R$6:$R$305=R90)*($B$6:$B$305&lt;B90)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T90">
@@ -19940,7 +19940,7 @@
         <v/>
       </c>
       <c r="S91">
-        <f>IF(OR(B91="",COUNTIF($B$6:$B91,B91)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R91)+(($R$6:$R$305=R91)*(ROW($B$6:$B$305)&lt;ROW(B91)))))+1)</f>
+        <f>IF(OR(B91="",COUNTIF($B$6:$B91,B91)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R91)+(($R$6:$R$305=R91)*($B$6:$B$305&lt;B91)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T91">
@@ -19978,7 +19978,7 @@
         <v/>
       </c>
       <c r="S92">
-        <f>IF(OR(B92="",COUNTIF($B$6:$B92,B92)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R92)+(($R$6:$R$305=R92)*(ROW($B$6:$B$305)&lt;ROW(B92)))))+1)</f>
+        <f>IF(OR(B92="",COUNTIF($B$6:$B92,B92)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R92)+(($R$6:$R$305=R92)*($B$6:$B$305&lt;B92)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T92">
@@ -20016,7 +20016,7 @@
         <v/>
       </c>
       <c r="S93">
-        <f>IF(OR(B93="",COUNTIF($B$6:$B93,B93)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R93)+(($R$6:$R$305=R93)*(ROW($B$6:$B$305)&lt;ROW(B93)))))+1)</f>
+        <f>IF(OR(B93="",COUNTIF($B$6:$B93,B93)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R93)+(($R$6:$R$305=R93)*($B$6:$B$305&lt;B93)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T93">
@@ -20054,7 +20054,7 @@
         <v/>
       </c>
       <c r="S94">
-        <f>IF(OR(B94="",COUNTIF($B$6:$B94,B94)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R94)+(($R$6:$R$305=R94)*(ROW($B$6:$B$305)&lt;ROW(B94)))))+1)</f>
+        <f>IF(OR(B94="",COUNTIF($B$6:$B94,B94)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R94)+(($R$6:$R$305=R94)*($B$6:$B$305&lt;B94)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T94">
@@ -20092,7 +20092,7 @@
         <v/>
       </c>
       <c r="S95">
-        <f>IF(OR(B95="",COUNTIF($B$6:$B95,B95)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R95)+(($R$6:$R$305=R95)*(ROW($B$6:$B$305)&lt;ROW(B95)))))+1)</f>
+        <f>IF(OR(B95="",COUNTIF($B$6:$B95,B95)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R95)+(($R$6:$R$305=R95)*($B$6:$B$305&lt;B95)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T95">
@@ -20130,7 +20130,7 @@
         <v/>
       </c>
       <c r="S96">
-        <f>IF(OR(B96="",COUNTIF($B$6:$B96,B96)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R96)+(($R$6:$R$305=R96)*(ROW($B$6:$B$305)&lt;ROW(B96)))))+1)</f>
+        <f>IF(OR(B96="",COUNTIF($B$6:$B96,B96)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R96)+(($R$6:$R$305=R96)*($B$6:$B$305&lt;B96)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T96">
@@ -20168,7 +20168,7 @@
         <v/>
       </c>
       <c r="S97">
-        <f>IF(OR(B97="",COUNTIF($B$6:$B97,B97)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R97)+(($R$6:$R$305=R97)*(ROW($B$6:$B$305)&lt;ROW(B97)))))+1)</f>
+        <f>IF(OR(B97="",COUNTIF($B$6:$B97,B97)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R97)+(($R$6:$R$305=R97)*($B$6:$B$305&lt;B97)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T97">
@@ -20206,7 +20206,7 @@
         <v/>
       </c>
       <c r="S98">
-        <f>IF(OR(B98="",COUNTIF($B$6:$B98,B98)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R98)+(($R$6:$R$305=R98)*(ROW($B$6:$B$305)&lt;ROW(B98)))))+1)</f>
+        <f>IF(OR(B98="",COUNTIF($B$6:$B98,B98)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R98)+(($R$6:$R$305=R98)*($B$6:$B$305&lt;B98)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T98">
@@ -20244,7 +20244,7 @@
         <v/>
       </c>
       <c r="S99">
-        <f>IF(OR(B99="",COUNTIF($B$6:$B99,B99)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R99)+(($R$6:$R$305=R99)*(ROW($B$6:$B$305)&lt;ROW(B99)))))+1)</f>
+        <f>IF(OR(B99="",COUNTIF($B$6:$B99,B99)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R99)+(($R$6:$R$305=R99)*($B$6:$B$305&lt;B99)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T99">
@@ -20282,7 +20282,7 @@
         <v/>
       </c>
       <c r="S100">
-        <f>IF(OR(B100="",COUNTIF($B$6:$B100,B100)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R100)+(($R$6:$R$305=R100)*(ROW($B$6:$B$305)&lt;ROW(B100)))))+1)</f>
+        <f>IF(OR(B100="",COUNTIF($B$6:$B100,B100)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R100)+(($R$6:$R$305=R100)*($B$6:$B$305&lt;B100)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T100">
@@ -20320,7 +20320,7 @@
         <v/>
       </c>
       <c r="S101">
-        <f>IF(OR(B101="",COUNTIF($B$6:$B101,B101)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R101)+(($R$6:$R$305=R101)*(ROW($B$6:$B$305)&lt;ROW(B101)))))+1)</f>
+        <f>IF(OR(B101="",COUNTIF($B$6:$B101,B101)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R101)+(($R$6:$R$305=R101)*($B$6:$B$305&lt;B101)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T101">
@@ -20358,7 +20358,7 @@
         <v/>
       </c>
       <c r="S102">
-        <f>IF(OR(B102="",COUNTIF($B$6:$B102,B102)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R102)+(($R$6:$R$305=R102)*(ROW($B$6:$B$305)&lt;ROW(B102)))))+1)</f>
+        <f>IF(OR(B102="",COUNTIF($B$6:$B102,B102)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R102)+(($R$6:$R$305=R102)*($B$6:$B$305&lt;B102)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T102">
@@ -20396,7 +20396,7 @@
         <v/>
       </c>
       <c r="S103">
-        <f>IF(OR(B103="",COUNTIF($B$6:$B103,B103)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R103)+(($R$6:$R$305=R103)*(ROW($B$6:$B$305)&lt;ROW(B103)))))+1)</f>
+        <f>IF(OR(B103="",COUNTIF($B$6:$B103,B103)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R103)+(($R$6:$R$305=R103)*($B$6:$B$305&lt;B103)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T103">
@@ -20434,7 +20434,7 @@
         <v/>
       </c>
       <c r="S104">
-        <f>IF(OR(B104="",COUNTIF($B$6:$B104,B104)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R104)+(($R$6:$R$305=R104)*(ROW($B$6:$B$305)&lt;ROW(B104)))))+1)</f>
+        <f>IF(OR(B104="",COUNTIF($B$6:$B104,B104)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R104)+(($R$6:$R$305=R104)*($B$6:$B$305&lt;B104)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T104">
@@ -20472,7 +20472,7 @@
         <v/>
       </c>
       <c r="S105">
-        <f>IF(OR(B105="",COUNTIF($B$6:$B105,B105)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R105)+(($R$6:$R$305=R105)*(ROW($B$6:$B$305)&lt;ROW(B105)))))+1)</f>
+        <f>IF(OR(B105="",COUNTIF($B$6:$B105,B105)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R105)+(($R$6:$R$305=R105)*($B$6:$B$305&lt;B105)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
       <c r="T105">
@@ -20510,7 +20510,7 @@
         <v/>
       </c>
       <c r="S106">
-        <f>IF(OR(B106="",COUNTIF($B$6:$B106,B106)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R106)+(($R$6:$R$305=R106)*(ROW($B$6:$B$305)&lt;ROW(B106)))))+1)</f>
+        <f>IF(OR(B106="",COUNTIF($B$6:$B106,B106)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R106)+(($R$6:$R$305=R106)*($B$6:$B$305&lt;B106)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20532,7 +20532,7 @@
         <v/>
       </c>
       <c r="S107">
-        <f>IF(OR(B107="",COUNTIF($B$6:$B107,B107)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R107)+(($R$6:$R$305=R107)*(ROW($B$6:$B$305)&lt;ROW(B107)))))+1)</f>
+        <f>IF(OR(B107="",COUNTIF($B$6:$B107,B107)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R107)+(($R$6:$R$305=R107)*($B$6:$B$305&lt;B107)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20554,7 +20554,7 @@
         <v/>
       </c>
       <c r="S108">
-        <f>IF(OR(B108="",COUNTIF($B$6:$B108,B108)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R108)+(($R$6:$R$305=R108)*(ROW($B$6:$B$305)&lt;ROW(B108)))))+1)</f>
+        <f>IF(OR(B108="",COUNTIF($B$6:$B108,B108)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R108)+(($R$6:$R$305=R108)*($B$6:$B$305&lt;B108)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20576,7 +20576,7 @@
         <v/>
       </c>
       <c r="S109">
-        <f>IF(OR(B109="",COUNTIF($B$6:$B109,B109)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R109)+(($R$6:$R$305=R109)*(ROW($B$6:$B$305)&lt;ROW(B109)))))+1)</f>
+        <f>IF(OR(B109="",COUNTIF($B$6:$B109,B109)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R109)+(($R$6:$R$305=R109)*($B$6:$B$305&lt;B109)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20598,7 +20598,7 @@
         <v/>
       </c>
       <c r="S110">
-        <f>IF(OR(B110="",COUNTIF($B$6:$B110,B110)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R110)+(($R$6:$R$305=R110)*(ROW($B$6:$B$305)&lt;ROW(B110)))))+1)</f>
+        <f>IF(OR(B110="",COUNTIF($B$6:$B110,B110)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R110)+(($R$6:$R$305=R110)*($B$6:$B$305&lt;B110)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20620,7 +20620,7 @@
         <v/>
       </c>
       <c r="S111">
-        <f>IF(OR(B111="",COUNTIF($B$6:$B111,B111)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R111)+(($R$6:$R$305=R111)*(ROW($B$6:$B$305)&lt;ROW(B111)))))+1)</f>
+        <f>IF(OR(B111="",COUNTIF($B$6:$B111,B111)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R111)+(($R$6:$R$305=R111)*($B$6:$B$305&lt;B111)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20642,7 +20642,7 @@
         <v/>
       </c>
       <c r="S112">
-        <f>IF(OR(B112="",COUNTIF($B$6:$B112,B112)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R112)+(($R$6:$R$305=R112)*(ROW($B$6:$B$305)&lt;ROW(B112)))))+1)</f>
+        <f>IF(OR(B112="",COUNTIF($B$6:$B112,B112)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R112)+(($R$6:$R$305=R112)*($B$6:$B$305&lt;B112)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20664,7 +20664,7 @@
         <v/>
       </c>
       <c r="S113">
-        <f>IF(OR(B113="",COUNTIF($B$6:$B113,B113)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R113)+(($R$6:$R$305=R113)*(ROW($B$6:$B$305)&lt;ROW(B113)))))+1)</f>
+        <f>IF(OR(B113="",COUNTIF($B$6:$B113,B113)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R113)+(($R$6:$R$305=R113)*($B$6:$B$305&lt;B113)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20686,7 +20686,7 @@
         <v/>
       </c>
       <c r="S114">
-        <f>IF(OR(B114="",COUNTIF($B$6:$B114,B114)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R114)+(($R$6:$R$305=R114)*(ROW($B$6:$B$305)&lt;ROW(B114)))))+1)</f>
+        <f>IF(OR(B114="",COUNTIF($B$6:$B114,B114)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R114)+(($R$6:$R$305=R114)*($B$6:$B$305&lt;B114)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20708,7 +20708,7 @@
         <v/>
       </c>
       <c r="S115">
-        <f>IF(OR(B115="",COUNTIF($B$6:$B115,B115)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R115)+(($R$6:$R$305=R115)*(ROW($B$6:$B$305)&lt;ROW(B115)))))+1)</f>
+        <f>IF(OR(B115="",COUNTIF($B$6:$B115,B115)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R115)+(($R$6:$R$305=R115)*($B$6:$B$305&lt;B115)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
         <v/>
       </c>
       <c r="S116">
-        <f>IF(OR(B116="",COUNTIF($B$6:$B116,B116)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R116)+(($R$6:$R$305=R116)*(ROW($B$6:$B$305)&lt;ROW(B116)))))+1)</f>
+        <f>IF(OR(B116="",COUNTIF($B$6:$B116,B116)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R116)+(($R$6:$R$305=R116)*($B$6:$B$305&lt;B116)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20752,7 +20752,7 @@
         <v/>
       </c>
       <c r="S117">
-        <f>IF(OR(B117="",COUNTIF($B$6:$B117,B117)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R117)+(($R$6:$R$305=R117)*(ROW($B$6:$B$305)&lt;ROW(B117)))))+1)</f>
+        <f>IF(OR(B117="",COUNTIF($B$6:$B117,B117)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R117)+(($R$6:$R$305=R117)*($B$6:$B$305&lt;B117)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
         <v/>
       </c>
       <c r="S118">
-        <f>IF(OR(B118="",COUNTIF($B$6:$B118,B118)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R118)+(($R$6:$R$305=R118)*(ROW($B$6:$B$305)&lt;ROW(B118)))))+1)</f>
+        <f>IF(OR(B118="",COUNTIF($B$6:$B118,B118)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R118)+(($R$6:$R$305=R118)*($B$6:$B$305&lt;B118)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20796,7 +20796,7 @@
         <v/>
       </c>
       <c r="S119">
-        <f>IF(OR(B119="",COUNTIF($B$6:$B119,B119)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R119)+(($R$6:$R$305=R119)*(ROW($B$6:$B$305)&lt;ROW(B119)))))+1)</f>
+        <f>IF(OR(B119="",COUNTIF($B$6:$B119,B119)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R119)+(($R$6:$R$305=R119)*($B$6:$B$305&lt;B119)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20818,7 +20818,7 @@
         <v/>
       </c>
       <c r="S120">
-        <f>IF(OR(B120="",COUNTIF($B$6:$B120,B120)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R120)+(($R$6:$R$305=R120)*(ROW($B$6:$B$305)&lt;ROW(B120)))))+1)</f>
+        <f>IF(OR(B120="",COUNTIF($B$6:$B120,B120)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R120)+(($R$6:$R$305=R120)*($B$6:$B$305&lt;B120)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20840,7 +20840,7 @@
         <v/>
       </c>
       <c r="S121">
-        <f>IF(OR(B121="",COUNTIF($B$6:$B121,B121)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R121)+(($R$6:$R$305=R121)*(ROW($B$6:$B$305)&lt;ROW(B121)))))+1)</f>
+        <f>IF(OR(B121="",COUNTIF($B$6:$B121,B121)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R121)+(($R$6:$R$305=R121)*($B$6:$B$305&lt;B121)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20862,7 +20862,7 @@
         <v/>
       </c>
       <c r="S122">
-        <f>IF(OR(B122="",COUNTIF($B$6:$B122,B122)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R122)+(($R$6:$R$305=R122)*(ROW($B$6:$B$305)&lt;ROW(B122)))))+1)</f>
+        <f>IF(OR(B122="",COUNTIF($B$6:$B122,B122)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R122)+(($R$6:$R$305=R122)*($B$6:$B$305&lt;B122)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20884,7 +20884,7 @@
         <v/>
       </c>
       <c r="S123">
-        <f>IF(OR(B123="",COUNTIF($B$6:$B123,B123)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R123)+(($R$6:$R$305=R123)*(ROW($B$6:$B$305)&lt;ROW(B123)))))+1)</f>
+        <f>IF(OR(B123="",COUNTIF($B$6:$B123,B123)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R123)+(($R$6:$R$305=R123)*($B$6:$B$305&lt;B123)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20906,7 +20906,7 @@
         <v/>
       </c>
       <c r="S124">
-        <f>IF(OR(B124="",COUNTIF($B$6:$B124,B124)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R124)+(($R$6:$R$305=R124)*(ROW($B$6:$B$305)&lt;ROW(B124)))))+1)</f>
+        <f>IF(OR(B124="",COUNTIF($B$6:$B124,B124)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R124)+(($R$6:$R$305=R124)*($B$6:$B$305&lt;B124)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20928,7 +20928,7 @@
         <v/>
       </c>
       <c r="S125">
-        <f>IF(OR(B125="",COUNTIF($B$6:$B125,B125)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R125)+(($R$6:$R$305=R125)*(ROW($B$6:$B$305)&lt;ROW(B125)))))+1)</f>
+        <f>IF(OR(B125="",COUNTIF($B$6:$B125,B125)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R125)+(($R$6:$R$305=R125)*($B$6:$B$305&lt;B125)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20950,7 +20950,7 @@
         <v/>
       </c>
       <c r="S126">
-        <f>IF(OR(B126="",COUNTIF($B$6:$B126,B126)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R126)+(($R$6:$R$305=R126)*(ROW($B$6:$B$305)&lt;ROW(B126)))))+1)</f>
+        <f>IF(OR(B126="",COUNTIF($B$6:$B126,B126)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R126)+(($R$6:$R$305=R126)*($B$6:$B$305&lt;B126)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20972,7 +20972,7 @@
         <v/>
       </c>
       <c r="S127">
-        <f>IF(OR(B127="",COUNTIF($B$6:$B127,B127)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R127)+(($R$6:$R$305=R127)*(ROW($B$6:$B$305)&lt;ROW(B127)))))+1)</f>
+        <f>IF(OR(B127="",COUNTIF($B$6:$B127,B127)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R127)+(($R$6:$R$305=R127)*($B$6:$B$305&lt;B127)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -20994,7 +20994,7 @@
         <v/>
       </c>
       <c r="S128">
-        <f>IF(OR(B128="",COUNTIF($B$6:$B128,B128)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R128)+(($R$6:$R$305=R128)*(ROW($B$6:$B$305)&lt;ROW(B128)))))+1)</f>
+        <f>IF(OR(B128="",COUNTIF($B$6:$B128,B128)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R128)+(($R$6:$R$305=R128)*($B$6:$B$305&lt;B128)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21016,7 +21016,7 @@
         <v/>
       </c>
       <c r="S129">
-        <f>IF(OR(B129="",COUNTIF($B$6:$B129,B129)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R129)+(($R$6:$R$305=R129)*(ROW($B$6:$B$305)&lt;ROW(B129)))))+1)</f>
+        <f>IF(OR(B129="",COUNTIF($B$6:$B129,B129)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R129)+(($R$6:$R$305=R129)*($B$6:$B$305&lt;B129)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
         <v/>
       </c>
       <c r="S130">
-        <f>IF(OR(B130="",COUNTIF($B$6:$B130,B130)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R130)+(($R$6:$R$305=R130)*(ROW($B$6:$B$305)&lt;ROW(B130)))))+1)</f>
+        <f>IF(OR(B130="",COUNTIF($B$6:$B130,B130)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R130)+(($R$6:$R$305=R130)*($B$6:$B$305&lt;B130)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21060,7 +21060,7 @@
         <v/>
       </c>
       <c r="S131">
-        <f>IF(OR(B131="",COUNTIF($B$6:$B131,B131)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R131)+(($R$6:$R$305=R131)*(ROW($B$6:$B$305)&lt;ROW(B131)))))+1)</f>
+        <f>IF(OR(B131="",COUNTIF($B$6:$B131,B131)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R131)+(($R$6:$R$305=R131)*($B$6:$B$305&lt;B131)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21082,7 +21082,7 @@
         <v/>
       </c>
       <c r="S132">
-        <f>IF(OR(B132="",COUNTIF($B$6:$B132,B132)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R132)+(($R$6:$R$305=R132)*(ROW($B$6:$B$305)&lt;ROW(B132)))))+1)</f>
+        <f>IF(OR(B132="",COUNTIF($B$6:$B132,B132)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R132)+(($R$6:$R$305=R132)*($B$6:$B$305&lt;B132)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21104,7 +21104,7 @@
         <v/>
       </c>
       <c r="S133">
-        <f>IF(OR(B133="",COUNTIF($B$6:$B133,B133)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R133)+(($R$6:$R$305=R133)*(ROW($B$6:$B$305)&lt;ROW(B133)))))+1)</f>
+        <f>IF(OR(B133="",COUNTIF($B$6:$B133,B133)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R133)+(($R$6:$R$305=R133)*($B$6:$B$305&lt;B133)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21126,7 +21126,7 @@
         <v/>
       </c>
       <c r="S134">
-        <f>IF(OR(B134="",COUNTIF($B$6:$B134,B134)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R134)+(($R$6:$R$305=R134)*(ROW($B$6:$B$305)&lt;ROW(B134)))))+1)</f>
+        <f>IF(OR(B134="",COUNTIF($B$6:$B134,B134)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R134)+(($R$6:$R$305=R134)*($B$6:$B$305&lt;B134)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21148,7 +21148,7 @@
         <v/>
       </c>
       <c r="S135">
-        <f>IF(OR(B135="",COUNTIF($B$6:$B135,B135)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R135)+(($R$6:$R$305=R135)*(ROW($B$6:$B$305)&lt;ROW(B135)))))+1)</f>
+        <f>IF(OR(B135="",COUNTIF($B$6:$B135,B135)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R135)+(($R$6:$R$305=R135)*($B$6:$B$305&lt;B135)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21170,7 +21170,7 @@
         <v/>
       </c>
       <c r="S136">
-        <f>IF(OR(B136="",COUNTIF($B$6:$B136,B136)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R136)+(($R$6:$R$305=R136)*(ROW($B$6:$B$305)&lt;ROW(B136)))))+1)</f>
+        <f>IF(OR(B136="",COUNTIF($B$6:$B136,B136)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R136)+(($R$6:$R$305=R136)*($B$6:$B$305&lt;B136)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21192,7 +21192,7 @@
         <v/>
       </c>
       <c r="S137">
-        <f>IF(OR(B137="",COUNTIF($B$6:$B137,B137)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R137)+(($R$6:$R$305=R137)*(ROW($B$6:$B$305)&lt;ROW(B137)))))+1)</f>
+        <f>IF(OR(B137="",COUNTIF($B$6:$B137,B137)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R137)+(($R$6:$R$305=R137)*($B$6:$B$305&lt;B137)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21214,7 +21214,7 @@
         <v/>
       </c>
       <c r="S138">
-        <f>IF(OR(B138="",COUNTIF($B$6:$B138,B138)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R138)+(($R$6:$R$305=R138)*(ROW($B$6:$B$305)&lt;ROW(B138)))))+1)</f>
+        <f>IF(OR(B138="",COUNTIF($B$6:$B138,B138)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R138)+(($R$6:$R$305=R138)*($B$6:$B$305&lt;B138)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21236,7 +21236,7 @@
         <v/>
       </c>
       <c r="S139">
-        <f>IF(OR(B139="",COUNTIF($B$6:$B139,B139)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R139)+(($R$6:$R$305=R139)*(ROW($B$6:$B$305)&lt;ROW(B139)))))+1)</f>
+        <f>IF(OR(B139="",COUNTIF($B$6:$B139,B139)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R139)+(($R$6:$R$305=R139)*($B$6:$B$305&lt;B139)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21258,7 +21258,7 @@
         <v/>
       </c>
       <c r="S140">
-        <f>IF(OR(B140="",COUNTIF($B$6:$B140,B140)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R140)+(($R$6:$R$305=R140)*(ROW($B$6:$B$305)&lt;ROW(B140)))))+1)</f>
+        <f>IF(OR(B140="",COUNTIF($B$6:$B140,B140)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R140)+(($R$6:$R$305=R140)*($B$6:$B$305&lt;B140)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21280,7 +21280,7 @@
         <v/>
       </c>
       <c r="S141">
-        <f>IF(OR(B141="",COUNTIF($B$6:$B141,B141)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R141)+(($R$6:$R$305=R141)*(ROW($B$6:$B$305)&lt;ROW(B141)))))+1)</f>
+        <f>IF(OR(B141="",COUNTIF($B$6:$B141,B141)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R141)+(($R$6:$R$305=R141)*($B$6:$B$305&lt;B141)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21302,7 +21302,7 @@
         <v/>
       </c>
       <c r="S142">
-        <f>IF(OR(B142="",COUNTIF($B$6:$B142,B142)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R142)+(($R$6:$R$305=R142)*(ROW($B$6:$B$305)&lt;ROW(B142)))))+1)</f>
+        <f>IF(OR(B142="",COUNTIF($B$6:$B142,B142)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R142)+(($R$6:$R$305=R142)*($B$6:$B$305&lt;B142)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21324,7 +21324,7 @@
         <v/>
       </c>
       <c r="S143">
-        <f>IF(OR(B143="",COUNTIF($B$6:$B143,B143)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R143)+(($R$6:$R$305=R143)*(ROW($B$6:$B$305)&lt;ROW(B143)))))+1)</f>
+        <f>IF(OR(B143="",COUNTIF($B$6:$B143,B143)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R143)+(($R$6:$R$305=R143)*($B$6:$B$305&lt;B143)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21346,7 +21346,7 @@
         <v/>
       </c>
       <c r="S144">
-        <f>IF(OR(B144="",COUNTIF($B$6:$B144,B144)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R144)+(($R$6:$R$305=R144)*(ROW($B$6:$B$305)&lt;ROW(B144)))))+1)</f>
+        <f>IF(OR(B144="",COUNTIF($B$6:$B144,B144)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R144)+(($R$6:$R$305=R144)*($B$6:$B$305&lt;B144)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21368,7 +21368,7 @@
         <v/>
       </c>
       <c r="S145">
-        <f>IF(OR(B145="",COUNTIF($B$6:$B145,B145)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R145)+(($R$6:$R$305=R145)*(ROW($B$6:$B$305)&lt;ROW(B145)))))+1)</f>
+        <f>IF(OR(B145="",COUNTIF($B$6:$B145,B145)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R145)+(($R$6:$R$305=R145)*($B$6:$B$305&lt;B145)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21390,7 +21390,7 @@
         <v/>
       </c>
       <c r="S146">
-        <f>IF(OR(B146="",COUNTIF($B$6:$B146,B146)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R146)+(($R$6:$R$305=R146)*(ROW($B$6:$B$305)&lt;ROW(B146)))))+1)</f>
+        <f>IF(OR(B146="",COUNTIF($B$6:$B146,B146)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R146)+(($R$6:$R$305=R146)*($B$6:$B$305&lt;B146)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
         <v/>
       </c>
       <c r="S147">
-        <f>IF(OR(B147="",COUNTIF($B$6:$B147,B147)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R147)+(($R$6:$R$305=R147)*(ROW($B$6:$B$305)&lt;ROW(B147)))))+1)</f>
+        <f>IF(OR(B147="",COUNTIF($B$6:$B147,B147)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R147)+(($R$6:$R$305=R147)*($B$6:$B$305&lt;B147)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
         <v/>
       </c>
       <c r="S148">
-        <f>IF(OR(B148="",COUNTIF($B$6:$B148,B148)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R148)+(($R$6:$R$305=R148)*(ROW($B$6:$B$305)&lt;ROW(B148)))))+1)</f>
+        <f>IF(OR(B148="",COUNTIF($B$6:$B148,B148)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R148)+(($R$6:$R$305=R148)*($B$6:$B$305&lt;B148)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21456,7 +21456,7 @@
         <v/>
       </c>
       <c r="S149">
-        <f>IF(OR(B149="",COUNTIF($B$6:$B149,B149)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R149)+(($R$6:$R$305=R149)*(ROW($B$6:$B$305)&lt;ROW(B149)))))+1)</f>
+        <f>IF(OR(B149="",COUNTIF($B$6:$B149,B149)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R149)+(($R$6:$R$305=R149)*($B$6:$B$305&lt;B149)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21478,7 +21478,7 @@
         <v/>
       </c>
       <c r="S150">
-        <f>IF(OR(B150="",COUNTIF($B$6:$B150,B150)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R150)+(($R$6:$R$305=R150)*(ROW($B$6:$B$305)&lt;ROW(B150)))))+1)</f>
+        <f>IF(OR(B150="",COUNTIF($B$6:$B150,B150)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R150)+(($R$6:$R$305=R150)*($B$6:$B$305&lt;B150)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21500,7 +21500,7 @@
         <v/>
       </c>
       <c r="S151">
-        <f>IF(OR(B151="",COUNTIF($B$6:$B151,B151)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R151)+(($R$6:$R$305=R151)*(ROW($B$6:$B$305)&lt;ROW(B151)))))+1)</f>
+        <f>IF(OR(B151="",COUNTIF($B$6:$B151,B151)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R151)+(($R$6:$R$305=R151)*($B$6:$B$305&lt;B151)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
         <v/>
       </c>
       <c r="S152">
-        <f>IF(OR(B152="",COUNTIF($B$6:$B152,B152)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R152)+(($R$6:$R$305=R152)*(ROW($B$6:$B$305)&lt;ROW(B152)))))+1)</f>
+        <f>IF(OR(B152="",COUNTIF($B$6:$B152,B152)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R152)+(($R$6:$R$305=R152)*($B$6:$B$305&lt;B152)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21544,7 +21544,7 @@
         <v/>
       </c>
       <c r="S153">
-        <f>IF(OR(B153="",COUNTIF($B$6:$B153,B153)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R153)+(($R$6:$R$305=R153)*(ROW($B$6:$B$305)&lt;ROW(B153)))))+1)</f>
+        <f>IF(OR(B153="",COUNTIF($B$6:$B153,B153)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R153)+(($R$6:$R$305=R153)*($B$6:$B$305&lt;B153)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21566,7 +21566,7 @@
         <v/>
       </c>
       <c r="S154">
-        <f>IF(OR(B154="",COUNTIF($B$6:$B154,B154)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R154)+(($R$6:$R$305=R154)*(ROW($B$6:$B$305)&lt;ROW(B154)))))+1)</f>
+        <f>IF(OR(B154="",COUNTIF($B$6:$B154,B154)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R154)+(($R$6:$R$305=R154)*($B$6:$B$305&lt;B154)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
         <v/>
       </c>
       <c r="S155">
-        <f>IF(OR(B155="",COUNTIF($B$6:$B155,B155)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R155)+(($R$6:$R$305=R155)*(ROW($B$6:$B$305)&lt;ROW(B155)))))+1)</f>
+        <f>IF(OR(B155="",COUNTIF($B$6:$B155,B155)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R155)+(($R$6:$R$305=R155)*($B$6:$B$305&lt;B155)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21610,7 +21610,7 @@
         <v/>
       </c>
       <c r="S156">
-        <f>IF(OR(B156="",COUNTIF($B$6:$B156,B156)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R156)+(($R$6:$R$305=R156)*(ROW($B$6:$B$305)&lt;ROW(B156)))))+1)</f>
+        <f>IF(OR(B156="",COUNTIF($B$6:$B156,B156)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R156)+(($R$6:$R$305=R156)*($B$6:$B$305&lt;B156)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21632,7 +21632,7 @@
         <v/>
       </c>
       <c r="S157">
-        <f>IF(OR(B157="",COUNTIF($B$6:$B157,B157)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R157)+(($R$6:$R$305=R157)*(ROW($B$6:$B$305)&lt;ROW(B157)))))+1)</f>
+        <f>IF(OR(B157="",COUNTIF($B$6:$B157,B157)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R157)+(($R$6:$R$305=R157)*($B$6:$B$305&lt;B157)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21654,7 +21654,7 @@
         <v/>
       </c>
       <c r="S158">
-        <f>IF(OR(B158="",COUNTIF($B$6:$B158,B158)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R158)+(($R$6:$R$305=R158)*(ROW($B$6:$B$305)&lt;ROW(B158)))))+1)</f>
+        <f>IF(OR(B158="",COUNTIF($B$6:$B158,B158)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R158)+(($R$6:$R$305=R158)*($B$6:$B$305&lt;B158)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21676,7 +21676,7 @@
         <v/>
       </c>
       <c r="S159">
-        <f>IF(OR(B159="",COUNTIF($B$6:$B159,B159)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R159)+(($R$6:$R$305=R159)*(ROW($B$6:$B$305)&lt;ROW(B159)))))+1)</f>
+        <f>IF(OR(B159="",COUNTIF($B$6:$B159,B159)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R159)+(($R$6:$R$305=R159)*($B$6:$B$305&lt;B159)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21698,7 +21698,7 @@
         <v/>
       </c>
       <c r="S160">
-        <f>IF(OR(B160="",COUNTIF($B$6:$B160,B160)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R160)+(($R$6:$R$305=R160)*(ROW($B$6:$B$305)&lt;ROW(B160)))))+1)</f>
+        <f>IF(OR(B160="",COUNTIF($B$6:$B160,B160)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R160)+(($R$6:$R$305=R160)*($B$6:$B$305&lt;B160)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21720,7 +21720,7 @@
         <v/>
       </c>
       <c r="S161">
-        <f>IF(OR(B161="",COUNTIF($B$6:$B161,B161)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R161)+(($R$6:$R$305=R161)*(ROW($B$6:$B$305)&lt;ROW(B161)))))+1)</f>
+        <f>IF(OR(B161="",COUNTIF($B$6:$B161,B161)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R161)+(($R$6:$R$305=R161)*($B$6:$B$305&lt;B161)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21742,7 +21742,7 @@
         <v/>
       </c>
       <c r="S162">
-        <f>IF(OR(B162="",COUNTIF($B$6:$B162,B162)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R162)+(($R$6:$R$305=R162)*(ROW($B$6:$B$305)&lt;ROW(B162)))))+1)</f>
+        <f>IF(OR(B162="",COUNTIF($B$6:$B162,B162)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R162)+(($R$6:$R$305=R162)*($B$6:$B$305&lt;B162)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
         <v/>
       </c>
       <c r="S163">
-        <f>IF(OR(B163="",COUNTIF($B$6:$B163,B163)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R163)+(($R$6:$R$305=R163)*(ROW($B$6:$B$305)&lt;ROW(B163)))))+1)</f>
+        <f>IF(OR(B163="",COUNTIF($B$6:$B163,B163)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R163)+(($R$6:$R$305=R163)*($B$6:$B$305&lt;B163)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
         <v/>
       </c>
       <c r="S164">
-        <f>IF(OR(B164="",COUNTIF($B$6:$B164,B164)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R164)+(($R$6:$R$305=R164)*(ROW($B$6:$B$305)&lt;ROW(B164)))))+1)</f>
+        <f>IF(OR(B164="",COUNTIF($B$6:$B164,B164)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R164)+(($R$6:$R$305=R164)*($B$6:$B$305&lt;B164)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21808,7 +21808,7 @@
         <v/>
       </c>
       <c r="S165">
-        <f>IF(OR(B165="",COUNTIF($B$6:$B165,B165)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R165)+(($R$6:$R$305=R165)*(ROW($B$6:$B$305)&lt;ROW(B165)))))+1)</f>
+        <f>IF(OR(B165="",COUNTIF($B$6:$B165,B165)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R165)+(($R$6:$R$305=R165)*($B$6:$B$305&lt;B165)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21830,7 +21830,7 @@
         <v/>
       </c>
       <c r="S166">
-        <f>IF(OR(B166="",COUNTIF($B$6:$B166,B166)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R166)+(($R$6:$R$305=R166)*(ROW($B$6:$B$305)&lt;ROW(B166)))))+1)</f>
+        <f>IF(OR(B166="",COUNTIF($B$6:$B166,B166)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R166)+(($R$6:$R$305=R166)*($B$6:$B$305&lt;B166)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21852,7 +21852,7 @@
         <v/>
       </c>
       <c r="S167">
-        <f>IF(OR(B167="",COUNTIF($B$6:$B167,B167)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R167)+(($R$6:$R$305=R167)*(ROW($B$6:$B$305)&lt;ROW(B167)))))+1)</f>
+        <f>IF(OR(B167="",COUNTIF($B$6:$B167,B167)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R167)+(($R$6:$R$305=R167)*($B$6:$B$305&lt;B167)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
         <v/>
       </c>
       <c r="S168">
-        <f>IF(OR(B168="",COUNTIF($B$6:$B168,B168)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R168)+(($R$6:$R$305=R168)*(ROW($B$6:$B$305)&lt;ROW(B168)))))+1)</f>
+        <f>IF(OR(B168="",COUNTIF($B$6:$B168,B168)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R168)+(($R$6:$R$305=R168)*($B$6:$B$305&lt;B168)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21896,7 +21896,7 @@
         <v/>
       </c>
       <c r="S169">
-        <f>IF(OR(B169="",COUNTIF($B$6:$B169,B169)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R169)+(($R$6:$R$305=R169)*(ROW($B$6:$B$305)&lt;ROW(B169)))))+1)</f>
+        <f>IF(OR(B169="",COUNTIF($B$6:$B169,B169)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R169)+(($R$6:$R$305=R169)*($B$6:$B$305&lt;B169)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21918,7 +21918,7 @@
         <v/>
       </c>
       <c r="S170">
-        <f>IF(OR(B170="",COUNTIF($B$6:$B170,B170)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R170)+(($R$6:$R$305=R170)*(ROW($B$6:$B$305)&lt;ROW(B170)))))+1)</f>
+        <f>IF(OR(B170="",COUNTIF($B$6:$B170,B170)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R170)+(($R$6:$R$305=R170)*($B$6:$B$305&lt;B170)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21940,7 +21940,7 @@
         <v/>
       </c>
       <c r="S171">
-        <f>IF(OR(B171="",COUNTIF($B$6:$B171,B171)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R171)+(($R$6:$R$305=R171)*(ROW($B$6:$B$305)&lt;ROW(B171)))))+1)</f>
+        <f>IF(OR(B171="",COUNTIF($B$6:$B171,B171)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R171)+(($R$6:$R$305=R171)*($B$6:$B$305&lt;B171)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21962,7 +21962,7 @@
         <v/>
       </c>
       <c r="S172">
-        <f>IF(OR(B172="",COUNTIF($B$6:$B172,B172)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R172)+(($R$6:$R$305=R172)*(ROW($B$6:$B$305)&lt;ROW(B172)))))+1)</f>
+        <f>IF(OR(B172="",COUNTIF($B$6:$B172,B172)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R172)+(($R$6:$R$305=R172)*($B$6:$B$305&lt;B172)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -21984,7 +21984,7 @@
         <v/>
       </c>
       <c r="S173">
-        <f>IF(OR(B173="",COUNTIF($B$6:$B173,B173)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R173)+(($R$6:$R$305=R173)*(ROW($B$6:$B$305)&lt;ROW(B173)))))+1)</f>
+        <f>IF(OR(B173="",COUNTIF($B$6:$B173,B173)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R173)+(($R$6:$R$305=R173)*($B$6:$B$305&lt;B173)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22006,7 +22006,7 @@
         <v/>
       </c>
       <c r="S174">
-        <f>IF(OR(B174="",COUNTIF($B$6:$B174,B174)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R174)+(($R$6:$R$305=R174)*(ROW($B$6:$B$305)&lt;ROW(B174)))))+1)</f>
+        <f>IF(OR(B174="",COUNTIF($B$6:$B174,B174)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R174)+(($R$6:$R$305=R174)*($B$6:$B$305&lt;B174)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
         <v/>
       </c>
       <c r="S175">
-        <f>IF(OR(B175="",COUNTIF($B$6:$B175,B175)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R175)+(($R$6:$R$305=R175)*(ROW($B$6:$B$305)&lt;ROW(B175)))))+1)</f>
+        <f>IF(OR(B175="",COUNTIF($B$6:$B175,B175)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R175)+(($R$6:$R$305=R175)*($B$6:$B$305&lt;B175)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22050,7 +22050,7 @@
         <v/>
       </c>
       <c r="S176">
-        <f>IF(OR(B176="",COUNTIF($B$6:$B176,B176)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R176)+(($R$6:$R$305=R176)*(ROW($B$6:$B$305)&lt;ROW(B176)))))+1)</f>
+        <f>IF(OR(B176="",COUNTIF($B$6:$B176,B176)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R176)+(($R$6:$R$305=R176)*($B$6:$B$305&lt;B176)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22072,7 +22072,7 @@
         <v/>
       </c>
       <c r="S177">
-        <f>IF(OR(B177="",COUNTIF($B$6:$B177,B177)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R177)+(($R$6:$R$305=R177)*(ROW($B$6:$B$305)&lt;ROW(B177)))))+1)</f>
+        <f>IF(OR(B177="",COUNTIF($B$6:$B177,B177)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R177)+(($R$6:$R$305=R177)*($B$6:$B$305&lt;B177)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22094,7 +22094,7 @@
         <v/>
       </c>
       <c r="S178">
-        <f>IF(OR(B178="",COUNTIF($B$6:$B178,B178)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R178)+(($R$6:$R$305=R178)*(ROW($B$6:$B$305)&lt;ROW(B178)))))+1)</f>
+        <f>IF(OR(B178="",COUNTIF($B$6:$B178,B178)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R178)+(($R$6:$R$305=R178)*($B$6:$B$305&lt;B178)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22116,7 +22116,7 @@
         <v/>
       </c>
       <c r="S179">
-        <f>IF(OR(B179="",COUNTIF($B$6:$B179,B179)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R179)+(($R$6:$R$305=R179)*(ROW($B$6:$B$305)&lt;ROW(B179)))))+1)</f>
+        <f>IF(OR(B179="",COUNTIF($B$6:$B179,B179)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R179)+(($R$6:$R$305=R179)*($B$6:$B$305&lt;B179)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
         <v/>
       </c>
       <c r="S180">
-        <f>IF(OR(B180="",COUNTIF($B$6:$B180,B180)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R180)+(($R$6:$R$305=R180)*(ROW($B$6:$B$305)&lt;ROW(B180)))))+1)</f>
+        <f>IF(OR(B180="",COUNTIF($B$6:$B180,B180)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R180)+(($R$6:$R$305=R180)*($B$6:$B$305&lt;B180)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
         <v/>
       </c>
       <c r="S181">
-        <f>IF(OR(B181="",COUNTIF($B$6:$B181,B181)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R181)+(($R$6:$R$305=R181)*(ROW($B$6:$B$305)&lt;ROW(B181)))))+1)</f>
+        <f>IF(OR(B181="",COUNTIF($B$6:$B181,B181)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R181)+(($R$6:$R$305=R181)*($B$6:$B$305&lt;B181)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22182,7 +22182,7 @@
         <v/>
       </c>
       <c r="S182">
-        <f>IF(OR(B182="",COUNTIF($B$6:$B182,B182)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R182)+(($R$6:$R$305=R182)*(ROW($B$6:$B$305)&lt;ROW(B182)))))+1)</f>
+        <f>IF(OR(B182="",COUNTIF($B$6:$B182,B182)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R182)+(($R$6:$R$305=R182)*($B$6:$B$305&lt;B182)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22204,7 +22204,7 @@
         <v/>
       </c>
       <c r="S183">
-        <f>IF(OR(B183="",COUNTIF($B$6:$B183,B183)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R183)+(($R$6:$R$305=R183)*(ROW($B$6:$B$305)&lt;ROW(B183)))))+1)</f>
+        <f>IF(OR(B183="",COUNTIF($B$6:$B183,B183)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R183)+(($R$6:$R$305=R183)*($B$6:$B$305&lt;B183)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22226,7 +22226,7 @@
         <v/>
       </c>
       <c r="S184">
-        <f>IF(OR(B184="",COUNTIF($B$6:$B184,B184)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R184)+(($R$6:$R$305=R184)*(ROW($B$6:$B$305)&lt;ROW(B184)))))+1)</f>
+        <f>IF(OR(B184="",COUNTIF($B$6:$B184,B184)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R184)+(($R$6:$R$305=R184)*($B$6:$B$305&lt;B184)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22248,7 +22248,7 @@
         <v/>
       </c>
       <c r="S185">
-        <f>IF(OR(B185="",COUNTIF($B$6:$B185,B185)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R185)+(($R$6:$R$305=R185)*(ROW($B$6:$B$305)&lt;ROW(B185)))))+1)</f>
+        <f>IF(OR(B185="",COUNTIF($B$6:$B185,B185)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R185)+(($R$6:$R$305=R185)*($B$6:$B$305&lt;B185)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22270,7 +22270,7 @@
         <v/>
       </c>
       <c r="S186">
-        <f>IF(OR(B186="",COUNTIF($B$6:$B186,B186)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R186)+(($R$6:$R$305=R186)*(ROW($B$6:$B$305)&lt;ROW(B186)))))+1)</f>
+        <f>IF(OR(B186="",COUNTIF($B$6:$B186,B186)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R186)+(($R$6:$R$305=R186)*($B$6:$B$305&lt;B186)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22292,7 +22292,7 @@
         <v/>
       </c>
       <c r="S187">
-        <f>IF(OR(B187="",COUNTIF($B$6:$B187,B187)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R187)+(($R$6:$R$305=R187)*(ROW($B$6:$B$305)&lt;ROW(B187)))))+1)</f>
+        <f>IF(OR(B187="",COUNTIF($B$6:$B187,B187)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R187)+(($R$6:$R$305=R187)*($B$6:$B$305&lt;B187)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
         <v/>
       </c>
       <c r="S188">
-        <f>IF(OR(B188="",COUNTIF($B$6:$B188,B188)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R188)+(($R$6:$R$305=R188)*(ROW($B$6:$B$305)&lt;ROW(B188)))))+1)</f>
+        <f>IF(OR(B188="",COUNTIF($B$6:$B188,B188)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R188)+(($R$6:$R$305=R188)*($B$6:$B$305&lt;B188)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22336,7 +22336,7 @@
         <v/>
       </c>
       <c r="S189">
-        <f>IF(OR(B189="",COUNTIF($B$6:$B189,B189)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R189)+(($R$6:$R$305=R189)*(ROW($B$6:$B$305)&lt;ROW(B189)))))+1)</f>
+        <f>IF(OR(B189="",COUNTIF($B$6:$B189,B189)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R189)+(($R$6:$R$305=R189)*($B$6:$B$305&lt;B189)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22358,7 +22358,7 @@
         <v/>
       </c>
       <c r="S190">
-        <f>IF(OR(B190="",COUNTIF($B$6:$B190,B190)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R190)+(($R$6:$R$305=R190)*(ROW($B$6:$B$305)&lt;ROW(B190)))))+1)</f>
+        <f>IF(OR(B190="",COUNTIF($B$6:$B190,B190)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R190)+(($R$6:$R$305=R190)*($B$6:$B$305&lt;B190)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22380,7 +22380,7 @@
         <v/>
       </c>
       <c r="S191">
-        <f>IF(OR(B191="",COUNTIF($B$6:$B191,B191)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R191)+(($R$6:$R$305=R191)*(ROW($B$6:$B$305)&lt;ROW(B191)))))+1)</f>
+        <f>IF(OR(B191="",COUNTIF($B$6:$B191,B191)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R191)+(($R$6:$R$305=R191)*($B$6:$B$305&lt;B191)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
         <v/>
       </c>
       <c r="S192">
-        <f>IF(OR(B192="",COUNTIF($B$6:$B192,B192)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R192)+(($R$6:$R$305=R192)*(ROW($B$6:$B$305)&lt;ROW(B192)))))+1)</f>
+        <f>IF(OR(B192="",COUNTIF($B$6:$B192,B192)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R192)+(($R$6:$R$305=R192)*($B$6:$B$305&lt;B192)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22424,7 +22424,7 @@
         <v/>
       </c>
       <c r="S193">
-        <f>IF(OR(B193="",COUNTIF($B$6:$B193,B193)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R193)+(($R$6:$R$305=R193)*(ROW($B$6:$B$305)&lt;ROW(B193)))))+1)</f>
+        <f>IF(OR(B193="",COUNTIF($B$6:$B193,B193)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R193)+(($R$6:$R$305=R193)*($B$6:$B$305&lt;B193)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
         <v/>
       </c>
       <c r="S194">
-        <f>IF(OR(B194="",COUNTIF($B$6:$B194,B194)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R194)+(($R$6:$R$305=R194)*(ROW($B$6:$B$305)&lt;ROW(B194)))))+1)</f>
+        <f>IF(OR(B194="",COUNTIF($B$6:$B194,B194)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R194)+(($R$6:$R$305=R194)*($B$6:$B$305&lt;B194)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
         <v/>
       </c>
       <c r="S195">
-        <f>IF(OR(B195="",COUNTIF($B$6:$B195,B195)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R195)+(($R$6:$R$305=R195)*(ROW($B$6:$B$305)&lt;ROW(B195)))))+1)</f>
+        <f>IF(OR(B195="",COUNTIF($B$6:$B195,B195)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R195)+(($R$6:$R$305=R195)*($B$6:$B$305&lt;B195)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22490,7 +22490,7 @@
         <v/>
       </c>
       <c r="S196">
-        <f>IF(OR(B196="",COUNTIF($B$6:$B196,B196)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R196)+(($R$6:$R$305=R196)*(ROW($B$6:$B$305)&lt;ROW(B196)))))+1)</f>
+        <f>IF(OR(B196="",COUNTIF($B$6:$B196,B196)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R196)+(($R$6:$R$305=R196)*($B$6:$B$305&lt;B196)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22512,7 +22512,7 @@
         <v/>
       </c>
       <c r="S197">
-        <f>IF(OR(B197="",COUNTIF($B$6:$B197,B197)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R197)+(($R$6:$R$305=R197)*(ROW($B$6:$B$305)&lt;ROW(B197)))))+1)</f>
+        <f>IF(OR(B197="",COUNTIF($B$6:$B197,B197)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R197)+(($R$6:$R$305=R197)*($B$6:$B$305&lt;B197)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
         <v/>
       </c>
       <c r="S198">
-        <f>IF(OR(B198="",COUNTIF($B$6:$B198,B198)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R198)+(($R$6:$R$305=R198)*(ROW($B$6:$B$305)&lt;ROW(B198)))))+1)</f>
+        <f>IF(OR(B198="",COUNTIF($B$6:$B198,B198)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R198)+(($R$6:$R$305=R198)*($B$6:$B$305&lt;B198)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22556,7 +22556,7 @@
         <v/>
       </c>
       <c r="S199">
-        <f>IF(OR(B199="",COUNTIF($B$6:$B199,B199)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R199)+(($R$6:$R$305=R199)*(ROW($B$6:$B$305)&lt;ROW(B199)))))+1)</f>
+        <f>IF(OR(B199="",COUNTIF($B$6:$B199,B199)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R199)+(($R$6:$R$305=R199)*($B$6:$B$305&lt;B199)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
         <v/>
       </c>
       <c r="S200">
-        <f>IF(OR(B200="",COUNTIF($B$6:$B200,B200)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R200)+(($R$6:$R$305=R200)*(ROW($B$6:$B$305)&lt;ROW(B200)))))+1)</f>
+        <f>IF(OR(B200="",COUNTIF($B$6:$B200,B200)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R200)+(($R$6:$R$305=R200)*($B$6:$B$305&lt;B200)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22600,7 +22600,7 @@
         <v/>
       </c>
       <c r="S201">
-        <f>IF(OR(B201="",COUNTIF($B$6:$B201,B201)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R201)+(($R$6:$R$305=R201)*(ROW($B$6:$B$305)&lt;ROW(B201)))))+1)</f>
+        <f>IF(OR(B201="",COUNTIF($B$6:$B201,B201)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R201)+(($R$6:$R$305=R201)*($B$6:$B$305&lt;B201)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22622,7 +22622,7 @@
         <v/>
       </c>
       <c r="S202">
-        <f>IF(OR(B202="",COUNTIF($B$6:$B202,B202)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R202)+(($R$6:$R$305=R202)*(ROW($B$6:$B$305)&lt;ROW(B202)))))+1)</f>
+        <f>IF(OR(B202="",COUNTIF($B$6:$B202,B202)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R202)+(($R$6:$R$305=R202)*($B$6:$B$305&lt;B202)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22644,7 +22644,7 @@
         <v/>
       </c>
       <c r="S203">
-        <f>IF(OR(B203="",COUNTIF($B$6:$B203,B203)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R203)+(($R$6:$R$305=R203)*(ROW($B$6:$B$305)&lt;ROW(B203)))))+1)</f>
+        <f>IF(OR(B203="",COUNTIF($B$6:$B203,B203)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R203)+(($R$6:$R$305=R203)*($B$6:$B$305&lt;B203)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22666,7 +22666,7 @@
         <v/>
       </c>
       <c r="S204">
-        <f>IF(OR(B204="",COUNTIF($B$6:$B204,B204)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R204)+(($R$6:$R$305=R204)*(ROW($B$6:$B$305)&lt;ROW(B204)))))+1)</f>
+        <f>IF(OR(B204="",COUNTIF($B$6:$B204,B204)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R204)+(($R$6:$R$305=R204)*($B$6:$B$305&lt;B204)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22688,7 +22688,7 @@
         <v/>
       </c>
       <c r="S205">
-        <f>IF(OR(B205="",COUNTIF($B$6:$B205,B205)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R205)+(($R$6:$R$305=R205)*(ROW($B$6:$B$305)&lt;ROW(B205)))))+1)</f>
+        <f>IF(OR(B205="",COUNTIF($B$6:$B205,B205)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R205)+(($R$6:$R$305=R205)*($B$6:$B$305&lt;B205)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22710,7 +22710,7 @@
         <v/>
       </c>
       <c r="S206">
-        <f>IF(OR(B206="",COUNTIF($B$6:$B206,B206)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R206)+(($R$6:$R$305=R206)*(ROW($B$6:$B$305)&lt;ROW(B206)))))+1)</f>
+        <f>IF(OR(B206="",COUNTIF($B$6:$B206,B206)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R206)+(($R$6:$R$305=R206)*($B$6:$B$305&lt;B206)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
         <v/>
       </c>
       <c r="S207">
-        <f>IF(OR(B207="",COUNTIF($B$6:$B207,B207)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R207)+(($R$6:$R$305=R207)*(ROW($B$6:$B$305)&lt;ROW(B207)))))+1)</f>
+        <f>IF(OR(B207="",COUNTIF($B$6:$B207,B207)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R207)+(($R$6:$R$305=R207)*($B$6:$B$305&lt;B207)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22754,7 +22754,7 @@
         <v/>
       </c>
       <c r="S208">
-        <f>IF(OR(B208="",COUNTIF($B$6:$B208,B208)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R208)+(($R$6:$R$305=R208)*(ROW($B$6:$B$305)&lt;ROW(B208)))))+1)</f>
+        <f>IF(OR(B208="",COUNTIF($B$6:$B208,B208)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R208)+(($R$6:$R$305=R208)*($B$6:$B$305&lt;B208)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22776,7 +22776,7 @@
         <v/>
       </c>
       <c r="S209">
-        <f>IF(OR(B209="",COUNTIF($B$6:$B209,B209)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R209)+(($R$6:$R$305=R209)*(ROW($B$6:$B$305)&lt;ROW(B209)))))+1)</f>
+        <f>IF(OR(B209="",COUNTIF($B$6:$B209,B209)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R209)+(($R$6:$R$305=R209)*($B$6:$B$305&lt;B209)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22798,7 +22798,7 @@
         <v/>
       </c>
       <c r="S210">
-        <f>IF(OR(B210="",COUNTIF($B$6:$B210,B210)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R210)+(($R$6:$R$305=R210)*(ROW($B$6:$B$305)&lt;ROW(B210)))))+1)</f>
+        <f>IF(OR(B210="",COUNTIF($B$6:$B210,B210)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R210)+(($R$6:$R$305=R210)*($B$6:$B$305&lt;B210)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22820,7 +22820,7 @@
         <v/>
       </c>
       <c r="S211">
-        <f>IF(OR(B211="",COUNTIF($B$6:$B211,B211)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R211)+(($R$6:$R$305=R211)*(ROW($B$6:$B$305)&lt;ROW(B211)))))+1)</f>
+        <f>IF(OR(B211="",COUNTIF($B$6:$B211,B211)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R211)+(($R$6:$R$305=R211)*($B$6:$B$305&lt;B211)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
         <v/>
       </c>
       <c r="S212">
-        <f>IF(OR(B212="",COUNTIF($B$6:$B212,B212)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R212)+(($R$6:$R$305=R212)*(ROW($B$6:$B$305)&lt;ROW(B212)))))+1)</f>
+        <f>IF(OR(B212="",COUNTIF($B$6:$B212,B212)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R212)+(($R$6:$R$305=R212)*($B$6:$B$305&lt;B212)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22864,7 +22864,7 @@
         <v/>
       </c>
       <c r="S213">
-        <f>IF(OR(B213="",COUNTIF($B$6:$B213,B213)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R213)+(($R$6:$R$305=R213)*(ROW($B$6:$B$305)&lt;ROW(B213)))))+1)</f>
+        <f>IF(OR(B213="",COUNTIF($B$6:$B213,B213)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R213)+(($R$6:$R$305=R213)*($B$6:$B$305&lt;B213)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22886,7 +22886,7 @@
         <v/>
       </c>
       <c r="S214">
-        <f>IF(OR(B214="",COUNTIF($B$6:$B214,B214)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R214)+(($R$6:$R$305=R214)*(ROW($B$6:$B$305)&lt;ROW(B214)))))+1)</f>
+        <f>IF(OR(B214="",COUNTIF($B$6:$B214,B214)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R214)+(($R$6:$R$305=R214)*($B$6:$B$305&lt;B214)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
         <v/>
       </c>
       <c r="S215">
-        <f>IF(OR(B215="",COUNTIF($B$6:$B215,B215)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R215)+(($R$6:$R$305=R215)*(ROW($B$6:$B$305)&lt;ROW(B215)))))+1)</f>
+        <f>IF(OR(B215="",COUNTIF($B$6:$B215,B215)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R215)+(($R$6:$R$305=R215)*($B$6:$B$305&lt;B215)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22930,7 +22930,7 @@
         <v/>
       </c>
       <c r="S216">
-        <f>IF(OR(B216="",COUNTIF($B$6:$B216,B216)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R216)+(($R$6:$R$305=R216)*(ROW($B$6:$B$305)&lt;ROW(B216)))))+1)</f>
+        <f>IF(OR(B216="",COUNTIF($B$6:$B216,B216)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R216)+(($R$6:$R$305=R216)*($B$6:$B$305&lt;B216)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
         <v/>
       </c>
       <c r="S217">
-        <f>IF(OR(B217="",COUNTIF($B$6:$B217,B217)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R217)+(($R$6:$R$305=R217)*(ROW($B$6:$B$305)&lt;ROW(B217)))))+1)</f>
+        <f>IF(OR(B217="",COUNTIF($B$6:$B217,B217)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R217)+(($R$6:$R$305=R217)*($B$6:$B$305&lt;B217)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22974,7 +22974,7 @@
         <v/>
       </c>
       <c r="S218">
-        <f>IF(OR(B218="",COUNTIF($B$6:$B218,B218)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R218)+(($R$6:$R$305=R218)*(ROW($B$6:$B$305)&lt;ROW(B218)))))+1)</f>
+        <f>IF(OR(B218="",COUNTIF($B$6:$B218,B218)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R218)+(($R$6:$R$305=R218)*($B$6:$B$305&lt;B218)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -22996,7 +22996,7 @@
         <v/>
       </c>
       <c r="S219">
-        <f>IF(OR(B219="",COUNTIF($B$6:$B219,B219)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R219)+(($R$6:$R$305=R219)*(ROW($B$6:$B$305)&lt;ROW(B219)))))+1)</f>
+        <f>IF(OR(B219="",COUNTIF($B$6:$B219,B219)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R219)+(($R$6:$R$305=R219)*($B$6:$B$305&lt;B219)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
         <v/>
       </c>
       <c r="S220">
-        <f>IF(OR(B220="",COUNTIF($B$6:$B220,B220)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R220)+(($R$6:$R$305=R220)*(ROW($B$6:$B$305)&lt;ROW(B220)))))+1)</f>
+        <f>IF(OR(B220="",COUNTIF($B$6:$B220,B220)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R220)+(($R$6:$R$305=R220)*($B$6:$B$305&lt;B220)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23040,7 +23040,7 @@
         <v/>
       </c>
       <c r="S221">
-        <f>IF(OR(B221="",COUNTIF($B$6:$B221,B221)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R221)+(($R$6:$R$305=R221)*(ROW($B$6:$B$305)&lt;ROW(B221)))))+1)</f>
+        <f>IF(OR(B221="",COUNTIF($B$6:$B221,B221)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R221)+(($R$6:$R$305=R221)*($B$6:$B$305&lt;B221)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23062,7 +23062,7 @@
         <v/>
       </c>
       <c r="S222">
-        <f>IF(OR(B222="",COUNTIF($B$6:$B222,B222)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R222)+(($R$6:$R$305=R222)*(ROW($B$6:$B$305)&lt;ROW(B222)))))+1)</f>
+        <f>IF(OR(B222="",COUNTIF($B$6:$B222,B222)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R222)+(($R$6:$R$305=R222)*($B$6:$B$305&lt;B222)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23084,7 +23084,7 @@
         <v/>
       </c>
       <c r="S223">
-        <f>IF(OR(B223="",COUNTIF($B$6:$B223,B223)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R223)+(($R$6:$R$305=R223)*(ROW($B$6:$B$305)&lt;ROW(B223)))))+1)</f>
+        <f>IF(OR(B223="",COUNTIF($B$6:$B223,B223)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R223)+(($R$6:$R$305=R223)*($B$6:$B$305&lt;B223)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23106,7 +23106,7 @@
         <v/>
       </c>
       <c r="S224">
-        <f>IF(OR(B224="",COUNTIF($B$6:$B224,B224)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R224)+(($R$6:$R$305=R224)*(ROW($B$6:$B$305)&lt;ROW(B224)))))+1)</f>
+        <f>IF(OR(B224="",COUNTIF($B$6:$B224,B224)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R224)+(($R$6:$R$305=R224)*($B$6:$B$305&lt;B224)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23128,7 +23128,7 @@
         <v/>
       </c>
       <c r="S225">
-        <f>IF(OR(B225="",COUNTIF($B$6:$B225,B225)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R225)+(($R$6:$R$305=R225)*(ROW($B$6:$B$305)&lt;ROW(B225)))))+1)</f>
+        <f>IF(OR(B225="",COUNTIF($B$6:$B225,B225)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R225)+(($R$6:$R$305=R225)*($B$6:$B$305&lt;B225)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
         <v/>
       </c>
       <c r="S226">
-        <f>IF(OR(B226="",COUNTIF($B$6:$B226,B226)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R226)+(($R$6:$R$305=R226)*(ROW($B$6:$B$305)&lt;ROW(B226)))))+1)</f>
+        <f>IF(OR(B226="",COUNTIF($B$6:$B226,B226)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R226)+(($R$6:$R$305=R226)*($B$6:$B$305&lt;B226)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23172,7 +23172,7 @@
         <v/>
       </c>
       <c r="S227">
-        <f>IF(OR(B227="",COUNTIF($B$6:$B227,B227)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R227)+(($R$6:$R$305=R227)*(ROW($B$6:$B$305)&lt;ROW(B227)))))+1)</f>
+        <f>IF(OR(B227="",COUNTIF($B$6:$B227,B227)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R227)+(($R$6:$R$305=R227)*($B$6:$B$305&lt;B227)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
         <v/>
       </c>
       <c r="S228">
-        <f>IF(OR(B228="",COUNTIF($B$6:$B228,B228)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R228)+(($R$6:$R$305=R228)*(ROW($B$6:$B$305)&lt;ROW(B228)))))+1)</f>
+        <f>IF(OR(B228="",COUNTIF($B$6:$B228,B228)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R228)+(($R$6:$R$305=R228)*($B$6:$B$305&lt;B228)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23216,7 +23216,7 @@
         <v/>
       </c>
       <c r="S229">
-        <f>IF(OR(B229="",COUNTIF($B$6:$B229,B229)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R229)+(($R$6:$R$305=R229)*(ROW($B$6:$B$305)&lt;ROW(B229)))))+1)</f>
+        <f>IF(OR(B229="",COUNTIF($B$6:$B229,B229)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R229)+(($R$6:$R$305=R229)*($B$6:$B$305&lt;B229)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23238,7 +23238,7 @@
         <v/>
       </c>
       <c r="S230">
-        <f>IF(OR(B230="",COUNTIF($B$6:$B230,B230)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R230)+(($R$6:$R$305=R230)*(ROW($B$6:$B$305)&lt;ROW(B230)))))+1)</f>
+        <f>IF(OR(B230="",COUNTIF($B$6:$B230,B230)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R230)+(($R$6:$R$305=R230)*($B$6:$B$305&lt;B230)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23260,7 +23260,7 @@
         <v/>
       </c>
       <c r="S231">
-        <f>IF(OR(B231="",COUNTIF($B$6:$B231,B231)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R231)+(($R$6:$R$305=R231)*(ROW($B$6:$B$305)&lt;ROW(B231)))))+1)</f>
+        <f>IF(OR(B231="",COUNTIF($B$6:$B231,B231)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R231)+(($R$6:$R$305=R231)*($B$6:$B$305&lt;B231)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
         <v/>
       </c>
       <c r="S232">
-        <f>IF(OR(B232="",COUNTIF($B$6:$B232,B232)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R232)+(($R$6:$R$305=R232)*(ROW($B$6:$B$305)&lt;ROW(B232)))))+1)</f>
+        <f>IF(OR(B232="",COUNTIF($B$6:$B232,B232)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R232)+(($R$6:$R$305=R232)*($B$6:$B$305&lt;B232)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23304,7 +23304,7 @@
         <v/>
       </c>
       <c r="S233">
-        <f>IF(OR(B233="",COUNTIF($B$6:$B233,B233)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R233)+(($R$6:$R$305=R233)*(ROW($B$6:$B$305)&lt;ROW(B233)))))+1)</f>
+        <f>IF(OR(B233="",COUNTIF($B$6:$B233,B233)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R233)+(($R$6:$R$305=R233)*($B$6:$B$305&lt;B233)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23326,7 +23326,7 @@
         <v/>
       </c>
       <c r="S234">
-        <f>IF(OR(B234="",COUNTIF($B$6:$B234,B234)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R234)+(($R$6:$R$305=R234)*(ROW($B$6:$B$305)&lt;ROW(B234)))))+1)</f>
+        <f>IF(OR(B234="",COUNTIF($B$6:$B234,B234)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R234)+(($R$6:$R$305=R234)*($B$6:$B$305&lt;B234)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23348,7 +23348,7 @@
         <v/>
       </c>
       <c r="S235">
-        <f>IF(OR(B235="",COUNTIF($B$6:$B235,B235)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R235)+(($R$6:$R$305=R235)*(ROW($B$6:$B$305)&lt;ROW(B235)))))+1)</f>
+        <f>IF(OR(B235="",COUNTIF($B$6:$B235,B235)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R235)+(($R$6:$R$305=R235)*($B$6:$B$305&lt;B235)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23370,7 +23370,7 @@
         <v/>
       </c>
       <c r="S236">
-        <f>IF(OR(B236="",COUNTIF($B$6:$B236,B236)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R236)+(($R$6:$R$305=R236)*(ROW($B$6:$B$305)&lt;ROW(B236)))))+1)</f>
+        <f>IF(OR(B236="",COUNTIF($B$6:$B236,B236)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R236)+(($R$6:$R$305=R236)*($B$6:$B$305&lt;B236)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23392,7 +23392,7 @@
         <v/>
       </c>
       <c r="S237">
-        <f>IF(OR(B237="",COUNTIF($B$6:$B237,B237)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R237)+(($R$6:$R$305=R237)*(ROW($B$6:$B$305)&lt;ROW(B237)))))+1)</f>
+        <f>IF(OR(B237="",COUNTIF($B$6:$B237,B237)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R237)+(($R$6:$R$305=R237)*($B$6:$B$305&lt;B237)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
         <v/>
       </c>
       <c r="S238">
-        <f>IF(OR(B238="",COUNTIF($B$6:$B238,B238)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R238)+(($R$6:$R$305=R238)*(ROW($B$6:$B$305)&lt;ROW(B238)))))+1)</f>
+        <f>IF(OR(B238="",COUNTIF($B$6:$B238,B238)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R238)+(($R$6:$R$305=R238)*($B$6:$B$305&lt;B238)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23436,7 +23436,7 @@
         <v/>
       </c>
       <c r="S239">
-        <f>IF(OR(B239="",COUNTIF($B$6:$B239,B239)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R239)+(($R$6:$R$305=R239)*(ROW($B$6:$B$305)&lt;ROW(B239)))))+1)</f>
+        <f>IF(OR(B239="",COUNTIF($B$6:$B239,B239)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R239)+(($R$6:$R$305=R239)*($B$6:$B$305&lt;B239)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
         <v/>
       </c>
       <c r="S240">
-        <f>IF(OR(B240="",COUNTIF($B$6:$B240,B240)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R240)+(($R$6:$R$305=R240)*(ROW($B$6:$B$305)&lt;ROW(B240)))))+1)</f>
+        <f>IF(OR(B240="",COUNTIF($B$6:$B240,B240)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R240)+(($R$6:$R$305=R240)*($B$6:$B$305&lt;B240)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23480,7 +23480,7 @@
         <v/>
       </c>
       <c r="S241">
-        <f>IF(OR(B241="",COUNTIF($B$6:$B241,B241)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R241)+(($R$6:$R$305=R241)*(ROW($B$6:$B$305)&lt;ROW(B241)))))+1)</f>
+        <f>IF(OR(B241="",COUNTIF($B$6:$B241,B241)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R241)+(($R$6:$R$305=R241)*($B$6:$B$305&lt;B241)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
         <v/>
       </c>
       <c r="S242">
-        <f>IF(OR(B242="",COUNTIF($B$6:$B242,B242)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R242)+(($R$6:$R$305=R242)*(ROW($B$6:$B$305)&lt;ROW(B242)))))+1)</f>
+        <f>IF(OR(B242="",COUNTIF($B$6:$B242,B242)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R242)+(($R$6:$R$305=R242)*($B$6:$B$305&lt;B242)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23524,7 +23524,7 @@
         <v/>
       </c>
       <c r="S243">
-        <f>IF(OR(B243="",COUNTIF($B$6:$B243,B243)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R243)+(($R$6:$R$305=R243)*(ROW($B$6:$B$305)&lt;ROW(B243)))))+1)</f>
+        <f>IF(OR(B243="",COUNTIF($B$6:$B243,B243)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R243)+(($R$6:$R$305=R243)*($B$6:$B$305&lt;B243)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23546,7 +23546,7 @@
         <v/>
       </c>
       <c r="S244">
-        <f>IF(OR(B244="",COUNTIF($B$6:$B244,B244)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R244)+(($R$6:$R$305=R244)*(ROW($B$6:$B$305)&lt;ROW(B244)))))+1)</f>
+        <f>IF(OR(B244="",COUNTIF($B$6:$B244,B244)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R244)+(($R$6:$R$305=R244)*($B$6:$B$305&lt;B244)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23568,7 +23568,7 @@
         <v/>
       </c>
       <c r="S245">
-        <f>IF(OR(B245="",COUNTIF($B$6:$B245,B245)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R245)+(($R$6:$R$305=R245)*(ROW($B$6:$B$305)&lt;ROW(B245)))))+1)</f>
+        <f>IF(OR(B245="",COUNTIF($B$6:$B245,B245)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R245)+(($R$6:$R$305=R245)*($B$6:$B$305&lt;B245)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23590,7 +23590,7 @@
         <v/>
       </c>
       <c r="S246">
-        <f>IF(OR(B246="",COUNTIF($B$6:$B246,B246)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R246)+(($R$6:$R$305=R246)*(ROW($B$6:$B$305)&lt;ROW(B246)))))+1)</f>
+        <f>IF(OR(B246="",COUNTIF($B$6:$B246,B246)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R246)+(($R$6:$R$305=R246)*($B$6:$B$305&lt;B246)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23612,7 +23612,7 @@
         <v/>
       </c>
       <c r="S247">
-        <f>IF(OR(B247="",COUNTIF($B$6:$B247,B247)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R247)+(($R$6:$R$305=R247)*(ROW($B$6:$B$305)&lt;ROW(B247)))))+1)</f>
+        <f>IF(OR(B247="",COUNTIF($B$6:$B247,B247)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R247)+(($R$6:$R$305=R247)*($B$6:$B$305&lt;B247)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
         <v/>
       </c>
       <c r="S248">
-        <f>IF(OR(B248="",COUNTIF($B$6:$B248,B248)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R248)+(($R$6:$R$305=R248)*(ROW($B$6:$B$305)&lt;ROW(B248)))))+1)</f>
+        <f>IF(OR(B248="",COUNTIF($B$6:$B248,B248)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R248)+(($R$6:$R$305=R248)*($B$6:$B$305&lt;B248)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23656,7 +23656,7 @@
         <v/>
       </c>
       <c r="S249">
-        <f>IF(OR(B249="",COUNTIF($B$6:$B249,B249)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R249)+(($R$6:$R$305=R249)*(ROW($B$6:$B$305)&lt;ROW(B249)))))+1)</f>
+        <f>IF(OR(B249="",COUNTIF($B$6:$B249,B249)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R249)+(($R$6:$R$305=R249)*($B$6:$B$305&lt;B249)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23678,7 +23678,7 @@
         <v/>
       </c>
       <c r="S250">
-        <f>IF(OR(B250="",COUNTIF($B$6:$B250,B250)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R250)+(($R$6:$R$305=R250)*(ROW($B$6:$B$305)&lt;ROW(B250)))))+1)</f>
+        <f>IF(OR(B250="",COUNTIF($B$6:$B250,B250)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R250)+(($R$6:$R$305=R250)*($B$6:$B$305&lt;B250)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23700,7 +23700,7 @@
         <v/>
       </c>
       <c r="S251">
-        <f>IF(OR(B251="",COUNTIF($B$6:$B251,B251)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R251)+(($R$6:$R$305=R251)*(ROW($B$6:$B$305)&lt;ROW(B251)))))+1)</f>
+        <f>IF(OR(B251="",COUNTIF($B$6:$B251,B251)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R251)+(($R$6:$R$305=R251)*($B$6:$B$305&lt;B251)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23722,7 +23722,7 @@
         <v/>
       </c>
       <c r="S252">
-        <f>IF(OR(B252="",COUNTIF($B$6:$B252,B252)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R252)+(($R$6:$R$305=R252)*(ROW($B$6:$B$305)&lt;ROW(B252)))))+1)</f>
+        <f>IF(OR(B252="",COUNTIF($B$6:$B252,B252)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R252)+(($R$6:$R$305=R252)*($B$6:$B$305&lt;B252)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23744,7 +23744,7 @@
         <v/>
       </c>
       <c r="S253">
-        <f>IF(OR(B253="",COUNTIF($B$6:$B253,B253)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R253)+(($R$6:$R$305=R253)*(ROW($B$6:$B$305)&lt;ROW(B253)))))+1)</f>
+        <f>IF(OR(B253="",COUNTIF($B$6:$B253,B253)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R253)+(($R$6:$R$305=R253)*($B$6:$B$305&lt;B253)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
         <v/>
       </c>
       <c r="S254">
-        <f>IF(OR(B254="",COUNTIF($B$6:$B254,B254)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R254)+(($R$6:$R$305=R254)*(ROW($B$6:$B$305)&lt;ROW(B254)))))+1)</f>
+        <f>IF(OR(B254="",COUNTIF($B$6:$B254,B254)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R254)+(($R$6:$R$305=R254)*($B$6:$B$305&lt;B254)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
         <v/>
       </c>
       <c r="S255">
-        <f>IF(OR(B255="",COUNTIF($B$6:$B255,B255)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R255)+(($R$6:$R$305=R255)*(ROW($B$6:$B$305)&lt;ROW(B255)))))+1)</f>
+        <f>IF(OR(B255="",COUNTIF($B$6:$B255,B255)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R255)+(($R$6:$R$305=R255)*($B$6:$B$305&lt;B255)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23810,7 +23810,7 @@
         <v/>
       </c>
       <c r="S256">
-        <f>IF(OR(B256="",COUNTIF($B$6:$B256,B256)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R256)+(($R$6:$R$305=R256)*(ROW($B$6:$B$305)&lt;ROW(B256)))))+1)</f>
+        <f>IF(OR(B256="",COUNTIF($B$6:$B256,B256)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R256)+(($R$6:$R$305=R256)*($B$6:$B$305&lt;B256)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23832,7 +23832,7 @@
         <v/>
       </c>
       <c r="S257">
-        <f>IF(OR(B257="",COUNTIF($B$6:$B257,B257)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R257)+(($R$6:$R$305=R257)*(ROW($B$6:$B$305)&lt;ROW(B257)))))+1)</f>
+        <f>IF(OR(B257="",COUNTIF($B$6:$B257,B257)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R257)+(($R$6:$R$305=R257)*($B$6:$B$305&lt;B257)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23854,7 +23854,7 @@
         <v/>
       </c>
       <c r="S258">
-        <f>IF(OR(B258="",COUNTIF($B$6:$B258,B258)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R258)+(($R$6:$R$305=R258)*(ROW($B$6:$B$305)&lt;ROW(B258)))))+1)</f>
+        <f>IF(OR(B258="",COUNTIF($B$6:$B258,B258)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R258)+(($R$6:$R$305=R258)*($B$6:$B$305&lt;B258)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23876,7 +23876,7 @@
         <v/>
       </c>
       <c r="S259">
-        <f>IF(OR(B259="",COUNTIF($B$6:$B259,B259)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R259)+(($R$6:$R$305=R259)*(ROW($B$6:$B$305)&lt;ROW(B259)))))+1)</f>
+        <f>IF(OR(B259="",COUNTIF($B$6:$B259,B259)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R259)+(($R$6:$R$305=R259)*($B$6:$B$305&lt;B259)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23898,7 +23898,7 @@
         <v/>
       </c>
       <c r="S260">
-        <f>IF(OR(B260="",COUNTIF($B$6:$B260,B260)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R260)+(($R$6:$R$305=R260)*(ROW($B$6:$B$305)&lt;ROW(B260)))))+1)</f>
+        <f>IF(OR(B260="",COUNTIF($B$6:$B260,B260)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R260)+(($R$6:$R$305=R260)*($B$6:$B$305&lt;B260)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23920,7 +23920,7 @@
         <v/>
       </c>
       <c r="S261">
-        <f>IF(OR(B261="",COUNTIF($B$6:$B261,B261)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R261)+(($R$6:$R$305=R261)*(ROW($B$6:$B$305)&lt;ROW(B261)))))+1)</f>
+        <f>IF(OR(B261="",COUNTIF($B$6:$B261,B261)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R261)+(($R$6:$R$305=R261)*($B$6:$B$305&lt;B261)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23942,7 +23942,7 @@
         <v/>
       </c>
       <c r="S262">
-        <f>IF(OR(B262="",COUNTIF($B$6:$B262,B262)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R262)+(($R$6:$R$305=R262)*(ROW($B$6:$B$305)&lt;ROW(B262)))))+1)</f>
+        <f>IF(OR(B262="",COUNTIF($B$6:$B262,B262)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R262)+(($R$6:$R$305=R262)*($B$6:$B$305&lt;B262)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23964,7 +23964,7 @@
         <v/>
       </c>
       <c r="S263">
-        <f>IF(OR(B263="",COUNTIF($B$6:$B263,B263)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R263)+(($R$6:$R$305=R263)*(ROW($B$6:$B$305)&lt;ROW(B263)))))+1)</f>
+        <f>IF(OR(B263="",COUNTIF($B$6:$B263,B263)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R263)+(($R$6:$R$305=R263)*($B$6:$B$305&lt;B263)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -23986,7 +23986,7 @@
         <v/>
       </c>
       <c r="S264">
-        <f>IF(OR(B264="",COUNTIF($B$6:$B264,B264)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R264)+(($R$6:$R$305=R264)*(ROW($B$6:$B$305)&lt;ROW(B264)))))+1)</f>
+        <f>IF(OR(B264="",COUNTIF($B$6:$B264,B264)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R264)+(($R$6:$R$305=R264)*($B$6:$B$305&lt;B264)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24008,7 +24008,7 @@
         <v/>
       </c>
       <c r="S265">
-        <f>IF(OR(B265="",COUNTIF($B$6:$B265,B265)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R265)+(($R$6:$R$305=R265)*(ROW($B$6:$B$305)&lt;ROW(B265)))))+1)</f>
+        <f>IF(OR(B265="",COUNTIF($B$6:$B265,B265)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R265)+(($R$6:$R$305=R265)*($B$6:$B$305&lt;B265)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24030,7 +24030,7 @@
         <v/>
       </c>
       <c r="S266">
-        <f>IF(OR(B266="",COUNTIF($B$6:$B266,B266)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R266)+(($R$6:$R$305=R266)*(ROW($B$6:$B$305)&lt;ROW(B266)))))+1)</f>
+        <f>IF(OR(B266="",COUNTIF($B$6:$B266,B266)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R266)+(($R$6:$R$305=R266)*($B$6:$B$305&lt;B266)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24052,7 +24052,7 @@
         <v/>
       </c>
       <c r="S267">
-        <f>IF(OR(B267="",COUNTIF($B$6:$B267,B267)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R267)+(($R$6:$R$305=R267)*(ROW($B$6:$B$305)&lt;ROW(B267)))))+1)</f>
+        <f>IF(OR(B267="",COUNTIF($B$6:$B267,B267)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R267)+(($R$6:$R$305=R267)*($B$6:$B$305&lt;B267)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24074,7 +24074,7 @@
         <v/>
       </c>
       <c r="S268">
-        <f>IF(OR(B268="",COUNTIF($B$6:$B268,B268)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R268)+(($R$6:$R$305=R268)*(ROW($B$6:$B$305)&lt;ROW(B268)))))+1)</f>
+        <f>IF(OR(B268="",COUNTIF($B$6:$B268,B268)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R268)+(($R$6:$R$305=R268)*($B$6:$B$305&lt;B268)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
         <v/>
       </c>
       <c r="S269">
-        <f>IF(OR(B269="",COUNTIF($B$6:$B269,B269)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R269)+(($R$6:$R$305=R269)*(ROW($B$6:$B$305)&lt;ROW(B269)))))+1)</f>
+        <f>IF(OR(B269="",COUNTIF($B$6:$B269,B269)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R269)+(($R$6:$R$305=R269)*($B$6:$B$305&lt;B269)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24118,7 +24118,7 @@
         <v/>
       </c>
       <c r="S270">
-        <f>IF(OR(B270="",COUNTIF($B$6:$B270,B270)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R270)+(($R$6:$R$305=R270)*(ROW($B$6:$B$305)&lt;ROW(B270)))))+1)</f>
+        <f>IF(OR(B270="",COUNTIF($B$6:$B270,B270)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R270)+(($R$6:$R$305=R270)*($B$6:$B$305&lt;B270)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24140,7 +24140,7 @@
         <v/>
       </c>
       <c r="S271">
-        <f>IF(OR(B271="",COUNTIF($B$6:$B271,B271)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R271)+(($R$6:$R$305=R271)*(ROW($B$6:$B$305)&lt;ROW(B271)))))+1)</f>
+        <f>IF(OR(B271="",COUNTIF($B$6:$B271,B271)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R271)+(($R$6:$R$305=R271)*($B$6:$B$305&lt;B271)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24162,7 +24162,7 @@
         <v/>
       </c>
       <c r="S272">
-        <f>IF(OR(B272="",COUNTIF($B$6:$B272,B272)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R272)+(($R$6:$R$305=R272)*(ROW($B$6:$B$305)&lt;ROW(B272)))))+1)</f>
+        <f>IF(OR(B272="",COUNTIF($B$6:$B272,B272)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R272)+(($R$6:$R$305=R272)*($B$6:$B$305&lt;B272)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24184,7 +24184,7 @@
         <v/>
       </c>
       <c r="S273">
-        <f>IF(OR(B273="",COUNTIF($B$6:$B273,B273)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R273)+(($R$6:$R$305=R273)*(ROW($B$6:$B$305)&lt;ROW(B273)))))+1)</f>
+        <f>IF(OR(B273="",COUNTIF($B$6:$B273,B273)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R273)+(($R$6:$R$305=R273)*($B$6:$B$305&lt;B273)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24206,7 +24206,7 @@
         <v/>
       </c>
       <c r="S274">
-        <f>IF(OR(B274="",COUNTIF($B$6:$B274,B274)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R274)+(($R$6:$R$305=R274)*(ROW($B$6:$B$305)&lt;ROW(B274)))))+1)</f>
+        <f>IF(OR(B274="",COUNTIF($B$6:$B274,B274)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R274)+(($R$6:$R$305=R274)*($B$6:$B$305&lt;B274)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24228,7 +24228,7 @@
         <v/>
       </c>
       <c r="S275">
-        <f>IF(OR(B275="",COUNTIF($B$6:$B275,B275)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R275)+(($R$6:$R$305=R275)*(ROW($B$6:$B$305)&lt;ROW(B275)))))+1)</f>
+        <f>IF(OR(B275="",COUNTIF($B$6:$B275,B275)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R275)+(($R$6:$R$305=R275)*($B$6:$B$305&lt;B275)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24250,7 +24250,7 @@
         <v/>
       </c>
       <c r="S276">
-        <f>IF(OR(B276="",COUNTIF($B$6:$B276,B276)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R276)+(($R$6:$R$305=R276)*(ROW($B$6:$B$305)&lt;ROW(B276)))))+1)</f>
+        <f>IF(OR(B276="",COUNTIF($B$6:$B276,B276)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R276)+(($R$6:$R$305=R276)*($B$6:$B$305&lt;B276)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24272,7 +24272,7 @@
         <v/>
       </c>
       <c r="S277">
-        <f>IF(OR(B277="",COUNTIF($B$6:$B277,B277)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R277)+(($R$6:$R$305=R277)*(ROW($B$6:$B$305)&lt;ROW(B277)))))+1)</f>
+        <f>IF(OR(B277="",COUNTIF($B$6:$B277,B277)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R277)+(($R$6:$R$305=R277)*($B$6:$B$305&lt;B277)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24294,7 +24294,7 @@
         <v/>
       </c>
       <c r="S278">
-        <f>IF(OR(B278="",COUNTIF($B$6:$B278,B278)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R278)+(($R$6:$R$305=R278)*(ROW($B$6:$B$305)&lt;ROW(B278)))))+1)</f>
+        <f>IF(OR(B278="",COUNTIF($B$6:$B278,B278)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R278)+(($R$6:$R$305=R278)*($B$6:$B$305&lt;B278)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24316,7 +24316,7 @@
         <v/>
       </c>
       <c r="S279">
-        <f>IF(OR(B279="",COUNTIF($B$6:$B279,B279)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R279)+(($R$6:$R$305=R279)*(ROW($B$6:$B$305)&lt;ROW(B279)))))+1)</f>
+        <f>IF(OR(B279="",COUNTIF($B$6:$B279,B279)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R279)+(($R$6:$R$305=R279)*($B$6:$B$305&lt;B279)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24338,7 +24338,7 @@
         <v/>
       </c>
       <c r="S280">
-        <f>IF(OR(B280="",COUNTIF($B$6:$B280,B280)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R280)+(($R$6:$R$305=R280)*(ROW($B$6:$B$305)&lt;ROW(B280)))))+1)</f>
+        <f>IF(OR(B280="",COUNTIF($B$6:$B280,B280)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R280)+(($R$6:$R$305=R280)*($B$6:$B$305&lt;B280)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24360,7 +24360,7 @@
         <v/>
       </c>
       <c r="S281">
-        <f>IF(OR(B281="",COUNTIF($B$6:$B281,B281)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R281)+(($R$6:$R$305=R281)*(ROW($B$6:$B$305)&lt;ROW(B281)))))+1)</f>
+        <f>IF(OR(B281="",COUNTIF($B$6:$B281,B281)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R281)+(($R$6:$R$305=R281)*($B$6:$B$305&lt;B281)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24382,7 +24382,7 @@
         <v/>
       </c>
       <c r="S282">
-        <f>IF(OR(B282="",COUNTIF($B$6:$B282,B282)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R282)+(($R$6:$R$305=R282)*(ROW($B$6:$B$305)&lt;ROW(B282)))))+1)</f>
+        <f>IF(OR(B282="",COUNTIF($B$6:$B282,B282)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R282)+(($R$6:$R$305=R282)*($B$6:$B$305&lt;B282)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24404,7 +24404,7 @@
         <v/>
       </c>
       <c r="S283">
-        <f>IF(OR(B283="",COUNTIF($B$6:$B283,B283)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R283)+(($R$6:$R$305=R283)*(ROW($B$6:$B$305)&lt;ROW(B283)))))+1)</f>
+        <f>IF(OR(B283="",COUNTIF($B$6:$B283,B283)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R283)+(($R$6:$R$305=R283)*($B$6:$B$305&lt;B283)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24426,7 +24426,7 @@
         <v/>
       </c>
       <c r="S284">
-        <f>IF(OR(B284="",COUNTIF($B$6:$B284,B284)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R284)+(($R$6:$R$305=R284)*(ROW($B$6:$B$305)&lt;ROW(B284)))))+1)</f>
+        <f>IF(OR(B284="",COUNTIF($B$6:$B284,B284)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R284)+(($R$6:$R$305=R284)*($B$6:$B$305&lt;B284)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24448,7 +24448,7 @@
         <v/>
       </c>
       <c r="S285">
-        <f>IF(OR(B285="",COUNTIF($B$6:$B285,B285)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R285)+(($R$6:$R$305=R285)*(ROW($B$6:$B$305)&lt;ROW(B285)))))+1)</f>
+        <f>IF(OR(B285="",COUNTIF($B$6:$B285,B285)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R285)+(($R$6:$R$305=R285)*($B$6:$B$305&lt;B285)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24470,7 +24470,7 @@
         <v/>
       </c>
       <c r="S286">
-        <f>IF(OR(B286="",COUNTIF($B$6:$B286,B286)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R286)+(($R$6:$R$305=R286)*(ROW($B$6:$B$305)&lt;ROW(B286)))))+1)</f>
+        <f>IF(OR(B286="",COUNTIF($B$6:$B286,B286)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R286)+(($R$6:$R$305=R286)*($B$6:$B$305&lt;B286)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24492,7 +24492,7 @@
         <v/>
       </c>
       <c r="S287">
-        <f>IF(OR(B287="",COUNTIF($B$6:$B287,B287)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R287)+(($R$6:$R$305=R287)*(ROW($B$6:$B$305)&lt;ROW(B287)))))+1)</f>
+        <f>IF(OR(B287="",COUNTIF($B$6:$B287,B287)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R287)+(($R$6:$R$305=R287)*($B$6:$B$305&lt;B287)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
         <v/>
       </c>
       <c r="S288">
-        <f>IF(OR(B288="",COUNTIF($B$6:$B288,B288)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R288)+(($R$6:$R$305=R288)*(ROW($B$6:$B$305)&lt;ROW(B288)))))+1)</f>
+        <f>IF(OR(B288="",COUNTIF($B$6:$B288,B288)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R288)+(($R$6:$R$305=R288)*($B$6:$B$305&lt;B288)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24536,7 +24536,7 @@
         <v/>
       </c>
       <c r="S289">
-        <f>IF(OR(B289="",COUNTIF($B$6:$B289,B289)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R289)+(($R$6:$R$305=R289)*(ROW($B$6:$B$305)&lt;ROW(B289)))))+1)</f>
+        <f>IF(OR(B289="",COUNTIF($B$6:$B289,B289)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R289)+(($R$6:$R$305=R289)*($B$6:$B$305&lt;B289)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24558,7 +24558,7 @@
         <v/>
       </c>
       <c r="S290">
-        <f>IF(OR(B290="",COUNTIF($B$6:$B290,B290)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R290)+(($R$6:$R$305=R290)*(ROW($B$6:$B$305)&lt;ROW(B290)))))+1)</f>
+        <f>IF(OR(B290="",COUNTIF($B$6:$B290,B290)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R290)+(($R$6:$R$305=R290)*($B$6:$B$305&lt;B290)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24580,7 +24580,7 @@
         <v/>
       </c>
       <c r="S291">
-        <f>IF(OR(B291="",COUNTIF($B$6:$B291,B291)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R291)+(($R$6:$R$305=R291)*(ROW($B$6:$B$305)&lt;ROW(B291)))))+1)</f>
+        <f>IF(OR(B291="",COUNTIF($B$6:$B291,B291)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R291)+(($R$6:$R$305=R291)*($B$6:$B$305&lt;B291)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24602,7 +24602,7 @@
         <v/>
       </c>
       <c r="S292">
-        <f>IF(OR(B292="",COUNTIF($B$6:$B292,B292)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R292)+(($R$6:$R$305=R292)*(ROW($B$6:$B$305)&lt;ROW(B292)))))+1)</f>
+        <f>IF(OR(B292="",COUNTIF($B$6:$B292,B292)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R292)+(($R$6:$R$305=R292)*($B$6:$B$305&lt;B292)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
         <v/>
       </c>
       <c r="S293">
-        <f>IF(OR(B293="",COUNTIF($B$6:$B293,B293)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R293)+(($R$6:$R$305=R293)*(ROW($B$6:$B$305)&lt;ROW(B293)))))+1)</f>
+        <f>IF(OR(B293="",COUNTIF($B$6:$B293,B293)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R293)+(($R$6:$R$305=R293)*($B$6:$B$305&lt;B293)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24646,7 +24646,7 @@
         <v/>
       </c>
       <c r="S294">
-        <f>IF(OR(B294="",COUNTIF($B$6:$B294,B294)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R294)+(($R$6:$R$305=R294)*(ROW($B$6:$B$305)&lt;ROW(B294)))))+1)</f>
+        <f>IF(OR(B294="",COUNTIF($B$6:$B294,B294)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R294)+(($R$6:$R$305=R294)*($B$6:$B$305&lt;B294)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24668,7 +24668,7 @@
         <v/>
       </c>
       <c r="S295">
-        <f>IF(OR(B295="",COUNTIF($B$6:$B295,B295)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R295)+(($R$6:$R$305=R295)*(ROW($B$6:$B$305)&lt;ROW(B295)))))+1)</f>
+        <f>IF(OR(B295="",COUNTIF($B$6:$B295,B295)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R295)+(($R$6:$R$305=R295)*($B$6:$B$305&lt;B295)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
         <v/>
       </c>
       <c r="S296">
-        <f>IF(OR(B296="",COUNTIF($B$6:$B296,B296)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R296)+(($R$6:$R$305=R296)*(ROW($B$6:$B$305)&lt;ROW(B296)))))+1)</f>
+        <f>IF(OR(B296="",COUNTIF($B$6:$B296,B296)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R296)+(($R$6:$R$305=R296)*($B$6:$B$305&lt;B296)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24712,7 +24712,7 @@
         <v/>
       </c>
       <c r="S297">
-        <f>IF(OR(B297="",COUNTIF($B$6:$B297,B297)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R297)+(($R$6:$R$305=R297)*(ROW($B$6:$B$305)&lt;ROW(B297)))))+1)</f>
+        <f>IF(OR(B297="",COUNTIF($B$6:$B297,B297)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R297)+(($R$6:$R$305=R297)*($B$6:$B$305&lt;B297)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24734,7 +24734,7 @@
         <v/>
       </c>
       <c r="S298">
-        <f>IF(OR(B298="",COUNTIF($B$6:$B298,B298)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R298)+(($R$6:$R$305=R298)*(ROW($B$6:$B$305)&lt;ROW(B298)))))+1)</f>
+        <f>IF(OR(B298="",COUNTIF($B$6:$B298,B298)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R298)+(($R$6:$R$305=R298)*($B$6:$B$305&lt;B298)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24756,7 +24756,7 @@
         <v/>
       </c>
       <c r="S299">
-        <f>IF(OR(B299="",COUNTIF($B$6:$B299,B299)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R299)+(($R$6:$R$305=R299)*(ROW($B$6:$B$305)&lt;ROW(B299)))))+1)</f>
+        <f>IF(OR(B299="",COUNTIF($B$6:$B299,B299)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R299)+(($R$6:$R$305=R299)*($B$6:$B$305&lt;B299)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
         <v/>
       </c>
       <c r="S300">
-        <f>IF(OR(B300="",COUNTIF($B$6:$B300,B300)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R300)+(($R$6:$R$305=R300)*(ROW($B$6:$B$305)&lt;ROW(B300)))))+1)</f>
+        <f>IF(OR(B300="",COUNTIF($B$6:$B300,B300)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R300)+(($R$6:$R$305=R300)*($B$6:$B$305&lt;B300)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24800,7 +24800,7 @@
         <v/>
       </c>
       <c r="S301">
-        <f>IF(OR(B301="",COUNTIF($B$6:$B301,B301)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R301)+(($R$6:$R$305=R301)*(ROW($B$6:$B$305)&lt;ROW(B301)))))+1)</f>
+        <f>IF(OR(B301="",COUNTIF($B$6:$B301,B301)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R301)+(($R$6:$R$305=R301)*($B$6:$B$305&lt;B301)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24822,7 +24822,7 @@
         <v/>
       </c>
       <c r="S302">
-        <f>IF(OR(B302="",COUNTIF($B$6:$B302,B302)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R302)+(($R$6:$R$305=R302)*(ROW($B$6:$B$305)&lt;ROW(B302)))))+1)</f>
+        <f>IF(OR(B302="",COUNTIF($B$6:$B302,B302)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R302)+(($R$6:$R$305=R302)*($B$6:$B$305&lt;B302)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24844,7 +24844,7 @@
         <v/>
       </c>
       <c r="S303">
-        <f>IF(OR(B303="",COUNTIF($B$6:$B303,B303)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R303)+(($R$6:$R$305=R303)*(ROW($B$6:$B$305)&lt;ROW(B303)))))+1)</f>
+        <f>IF(OR(B303="",COUNTIF($B$6:$B303,B303)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R303)+(($R$6:$R$305=R303)*($B$6:$B$305&lt;B303)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
         <v/>
       </c>
       <c r="S304">
-        <f>IF(OR(B304="",COUNTIF($B$6:$B304,B304)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R304)+(($R$6:$R$305=R304)*(ROW($B$6:$B$305)&lt;ROW(B304)))))+1)</f>
+        <f>IF(OR(B304="",COUNTIF($B$6:$B304,B304)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R304)+(($R$6:$R$305=R304)*($B$6:$B$305&lt;B304)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>
@@ -24888,7 +24888,7 @@
         <v/>
       </c>
       <c r="S305">
-        <f>IF(OR(B305="",COUNTIF($B$6:$B305,B305)&gt;1),"",SUMPRODUCT((MATCH($B$6:$B$305,$B$6:$B$305,0)=ROW($B$6:$B$305)-ROW($B$5))*($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R305)+(($R$6:$R$305=R305)*(ROW($B$6:$B$305)&lt;ROW(B305)))))+1)</f>
+        <f>IF(OR(B305="",COUNTIF($B$6:$B305,B305)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R305)+(($R$6:$R$305=R305)*($B$6:$B$305&lt;B305)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
         <v/>
       </c>
     </row>

--- a/WorldCup2026_Sweepstake.xlsx
+++ b/WorldCup2026_Sweepstake.xlsx
@@ -15528,19 +15528,19 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(B6="","",B6)</f>
+        <f>IF(OR(B6="",COUNTIF($B$6:$B6,B6)&gt;1),"",B6)</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF(C6="","",C6)</f>
+        <f>IF(P6="","",C6)</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF(B6="","",SUMIF($B$6:$B$305,B6,$D$6:$D$305))</f>
+        <f>IF(P6="","",SUMIF($B$6:$B$305,B6,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S6">
-        <f>IF(OR(B6="",COUNTIF($B$6:$B6,B6)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R6)+(($R$6:$R$305=R6)*($B$6:$B$305&lt;B6)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P6="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R6,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R6,"="&amp;R6,$P$6:$P6,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T6">
@@ -15596,19 +15596,19 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(B7="","",B7)</f>
+        <f>IF(OR(B7="",COUNTIF($B$6:$B7,B7)&gt;1),"",B7)</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF(C7="","",C7)</f>
+        <f>IF(P7="","",C7)</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF(B7="","",SUMIF($B$6:$B$305,B7,$D$6:$D$305))</f>
+        <f>IF(P7="","",SUMIF($B$6:$B$305,B7,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S7">
-        <f>IF(OR(B7="",COUNTIF($B$6:$B7,B7)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R7)+(($R$6:$R$305=R7)*($B$6:$B$305&lt;B7)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P7="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R7,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R7,"="&amp;R7,$P$6:$P7,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T7">
@@ -15664,19 +15664,19 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(B8="","",B8)</f>
+        <f>IF(OR(B8="",COUNTIF($B$6:$B8,B8)&gt;1),"",B8)</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF(C8="","",C8)</f>
+        <f>IF(P8="","",C8)</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF(B8="","",SUMIF($B$6:$B$305,B8,$D$6:$D$305))</f>
+        <f>IF(P8="","",SUMIF($B$6:$B$305,B8,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S8">
-        <f>IF(OR(B8="",COUNTIF($B$6:$B8,B8)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R8)+(($R$6:$R$305=R8)*($B$6:$B$305&lt;B8)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P8="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R8,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R8,"="&amp;R8,$P$6:$P8,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T8">
@@ -15732,19 +15732,19 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(B9="","",B9)</f>
+        <f>IF(OR(B9="",COUNTIF($B$6:$B9,B9)&gt;1),"",B9)</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF(C9="","",C9)</f>
+        <f>IF(P9="","",C9)</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF(B9="","",SUMIF($B$6:$B$305,B9,$D$6:$D$305))</f>
+        <f>IF(P9="","",SUMIF($B$6:$B$305,B9,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S9">
-        <f>IF(OR(B9="",COUNTIF($B$6:$B9,B9)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R9)+(($R$6:$R$305=R9)*($B$6:$B$305&lt;B9)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P9="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R9,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R9,"="&amp;R9,$P$6:$P9,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T9">
@@ -15800,19 +15800,19 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(B10="","",B10)</f>
+        <f>IF(OR(B10="",COUNTIF($B$6:$B10,B10)&gt;1),"",B10)</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF(C10="","",C10)</f>
+        <f>IF(P10="","",C10)</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF(B10="","",SUMIF($B$6:$B$305,B10,$D$6:$D$305))</f>
+        <f>IF(P10="","",SUMIF($B$6:$B$305,B10,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S10">
-        <f>IF(OR(B10="",COUNTIF($B$6:$B10,B10)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R10)+(($R$6:$R$305=R10)*($B$6:$B$305&lt;B10)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P10="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R10,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R10,"="&amp;R10,$P$6:$P10,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T10">
@@ -15868,19 +15868,19 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(B11="","",B11)</f>
+        <f>IF(OR(B11="",COUNTIF($B$6:$B11,B11)&gt;1),"",B11)</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF(C11="","",C11)</f>
+        <f>IF(P11="","",C11)</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF(B11="","",SUMIF($B$6:$B$305,B11,$D$6:$D$305))</f>
+        <f>IF(P11="","",SUMIF($B$6:$B$305,B11,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S11">
-        <f>IF(OR(B11="",COUNTIF($B$6:$B11,B11)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R11)+(($R$6:$R$305=R11)*($B$6:$B$305&lt;B11)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P11="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R11,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R11,"="&amp;R11,$P$6:$P11,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T11">
@@ -15936,19 +15936,19 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(B12="","",B12)</f>
+        <f>IF(OR(B12="",COUNTIF($B$6:$B12,B12)&gt;1),"",B12)</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF(C12="","",C12)</f>
+        <f>IF(P12="","",C12)</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF(B12="","",SUMIF($B$6:$B$305,B12,$D$6:$D$305))</f>
+        <f>IF(P12="","",SUMIF($B$6:$B$305,B12,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S12">
-        <f>IF(OR(B12="",COUNTIF($B$6:$B12,B12)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R12)+(($R$6:$R$305=R12)*($B$6:$B$305&lt;B12)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P12="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R12,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R12,"="&amp;R12,$P$6:$P12,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T12">
@@ -16004,19 +16004,19 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(B13="","",B13)</f>
+        <f>IF(OR(B13="",COUNTIF($B$6:$B13,B13)&gt;1),"",B13)</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF(C13="","",C13)</f>
+        <f>IF(P13="","",C13)</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF(B13="","",SUMIF($B$6:$B$305,B13,$D$6:$D$305))</f>
+        <f>IF(P13="","",SUMIF($B$6:$B$305,B13,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S13">
-        <f>IF(OR(B13="",COUNTIF($B$6:$B13,B13)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R13)+(($R$6:$R$305=R13)*($B$6:$B$305&lt;B13)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P13="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R13,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R13,"="&amp;R13,$P$6:$P13,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T13">
@@ -16072,19 +16072,19 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(B14="","",B14)</f>
+        <f>IF(OR(B14="",COUNTIF($B$6:$B14,B14)&gt;1),"",B14)</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF(C14="","",C14)</f>
+        <f>IF(P14="","",C14)</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF(B14="","",SUMIF($B$6:$B$305,B14,$D$6:$D$305))</f>
+        <f>IF(P14="","",SUMIF($B$6:$B$305,B14,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S14">
-        <f>IF(OR(B14="",COUNTIF($B$6:$B14,B14)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R14)+(($R$6:$R$305=R14)*($B$6:$B$305&lt;B14)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P14="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R14,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R14,"="&amp;R14,$P$6:$P14,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T14">
@@ -16140,19 +16140,19 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(B15="","",B15)</f>
+        <f>IF(OR(B15="",COUNTIF($B$6:$B15,B15)&gt;1),"",B15)</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF(C15="","",C15)</f>
+        <f>IF(P15="","",C15)</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF(B15="","",SUMIF($B$6:$B$305,B15,$D$6:$D$305))</f>
+        <f>IF(P15="","",SUMIF($B$6:$B$305,B15,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S15">
-        <f>IF(OR(B15="",COUNTIF($B$6:$B15,B15)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R15)+(($R$6:$R$305=R15)*($B$6:$B$305&lt;B15)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P15="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R15,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R15,"="&amp;R15,$P$6:$P15,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T15">
@@ -16208,19 +16208,19 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(B16="","",B16)</f>
+        <f>IF(OR(B16="",COUNTIF($B$6:$B16,B16)&gt;1),"",B16)</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF(C16="","",C16)</f>
+        <f>IF(P16="","",C16)</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF(B16="","",SUMIF($B$6:$B$305,B16,$D$6:$D$305))</f>
+        <f>IF(P16="","",SUMIF($B$6:$B$305,B16,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S16">
-        <f>IF(OR(B16="",COUNTIF($B$6:$B16,B16)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R16)+(($R$6:$R$305=R16)*($B$6:$B$305&lt;B16)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P16="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R16,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R16,"="&amp;R16,$P$6:$P16,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T16">
@@ -16276,19 +16276,19 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(B17="","",B17)</f>
+        <f>IF(OR(B17="",COUNTIF($B$6:$B17,B17)&gt;1),"",B17)</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF(C17="","",C17)</f>
+        <f>IF(P17="","",C17)</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF(B17="","",SUMIF($B$6:$B$305,B17,$D$6:$D$305))</f>
+        <f>IF(P17="","",SUMIF($B$6:$B$305,B17,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S17">
-        <f>IF(OR(B17="",COUNTIF($B$6:$B17,B17)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R17)+(($R$6:$R$305=R17)*($B$6:$B$305&lt;B17)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P17="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R17,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R17,"="&amp;R17,$P$6:$P17,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T17">
@@ -16344,19 +16344,19 @@
         <v/>
       </c>
       <c r="P18">
-        <f>IF(B18="","",B18)</f>
+        <f>IF(OR(B18="",COUNTIF($B$6:$B18,B18)&gt;1),"",B18)</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF(C18="","",C18)</f>
+        <f>IF(P18="","",C18)</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF(B18="","",SUMIF($B$6:$B$305,B18,$D$6:$D$305))</f>
+        <f>IF(P18="","",SUMIF($B$6:$B$305,B18,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S18">
-        <f>IF(OR(B18="",COUNTIF($B$6:$B18,B18)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R18)+(($R$6:$R$305=R18)*($B$6:$B$305&lt;B18)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P18="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R18,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R18,"="&amp;R18,$P$6:$P18,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T18">
@@ -16412,19 +16412,19 @@
         <v/>
       </c>
       <c r="P19">
-        <f>IF(B19="","",B19)</f>
+        <f>IF(OR(B19="",COUNTIF($B$6:$B19,B19)&gt;1),"",B19)</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF(C19="","",C19)</f>
+        <f>IF(P19="","",C19)</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF(B19="","",SUMIF($B$6:$B$305,B19,$D$6:$D$305))</f>
+        <f>IF(P19="","",SUMIF($B$6:$B$305,B19,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S19">
-        <f>IF(OR(B19="",COUNTIF($B$6:$B19,B19)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R19)+(($R$6:$R$305=R19)*($B$6:$B$305&lt;B19)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P19="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R19,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R19,"="&amp;R19,$P$6:$P19,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T19">
@@ -16480,19 +16480,19 @@
         <v/>
       </c>
       <c r="P20">
-        <f>IF(B20="","",B20)</f>
+        <f>IF(OR(B20="",COUNTIF($B$6:$B20,B20)&gt;1),"",B20)</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF(C20="","",C20)</f>
+        <f>IF(P20="","",C20)</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF(B20="","",SUMIF($B$6:$B$305,B20,$D$6:$D$305))</f>
+        <f>IF(P20="","",SUMIF($B$6:$B$305,B20,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S20">
-        <f>IF(OR(B20="",COUNTIF($B$6:$B20,B20)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R20)+(($R$6:$R$305=R20)*($B$6:$B$305&lt;B20)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P20="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R20,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R20,"="&amp;R20,$P$6:$P20,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T20">
@@ -16548,19 +16548,19 @@
         <v/>
       </c>
       <c r="P21">
-        <f>IF(B21="","",B21)</f>
+        <f>IF(OR(B21="",COUNTIF($B$6:$B21,B21)&gt;1),"",B21)</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF(C21="","",C21)</f>
+        <f>IF(P21="","",C21)</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF(B21="","",SUMIF($B$6:$B$305,B21,$D$6:$D$305))</f>
+        <f>IF(P21="","",SUMIF($B$6:$B$305,B21,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S21">
-        <f>IF(OR(B21="",COUNTIF($B$6:$B21,B21)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R21)+(($R$6:$R$305=R21)*($B$6:$B$305&lt;B21)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P21="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R21,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R21,"="&amp;R21,$P$6:$P21,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T21">
@@ -16616,19 +16616,19 @@
         <v/>
       </c>
       <c r="P22">
-        <f>IF(B22="","",B22)</f>
+        <f>IF(OR(B22="",COUNTIF($B$6:$B22,B22)&gt;1),"",B22)</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF(C22="","",C22)</f>
+        <f>IF(P22="","",C22)</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF(B22="","",SUMIF($B$6:$B$305,B22,$D$6:$D$305))</f>
+        <f>IF(P22="","",SUMIF($B$6:$B$305,B22,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S22">
-        <f>IF(OR(B22="",COUNTIF($B$6:$B22,B22)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R22)+(($R$6:$R$305=R22)*($B$6:$B$305&lt;B22)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P22="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R22,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R22,"="&amp;R22,$P$6:$P22,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T22">
@@ -16684,19 +16684,19 @@
         <v/>
       </c>
       <c r="P23">
-        <f>IF(B23="","",B23)</f>
+        <f>IF(OR(B23="",COUNTIF($B$6:$B23,B23)&gt;1),"",B23)</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF(C23="","",C23)</f>
+        <f>IF(P23="","",C23)</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF(B23="","",SUMIF($B$6:$B$305,B23,$D$6:$D$305))</f>
+        <f>IF(P23="","",SUMIF($B$6:$B$305,B23,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S23">
-        <f>IF(OR(B23="",COUNTIF($B$6:$B23,B23)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R23)+(($R$6:$R$305=R23)*($B$6:$B$305&lt;B23)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P23="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R23,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R23,"="&amp;R23,$P$6:$P23,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T23">
@@ -16752,19 +16752,19 @@
         <v/>
       </c>
       <c r="P24">
-        <f>IF(B24="","",B24)</f>
+        <f>IF(OR(B24="",COUNTIF($B$6:$B24,B24)&gt;1),"",B24)</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF(C24="","",C24)</f>
+        <f>IF(P24="","",C24)</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF(B24="","",SUMIF($B$6:$B$305,B24,$D$6:$D$305))</f>
+        <f>IF(P24="","",SUMIF($B$6:$B$305,B24,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S24">
-        <f>IF(OR(B24="",COUNTIF($B$6:$B24,B24)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R24)+(($R$6:$R$305=R24)*($B$6:$B$305&lt;B24)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P24="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R24,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R24,"="&amp;R24,$P$6:$P24,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T24">
@@ -16820,19 +16820,19 @@
         <v/>
       </c>
       <c r="P25">
-        <f>IF(B25="","",B25)</f>
+        <f>IF(OR(B25="",COUNTIF($B$6:$B25,B25)&gt;1),"",B25)</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF(C25="","",C25)</f>
+        <f>IF(P25="","",C25)</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF(B25="","",SUMIF($B$6:$B$305,B25,$D$6:$D$305))</f>
+        <f>IF(P25="","",SUMIF($B$6:$B$305,B25,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S25">
-        <f>IF(OR(B25="",COUNTIF($B$6:$B25,B25)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R25)+(($R$6:$R$305=R25)*($B$6:$B$305&lt;B25)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P25="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R25,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R25,"="&amp;R25,$P$6:$P25,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T25">
@@ -16888,19 +16888,19 @@
         <v/>
       </c>
       <c r="P26">
-        <f>IF(B26="","",B26)</f>
+        <f>IF(OR(B26="",COUNTIF($B$6:$B26,B26)&gt;1),"",B26)</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF(C26="","",C26)</f>
+        <f>IF(P26="","",C26)</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF(B26="","",SUMIF($B$6:$B$305,B26,$D$6:$D$305))</f>
+        <f>IF(P26="","",SUMIF($B$6:$B$305,B26,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S26">
-        <f>IF(OR(B26="",COUNTIF($B$6:$B26,B26)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R26)+(($R$6:$R$305=R26)*($B$6:$B$305&lt;B26)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P26="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R26,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R26,"="&amp;R26,$P$6:$P26,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T26">
@@ -16956,19 +16956,19 @@
         <v/>
       </c>
       <c r="P27">
-        <f>IF(B27="","",B27)</f>
+        <f>IF(OR(B27="",COUNTIF($B$6:$B27,B27)&gt;1),"",B27)</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF(C27="","",C27)</f>
+        <f>IF(P27="","",C27)</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF(B27="","",SUMIF($B$6:$B$305,B27,$D$6:$D$305))</f>
+        <f>IF(P27="","",SUMIF($B$6:$B$305,B27,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S27">
-        <f>IF(OR(B27="",COUNTIF($B$6:$B27,B27)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R27)+(($R$6:$R$305=R27)*($B$6:$B$305&lt;B27)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P27="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R27,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R27,"="&amp;R27,$P$6:$P27,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T27">
@@ -17024,19 +17024,19 @@
         <v/>
       </c>
       <c r="P28">
-        <f>IF(B28="","",B28)</f>
+        <f>IF(OR(B28="",COUNTIF($B$6:$B28,B28)&gt;1),"",B28)</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF(C28="","",C28)</f>
+        <f>IF(P28="","",C28)</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF(B28="","",SUMIF($B$6:$B$305,B28,$D$6:$D$305))</f>
+        <f>IF(P28="","",SUMIF($B$6:$B$305,B28,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S28">
-        <f>IF(OR(B28="",COUNTIF($B$6:$B28,B28)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R28)+(($R$6:$R$305=R28)*($B$6:$B$305&lt;B28)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P28="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R28,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R28,"="&amp;R28,$P$6:$P28,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T28">
@@ -17092,19 +17092,19 @@
         <v/>
       </c>
       <c r="P29">
-        <f>IF(B29="","",B29)</f>
+        <f>IF(OR(B29="",COUNTIF($B$6:$B29,B29)&gt;1),"",B29)</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF(C29="","",C29)</f>
+        <f>IF(P29="","",C29)</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF(B29="","",SUMIF($B$6:$B$305,B29,$D$6:$D$305))</f>
+        <f>IF(P29="","",SUMIF($B$6:$B$305,B29,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S29">
-        <f>IF(OR(B29="",COUNTIF($B$6:$B29,B29)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R29)+(($R$6:$R$305=R29)*($B$6:$B$305&lt;B29)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P29="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R29,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R29,"="&amp;R29,$P$6:$P29,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T29">
@@ -17160,19 +17160,19 @@
         <v/>
       </c>
       <c r="P30">
-        <f>IF(B30="","",B30)</f>
+        <f>IF(OR(B30="",COUNTIF($B$6:$B30,B30)&gt;1),"",B30)</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF(C30="","",C30)</f>
+        <f>IF(P30="","",C30)</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF(B30="","",SUMIF($B$6:$B$305,B30,$D$6:$D$305))</f>
+        <f>IF(P30="","",SUMIF($B$6:$B$305,B30,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S30">
-        <f>IF(OR(B30="",COUNTIF($B$6:$B30,B30)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R30)+(($R$6:$R$305=R30)*($B$6:$B$305&lt;B30)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P30="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R30,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R30,"="&amp;R30,$P$6:$P30,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T30">
@@ -17228,19 +17228,19 @@
         <v/>
       </c>
       <c r="P31">
-        <f>IF(B31="","",B31)</f>
+        <f>IF(OR(B31="",COUNTIF($B$6:$B31,B31)&gt;1),"",B31)</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF(C31="","",C31)</f>
+        <f>IF(P31="","",C31)</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF(B31="","",SUMIF($B$6:$B$305,B31,$D$6:$D$305))</f>
+        <f>IF(P31="","",SUMIF($B$6:$B$305,B31,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S31">
-        <f>IF(OR(B31="",COUNTIF($B$6:$B31,B31)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R31)+(($R$6:$R$305=R31)*($B$6:$B$305&lt;B31)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P31="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R31,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R31,"="&amp;R31,$P$6:$P31,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T31">
@@ -17296,19 +17296,19 @@
         <v/>
       </c>
       <c r="P32">
-        <f>IF(B32="","",B32)</f>
+        <f>IF(OR(B32="",COUNTIF($B$6:$B32,B32)&gt;1),"",B32)</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF(C32="","",C32)</f>
+        <f>IF(P32="","",C32)</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF(B32="","",SUMIF($B$6:$B$305,B32,$D$6:$D$305))</f>
+        <f>IF(P32="","",SUMIF($B$6:$B$305,B32,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S32">
-        <f>IF(OR(B32="",COUNTIF($B$6:$B32,B32)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R32)+(($R$6:$R$305=R32)*($B$6:$B$305&lt;B32)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P32="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R32,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R32,"="&amp;R32,$P$6:$P32,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T32">
@@ -17364,19 +17364,19 @@
         <v/>
       </c>
       <c r="P33">
-        <f>IF(B33="","",B33)</f>
+        <f>IF(OR(B33="",COUNTIF($B$6:$B33,B33)&gt;1),"",B33)</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF(C33="","",C33)</f>
+        <f>IF(P33="","",C33)</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF(B33="","",SUMIF($B$6:$B$305,B33,$D$6:$D$305))</f>
+        <f>IF(P33="","",SUMIF($B$6:$B$305,B33,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S33">
-        <f>IF(OR(B33="",COUNTIF($B$6:$B33,B33)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R33)+(($R$6:$R$305=R33)*($B$6:$B$305&lt;B33)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P33="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R33,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R33,"="&amp;R33,$P$6:$P33,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T33">
@@ -17432,19 +17432,19 @@
         <v/>
       </c>
       <c r="P34">
-        <f>IF(B34="","",B34)</f>
+        <f>IF(OR(B34="",COUNTIF($B$6:$B34,B34)&gt;1),"",B34)</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF(C34="","",C34)</f>
+        <f>IF(P34="","",C34)</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF(B34="","",SUMIF($B$6:$B$305,B34,$D$6:$D$305))</f>
+        <f>IF(P34="","",SUMIF($B$6:$B$305,B34,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S34">
-        <f>IF(OR(B34="",COUNTIF($B$6:$B34,B34)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R34)+(($R$6:$R$305=R34)*($B$6:$B$305&lt;B34)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P34="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R34,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R34,"="&amp;R34,$P$6:$P34,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T34">
@@ -17500,19 +17500,19 @@
         <v/>
       </c>
       <c r="P35">
-        <f>IF(B35="","",B35)</f>
+        <f>IF(OR(B35="",COUNTIF($B$6:$B35,B35)&gt;1),"",B35)</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF(C35="","",C35)</f>
+        <f>IF(P35="","",C35)</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF(B35="","",SUMIF($B$6:$B$305,B35,$D$6:$D$305))</f>
+        <f>IF(P35="","",SUMIF($B$6:$B$305,B35,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S35">
-        <f>IF(OR(B35="",COUNTIF($B$6:$B35,B35)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R35)+(($R$6:$R$305=R35)*($B$6:$B$305&lt;B35)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P35="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R35,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R35,"="&amp;R35,$P$6:$P35,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T35">
@@ -17553,19 +17553,19 @@
         <v/>
       </c>
       <c r="P36">
-        <f>IF(B36="","",B36)</f>
+        <f>IF(OR(B36="",COUNTIF($B$6:$B36,B36)&gt;1),"",B36)</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF(C36="","",C36)</f>
+        <f>IF(P36="","",C36)</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF(B36="","",SUMIF($B$6:$B$305,B36,$D$6:$D$305))</f>
+        <f>IF(P36="","",SUMIF($B$6:$B$305,B36,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S36">
-        <f>IF(OR(B36="",COUNTIF($B$6:$B36,B36)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R36)+(($R$6:$R$305=R36)*($B$6:$B$305&lt;B36)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P36="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R36,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R36,"="&amp;R36,$P$6:$P36,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T36">
@@ -17606,19 +17606,19 @@
         <v/>
       </c>
       <c r="P37">
-        <f>IF(B37="","",B37)</f>
+        <f>IF(OR(B37="",COUNTIF($B$6:$B37,B37)&gt;1),"",B37)</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF(C37="","",C37)</f>
+        <f>IF(P37="","",C37)</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF(B37="","",SUMIF($B$6:$B$305,B37,$D$6:$D$305))</f>
+        <f>IF(P37="","",SUMIF($B$6:$B$305,B37,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S37">
-        <f>IF(OR(B37="",COUNTIF($B$6:$B37,B37)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R37)+(($R$6:$R$305=R37)*($B$6:$B$305&lt;B37)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P37="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R37,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R37,"="&amp;R37,$P$6:$P37,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T37">
@@ -17659,19 +17659,19 @@
         <v/>
       </c>
       <c r="P38">
-        <f>IF(B38="","",B38)</f>
+        <f>IF(OR(B38="",COUNTIF($B$6:$B38,B38)&gt;1),"",B38)</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF(C38="","",C38)</f>
+        <f>IF(P38="","",C38)</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF(B38="","",SUMIF($B$6:$B$305,B38,$D$6:$D$305))</f>
+        <f>IF(P38="","",SUMIF($B$6:$B$305,B38,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S38">
-        <f>IF(OR(B38="",COUNTIF($B$6:$B38,B38)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R38)+(($R$6:$R$305=R38)*($B$6:$B$305&lt;B38)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P38="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R38,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R38,"="&amp;R38,$P$6:$P38,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T38">
@@ -17712,19 +17712,19 @@
         <v/>
       </c>
       <c r="P39">
-        <f>IF(B39="","",B39)</f>
+        <f>IF(OR(B39="",COUNTIF($B$6:$B39,B39)&gt;1),"",B39)</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF(C39="","",C39)</f>
+        <f>IF(P39="","",C39)</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF(B39="","",SUMIF($B$6:$B$305,B39,$D$6:$D$305))</f>
+        <f>IF(P39="","",SUMIF($B$6:$B$305,B39,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S39">
-        <f>IF(OR(B39="",COUNTIF($B$6:$B39,B39)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R39)+(($R$6:$R$305=R39)*($B$6:$B$305&lt;B39)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P39="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R39,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R39,"="&amp;R39,$P$6:$P39,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T39">
@@ -17765,19 +17765,19 @@
         <v/>
       </c>
       <c r="P40">
-        <f>IF(B40="","",B40)</f>
+        <f>IF(OR(B40="",COUNTIF($B$6:$B40,B40)&gt;1),"",B40)</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF(C40="","",C40)</f>
+        <f>IF(P40="","",C40)</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF(B40="","",SUMIF($B$6:$B$305,B40,$D$6:$D$305))</f>
+        <f>IF(P40="","",SUMIF($B$6:$B$305,B40,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S40">
-        <f>IF(OR(B40="",COUNTIF($B$6:$B40,B40)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R40)+(($R$6:$R$305=R40)*($B$6:$B$305&lt;B40)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P40="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R40,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R40,"="&amp;R40,$P$6:$P40,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T40">
@@ -17818,19 +17818,19 @@
         <v/>
       </c>
       <c r="P41">
-        <f>IF(B41="","",B41)</f>
+        <f>IF(OR(B41="",COUNTIF($B$6:$B41,B41)&gt;1),"",B41)</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF(C41="","",C41)</f>
+        <f>IF(P41="","",C41)</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF(B41="","",SUMIF($B$6:$B$305,B41,$D$6:$D$305))</f>
+        <f>IF(P41="","",SUMIF($B$6:$B$305,B41,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S41">
-        <f>IF(OR(B41="",COUNTIF($B$6:$B41,B41)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R41)+(($R$6:$R$305=R41)*($B$6:$B$305&lt;B41)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P41="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R41,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R41,"="&amp;R41,$P$6:$P41,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T41">
@@ -17871,19 +17871,19 @@
         <v/>
       </c>
       <c r="P42">
-        <f>IF(B42="","",B42)</f>
+        <f>IF(OR(B42="",COUNTIF($B$6:$B42,B42)&gt;1),"",B42)</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF(C42="","",C42)</f>
+        <f>IF(P42="","",C42)</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF(B42="","",SUMIF($B$6:$B$305,B42,$D$6:$D$305))</f>
+        <f>IF(P42="","",SUMIF($B$6:$B$305,B42,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S42">
-        <f>IF(OR(B42="",COUNTIF($B$6:$B42,B42)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R42)+(($R$6:$R$305=R42)*($B$6:$B$305&lt;B42)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P42="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R42,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R42,"="&amp;R42,$P$6:$P42,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T42">
@@ -17924,19 +17924,19 @@
         <v/>
       </c>
       <c r="P43">
-        <f>IF(B43="","",B43)</f>
+        <f>IF(OR(B43="",COUNTIF($B$6:$B43,B43)&gt;1),"",B43)</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF(C43="","",C43)</f>
+        <f>IF(P43="","",C43)</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF(B43="","",SUMIF($B$6:$B$305,B43,$D$6:$D$305))</f>
+        <f>IF(P43="","",SUMIF($B$6:$B$305,B43,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S43">
-        <f>IF(OR(B43="",COUNTIF($B$6:$B43,B43)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R43)+(($R$6:$R$305=R43)*($B$6:$B$305&lt;B43)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P43="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R43,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R43,"="&amp;R43,$P$6:$P43,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T43">
@@ -17977,19 +17977,19 @@
         <v/>
       </c>
       <c r="P44">
-        <f>IF(B44="","",B44)</f>
+        <f>IF(OR(B44="",COUNTIF($B$6:$B44,B44)&gt;1),"",B44)</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF(C44="","",C44)</f>
+        <f>IF(P44="","",C44)</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF(B44="","",SUMIF($B$6:$B$305,B44,$D$6:$D$305))</f>
+        <f>IF(P44="","",SUMIF($B$6:$B$305,B44,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S44">
-        <f>IF(OR(B44="",COUNTIF($B$6:$B44,B44)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R44)+(($R$6:$R$305=R44)*($B$6:$B$305&lt;B44)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P44="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R44,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R44,"="&amp;R44,$P$6:$P44,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T44">
@@ -18030,19 +18030,19 @@
         <v/>
       </c>
       <c r="P45">
-        <f>IF(B45="","",B45)</f>
+        <f>IF(OR(B45="",COUNTIF($B$6:$B45,B45)&gt;1),"",B45)</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF(C45="","",C45)</f>
+        <f>IF(P45="","",C45)</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF(B45="","",SUMIF($B$6:$B$305,B45,$D$6:$D$305))</f>
+        <f>IF(P45="","",SUMIF($B$6:$B$305,B45,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S45">
-        <f>IF(OR(B45="",COUNTIF($B$6:$B45,B45)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R45)+(($R$6:$R$305=R45)*($B$6:$B$305&lt;B45)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P45="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R45,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R45,"="&amp;R45,$P$6:$P45,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T45">
@@ -18083,19 +18083,19 @@
         <v/>
       </c>
       <c r="P46">
-        <f>IF(B46="","",B46)</f>
+        <f>IF(OR(B46="",COUNTIF($B$6:$B46,B46)&gt;1),"",B46)</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF(C46="","",C46)</f>
+        <f>IF(P46="","",C46)</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF(B46="","",SUMIF($B$6:$B$305,B46,$D$6:$D$305))</f>
+        <f>IF(P46="","",SUMIF($B$6:$B$305,B46,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S46">
-        <f>IF(OR(B46="",COUNTIF($B$6:$B46,B46)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R46)+(($R$6:$R$305=R46)*($B$6:$B$305&lt;B46)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P46="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R46,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R46,"="&amp;R46,$P$6:$P46,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T46">
@@ -18136,19 +18136,19 @@
         <v/>
       </c>
       <c r="P47">
-        <f>IF(B47="","",B47)</f>
+        <f>IF(OR(B47="",COUNTIF($B$6:$B47,B47)&gt;1),"",B47)</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF(C47="","",C47)</f>
+        <f>IF(P47="","",C47)</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF(B47="","",SUMIF($B$6:$B$305,B47,$D$6:$D$305))</f>
+        <f>IF(P47="","",SUMIF($B$6:$B$305,B47,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S47">
-        <f>IF(OR(B47="",COUNTIF($B$6:$B47,B47)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R47)+(($R$6:$R$305=R47)*($B$6:$B$305&lt;B47)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P47="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R47,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R47,"="&amp;R47,$P$6:$P47,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T47">
@@ -18189,19 +18189,19 @@
         <v/>
       </c>
       <c r="P48">
-        <f>IF(B48="","",B48)</f>
+        <f>IF(OR(B48="",COUNTIF($B$6:$B48,B48)&gt;1),"",B48)</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF(C48="","",C48)</f>
+        <f>IF(P48="","",C48)</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF(B48="","",SUMIF($B$6:$B$305,B48,$D$6:$D$305))</f>
+        <f>IF(P48="","",SUMIF($B$6:$B$305,B48,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S48">
-        <f>IF(OR(B48="",COUNTIF($B$6:$B48,B48)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R48)+(($R$6:$R$305=R48)*($B$6:$B$305&lt;B48)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P48="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R48,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R48,"="&amp;R48,$P$6:$P48,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T48">
@@ -18242,19 +18242,19 @@
         <v/>
       </c>
       <c r="P49">
-        <f>IF(B49="","",B49)</f>
+        <f>IF(OR(B49="",COUNTIF($B$6:$B49,B49)&gt;1),"",B49)</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF(C49="","",C49)</f>
+        <f>IF(P49="","",C49)</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF(B49="","",SUMIF($B$6:$B$305,B49,$D$6:$D$305))</f>
+        <f>IF(P49="","",SUMIF($B$6:$B$305,B49,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S49">
-        <f>IF(OR(B49="",COUNTIF($B$6:$B49,B49)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R49)+(($R$6:$R$305=R49)*($B$6:$B$305&lt;B49)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P49="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R49,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R49,"="&amp;R49,$P$6:$P49,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T49">
@@ -18295,19 +18295,19 @@
         <v/>
       </c>
       <c r="P50">
-        <f>IF(B50="","",B50)</f>
+        <f>IF(OR(B50="",COUNTIF($B$6:$B50,B50)&gt;1),"",B50)</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF(C50="","",C50)</f>
+        <f>IF(P50="","",C50)</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF(B50="","",SUMIF($B$6:$B$305,B50,$D$6:$D$305))</f>
+        <f>IF(P50="","",SUMIF($B$6:$B$305,B50,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S50">
-        <f>IF(OR(B50="",COUNTIF($B$6:$B50,B50)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R50)+(($R$6:$R$305=R50)*($B$6:$B$305&lt;B50)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P50="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R50,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R50,"="&amp;R50,$P$6:$P50,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T50">
@@ -18348,19 +18348,19 @@
         <v/>
       </c>
       <c r="P51">
-        <f>IF(B51="","",B51)</f>
+        <f>IF(OR(B51="",COUNTIF($B$6:$B51,B51)&gt;1),"",B51)</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF(C51="","",C51)</f>
+        <f>IF(P51="","",C51)</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF(B51="","",SUMIF($B$6:$B$305,B51,$D$6:$D$305))</f>
+        <f>IF(P51="","",SUMIF($B$6:$B$305,B51,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S51">
-        <f>IF(OR(B51="",COUNTIF($B$6:$B51,B51)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R51)+(($R$6:$R$305=R51)*($B$6:$B$305&lt;B51)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P51="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R51,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R51,"="&amp;R51,$P$6:$P51,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T51">
@@ -18401,19 +18401,19 @@
         <v/>
       </c>
       <c r="P52">
-        <f>IF(B52="","",B52)</f>
+        <f>IF(OR(B52="",COUNTIF($B$6:$B52,B52)&gt;1),"",B52)</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF(C52="","",C52)</f>
+        <f>IF(P52="","",C52)</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF(B52="","",SUMIF($B$6:$B$305,B52,$D$6:$D$305))</f>
+        <f>IF(P52="","",SUMIF($B$6:$B$305,B52,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S52">
-        <f>IF(OR(B52="",COUNTIF($B$6:$B52,B52)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R52)+(($R$6:$R$305=R52)*($B$6:$B$305&lt;B52)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P52="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R52,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R52,"="&amp;R52,$P$6:$P52,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T52">
@@ -18454,19 +18454,19 @@
         <v/>
       </c>
       <c r="P53">
-        <f>IF(B53="","",B53)</f>
+        <f>IF(OR(B53="",COUNTIF($B$6:$B53,B53)&gt;1),"",B53)</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF(C53="","",C53)</f>
+        <f>IF(P53="","",C53)</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF(B53="","",SUMIF($B$6:$B$305,B53,$D$6:$D$305))</f>
+        <f>IF(P53="","",SUMIF($B$6:$B$305,B53,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S53">
-        <f>IF(OR(B53="",COUNTIF($B$6:$B53,B53)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R53)+(($R$6:$R$305=R53)*($B$6:$B$305&lt;B53)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P53="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R53,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R53,"="&amp;R53,$P$6:$P53,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T53">
@@ -18507,19 +18507,19 @@
         <v/>
       </c>
       <c r="P54">
-        <f>IF(B54="","",B54)</f>
+        <f>IF(OR(B54="",COUNTIF($B$6:$B54,B54)&gt;1),"",B54)</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF(C54="","",C54)</f>
+        <f>IF(P54="","",C54)</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF(B54="","",SUMIF($B$6:$B$305,B54,$D$6:$D$305))</f>
+        <f>IF(P54="","",SUMIF($B$6:$B$305,B54,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S54">
-        <f>IF(OR(B54="",COUNTIF($B$6:$B54,B54)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R54)+(($R$6:$R$305=R54)*($B$6:$B$305&lt;B54)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P54="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R54,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R54,"="&amp;R54,$P$6:$P54,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T54">
@@ -18560,19 +18560,19 @@
         <v/>
       </c>
       <c r="P55">
-        <f>IF(B55="","",B55)</f>
+        <f>IF(OR(B55="",COUNTIF($B$6:$B55,B55)&gt;1),"",B55)</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF(C55="","",C55)</f>
+        <f>IF(P55="","",C55)</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF(B55="","",SUMIF($B$6:$B$305,B55,$D$6:$D$305))</f>
+        <f>IF(P55="","",SUMIF($B$6:$B$305,B55,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S55">
-        <f>IF(OR(B55="",COUNTIF($B$6:$B55,B55)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R55)+(($R$6:$R$305=R55)*($B$6:$B$305&lt;B55)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P55="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R55,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R55,"="&amp;R55,$P$6:$P55,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T55">
@@ -18598,19 +18598,19 @@
       <c r="C56" s="56" t="n"/>
       <c r="D56" s="43" t="n"/>
       <c r="P56">
-        <f>IF(B56="","",B56)</f>
+        <f>IF(OR(B56="",COUNTIF($B$6:$B56,B56)&gt;1),"",B56)</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF(C56="","",C56)</f>
+        <f>IF(P56="","",C56)</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF(B56="","",SUMIF($B$6:$B$305,B56,$D$6:$D$305))</f>
+        <f>IF(P56="","",SUMIF($B$6:$B$305,B56,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S56">
-        <f>IF(OR(B56="",COUNTIF($B$6:$B56,B56)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R56)+(($R$6:$R$305=R56)*($B$6:$B$305&lt;B56)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P56="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R56,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R56,"="&amp;R56,$P$6:$P56,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T56">
@@ -18636,19 +18636,19 @@
       <c r="C57" s="56" t="n"/>
       <c r="D57" s="43" t="n"/>
       <c r="P57">
-        <f>IF(B57="","",B57)</f>
+        <f>IF(OR(B57="",COUNTIF($B$6:$B57,B57)&gt;1),"",B57)</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF(C57="","",C57)</f>
+        <f>IF(P57="","",C57)</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF(B57="","",SUMIF($B$6:$B$305,B57,$D$6:$D$305))</f>
+        <f>IF(P57="","",SUMIF($B$6:$B$305,B57,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S57">
-        <f>IF(OR(B57="",COUNTIF($B$6:$B57,B57)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R57)+(($R$6:$R$305=R57)*($B$6:$B$305&lt;B57)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P57="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R57,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R57,"="&amp;R57,$P$6:$P57,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T57">
@@ -18674,19 +18674,19 @@
       <c r="C58" s="56" t="n"/>
       <c r="D58" s="43" t="n"/>
       <c r="P58">
-        <f>IF(B58="","",B58)</f>
+        <f>IF(OR(B58="",COUNTIF($B$6:$B58,B58)&gt;1),"",B58)</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF(C58="","",C58)</f>
+        <f>IF(P58="","",C58)</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF(B58="","",SUMIF($B$6:$B$305,B58,$D$6:$D$305))</f>
+        <f>IF(P58="","",SUMIF($B$6:$B$305,B58,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S58">
-        <f>IF(OR(B58="",COUNTIF($B$6:$B58,B58)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R58)+(($R$6:$R$305=R58)*($B$6:$B$305&lt;B58)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P58="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R58,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R58,"="&amp;R58,$P$6:$P58,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T58">
@@ -18712,19 +18712,19 @@
       <c r="C59" s="56" t="n"/>
       <c r="D59" s="43" t="n"/>
       <c r="P59">
-        <f>IF(B59="","",B59)</f>
+        <f>IF(OR(B59="",COUNTIF($B$6:$B59,B59)&gt;1),"",B59)</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF(C59="","",C59)</f>
+        <f>IF(P59="","",C59)</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF(B59="","",SUMIF($B$6:$B$305,B59,$D$6:$D$305))</f>
+        <f>IF(P59="","",SUMIF($B$6:$B$305,B59,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S59">
-        <f>IF(OR(B59="",COUNTIF($B$6:$B59,B59)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R59)+(($R$6:$R$305=R59)*($B$6:$B$305&lt;B59)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P59="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R59,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R59,"="&amp;R59,$P$6:$P59,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T59">
@@ -18750,19 +18750,19 @@
       <c r="C60" s="56" t="n"/>
       <c r="D60" s="43" t="n"/>
       <c r="P60">
-        <f>IF(B60="","",B60)</f>
+        <f>IF(OR(B60="",COUNTIF($B$6:$B60,B60)&gt;1),"",B60)</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF(C60="","",C60)</f>
+        <f>IF(P60="","",C60)</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF(B60="","",SUMIF($B$6:$B$305,B60,$D$6:$D$305))</f>
+        <f>IF(P60="","",SUMIF($B$6:$B$305,B60,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S60">
-        <f>IF(OR(B60="",COUNTIF($B$6:$B60,B60)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R60)+(($R$6:$R$305=R60)*($B$6:$B$305&lt;B60)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P60="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R60,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R60,"="&amp;R60,$P$6:$P60,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T60">
@@ -18788,19 +18788,19 @@
       <c r="C61" s="56" t="n"/>
       <c r="D61" s="43" t="n"/>
       <c r="P61">
-        <f>IF(B61="","",B61)</f>
+        <f>IF(OR(B61="",COUNTIF($B$6:$B61,B61)&gt;1),"",B61)</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF(C61="","",C61)</f>
+        <f>IF(P61="","",C61)</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF(B61="","",SUMIF($B$6:$B$305,B61,$D$6:$D$305))</f>
+        <f>IF(P61="","",SUMIF($B$6:$B$305,B61,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S61">
-        <f>IF(OR(B61="",COUNTIF($B$6:$B61,B61)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R61)+(($R$6:$R$305=R61)*($B$6:$B$305&lt;B61)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P61="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R61,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R61,"="&amp;R61,$P$6:$P61,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T61">
@@ -18826,19 +18826,19 @@
       <c r="C62" s="56" t="n"/>
       <c r="D62" s="43" t="n"/>
       <c r="P62">
-        <f>IF(B62="","",B62)</f>
+        <f>IF(OR(B62="",COUNTIF($B$6:$B62,B62)&gt;1),"",B62)</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF(C62="","",C62)</f>
+        <f>IF(P62="","",C62)</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF(B62="","",SUMIF($B$6:$B$305,B62,$D$6:$D$305))</f>
+        <f>IF(P62="","",SUMIF($B$6:$B$305,B62,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S62">
-        <f>IF(OR(B62="",COUNTIF($B$6:$B62,B62)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R62)+(($R$6:$R$305=R62)*($B$6:$B$305&lt;B62)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P62="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R62,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R62,"="&amp;R62,$P$6:$P62,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T62">
@@ -18864,19 +18864,19 @@
       <c r="C63" s="56" t="n"/>
       <c r="D63" s="43" t="n"/>
       <c r="P63">
-        <f>IF(B63="","",B63)</f>
+        <f>IF(OR(B63="",COUNTIF($B$6:$B63,B63)&gt;1),"",B63)</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF(C63="","",C63)</f>
+        <f>IF(P63="","",C63)</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF(B63="","",SUMIF($B$6:$B$305,B63,$D$6:$D$305))</f>
+        <f>IF(P63="","",SUMIF($B$6:$B$305,B63,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S63">
-        <f>IF(OR(B63="",COUNTIF($B$6:$B63,B63)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R63)+(($R$6:$R$305=R63)*($B$6:$B$305&lt;B63)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P63="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R63,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R63,"="&amp;R63,$P$6:$P63,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T63">
@@ -18902,19 +18902,19 @@
       <c r="C64" s="56" t="n"/>
       <c r="D64" s="43" t="n"/>
       <c r="P64">
-        <f>IF(B64="","",B64)</f>
+        <f>IF(OR(B64="",COUNTIF($B$6:$B64,B64)&gt;1),"",B64)</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF(C64="","",C64)</f>
+        <f>IF(P64="","",C64)</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF(B64="","",SUMIF($B$6:$B$305,B64,$D$6:$D$305))</f>
+        <f>IF(P64="","",SUMIF($B$6:$B$305,B64,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S64">
-        <f>IF(OR(B64="",COUNTIF($B$6:$B64,B64)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R64)+(($R$6:$R$305=R64)*($B$6:$B$305&lt;B64)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P64="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R64,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R64,"="&amp;R64,$P$6:$P64,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T64">
@@ -18940,19 +18940,19 @@
       <c r="C65" s="56" t="n"/>
       <c r="D65" s="43" t="n"/>
       <c r="P65">
-        <f>IF(B65="","",B65)</f>
+        <f>IF(OR(B65="",COUNTIF($B$6:$B65,B65)&gt;1),"",B65)</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF(C65="","",C65)</f>
+        <f>IF(P65="","",C65)</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF(B65="","",SUMIF($B$6:$B$305,B65,$D$6:$D$305))</f>
+        <f>IF(P65="","",SUMIF($B$6:$B$305,B65,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S65">
-        <f>IF(OR(B65="",COUNTIF($B$6:$B65,B65)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R65)+(($R$6:$R$305=R65)*($B$6:$B$305&lt;B65)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P65="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R65,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R65,"="&amp;R65,$P$6:$P65,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T65">
@@ -18978,19 +18978,19 @@
       <c r="C66" s="56" t="n"/>
       <c r="D66" s="43" t="n"/>
       <c r="P66">
-        <f>IF(B66="","",B66)</f>
+        <f>IF(OR(B66="",COUNTIF($B$6:$B66,B66)&gt;1),"",B66)</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF(C66="","",C66)</f>
+        <f>IF(P66="","",C66)</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF(B66="","",SUMIF($B$6:$B$305,B66,$D$6:$D$305))</f>
+        <f>IF(P66="","",SUMIF($B$6:$B$305,B66,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S66">
-        <f>IF(OR(B66="",COUNTIF($B$6:$B66,B66)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R66)+(($R$6:$R$305=R66)*($B$6:$B$305&lt;B66)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P66="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R66,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R66,"="&amp;R66,$P$6:$P66,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T66">
@@ -19016,19 +19016,19 @@
       <c r="C67" s="56" t="n"/>
       <c r="D67" s="43" t="n"/>
       <c r="P67">
-        <f>IF(B67="","",B67)</f>
+        <f>IF(OR(B67="",COUNTIF($B$6:$B67,B67)&gt;1),"",B67)</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF(C67="","",C67)</f>
+        <f>IF(P67="","",C67)</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF(B67="","",SUMIF($B$6:$B$305,B67,$D$6:$D$305))</f>
+        <f>IF(P67="","",SUMIF($B$6:$B$305,B67,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S67">
-        <f>IF(OR(B67="",COUNTIF($B$6:$B67,B67)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R67)+(($R$6:$R$305=R67)*($B$6:$B$305&lt;B67)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P67="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R67,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R67,"="&amp;R67,$P$6:$P67,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T67">
@@ -19054,19 +19054,19 @@
       <c r="C68" s="56" t="n"/>
       <c r="D68" s="43" t="n"/>
       <c r="P68">
-        <f>IF(B68="","",B68)</f>
+        <f>IF(OR(B68="",COUNTIF($B$6:$B68,B68)&gt;1),"",B68)</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF(C68="","",C68)</f>
+        <f>IF(P68="","",C68)</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF(B68="","",SUMIF($B$6:$B$305,B68,$D$6:$D$305))</f>
+        <f>IF(P68="","",SUMIF($B$6:$B$305,B68,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S68">
-        <f>IF(OR(B68="",COUNTIF($B$6:$B68,B68)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R68)+(($R$6:$R$305=R68)*($B$6:$B$305&lt;B68)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P68="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R68,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R68,"="&amp;R68,$P$6:$P68,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T68">
@@ -19092,19 +19092,19 @@
       <c r="C69" s="56" t="n"/>
       <c r="D69" s="43" t="n"/>
       <c r="P69">
-        <f>IF(B69="","",B69)</f>
+        <f>IF(OR(B69="",COUNTIF($B$6:$B69,B69)&gt;1),"",B69)</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF(C69="","",C69)</f>
+        <f>IF(P69="","",C69)</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF(B69="","",SUMIF($B$6:$B$305,B69,$D$6:$D$305))</f>
+        <f>IF(P69="","",SUMIF($B$6:$B$305,B69,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S69">
-        <f>IF(OR(B69="",COUNTIF($B$6:$B69,B69)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R69)+(($R$6:$R$305=R69)*($B$6:$B$305&lt;B69)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P69="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R69,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R69,"="&amp;R69,$P$6:$P69,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T69">
@@ -19130,19 +19130,19 @@
       <c r="C70" s="56" t="n"/>
       <c r="D70" s="43" t="n"/>
       <c r="P70">
-        <f>IF(B70="","",B70)</f>
+        <f>IF(OR(B70="",COUNTIF($B$6:$B70,B70)&gt;1),"",B70)</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF(C70="","",C70)</f>
+        <f>IF(P70="","",C70)</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF(B70="","",SUMIF($B$6:$B$305,B70,$D$6:$D$305))</f>
+        <f>IF(P70="","",SUMIF($B$6:$B$305,B70,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S70">
-        <f>IF(OR(B70="",COUNTIF($B$6:$B70,B70)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R70)+(($R$6:$R$305=R70)*($B$6:$B$305&lt;B70)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P70="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R70,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R70,"="&amp;R70,$P$6:$P70,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T70">
@@ -19168,19 +19168,19 @@
       <c r="C71" s="56" t="n"/>
       <c r="D71" s="43" t="n"/>
       <c r="P71">
-        <f>IF(B71="","",B71)</f>
+        <f>IF(OR(B71="",COUNTIF($B$6:$B71,B71)&gt;1),"",B71)</f>
         <v/>
       </c>
       <c r="Q71">
-        <f>IF(C71="","",C71)</f>
+        <f>IF(P71="","",C71)</f>
         <v/>
       </c>
       <c r="R71">
-        <f>IF(B71="","",SUMIF($B$6:$B$305,B71,$D$6:$D$305))</f>
+        <f>IF(P71="","",SUMIF($B$6:$B$305,B71,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S71">
-        <f>IF(OR(B71="",COUNTIF($B$6:$B71,B71)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R71)+(($R$6:$R$305=R71)*($B$6:$B$305&lt;B71)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P71="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R71,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R71,"="&amp;R71,$P$6:$P71,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T71">
@@ -19206,19 +19206,19 @@
       <c r="C72" s="56" t="n"/>
       <c r="D72" s="43" t="n"/>
       <c r="P72">
-        <f>IF(B72="","",B72)</f>
+        <f>IF(OR(B72="",COUNTIF($B$6:$B72,B72)&gt;1),"",B72)</f>
         <v/>
       </c>
       <c r="Q72">
-        <f>IF(C72="","",C72)</f>
+        <f>IF(P72="","",C72)</f>
         <v/>
       </c>
       <c r="R72">
-        <f>IF(B72="","",SUMIF($B$6:$B$305,B72,$D$6:$D$305))</f>
+        <f>IF(P72="","",SUMIF($B$6:$B$305,B72,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S72">
-        <f>IF(OR(B72="",COUNTIF($B$6:$B72,B72)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R72)+(($R$6:$R$305=R72)*($B$6:$B$305&lt;B72)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P72="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R72,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R72,"="&amp;R72,$P$6:$P72,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T72">
@@ -19244,19 +19244,19 @@
       <c r="C73" s="56" t="n"/>
       <c r="D73" s="43" t="n"/>
       <c r="P73">
-        <f>IF(B73="","",B73)</f>
+        <f>IF(OR(B73="",COUNTIF($B$6:$B73,B73)&gt;1),"",B73)</f>
         <v/>
       </c>
       <c r="Q73">
-        <f>IF(C73="","",C73)</f>
+        <f>IF(P73="","",C73)</f>
         <v/>
       </c>
       <c r="R73">
-        <f>IF(B73="","",SUMIF($B$6:$B$305,B73,$D$6:$D$305))</f>
+        <f>IF(P73="","",SUMIF($B$6:$B$305,B73,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S73">
-        <f>IF(OR(B73="",COUNTIF($B$6:$B73,B73)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R73)+(($R$6:$R$305=R73)*($B$6:$B$305&lt;B73)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P73="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R73,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R73,"="&amp;R73,$P$6:$P73,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T73">
@@ -19282,19 +19282,19 @@
       <c r="C74" s="56" t="n"/>
       <c r="D74" s="43" t="n"/>
       <c r="P74">
-        <f>IF(B74="","",B74)</f>
+        <f>IF(OR(B74="",COUNTIF($B$6:$B74,B74)&gt;1),"",B74)</f>
         <v/>
       </c>
       <c r="Q74">
-        <f>IF(C74="","",C74)</f>
+        <f>IF(P74="","",C74)</f>
         <v/>
       </c>
       <c r="R74">
-        <f>IF(B74="","",SUMIF($B$6:$B$305,B74,$D$6:$D$305))</f>
+        <f>IF(P74="","",SUMIF($B$6:$B$305,B74,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S74">
-        <f>IF(OR(B74="",COUNTIF($B$6:$B74,B74)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R74)+(($R$6:$R$305=R74)*($B$6:$B$305&lt;B74)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P74="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R74,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R74,"="&amp;R74,$P$6:$P74,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T74">
@@ -19320,19 +19320,19 @@
       <c r="C75" s="56" t="n"/>
       <c r="D75" s="43" t="n"/>
       <c r="P75">
-        <f>IF(B75="","",B75)</f>
+        <f>IF(OR(B75="",COUNTIF($B$6:$B75,B75)&gt;1),"",B75)</f>
         <v/>
       </c>
       <c r="Q75">
-        <f>IF(C75="","",C75)</f>
+        <f>IF(P75="","",C75)</f>
         <v/>
       </c>
       <c r="R75">
-        <f>IF(B75="","",SUMIF($B$6:$B$305,B75,$D$6:$D$305))</f>
+        <f>IF(P75="","",SUMIF($B$6:$B$305,B75,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S75">
-        <f>IF(OR(B75="",COUNTIF($B$6:$B75,B75)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R75)+(($R$6:$R$305=R75)*($B$6:$B$305&lt;B75)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P75="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R75,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R75,"="&amp;R75,$P$6:$P75,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T75">
@@ -19358,19 +19358,19 @@
       <c r="C76" s="56" t="n"/>
       <c r="D76" s="43" t="n"/>
       <c r="P76">
-        <f>IF(B76="","",B76)</f>
+        <f>IF(OR(B76="",COUNTIF($B$6:$B76,B76)&gt;1),"",B76)</f>
         <v/>
       </c>
       <c r="Q76">
-        <f>IF(C76="","",C76)</f>
+        <f>IF(P76="","",C76)</f>
         <v/>
       </c>
       <c r="R76">
-        <f>IF(B76="","",SUMIF($B$6:$B$305,B76,$D$6:$D$305))</f>
+        <f>IF(P76="","",SUMIF($B$6:$B$305,B76,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S76">
-        <f>IF(OR(B76="",COUNTIF($B$6:$B76,B76)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R76)+(($R$6:$R$305=R76)*($B$6:$B$305&lt;B76)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P76="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R76,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R76,"="&amp;R76,$P$6:$P76,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T76">
@@ -19396,19 +19396,19 @@
       <c r="C77" s="56" t="n"/>
       <c r="D77" s="43" t="n"/>
       <c r="P77">
-        <f>IF(B77="","",B77)</f>
+        <f>IF(OR(B77="",COUNTIF($B$6:$B77,B77)&gt;1),"",B77)</f>
         <v/>
       </c>
       <c r="Q77">
-        <f>IF(C77="","",C77)</f>
+        <f>IF(P77="","",C77)</f>
         <v/>
       </c>
       <c r="R77">
-        <f>IF(B77="","",SUMIF($B$6:$B$305,B77,$D$6:$D$305))</f>
+        <f>IF(P77="","",SUMIF($B$6:$B$305,B77,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S77">
-        <f>IF(OR(B77="",COUNTIF($B$6:$B77,B77)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R77)+(($R$6:$R$305=R77)*($B$6:$B$305&lt;B77)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P77="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R77,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R77,"="&amp;R77,$P$6:$P77,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T77">
@@ -19434,19 +19434,19 @@
       <c r="C78" s="56" t="n"/>
       <c r="D78" s="43" t="n"/>
       <c r="P78">
-        <f>IF(B78="","",B78)</f>
+        <f>IF(OR(B78="",COUNTIF($B$6:$B78,B78)&gt;1),"",B78)</f>
         <v/>
       </c>
       <c r="Q78">
-        <f>IF(C78="","",C78)</f>
+        <f>IF(P78="","",C78)</f>
         <v/>
       </c>
       <c r="R78">
-        <f>IF(B78="","",SUMIF($B$6:$B$305,B78,$D$6:$D$305))</f>
+        <f>IF(P78="","",SUMIF($B$6:$B$305,B78,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S78">
-        <f>IF(OR(B78="",COUNTIF($B$6:$B78,B78)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R78)+(($R$6:$R$305=R78)*($B$6:$B$305&lt;B78)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P78="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R78,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R78,"="&amp;R78,$P$6:$P78,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T78">
@@ -19472,19 +19472,19 @@
       <c r="C79" s="56" t="n"/>
       <c r="D79" s="43" t="n"/>
       <c r="P79">
-        <f>IF(B79="","",B79)</f>
+        <f>IF(OR(B79="",COUNTIF($B$6:$B79,B79)&gt;1),"",B79)</f>
         <v/>
       </c>
       <c r="Q79">
-        <f>IF(C79="","",C79)</f>
+        <f>IF(P79="","",C79)</f>
         <v/>
       </c>
       <c r="R79">
-        <f>IF(B79="","",SUMIF($B$6:$B$305,B79,$D$6:$D$305))</f>
+        <f>IF(P79="","",SUMIF($B$6:$B$305,B79,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S79">
-        <f>IF(OR(B79="",COUNTIF($B$6:$B79,B79)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R79)+(($R$6:$R$305=R79)*($B$6:$B$305&lt;B79)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P79="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R79,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R79,"="&amp;R79,$P$6:$P79,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T79">
@@ -19510,19 +19510,19 @@
       <c r="C80" s="56" t="n"/>
       <c r="D80" s="43" t="n"/>
       <c r="P80">
-        <f>IF(B80="","",B80)</f>
+        <f>IF(OR(B80="",COUNTIF($B$6:$B80,B80)&gt;1),"",B80)</f>
         <v/>
       </c>
       <c r="Q80">
-        <f>IF(C80="","",C80)</f>
+        <f>IF(P80="","",C80)</f>
         <v/>
       </c>
       <c r="R80">
-        <f>IF(B80="","",SUMIF($B$6:$B$305,B80,$D$6:$D$305))</f>
+        <f>IF(P80="","",SUMIF($B$6:$B$305,B80,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S80">
-        <f>IF(OR(B80="",COUNTIF($B$6:$B80,B80)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R80)+(($R$6:$R$305=R80)*($B$6:$B$305&lt;B80)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P80="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R80,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R80,"="&amp;R80,$P$6:$P80,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T80">
@@ -19548,19 +19548,19 @@
       <c r="C81" s="56" t="n"/>
       <c r="D81" s="43" t="n"/>
       <c r="P81">
-        <f>IF(B81="","",B81)</f>
+        <f>IF(OR(B81="",COUNTIF($B$6:$B81,B81)&gt;1),"",B81)</f>
         <v/>
       </c>
       <c r="Q81">
-        <f>IF(C81="","",C81)</f>
+        <f>IF(P81="","",C81)</f>
         <v/>
       </c>
       <c r="R81">
-        <f>IF(B81="","",SUMIF($B$6:$B$305,B81,$D$6:$D$305))</f>
+        <f>IF(P81="","",SUMIF($B$6:$B$305,B81,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S81">
-        <f>IF(OR(B81="",COUNTIF($B$6:$B81,B81)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R81)+(($R$6:$R$305=R81)*($B$6:$B$305&lt;B81)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P81="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R81,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R81,"="&amp;R81,$P$6:$P81,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T81">
@@ -19586,19 +19586,19 @@
       <c r="C82" s="56" t="n"/>
       <c r="D82" s="43" t="n"/>
       <c r="P82">
-        <f>IF(B82="","",B82)</f>
+        <f>IF(OR(B82="",COUNTIF($B$6:$B82,B82)&gt;1),"",B82)</f>
         <v/>
       </c>
       <c r="Q82">
-        <f>IF(C82="","",C82)</f>
+        <f>IF(P82="","",C82)</f>
         <v/>
       </c>
       <c r="R82">
-        <f>IF(B82="","",SUMIF($B$6:$B$305,B82,$D$6:$D$305))</f>
+        <f>IF(P82="","",SUMIF($B$6:$B$305,B82,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S82">
-        <f>IF(OR(B82="",COUNTIF($B$6:$B82,B82)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R82)+(($R$6:$R$305=R82)*($B$6:$B$305&lt;B82)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P82="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R82,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R82,"="&amp;R82,$P$6:$P82,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T82">
@@ -19624,19 +19624,19 @@
       <c r="C83" s="56" t="n"/>
       <c r="D83" s="43" t="n"/>
       <c r="P83">
-        <f>IF(B83="","",B83)</f>
+        <f>IF(OR(B83="",COUNTIF($B$6:$B83,B83)&gt;1),"",B83)</f>
         <v/>
       </c>
       <c r="Q83">
-        <f>IF(C83="","",C83)</f>
+        <f>IF(P83="","",C83)</f>
         <v/>
       </c>
       <c r="R83">
-        <f>IF(B83="","",SUMIF($B$6:$B$305,B83,$D$6:$D$305))</f>
+        <f>IF(P83="","",SUMIF($B$6:$B$305,B83,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S83">
-        <f>IF(OR(B83="",COUNTIF($B$6:$B83,B83)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R83)+(($R$6:$R$305=R83)*($B$6:$B$305&lt;B83)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P83="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R83,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R83,"="&amp;R83,$P$6:$P83,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T83">
@@ -19662,19 +19662,19 @@
       <c r="C84" s="56" t="n"/>
       <c r="D84" s="43" t="n"/>
       <c r="P84">
-        <f>IF(B84="","",B84)</f>
+        <f>IF(OR(B84="",COUNTIF($B$6:$B84,B84)&gt;1),"",B84)</f>
         <v/>
       </c>
       <c r="Q84">
-        <f>IF(C84="","",C84)</f>
+        <f>IF(P84="","",C84)</f>
         <v/>
       </c>
       <c r="R84">
-        <f>IF(B84="","",SUMIF($B$6:$B$305,B84,$D$6:$D$305))</f>
+        <f>IF(P84="","",SUMIF($B$6:$B$305,B84,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S84">
-        <f>IF(OR(B84="",COUNTIF($B$6:$B84,B84)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R84)+(($R$6:$R$305=R84)*($B$6:$B$305&lt;B84)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P84="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R84,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R84,"="&amp;R84,$P$6:$P84,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T84">
@@ -19700,19 +19700,19 @@
       <c r="C85" s="56" t="n"/>
       <c r="D85" s="43" t="n"/>
       <c r="P85">
-        <f>IF(B85="","",B85)</f>
+        <f>IF(OR(B85="",COUNTIF($B$6:$B85,B85)&gt;1),"",B85)</f>
         <v/>
       </c>
       <c r="Q85">
-        <f>IF(C85="","",C85)</f>
+        <f>IF(P85="","",C85)</f>
         <v/>
       </c>
       <c r="R85">
-        <f>IF(B85="","",SUMIF($B$6:$B$305,B85,$D$6:$D$305))</f>
+        <f>IF(P85="","",SUMIF($B$6:$B$305,B85,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S85">
-        <f>IF(OR(B85="",COUNTIF($B$6:$B85,B85)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R85)+(($R$6:$R$305=R85)*($B$6:$B$305&lt;B85)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P85="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R85,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R85,"="&amp;R85,$P$6:$P85,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T85">
@@ -19738,19 +19738,19 @@
       <c r="C86" s="56" t="n"/>
       <c r="D86" s="43" t="n"/>
       <c r="P86">
-        <f>IF(B86="","",B86)</f>
+        <f>IF(OR(B86="",COUNTIF($B$6:$B86,B86)&gt;1),"",B86)</f>
         <v/>
       </c>
       <c r="Q86">
-        <f>IF(C86="","",C86)</f>
+        <f>IF(P86="","",C86)</f>
         <v/>
       </c>
       <c r="R86">
-        <f>IF(B86="","",SUMIF($B$6:$B$305,B86,$D$6:$D$305))</f>
+        <f>IF(P86="","",SUMIF($B$6:$B$305,B86,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S86">
-        <f>IF(OR(B86="",COUNTIF($B$6:$B86,B86)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R86)+(($R$6:$R$305=R86)*($B$6:$B$305&lt;B86)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P86="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R86,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R86,"="&amp;R86,$P$6:$P86,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T86">
@@ -19776,19 +19776,19 @@
       <c r="C87" s="56" t="n"/>
       <c r="D87" s="43" t="n"/>
       <c r="P87">
-        <f>IF(B87="","",B87)</f>
+        <f>IF(OR(B87="",COUNTIF($B$6:$B87,B87)&gt;1),"",B87)</f>
         <v/>
       </c>
       <c r="Q87">
-        <f>IF(C87="","",C87)</f>
+        <f>IF(P87="","",C87)</f>
         <v/>
       </c>
       <c r="R87">
-        <f>IF(B87="","",SUMIF($B$6:$B$305,B87,$D$6:$D$305))</f>
+        <f>IF(P87="","",SUMIF($B$6:$B$305,B87,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S87">
-        <f>IF(OR(B87="",COUNTIF($B$6:$B87,B87)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R87)+(($R$6:$R$305=R87)*($B$6:$B$305&lt;B87)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P87="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R87,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R87,"="&amp;R87,$P$6:$P87,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T87">
@@ -19814,19 +19814,19 @@
       <c r="C88" s="56" t="n"/>
       <c r="D88" s="43" t="n"/>
       <c r="P88">
-        <f>IF(B88="","",B88)</f>
+        <f>IF(OR(B88="",COUNTIF($B$6:$B88,B88)&gt;1),"",B88)</f>
         <v/>
       </c>
       <c r="Q88">
-        <f>IF(C88="","",C88)</f>
+        <f>IF(P88="","",C88)</f>
         <v/>
       </c>
       <c r="R88">
-        <f>IF(B88="","",SUMIF($B$6:$B$305,B88,$D$6:$D$305))</f>
+        <f>IF(P88="","",SUMIF($B$6:$B$305,B88,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S88">
-        <f>IF(OR(B88="",COUNTIF($B$6:$B88,B88)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R88)+(($R$6:$R$305=R88)*($B$6:$B$305&lt;B88)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P88="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R88,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R88,"="&amp;R88,$P$6:$P88,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T88">
@@ -19852,19 +19852,19 @@
       <c r="C89" s="56" t="n"/>
       <c r="D89" s="43" t="n"/>
       <c r="P89">
-        <f>IF(B89="","",B89)</f>
+        <f>IF(OR(B89="",COUNTIF($B$6:$B89,B89)&gt;1),"",B89)</f>
         <v/>
       </c>
       <c r="Q89">
-        <f>IF(C89="","",C89)</f>
+        <f>IF(P89="","",C89)</f>
         <v/>
       </c>
       <c r="R89">
-        <f>IF(B89="","",SUMIF($B$6:$B$305,B89,$D$6:$D$305))</f>
+        <f>IF(P89="","",SUMIF($B$6:$B$305,B89,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S89">
-        <f>IF(OR(B89="",COUNTIF($B$6:$B89,B89)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R89)+(($R$6:$R$305=R89)*($B$6:$B$305&lt;B89)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P89="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R89,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R89,"="&amp;R89,$P$6:$P89,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T89">
@@ -19890,19 +19890,19 @@
       <c r="C90" s="56" t="n"/>
       <c r="D90" s="43" t="n"/>
       <c r="P90">
-        <f>IF(B90="","",B90)</f>
+        <f>IF(OR(B90="",COUNTIF($B$6:$B90,B90)&gt;1),"",B90)</f>
         <v/>
       </c>
       <c r="Q90">
-        <f>IF(C90="","",C90)</f>
+        <f>IF(P90="","",C90)</f>
         <v/>
       </c>
       <c r="R90">
-        <f>IF(B90="","",SUMIF($B$6:$B$305,B90,$D$6:$D$305))</f>
+        <f>IF(P90="","",SUMIF($B$6:$B$305,B90,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S90">
-        <f>IF(OR(B90="",COUNTIF($B$6:$B90,B90)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R90)+(($R$6:$R$305=R90)*($B$6:$B$305&lt;B90)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P90="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R90,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R90,"="&amp;R90,$P$6:$P90,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T90">
@@ -19928,19 +19928,19 @@
       <c r="C91" s="56" t="n"/>
       <c r="D91" s="43" t="n"/>
       <c r="P91">
-        <f>IF(B91="","",B91)</f>
+        <f>IF(OR(B91="",COUNTIF($B$6:$B91,B91)&gt;1),"",B91)</f>
         <v/>
       </c>
       <c r="Q91">
-        <f>IF(C91="","",C91)</f>
+        <f>IF(P91="","",C91)</f>
         <v/>
       </c>
       <c r="R91">
-        <f>IF(B91="","",SUMIF($B$6:$B$305,B91,$D$6:$D$305))</f>
+        <f>IF(P91="","",SUMIF($B$6:$B$305,B91,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S91">
-        <f>IF(OR(B91="",COUNTIF($B$6:$B91,B91)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R91)+(($R$6:$R$305=R91)*($B$6:$B$305&lt;B91)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P91="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R91,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R91,"="&amp;R91,$P$6:$P91,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T91">
@@ -19966,19 +19966,19 @@
       <c r="C92" s="56" t="n"/>
       <c r="D92" s="43" t="n"/>
       <c r="P92">
-        <f>IF(B92="","",B92)</f>
+        <f>IF(OR(B92="",COUNTIF($B$6:$B92,B92)&gt;1),"",B92)</f>
         <v/>
       </c>
       <c r="Q92">
-        <f>IF(C92="","",C92)</f>
+        <f>IF(P92="","",C92)</f>
         <v/>
       </c>
       <c r="R92">
-        <f>IF(B92="","",SUMIF($B$6:$B$305,B92,$D$6:$D$305))</f>
+        <f>IF(P92="","",SUMIF($B$6:$B$305,B92,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S92">
-        <f>IF(OR(B92="",COUNTIF($B$6:$B92,B92)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R92)+(($R$6:$R$305=R92)*($B$6:$B$305&lt;B92)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P92="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R92,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R92,"="&amp;R92,$P$6:$P92,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T92">
@@ -20004,19 +20004,19 @@
       <c r="C93" s="56" t="n"/>
       <c r="D93" s="43" t="n"/>
       <c r="P93">
-        <f>IF(B93="","",B93)</f>
+        <f>IF(OR(B93="",COUNTIF($B$6:$B93,B93)&gt;1),"",B93)</f>
         <v/>
       </c>
       <c r="Q93">
-        <f>IF(C93="","",C93)</f>
+        <f>IF(P93="","",C93)</f>
         <v/>
       </c>
       <c r="R93">
-        <f>IF(B93="","",SUMIF($B$6:$B$305,B93,$D$6:$D$305))</f>
+        <f>IF(P93="","",SUMIF($B$6:$B$305,B93,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S93">
-        <f>IF(OR(B93="",COUNTIF($B$6:$B93,B93)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R93)+(($R$6:$R$305=R93)*($B$6:$B$305&lt;B93)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P93="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R93,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R93,"="&amp;R93,$P$6:$P93,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T93">
@@ -20042,19 +20042,19 @@
       <c r="C94" s="56" t="n"/>
       <c r="D94" s="43" t="n"/>
       <c r="P94">
-        <f>IF(B94="","",B94)</f>
+        <f>IF(OR(B94="",COUNTIF($B$6:$B94,B94)&gt;1),"",B94)</f>
         <v/>
       </c>
       <c r="Q94">
-        <f>IF(C94="","",C94)</f>
+        <f>IF(P94="","",C94)</f>
         <v/>
       </c>
       <c r="R94">
-        <f>IF(B94="","",SUMIF($B$6:$B$305,B94,$D$6:$D$305))</f>
+        <f>IF(P94="","",SUMIF($B$6:$B$305,B94,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S94">
-        <f>IF(OR(B94="",COUNTIF($B$6:$B94,B94)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R94)+(($R$6:$R$305=R94)*($B$6:$B$305&lt;B94)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P94="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R94,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R94,"="&amp;R94,$P$6:$P94,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T94">
@@ -20080,19 +20080,19 @@
       <c r="C95" s="56" t="n"/>
       <c r="D95" s="43" t="n"/>
       <c r="P95">
-        <f>IF(B95="","",B95)</f>
+        <f>IF(OR(B95="",COUNTIF($B$6:$B95,B95)&gt;1),"",B95)</f>
         <v/>
       </c>
       <c r="Q95">
-        <f>IF(C95="","",C95)</f>
+        <f>IF(P95="","",C95)</f>
         <v/>
       </c>
       <c r="R95">
-        <f>IF(B95="","",SUMIF($B$6:$B$305,B95,$D$6:$D$305))</f>
+        <f>IF(P95="","",SUMIF($B$6:$B$305,B95,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S95">
-        <f>IF(OR(B95="",COUNTIF($B$6:$B95,B95)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R95)+(($R$6:$R$305=R95)*($B$6:$B$305&lt;B95)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P95="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R95,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R95,"="&amp;R95,$P$6:$P95,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T95">
@@ -20118,19 +20118,19 @@
       <c r="C96" s="56" t="n"/>
       <c r="D96" s="43" t="n"/>
       <c r="P96">
-        <f>IF(B96="","",B96)</f>
+        <f>IF(OR(B96="",COUNTIF($B$6:$B96,B96)&gt;1),"",B96)</f>
         <v/>
       </c>
       <c r="Q96">
-        <f>IF(C96="","",C96)</f>
+        <f>IF(P96="","",C96)</f>
         <v/>
       </c>
       <c r="R96">
-        <f>IF(B96="","",SUMIF($B$6:$B$305,B96,$D$6:$D$305))</f>
+        <f>IF(P96="","",SUMIF($B$6:$B$305,B96,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S96">
-        <f>IF(OR(B96="",COUNTIF($B$6:$B96,B96)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R96)+(($R$6:$R$305=R96)*($B$6:$B$305&lt;B96)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P96="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R96,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R96,"="&amp;R96,$P$6:$P96,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T96">
@@ -20156,19 +20156,19 @@
       <c r="C97" s="56" t="n"/>
       <c r="D97" s="43" t="n"/>
       <c r="P97">
-        <f>IF(B97="","",B97)</f>
+        <f>IF(OR(B97="",COUNTIF($B$6:$B97,B97)&gt;1),"",B97)</f>
         <v/>
       </c>
       <c r="Q97">
-        <f>IF(C97="","",C97)</f>
+        <f>IF(P97="","",C97)</f>
         <v/>
       </c>
       <c r="R97">
-        <f>IF(B97="","",SUMIF($B$6:$B$305,B97,$D$6:$D$305))</f>
+        <f>IF(P97="","",SUMIF($B$6:$B$305,B97,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S97">
-        <f>IF(OR(B97="",COUNTIF($B$6:$B97,B97)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R97)+(($R$6:$R$305=R97)*($B$6:$B$305&lt;B97)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P97="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R97,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R97,"="&amp;R97,$P$6:$P97,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T97">
@@ -20194,19 +20194,19 @@
       <c r="C98" s="56" t="n"/>
       <c r="D98" s="43" t="n"/>
       <c r="P98">
-        <f>IF(B98="","",B98)</f>
+        <f>IF(OR(B98="",COUNTIF($B$6:$B98,B98)&gt;1),"",B98)</f>
         <v/>
       </c>
       <c r="Q98">
-        <f>IF(C98="","",C98)</f>
+        <f>IF(P98="","",C98)</f>
         <v/>
       </c>
       <c r="R98">
-        <f>IF(B98="","",SUMIF($B$6:$B$305,B98,$D$6:$D$305))</f>
+        <f>IF(P98="","",SUMIF($B$6:$B$305,B98,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S98">
-        <f>IF(OR(B98="",COUNTIF($B$6:$B98,B98)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R98)+(($R$6:$R$305=R98)*($B$6:$B$305&lt;B98)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P98="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R98,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R98,"="&amp;R98,$P$6:$P98,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T98">
@@ -20232,19 +20232,19 @@
       <c r="C99" s="56" t="n"/>
       <c r="D99" s="43" t="n"/>
       <c r="P99">
-        <f>IF(B99="","",B99)</f>
+        <f>IF(OR(B99="",COUNTIF($B$6:$B99,B99)&gt;1),"",B99)</f>
         <v/>
       </c>
       <c r="Q99">
-        <f>IF(C99="","",C99)</f>
+        <f>IF(P99="","",C99)</f>
         <v/>
       </c>
       <c r="R99">
-        <f>IF(B99="","",SUMIF($B$6:$B$305,B99,$D$6:$D$305))</f>
+        <f>IF(P99="","",SUMIF($B$6:$B$305,B99,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S99">
-        <f>IF(OR(B99="",COUNTIF($B$6:$B99,B99)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R99)+(($R$6:$R$305=R99)*($B$6:$B$305&lt;B99)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P99="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R99,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R99,"="&amp;R99,$P$6:$P99,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T99">
@@ -20270,19 +20270,19 @@
       <c r="C100" s="56" t="n"/>
       <c r="D100" s="43" t="n"/>
       <c r="P100">
-        <f>IF(B100="","",B100)</f>
+        <f>IF(OR(B100="",COUNTIF($B$6:$B100,B100)&gt;1),"",B100)</f>
         <v/>
       </c>
       <c r="Q100">
-        <f>IF(C100="","",C100)</f>
+        <f>IF(P100="","",C100)</f>
         <v/>
       </c>
       <c r="R100">
-        <f>IF(B100="","",SUMIF($B$6:$B$305,B100,$D$6:$D$305))</f>
+        <f>IF(P100="","",SUMIF($B$6:$B$305,B100,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S100">
-        <f>IF(OR(B100="",COUNTIF($B$6:$B100,B100)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R100)+(($R$6:$R$305=R100)*($B$6:$B$305&lt;B100)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P100="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R100,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R100,"="&amp;R100,$P$6:$P100,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T100">
@@ -20308,19 +20308,19 @@
       <c r="C101" s="56" t="n"/>
       <c r="D101" s="43" t="n"/>
       <c r="P101">
-        <f>IF(B101="","",B101)</f>
+        <f>IF(OR(B101="",COUNTIF($B$6:$B101,B101)&gt;1),"",B101)</f>
         <v/>
       </c>
       <c r="Q101">
-        <f>IF(C101="","",C101)</f>
+        <f>IF(P101="","",C101)</f>
         <v/>
       </c>
       <c r="R101">
-        <f>IF(B101="","",SUMIF($B$6:$B$305,B101,$D$6:$D$305))</f>
+        <f>IF(P101="","",SUMIF($B$6:$B$305,B101,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S101">
-        <f>IF(OR(B101="",COUNTIF($B$6:$B101,B101)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R101)+(($R$6:$R$305=R101)*($B$6:$B$305&lt;B101)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P101="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R101,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R101,"="&amp;R101,$P$6:$P101,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T101">
@@ -20346,19 +20346,19 @@
       <c r="C102" s="56" t="n"/>
       <c r="D102" s="43" t="n"/>
       <c r="P102">
-        <f>IF(B102="","",B102)</f>
+        <f>IF(OR(B102="",COUNTIF($B$6:$B102,B102)&gt;1),"",B102)</f>
         <v/>
       </c>
       <c r="Q102">
-        <f>IF(C102="","",C102)</f>
+        <f>IF(P102="","",C102)</f>
         <v/>
       </c>
       <c r="R102">
-        <f>IF(B102="","",SUMIF($B$6:$B$305,B102,$D$6:$D$305))</f>
+        <f>IF(P102="","",SUMIF($B$6:$B$305,B102,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S102">
-        <f>IF(OR(B102="",COUNTIF($B$6:$B102,B102)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R102)+(($R$6:$R$305=R102)*($B$6:$B$305&lt;B102)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P102="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R102,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R102,"="&amp;R102,$P$6:$P102,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T102">
@@ -20384,19 +20384,19 @@
       <c r="C103" s="56" t="n"/>
       <c r="D103" s="43" t="n"/>
       <c r="P103">
-        <f>IF(B103="","",B103)</f>
+        <f>IF(OR(B103="",COUNTIF($B$6:$B103,B103)&gt;1),"",B103)</f>
         <v/>
       </c>
       <c r="Q103">
-        <f>IF(C103="","",C103)</f>
+        <f>IF(P103="","",C103)</f>
         <v/>
       </c>
       <c r="R103">
-        <f>IF(B103="","",SUMIF($B$6:$B$305,B103,$D$6:$D$305))</f>
+        <f>IF(P103="","",SUMIF($B$6:$B$305,B103,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S103">
-        <f>IF(OR(B103="",COUNTIF($B$6:$B103,B103)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R103)+(($R$6:$R$305=R103)*($B$6:$B$305&lt;B103)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P103="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R103,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R103,"="&amp;R103,$P$6:$P103,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T103">
@@ -20422,19 +20422,19 @@
       <c r="C104" s="56" t="n"/>
       <c r="D104" s="43" t="n"/>
       <c r="P104">
-        <f>IF(B104="","",B104)</f>
+        <f>IF(OR(B104="",COUNTIF($B$6:$B104,B104)&gt;1),"",B104)</f>
         <v/>
       </c>
       <c r="Q104">
-        <f>IF(C104="","",C104)</f>
+        <f>IF(P104="","",C104)</f>
         <v/>
       </c>
       <c r="R104">
-        <f>IF(B104="","",SUMIF($B$6:$B$305,B104,$D$6:$D$305))</f>
+        <f>IF(P104="","",SUMIF($B$6:$B$305,B104,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S104">
-        <f>IF(OR(B104="",COUNTIF($B$6:$B104,B104)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R104)+(($R$6:$R$305=R104)*($B$6:$B$305&lt;B104)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P104="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R104,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R104,"="&amp;R104,$P$6:$P104,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T104">
@@ -20460,19 +20460,19 @@
       <c r="C105" s="56" t="n"/>
       <c r="D105" s="43" t="n"/>
       <c r="P105">
-        <f>IF(B105="","",B105)</f>
+        <f>IF(OR(B105="",COUNTIF($B$6:$B105,B105)&gt;1),"",B105)</f>
         <v/>
       </c>
       <c r="Q105">
-        <f>IF(C105="","",C105)</f>
+        <f>IF(P105="","",C105)</f>
         <v/>
       </c>
       <c r="R105">
-        <f>IF(B105="","",SUMIF($B$6:$B$305,B105,$D$6:$D$305))</f>
+        <f>IF(P105="","",SUMIF($B$6:$B$305,B105,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S105">
-        <f>IF(OR(B105="",COUNTIF($B$6:$B105,B105)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R105)+(($R$6:$R$305=R105)*($B$6:$B$305&lt;B105)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P105="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R105,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R105,"="&amp;R105,$P$6:$P105,"&lt;&gt;"))</f>
         <v/>
       </c>
       <c r="T105">
@@ -20498,19 +20498,19 @@
       <c r="C106" s="56" t="n"/>
       <c r="D106" s="43" t="n"/>
       <c r="P106">
-        <f>IF(B106="","",B106)</f>
+        <f>IF(OR(B106="",COUNTIF($B$6:$B106,B106)&gt;1),"",B106)</f>
         <v/>
       </c>
       <c r="Q106">
-        <f>IF(C106="","",C106)</f>
+        <f>IF(P106="","",C106)</f>
         <v/>
       </c>
       <c r="R106">
-        <f>IF(B106="","",SUMIF($B$6:$B$305,B106,$D$6:$D$305))</f>
+        <f>IF(P106="","",SUMIF($B$6:$B$305,B106,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S106">
-        <f>IF(OR(B106="",COUNTIF($B$6:$B106,B106)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R106)+(($R$6:$R$305=R106)*($B$6:$B$305&lt;B106)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P106="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R106,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R106,"="&amp;R106,$P$6:$P106,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20520,19 +20520,19 @@
       <c r="C107" s="56" t="n"/>
       <c r="D107" s="43" t="n"/>
       <c r="P107">
-        <f>IF(B107="","",B107)</f>
+        <f>IF(OR(B107="",COUNTIF($B$6:$B107,B107)&gt;1),"",B107)</f>
         <v/>
       </c>
       <c r="Q107">
-        <f>IF(C107="","",C107)</f>
+        <f>IF(P107="","",C107)</f>
         <v/>
       </c>
       <c r="R107">
-        <f>IF(B107="","",SUMIF($B$6:$B$305,B107,$D$6:$D$305))</f>
+        <f>IF(P107="","",SUMIF($B$6:$B$305,B107,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S107">
-        <f>IF(OR(B107="",COUNTIF($B$6:$B107,B107)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R107)+(($R$6:$R$305=R107)*($B$6:$B$305&lt;B107)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P107="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R107,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R107,"="&amp;R107,$P$6:$P107,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20542,19 +20542,19 @@
       <c r="C108" s="56" t="n"/>
       <c r="D108" s="43" t="n"/>
       <c r="P108">
-        <f>IF(B108="","",B108)</f>
+        <f>IF(OR(B108="",COUNTIF($B$6:$B108,B108)&gt;1),"",B108)</f>
         <v/>
       </c>
       <c r="Q108">
-        <f>IF(C108="","",C108)</f>
+        <f>IF(P108="","",C108)</f>
         <v/>
       </c>
       <c r="R108">
-        <f>IF(B108="","",SUMIF($B$6:$B$305,B108,$D$6:$D$305))</f>
+        <f>IF(P108="","",SUMIF($B$6:$B$305,B108,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S108">
-        <f>IF(OR(B108="",COUNTIF($B$6:$B108,B108)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R108)+(($R$6:$R$305=R108)*($B$6:$B$305&lt;B108)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P108="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R108,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R108,"="&amp;R108,$P$6:$P108,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20564,19 +20564,19 @@
       <c r="C109" s="56" t="n"/>
       <c r="D109" s="43" t="n"/>
       <c r="P109">
-        <f>IF(B109="","",B109)</f>
+        <f>IF(OR(B109="",COUNTIF($B$6:$B109,B109)&gt;1),"",B109)</f>
         <v/>
       </c>
       <c r="Q109">
-        <f>IF(C109="","",C109)</f>
+        <f>IF(P109="","",C109)</f>
         <v/>
       </c>
       <c r="R109">
-        <f>IF(B109="","",SUMIF($B$6:$B$305,B109,$D$6:$D$305))</f>
+        <f>IF(P109="","",SUMIF($B$6:$B$305,B109,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S109">
-        <f>IF(OR(B109="",COUNTIF($B$6:$B109,B109)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R109)+(($R$6:$R$305=R109)*($B$6:$B$305&lt;B109)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P109="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R109,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R109,"="&amp;R109,$P$6:$P109,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20586,19 +20586,19 @@
       <c r="C110" s="56" t="n"/>
       <c r="D110" s="43" t="n"/>
       <c r="P110">
-        <f>IF(B110="","",B110)</f>
+        <f>IF(OR(B110="",COUNTIF($B$6:$B110,B110)&gt;1),"",B110)</f>
         <v/>
       </c>
       <c r="Q110">
-        <f>IF(C110="","",C110)</f>
+        <f>IF(P110="","",C110)</f>
         <v/>
       </c>
       <c r="R110">
-        <f>IF(B110="","",SUMIF($B$6:$B$305,B110,$D$6:$D$305))</f>
+        <f>IF(P110="","",SUMIF($B$6:$B$305,B110,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S110">
-        <f>IF(OR(B110="",COUNTIF($B$6:$B110,B110)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R110)+(($R$6:$R$305=R110)*($B$6:$B$305&lt;B110)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P110="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R110,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R110,"="&amp;R110,$P$6:$P110,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20608,19 +20608,19 @@
       <c r="C111" s="56" t="n"/>
       <c r="D111" s="43" t="n"/>
       <c r="P111">
-        <f>IF(B111="","",B111)</f>
+        <f>IF(OR(B111="",COUNTIF($B$6:$B111,B111)&gt;1),"",B111)</f>
         <v/>
       </c>
       <c r="Q111">
-        <f>IF(C111="","",C111)</f>
+        <f>IF(P111="","",C111)</f>
         <v/>
       </c>
       <c r="R111">
-        <f>IF(B111="","",SUMIF($B$6:$B$305,B111,$D$6:$D$305))</f>
+        <f>IF(P111="","",SUMIF($B$6:$B$305,B111,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S111">
-        <f>IF(OR(B111="",COUNTIF($B$6:$B111,B111)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R111)+(($R$6:$R$305=R111)*($B$6:$B$305&lt;B111)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P111="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R111,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R111,"="&amp;R111,$P$6:$P111,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20630,19 +20630,19 @@
       <c r="C112" s="56" t="n"/>
       <c r="D112" s="43" t="n"/>
       <c r="P112">
-        <f>IF(B112="","",B112)</f>
+        <f>IF(OR(B112="",COUNTIF($B$6:$B112,B112)&gt;1),"",B112)</f>
         <v/>
       </c>
       <c r="Q112">
-        <f>IF(C112="","",C112)</f>
+        <f>IF(P112="","",C112)</f>
         <v/>
       </c>
       <c r="R112">
-        <f>IF(B112="","",SUMIF($B$6:$B$305,B112,$D$6:$D$305))</f>
+        <f>IF(P112="","",SUMIF($B$6:$B$305,B112,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S112">
-        <f>IF(OR(B112="",COUNTIF($B$6:$B112,B112)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R112)+(($R$6:$R$305=R112)*($B$6:$B$305&lt;B112)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P112="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R112,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R112,"="&amp;R112,$P$6:$P112,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20652,19 +20652,19 @@
       <c r="C113" s="56" t="n"/>
       <c r="D113" s="43" t="n"/>
       <c r="P113">
-        <f>IF(B113="","",B113)</f>
+        <f>IF(OR(B113="",COUNTIF($B$6:$B113,B113)&gt;1),"",B113)</f>
         <v/>
       </c>
       <c r="Q113">
-        <f>IF(C113="","",C113)</f>
+        <f>IF(P113="","",C113)</f>
         <v/>
       </c>
       <c r="R113">
-        <f>IF(B113="","",SUMIF($B$6:$B$305,B113,$D$6:$D$305))</f>
+        <f>IF(P113="","",SUMIF($B$6:$B$305,B113,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S113">
-        <f>IF(OR(B113="",COUNTIF($B$6:$B113,B113)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R113)+(($R$6:$R$305=R113)*($B$6:$B$305&lt;B113)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P113="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R113,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R113,"="&amp;R113,$P$6:$P113,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20674,19 +20674,19 @@
       <c r="C114" s="56" t="n"/>
       <c r="D114" s="43" t="n"/>
       <c r="P114">
-        <f>IF(B114="","",B114)</f>
+        <f>IF(OR(B114="",COUNTIF($B$6:$B114,B114)&gt;1),"",B114)</f>
         <v/>
       </c>
       <c r="Q114">
-        <f>IF(C114="","",C114)</f>
+        <f>IF(P114="","",C114)</f>
         <v/>
       </c>
       <c r="R114">
-        <f>IF(B114="","",SUMIF($B$6:$B$305,B114,$D$6:$D$305))</f>
+        <f>IF(P114="","",SUMIF($B$6:$B$305,B114,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S114">
-        <f>IF(OR(B114="",COUNTIF($B$6:$B114,B114)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R114)+(($R$6:$R$305=R114)*($B$6:$B$305&lt;B114)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P114="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R114,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R114,"="&amp;R114,$P$6:$P114,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20696,19 +20696,19 @@
       <c r="C115" s="56" t="n"/>
       <c r="D115" s="43" t="n"/>
       <c r="P115">
-        <f>IF(B115="","",B115)</f>
+        <f>IF(OR(B115="",COUNTIF($B$6:$B115,B115)&gt;1),"",B115)</f>
         <v/>
       </c>
       <c r="Q115">
-        <f>IF(C115="","",C115)</f>
+        <f>IF(P115="","",C115)</f>
         <v/>
       </c>
       <c r="R115">
-        <f>IF(B115="","",SUMIF($B$6:$B$305,B115,$D$6:$D$305))</f>
+        <f>IF(P115="","",SUMIF($B$6:$B$305,B115,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S115">
-        <f>IF(OR(B115="",COUNTIF($B$6:$B115,B115)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R115)+(($R$6:$R$305=R115)*($B$6:$B$305&lt;B115)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P115="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R115,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R115,"="&amp;R115,$P$6:$P115,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20718,19 +20718,19 @@
       <c r="C116" s="56" t="n"/>
       <c r="D116" s="43" t="n"/>
       <c r="P116">
-        <f>IF(B116="","",B116)</f>
+        <f>IF(OR(B116="",COUNTIF($B$6:$B116,B116)&gt;1),"",B116)</f>
         <v/>
       </c>
       <c r="Q116">
-        <f>IF(C116="","",C116)</f>
+        <f>IF(P116="","",C116)</f>
         <v/>
       </c>
       <c r="R116">
-        <f>IF(B116="","",SUMIF($B$6:$B$305,B116,$D$6:$D$305))</f>
+        <f>IF(P116="","",SUMIF($B$6:$B$305,B116,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S116">
-        <f>IF(OR(B116="",COUNTIF($B$6:$B116,B116)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R116)+(($R$6:$R$305=R116)*($B$6:$B$305&lt;B116)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P116="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R116,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R116,"="&amp;R116,$P$6:$P116,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20740,19 +20740,19 @@
       <c r="C117" s="56" t="n"/>
       <c r="D117" s="43" t="n"/>
       <c r="P117">
-        <f>IF(B117="","",B117)</f>
+        <f>IF(OR(B117="",COUNTIF($B$6:$B117,B117)&gt;1),"",B117)</f>
         <v/>
       </c>
       <c r="Q117">
-        <f>IF(C117="","",C117)</f>
+        <f>IF(P117="","",C117)</f>
         <v/>
       </c>
       <c r="R117">
-        <f>IF(B117="","",SUMIF($B$6:$B$305,B117,$D$6:$D$305))</f>
+        <f>IF(P117="","",SUMIF($B$6:$B$305,B117,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S117">
-        <f>IF(OR(B117="",COUNTIF($B$6:$B117,B117)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R117)+(($R$6:$R$305=R117)*($B$6:$B$305&lt;B117)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P117="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R117,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R117,"="&amp;R117,$P$6:$P117,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20762,19 +20762,19 @@
       <c r="C118" s="56" t="n"/>
       <c r="D118" s="43" t="n"/>
       <c r="P118">
-        <f>IF(B118="","",B118)</f>
+        <f>IF(OR(B118="",COUNTIF($B$6:$B118,B118)&gt;1),"",B118)</f>
         <v/>
       </c>
       <c r="Q118">
-        <f>IF(C118="","",C118)</f>
+        <f>IF(P118="","",C118)</f>
         <v/>
       </c>
       <c r="R118">
-        <f>IF(B118="","",SUMIF($B$6:$B$305,B118,$D$6:$D$305))</f>
+        <f>IF(P118="","",SUMIF($B$6:$B$305,B118,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S118">
-        <f>IF(OR(B118="",COUNTIF($B$6:$B118,B118)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R118)+(($R$6:$R$305=R118)*($B$6:$B$305&lt;B118)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P118="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R118,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R118,"="&amp;R118,$P$6:$P118,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20784,19 +20784,19 @@
       <c r="C119" s="56" t="n"/>
       <c r="D119" s="43" t="n"/>
       <c r="P119">
-        <f>IF(B119="","",B119)</f>
+        <f>IF(OR(B119="",COUNTIF($B$6:$B119,B119)&gt;1),"",B119)</f>
         <v/>
       </c>
       <c r="Q119">
-        <f>IF(C119="","",C119)</f>
+        <f>IF(P119="","",C119)</f>
         <v/>
       </c>
       <c r="R119">
-        <f>IF(B119="","",SUMIF($B$6:$B$305,B119,$D$6:$D$305))</f>
+        <f>IF(P119="","",SUMIF($B$6:$B$305,B119,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S119">
-        <f>IF(OR(B119="",COUNTIF($B$6:$B119,B119)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R119)+(($R$6:$R$305=R119)*($B$6:$B$305&lt;B119)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P119="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R119,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R119,"="&amp;R119,$P$6:$P119,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20806,19 +20806,19 @@
       <c r="C120" s="56" t="n"/>
       <c r="D120" s="43" t="n"/>
       <c r="P120">
-        <f>IF(B120="","",B120)</f>
+        <f>IF(OR(B120="",COUNTIF($B$6:$B120,B120)&gt;1),"",B120)</f>
         <v/>
       </c>
       <c r="Q120">
-        <f>IF(C120="","",C120)</f>
+        <f>IF(P120="","",C120)</f>
         <v/>
       </c>
       <c r="R120">
-        <f>IF(B120="","",SUMIF($B$6:$B$305,B120,$D$6:$D$305))</f>
+        <f>IF(P120="","",SUMIF($B$6:$B$305,B120,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S120">
-        <f>IF(OR(B120="",COUNTIF($B$6:$B120,B120)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R120)+(($R$6:$R$305=R120)*($B$6:$B$305&lt;B120)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P120="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R120,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R120,"="&amp;R120,$P$6:$P120,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20828,19 +20828,19 @@
       <c r="C121" s="56" t="n"/>
       <c r="D121" s="43" t="n"/>
       <c r="P121">
-        <f>IF(B121="","",B121)</f>
+        <f>IF(OR(B121="",COUNTIF($B$6:$B121,B121)&gt;1),"",B121)</f>
         <v/>
       </c>
       <c r="Q121">
-        <f>IF(C121="","",C121)</f>
+        <f>IF(P121="","",C121)</f>
         <v/>
       </c>
       <c r="R121">
-        <f>IF(B121="","",SUMIF($B$6:$B$305,B121,$D$6:$D$305))</f>
+        <f>IF(P121="","",SUMIF($B$6:$B$305,B121,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S121">
-        <f>IF(OR(B121="",COUNTIF($B$6:$B121,B121)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R121)+(($R$6:$R$305=R121)*($B$6:$B$305&lt;B121)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P121="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R121,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R121,"="&amp;R121,$P$6:$P121,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20850,19 +20850,19 @@
       <c r="C122" s="56" t="n"/>
       <c r="D122" s="43" t="n"/>
       <c r="P122">
-        <f>IF(B122="","",B122)</f>
+        <f>IF(OR(B122="",COUNTIF($B$6:$B122,B122)&gt;1),"",B122)</f>
         <v/>
       </c>
       <c r="Q122">
-        <f>IF(C122="","",C122)</f>
+        <f>IF(P122="","",C122)</f>
         <v/>
       </c>
       <c r="R122">
-        <f>IF(B122="","",SUMIF($B$6:$B$305,B122,$D$6:$D$305))</f>
+        <f>IF(P122="","",SUMIF($B$6:$B$305,B122,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S122">
-        <f>IF(OR(B122="",COUNTIF($B$6:$B122,B122)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R122)+(($R$6:$R$305=R122)*($B$6:$B$305&lt;B122)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P122="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R122,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R122,"="&amp;R122,$P$6:$P122,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20872,19 +20872,19 @@
       <c r="C123" s="56" t="n"/>
       <c r="D123" s="43" t="n"/>
       <c r="P123">
-        <f>IF(B123="","",B123)</f>
+        <f>IF(OR(B123="",COUNTIF($B$6:$B123,B123)&gt;1),"",B123)</f>
         <v/>
       </c>
       <c r="Q123">
-        <f>IF(C123="","",C123)</f>
+        <f>IF(P123="","",C123)</f>
         <v/>
       </c>
       <c r="R123">
-        <f>IF(B123="","",SUMIF($B$6:$B$305,B123,$D$6:$D$305))</f>
+        <f>IF(P123="","",SUMIF($B$6:$B$305,B123,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S123">
-        <f>IF(OR(B123="",COUNTIF($B$6:$B123,B123)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R123)+(($R$6:$R$305=R123)*($B$6:$B$305&lt;B123)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P123="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R123,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R123,"="&amp;R123,$P$6:$P123,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20894,19 +20894,19 @@
       <c r="C124" s="56" t="n"/>
       <c r="D124" s="43" t="n"/>
       <c r="P124">
-        <f>IF(B124="","",B124)</f>
+        <f>IF(OR(B124="",COUNTIF($B$6:$B124,B124)&gt;1),"",B124)</f>
         <v/>
       </c>
       <c r="Q124">
-        <f>IF(C124="","",C124)</f>
+        <f>IF(P124="","",C124)</f>
         <v/>
       </c>
       <c r="R124">
-        <f>IF(B124="","",SUMIF($B$6:$B$305,B124,$D$6:$D$305))</f>
+        <f>IF(P124="","",SUMIF($B$6:$B$305,B124,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S124">
-        <f>IF(OR(B124="",COUNTIF($B$6:$B124,B124)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R124)+(($R$6:$R$305=R124)*($B$6:$B$305&lt;B124)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P124="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R124,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R124,"="&amp;R124,$P$6:$P124,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20916,19 +20916,19 @@
       <c r="C125" s="56" t="n"/>
       <c r="D125" s="43" t="n"/>
       <c r="P125">
-        <f>IF(B125="","",B125)</f>
+        <f>IF(OR(B125="",COUNTIF($B$6:$B125,B125)&gt;1),"",B125)</f>
         <v/>
       </c>
       <c r="Q125">
-        <f>IF(C125="","",C125)</f>
+        <f>IF(P125="","",C125)</f>
         <v/>
       </c>
       <c r="R125">
-        <f>IF(B125="","",SUMIF($B$6:$B$305,B125,$D$6:$D$305))</f>
+        <f>IF(P125="","",SUMIF($B$6:$B$305,B125,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S125">
-        <f>IF(OR(B125="",COUNTIF($B$6:$B125,B125)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R125)+(($R$6:$R$305=R125)*($B$6:$B$305&lt;B125)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P125="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R125,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R125,"="&amp;R125,$P$6:$P125,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20938,19 +20938,19 @@
       <c r="C126" s="56" t="n"/>
       <c r="D126" s="43" t="n"/>
       <c r="P126">
-        <f>IF(B126="","",B126)</f>
+        <f>IF(OR(B126="",COUNTIF($B$6:$B126,B126)&gt;1),"",B126)</f>
         <v/>
       </c>
       <c r="Q126">
-        <f>IF(C126="","",C126)</f>
+        <f>IF(P126="","",C126)</f>
         <v/>
       </c>
       <c r="R126">
-        <f>IF(B126="","",SUMIF($B$6:$B$305,B126,$D$6:$D$305))</f>
+        <f>IF(P126="","",SUMIF($B$6:$B$305,B126,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S126">
-        <f>IF(OR(B126="",COUNTIF($B$6:$B126,B126)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R126)+(($R$6:$R$305=R126)*($B$6:$B$305&lt;B126)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P126="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R126,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R126,"="&amp;R126,$P$6:$P126,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20960,19 +20960,19 @@
       <c r="C127" s="56" t="n"/>
       <c r="D127" s="43" t="n"/>
       <c r="P127">
-        <f>IF(B127="","",B127)</f>
+        <f>IF(OR(B127="",COUNTIF($B$6:$B127,B127)&gt;1),"",B127)</f>
         <v/>
       </c>
       <c r="Q127">
-        <f>IF(C127="","",C127)</f>
+        <f>IF(P127="","",C127)</f>
         <v/>
       </c>
       <c r="R127">
-        <f>IF(B127="","",SUMIF($B$6:$B$305,B127,$D$6:$D$305))</f>
+        <f>IF(P127="","",SUMIF($B$6:$B$305,B127,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S127">
-        <f>IF(OR(B127="",COUNTIF($B$6:$B127,B127)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R127)+(($R$6:$R$305=R127)*($B$6:$B$305&lt;B127)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P127="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R127,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R127,"="&amp;R127,$P$6:$P127,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -20982,19 +20982,19 @@
       <c r="C128" s="56" t="n"/>
       <c r="D128" s="43" t="n"/>
       <c r="P128">
-        <f>IF(B128="","",B128)</f>
+        <f>IF(OR(B128="",COUNTIF($B$6:$B128,B128)&gt;1),"",B128)</f>
         <v/>
       </c>
       <c r="Q128">
-        <f>IF(C128="","",C128)</f>
+        <f>IF(P128="","",C128)</f>
         <v/>
       </c>
       <c r="R128">
-        <f>IF(B128="","",SUMIF($B$6:$B$305,B128,$D$6:$D$305))</f>
+        <f>IF(P128="","",SUMIF($B$6:$B$305,B128,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S128">
-        <f>IF(OR(B128="",COUNTIF($B$6:$B128,B128)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R128)+(($R$6:$R$305=R128)*($B$6:$B$305&lt;B128)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P128="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R128,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R128,"="&amp;R128,$P$6:$P128,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21004,19 +21004,19 @@
       <c r="C129" s="56" t="n"/>
       <c r="D129" s="43" t="n"/>
       <c r="P129">
-        <f>IF(B129="","",B129)</f>
+        <f>IF(OR(B129="",COUNTIF($B$6:$B129,B129)&gt;1),"",B129)</f>
         <v/>
       </c>
       <c r="Q129">
-        <f>IF(C129="","",C129)</f>
+        <f>IF(P129="","",C129)</f>
         <v/>
       </c>
       <c r="R129">
-        <f>IF(B129="","",SUMIF($B$6:$B$305,B129,$D$6:$D$305))</f>
+        <f>IF(P129="","",SUMIF($B$6:$B$305,B129,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S129">
-        <f>IF(OR(B129="",COUNTIF($B$6:$B129,B129)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R129)+(($R$6:$R$305=R129)*($B$6:$B$305&lt;B129)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P129="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R129,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R129,"="&amp;R129,$P$6:$P129,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21026,19 +21026,19 @@
       <c r="C130" s="56" t="n"/>
       <c r="D130" s="43" t="n"/>
       <c r="P130">
-        <f>IF(B130="","",B130)</f>
+        <f>IF(OR(B130="",COUNTIF($B$6:$B130,B130)&gt;1),"",B130)</f>
         <v/>
       </c>
       <c r="Q130">
-        <f>IF(C130="","",C130)</f>
+        <f>IF(P130="","",C130)</f>
         <v/>
       </c>
       <c r="R130">
-        <f>IF(B130="","",SUMIF($B$6:$B$305,B130,$D$6:$D$305))</f>
+        <f>IF(P130="","",SUMIF($B$6:$B$305,B130,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S130">
-        <f>IF(OR(B130="",COUNTIF($B$6:$B130,B130)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R130)+(($R$6:$R$305=R130)*($B$6:$B$305&lt;B130)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P130="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R130,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R130,"="&amp;R130,$P$6:$P130,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21048,19 +21048,19 @@
       <c r="C131" s="56" t="n"/>
       <c r="D131" s="43" t="n"/>
       <c r="P131">
-        <f>IF(B131="","",B131)</f>
+        <f>IF(OR(B131="",COUNTIF($B$6:$B131,B131)&gt;1),"",B131)</f>
         <v/>
       </c>
       <c r="Q131">
-        <f>IF(C131="","",C131)</f>
+        <f>IF(P131="","",C131)</f>
         <v/>
       </c>
       <c r="R131">
-        <f>IF(B131="","",SUMIF($B$6:$B$305,B131,$D$6:$D$305))</f>
+        <f>IF(P131="","",SUMIF($B$6:$B$305,B131,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S131">
-        <f>IF(OR(B131="",COUNTIF($B$6:$B131,B131)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R131)+(($R$6:$R$305=R131)*($B$6:$B$305&lt;B131)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P131="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R131,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R131,"="&amp;R131,$P$6:$P131,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21070,19 +21070,19 @@
       <c r="C132" s="56" t="n"/>
       <c r="D132" s="43" t="n"/>
       <c r="P132">
-        <f>IF(B132="","",B132)</f>
+        <f>IF(OR(B132="",COUNTIF($B$6:$B132,B132)&gt;1),"",B132)</f>
         <v/>
       </c>
       <c r="Q132">
-        <f>IF(C132="","",C132)</f>
+        <f>IF(P132="","",C132)</f>
         <v/>
       </c>
       <c r="R132">
-        <f>IF(B132="","",SUMIF($B$6:$B$305,B132,$D$6:$D$305))</f>
+        <f>IF(P132="","",SUMIF($B$6:$B$305,B132,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S132">
-        <f>IF(OR(B132="",COUNTIF($B$6:$B132,B132)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R132)+(($R$6:$R$305=R132)*($B$6:$B$305&lt;B132)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P132="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R132,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R132,"="&amp;R132,$P$6:$P132,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21092,19 +21092,19 @@
       <c r="C133" s="56" t="n"/>
       <c r="D133" s="43" t="n"/>
       <c r="P133">
-        <f>IF(B133="","",B133)</f>
+        <f>IF(OR(B133="",COUNTIF($B$6:$B133,B133)&gt;1),"",B133)</f>
         <v/>
       </c>
       <c r="Q133">
-        <f>IF(C133="","",C133)</f>
+        <f>IF(P133="","",C133)</f>
         <v/>
       </c>
       <c r="R133">
-        <f>IF(B133="","",SUMIF($B$6:$B$305,B133,$D$6:$D$305))</f>
+        <f>IF(P133="","",SUMIF($B$6:$B$305,B133,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S133">
-        <f>IF(OR(B133="",COUNTIF($B$6:$B133,B133)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R133)+(($R$6:$R$305=R133)*($B$6:$B$305&lt;B133)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P133="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R133,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R133,"="&amp;R133,$P$6:$P133,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21114,19 +21114,19 @@
       <c r="C134" s="56" t="n"/>
       <c r="D134" s="43" t="n"/>
       <c r="P134">
-        <f>IF(B134="","",B134)</f>
+        <f>IF(OR(B134="",COUNTIF($B$6:$B134,B134)&gt;1),"",B134)</f>
         <v/>
       </c>
       <c r="Q134">
-        <f>IF(C134="","",C134)</f>
+        <f>IF(P134="","",C134)</f>
         <v/>
       </c>
       <c r="R134">
-        <f>IF(B134="","",SUMIF($B$6:$B$305,B134,$D$6:$D$305))</f>
+        <f>IF(P134="","",SUMIF($B$6:$B$305,B134,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S134">
-        <f>IF(OR(B134="",COUNTIF($B$6:$B134,B134)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R134)+(($R$6:$R$305=R134)*($B$6:$B$305&lt;B134)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P134="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R134,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R134,"="&amp;R134,$P$6:$P134,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21136,19 +21136,19 @@
       <c r="C135" s="56" t="n"/>
       <c r="D135" s="43" t="n"/>
       <c r="P135">
-        <f>IF(B135="","",B135)</f>
+        <f>IF(OR(B135="",COUNTIF($B$6:$B135,B135)&gt;1),"",B135)</f>
         <v/>
       </c>
       <c r="Q135">
-        <f>IF(C135="","",C135)</f>
+        <f>IF(P135="","",C135)</f>
         <v/>
       </c>
       <c r="R135">
-        <f>IF(B135="","",SUMIF($B$6:$B$305,B135,$D$6:$D$305))</f>
+        <f>IF(P135="","",SUMIF($B$6:$B$305,B135,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S135">
-        <f>IF(OR(B135="",COUNTIF($B$6:$B135,B135)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R135)+(($R$6:$R$305=R135)*($B$6:$B$305&lt;B135)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P135="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R135,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R135,"="&amp;R135,$P$6:$P135,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21158,19 +21158,19 @@
       <c r="C136" s="56" t="n"/>
       <c r="D136" s="43" t="n"/>
       <c r="P136">
-        <f>IF(B136="","",B136)</f>
+        <f>IF(OR(B136="",COUNTIF($B$6:$B136,B136)&gt;1),"",B136)</f>
         <v/>
       </c>
       <c r="Q136">
-        <f>IF(C136="","",C136)</f>
+        <f>IF(P136="","",C136)</f>
         <v/>
       </c>
       <c r="R136">
-        <f>IF(B136="","",SUMIF($B$6:$B$305,B136,$D$6:$D$305))</f>
+        <f>IF(P136="","",SUMIF($B$6:$B$305,B136,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S136">
-        <f>IF(OR(B136="",COUNTIF($B$6:$B136,B136)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R136)+(($R$6:$R$305=R136)*($B$6:$B$305&lt;B136)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P136="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R136,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R136,"="&amp;R136,$P$6:$P136,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21180,19 +21180,19 @@
       <c r="C137" s="56" t="n"/>
       <c r="D137" s="43" t="n"/>
       <c r="P137">
-        <f>IF(B137="","",B137)</f>
+        <f>IF(OR(B137="",COUNTIF($B$6:$B137,B137)&gt;1),"",B137)</f>
         <v/>
       </c>
       <c r="Q137">
-        <f>IF(C137="","",C137)</f>
+        <f>IF(P137="","",C137)</f>
         <v/>
       </c>
       <c r="R137">
-        <f>IF(B137="","",SUMIF($B$6:$B$305,B137,$D$6:$D$305))</f>
+        <f>IF(P137="","",SUMIF($B$6:$B$305,B137,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S137">
-        <f>IF(OR(B137="",COUNTIF($B$6:$B137,B137)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R137)+(($R$6:$R$305=R137)*($B$6:$B$305&lt;B137)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P137="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R137,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R137,"="&amp;R137,$P$6:$P137,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21202,19 +21202,19 @@
       <c r="C138" s="56" t="n"/>
       <c r="D138" s="43" t="n"/>
       <c r="P138">
-        <f>IF(B138="","",B138)</f>
+        <f>IF(OR(B138="",COUNTIF($B$6:$B138,B138)&gt;1),"",B138)</f>
         <v/>
       </c>
       <c r="Q138">
-        <f>IF(C138="","",C138)</f>
+        <f>IF(P138="","",C138)</f>
         <v/>
       </c>
       <c r="R138">
-        <f>IF(B138="","",SUMIF($B$6:$B$305,B138,$D$6:$D$305))</f>
+        <f>IF(P138="","",SUMIF($B$6:$B$305,B138,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S138">
-        <f>IF(OR(B138="",COUNTIF($B$6:$B138,B138)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R138)+(($R$6:$R$305=R138)*($B$6:$B$305&lt;B138)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P138="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R138,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R138,"="&amp;R138,$P$6:$P138,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21224,19 +21224,19 @@
       <c r="C139" s="56" t="n"/>
       <c r="D139" s="43" t="n"/>
       <c r="P139">
-        <f>IF(B139="","",B139)</f>
+        <f>IF(OR(B139="",COUNTIF($B$6:$B139,B139)&gt;1),"",B139)</f>
         <v/>
       </c>
       <c r="Q139">
-        <f>IF(C139="","",C139)</f>
+        <f>IF(P139="","",C139)</f>
         <v/>
       </c>
       <c r="R139">
-        <f>IF(B139="","",SUMIF($B$6:$B$305,B139,$D$6:$D$305))</f>
+        <f>IF(P139="","",SUMIF($B$6:$B$305,B139,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S139">
-        <f>IF(OR(B139="",COUNTIF($B$6:$B139,B139)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R139)+(($R$6:$R$305=R139)*($B$6:$B$305&lt;B139)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P139="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R139,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R139,"="&amp;R139,$P$6:$P139,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21246,19 +21246,19 @@
       <c r="C140" s="56" t="n"/>
       <c r="D140" s="43" t="n"/>
       <c r="P140">
-        <f>IF(B140="","",B140)</f>
+        <f>IF(OR(B140="",COUNTIF($B$6:$B140,B140)&gt;1),"",B140)</f>
         <v/>
       </c>
       <c r="Q140">
-        <f>IF(C140="","",C140)</f>
+        <f>IF(P140="","",C140)</f>
         <v/>
       </c>
       <c r="R140">
-        <f>IF(B140="","",SUMIF($B$6:$B$305,B140,$D$6:$D$305))</f>
+        <f>IF(P140="","",SUMIF($B$6:$B$305,B140,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S140">
-        <f>IF(OR(B140="",COUNTIF($B$6:$B140,B140)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R140)+(($R$6:$R$305=R140)*($B$6:$B$305&lt;B140)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P140="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R140,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R140,"="&amp;R140,$P$6:$P140,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21268,19 +21268,19 @@
       <c r="C141" s="56" t="n"/>
       <c r="D141" s="43" t="n"/>
       <c r="P141">
-        <f>IF(B141="","",B141)</f>
+        <f>IF(OR(B141="",COUNTIF($B$6:$B141,B141)&gt;1),"",B141)</f>
         <v/>
       </c>
       <c r="Q141">
-        <f>IF(C141="","",C141)</f>
+        <f>IF(P141="","",C141)</f>
         <v/>
       </c>
       <c r="R141">
-        <f>IF(B141="","",SUMIF($B$6:$B$305,B141,$D$6:$D$305))</f>
+        <f>IF(P141="","",SUMIF($B$6:$B$305,B141,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S141">
-        <f>IF(OR(B141="",COUNTIF($B$6:$B141,B141)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R141)+(($R$6:$R$305=R141)*($B$6:$B$305&lt;B141)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P141="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R141,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R141,"="&amp;R141,$P$6:$P141,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21290,19 +21290,19 @@
       <c r="C142" s="56" t="n"/>
       <c r="D142" s="43" t="n"/>
       <c r="P142">
-        <f>IF(B142="","",B142)</f>
+        <f>IF(OR(B142="",COUNTIF($B$6:$B142,B142)&gt;1),"",B142)</f>
         <v/>
       </c>
       <c r="Q142">
-        <f>IF(C142="","",C142)</f>
+        <f>IF(P142="","",C142)</f>
         <v/>
       </c>
       <c r="R142">
-        <f>IF(B142="","",SUMIF($B$6:$B$305,B142,$D$6:$D$305))</f>
+        <f>IF(P142="","",SUMIF($B$6:$B$305,B142,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S142">
-        <f>IF(OR(B142="",COUNTIF($B$6:$B142,B142)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R142)+(($R$6:$R$305=R142)*($B$6:$B$305&lt;B142)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P142="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R142,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R142,"="&amp;R142,$P$6:$P142,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21312,19 +21312,19 @@
       <c r="C143" s="56" t="n"/>
       <c r="D143" s="43" t="n"/>
       <c r="P143">
-        <f>IF(B143="","",B143)</f>
+        <f>IF(OR(B143="",COUNTIF($B$6:$B143,B143)&gt;1),"",B143)</f>
         <v/>
       </c>
       <c r="Q143">
-        <f>IF(C143="","",C143)</f>
+        <f>IF(P143="","",C143)</f>
         <v/>
       </c>
       <c r="R143">
-        <f>IF(B143="","",SUMIF($B$6:$B$305,B143,$D$6:$D$305))</f>
+        <f>IF(P143="","",SUMIF($B$6:$B$305,B143,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S143">
-        <f>IF(OR(B143="",COUNTIF($B$6:$B143,B143)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R143)+(($R$6:$R$305=R143)*($B$6:$B$305&lt;B143)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P143="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R143,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R143,"="&amp;R143,$P$6:$P143,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21334,19 +21334,19 @@
       <c r="C144" s="56" t="n"/>
       <c r="D144" s="43" t="n"/>
       <c r="P144">
-        <f>IF(B144="","",B144)</f>
+        <f>IF(OR(B144="",COUNTIF($B$6:$B144,B144)&gt;1),"",B144)</f>
         <v/>
       </c>
       <c r="Q144">
-        <f>IF(C144="","",C144)</f>
+        <f>IF(P144="","",C144)</f>
         <v/>
       </c>
       <c r="R144">
-        <f>IF(B144="","",SUMIF($B$6:$B$305,B144,$D$6:$D$305))</f>
+        <f>IF(P144="","",SUMIF($B$6:$B$305,B144,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S144">
-        <f>IF(OR(B144="",COUNTIF($B$6:$B144,B144)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R144)+(($R$6:$R$305=R144)*($B$6:$B$305&lt;B144)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P144="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R144,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R144,"="&amp;R144,$P$6:$P144,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21356,19 +21356,19 @@
       <c r="C145" s="56" t="n"/>
       <c r="D145" s="43" t="n"/>
       <c r="P145">
-        <f>IF(B145="","",B145)</f>
+        <f>IF(OR(B145="",COUNTIF($B$6:$B145,B145)&gt;1),"",B145)</f>
         <v/>
       </c>
       <c r="Q145">
-        <f>IF(C145="","",C145)</f>
+        <f>IF(P145="","",C145)</f>
         <v/>
       </c>
       <c r="R145">
-        <f>IF(B145="","",SUMIF($B$6:$B$305,B145,$D$6:$D$305))</f>
+        <f>IF(P145="","",SUMIF($B$6:$B$305,B145,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S145">
-        <f>IF(OR(B145="",COUNTIF($B$6:$B145,B145)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R145)+(($R$6:$R$305=R145)*($B$6:$B$305&lt;B145)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P145="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R145,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R145,"="&amp;R145,$P$6:$P145,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21378,19 +21378,19 @@
       <c r="C146" s="56" t="n"/>
       <c r="D146" s="43" t="n"/>
       <c r="P146">
-        <f>IF(B146="","",B146)</f>
+        <f>IF(OR(B146="",COUNTIF($B$6:$B146,B146)&gt;1),"",B146)</f>
         <v/>
       </c>
       <c r="Q146">
-        <f>IF(C146="","",C146)</f>
+        <f>IF(P146="","",C146)</f>
         <v/>
       </c>
       <c r="R146">
-        <f>IF(B146="","",SUMIF($B$6:$B$305,B146,$D$6:$D$305))</f>
+        <f>IF(P146="","",SUMIF($B$6:$B$305,B146,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S146">
-        <f>IF(OR(B146="",COUNTIF($B$6:$B146,B146)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R146)+(($R$6:$R$305=R146)*($B$6:$B$305&lt;B146)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P146="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R146,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R146,"="&amp;R146,$P$6:$P146,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21400,19 +21400,19 @@
       <c r="C147" s="56" t="n"/>
       <c r="D147" s="43" t="n"/>
       <c r="P147">
-        <f>IF(B147="","",B147)</f>
+        <f>IF(OR(B147="",COUNTIF($B$6:$B147,B147)&gt;1),"",B147)</f>
         <v/>
       </c>
       <c r="Q147">
-        <f>IF(C147="","",C147)</f>
+        <f>IF(P147="","",C147)</f>
         <v/>
       </c>
       <c r="R147">
-        <f>IF(B147="","",SUMIF($B$6:$B$305,B147,$D$6:$D$305))</f>
+        <f>IF(P147="","",SUMIF($B$6:$B$305,B147,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S147">
-        <f>IF(OR(B147="",COUNTIF($B$6:$B147,B147)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R147)+(($R$6:$R$305=R147)*($B$6:$B$305&lt;B147)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P147="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R147,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R147,"="&amp;R147,$P$6:$P147,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21422,19 +21422,19 @@
       <c r="C148" s="56" t="n"/>
       <c r="D148" s="43" t="n"/>
       <c r="P148">
-        <f>IF(B148="","",B148)</f>
+        <f>IF(OR(B148="",COUNTIF($B$6:$B148,B148)&gt;1),"",B148)</f>
         <v/>
       </c>
       <c r="Q148">
-        <f>IF(C148="","",C148)</f>
+        <f>IF(P148="","",C148)</f>
         <v/>
       </c>
       <c r="R148">
-        <f>IF(B148="","",SUMIF($B$6:$B$305,B148,$D$6:$D$305))</f>
+        <f>IF(P148="","",SUMIF($B$6:$B$305,B148,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S148">
-        <f>IF(OR(B148="",COUNTIF($B$6:$B148,B148)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R148)+(($R$6:$R$305=R148)*($B$6:$B$305&lt;B148)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P148="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R148,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R148,"="&amp;R148,$P$6:$P148,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21444,19 +21444,19 @@
       <c r="C149" s="56" t="n"/>
       <c r="D149" s="43" t="n"/>
       <c r="P149">
-        <f>IF(B149="","",B149)</f>
+        <f>IF(OR(B149="",COUNTIF($B$6:$B149,B149)&gt;1),"",B149)</f>
         <v/>
       </c>
       <c r="Q149">
-        <f>IF(C149="","",C149)</f>
+        <f>IF(P149="","",C149)</f>
         <v/>
       </c>
       <c r="R149">
-        <f>IF(B149="","",SUMIF($B$6:$B$305,B149,$D$6:$D$305))</f>
+        <f>IF(P149="","",SUMIF($B$6:$B$305,B149,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S149">
-        <f>IF(OR(B149="",COUNTIF($B$6:$B149,B149)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R149)+(($R$6:$R$305=R149)*($B$6:$B$305&lt;B149)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P149="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R149,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R149,"="&amp;R149,$P$6:$P149,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21466,19 +21466,19 @@
       <c r="C150" s="56" t="n"/>
       <c r="D150" s="43" t="n"/>
       <c r="P150">
-        <f>IF(B150="","",B150)</f>
+        <f>IF(OR(B150="",COUNTIF($B$6:$B150,B150)&gt;1),"",B150)</f>
         <v/>
       </c>
       <c r="Q150">
-        <f>IF(C150="","",C150)</f>
+        <f>IF(P150="","",C150)</f>
         <v/>
       </c>
       <c r="R150">
-        <f>IF(B150="","",SUMIF($B$6:$B$305,B150,$D$6:$D$305))</f>
+        <f>IF(P150="","",SUMIF($B$6:$B$305,B150,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S150">
-        <f>IF(OR(B150="",COUNTIF($B$6:$B150,B150)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R150)+(($R$6:$R$305=R150)*($B$6:$B$305&lt;B150)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P150="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R150,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R150,"="&amp;R150,$P$6:$P150,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21488,19 +21488,19 @@
       <c r="C151" s="56" t="n"/>
       <c r="D151" s="43" t="n"/>
       <c r="P151">
-        <f>IF(B151="","",B151)</f>
+        <f>IF(OR(B151="",COUNTIF($B$6:$B151,B151)&gt;1),"",B151)</f>
         <v/>
       </c>
       <c r="Q151">
-        <f>IF(C151="","",C151)</f>
+        <f>IF(P151="","",C151)</f>
         <v/>
       </c>
       <c r="R151">
-        <f>IF(B151="","",SUMIF($B$6:$B$305,B151,$D$6:$D$305))</f>
+        <f>IF(P151="","",SUMIF($B$6:$B$305,B151,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S151">
-        <f>IF(OR(B151="",COUNTIF($B$6:$B151,B151)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R151)+(($R$6:$R$305=R151)*($B$6:$B$305&lt;B151)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P151="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R151,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R151,"="&amp;R151,$P$6:$P151,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21510,19 +21510,19 @@
       <c r="C152" s="56" t="n"/>
       <c r="D152" s="43" t="n"/>
       <c r="P152">
-        <f>IF(B152="","",B152)</f>
+        <f>IF(OR(B152="",COUNTIF($B$6:$B152,B152)&gt;1),"",B152)</f>
         <v/>
       </c>
       <c r="Q152">
-        <f>IF(C152="","",C152)</f>
+        <f>IF(P152="","",C152)</f>
         <v/>
       </c>
       <c r="R152">
-        <f>IF(B152="","",SUMIF($B$6:$B$305,B152,$D$6:$D$305))</f>
+        <f>IF(P152="","",SUMIF($B$6:$B$305,B152,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S152">
-        <f>IF(OR(B152="",COUNTIF($B$6:$B152,B152)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R152)+(($R$6:$R$305=R152)*($B$6:$B$305&lt;B152)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P152="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R152,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R152,"="&amp;R152,$P$6:$P152,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21532,19 +21532,19 @@
       <c r="C153" s="56" t="n"/>
       <c r="D153" s="43" t="n"/>
       <c r="P153">
-        <f>IF(B153="","",B153)</f>
+        <f>IF(OR(B153="",COUNTIF($B$6:$B153,B153)&gt;1),"",B153)</f>
         <v/>
       </c>
       <c r="Q153">
-        <f>IF(C153="","",C153)</f>
+        <f>IF(P153="","",C153)</f>
         <v/>
       </c>
       <c r="R153">
-        <f>IF(B153="","",SUMIF($B$6:$B$305,B153,$D$6:$D$305))</f>
+        <f>IF(P153="","",SUMIF($B$6:$B$305,B153,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S153">
-        <f>IF(OR(B153="",COUNTIF($B$6:$B153,B153)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R153)+(($R$6:$R$305=R153)*($B$6:$B$305&lt;B153)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P153="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R153,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R153,"="&amp;R153,$P$6:$P153,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21554,19 +21554,19 @@
       <c r="C154" s="56" t="n"/>
       <c r="D154" s="43" t="n"/>
       <c r="P154">
-        <f>IF(B154="","",B154)</f>
+        <f>IF(OR(B154="",COUNTIF($B$6:$B154,B154)&gt;1),"",B154)</f>
         <v/>
       </c>
       <c r="Q154">
-        <f>IF(C154="","",C154)</f>
+        <f>IF(P154="","",C154)</f>
         <v/>
       </c>
       <c r="R154">
-        <f>IF(B154="","",SUMIF($B$6:$B$305,B154,$D$6:$D$305))</f>
+        <f>IF(P154="","",SUMIF($B$6:$B$305,B154,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S154">
-        <f>IF(OR(B154="",COUNTIF($B$6:$B154,B154)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R154)+(($R$6:$R$305=R154)*($B$6:$B$305&lt;B154)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P154="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R154,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R154,"="&amp;R154,$P$6:$P154,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21576,19 +21576,19 @@
       <c r="C155" s="56" t="n"/>
       <c r="D155" s="43" t="n"/>
       <c r="P155">
-        <f>IF(B155="","",B155)</f>
+        <f>IF(OR(B155="",COUNTIF($B$6:$B155,B155)&gt;1),"",B155)</f>
         <v/>
       </c>
       <c r="Q155">
-        <f>IF(C155="","",C155)</f>
+        <f>IF(P155="","",C155)</f>
         <v/>
       </c>
       <c r="R155">
-        <f>IF(B155="","",SUMIF($B$6:$B$305,B155,$D$6:$D$305))</f>
+        <f>IF(P155="","",SUMIF($B$6:$B$305,B155,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S155">
-        <f>IF(OR(B155="",COUNTIF($B$6:$B155,B155)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R155)+(($R$6:$R$305=R155)*($B$6:$B$305&lt;B155)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P155="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R155,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R155,"="&amp;R155,$P$6:$P155,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21598,19 +21598,19 @@
       <c r="C156" s="56" t="n"/>
       <c r="D156" s="43" t="n"/>
       <c r="P156">
-        <f>IF(B156="","",B156)</f>
+        <f>IF(OR(B156="",COUNTIF($B$6:$B156,B156)&gt;1),"",B156)</f>
         <v/>
       </c>
       <c r="Q156">
-        <f>IF(C156="","",C156)</f>
+        <f>IF(P156="","",C156)</f>
         <v/>
       </c>
       <c r="R156">
-        <f>IF(B156="","",SUMIF($B$6:$B$305,B156,$D$6:$D$305))</f>
+        <f>IF(P156="","",SUMIF($B$6:$B$305,B156,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S156">
-        <f>IF(OR(B156="",COUNTIF($B$6:$B156,B156)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R156)+(($R$6:$R$305=R156)*($B$6:$B$305&lt;B156)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P156="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R156,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R156,"="&amp;R156,$P$6:$P156,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21620,19 +21620,19 @@
       <c r="C157" s="56" t="n"/>
       <c r="D157" s="43" t="n"/>
       <c r="P157">
-        <f>IF(B157="","",B157)</f>
+        <f>IF(OR(B157="",COUNTIF($B$6:$B157,B157)&gt;1),"",B157)</f>
         <v/>
       </c>
       <c r="Q157">
-        <f>IF(C157="","",C157)</f>
+        <f>IF(P157="","",C157)</f>
         <v/>
       </c>
       <c r="R157">
-        <f>IF(B157="","",SUMIF($B$6:$B$305,B157,$D$6:$D$305))</f>
+        <f>IF(P157="","",SUMIF($B$6:$B$305,B157,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S157">
-        <f>IF(OR(B157="",COUNTIF($B$6:$B157,B157)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R157)+(($R$6:$R$305=R157)*($B$6:$B$305&lt;B157)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P157="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R157,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R157,"="&amp;R157,$P$6:$P157,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21642,19 +21642,19 @@
       <c r="C158" s="56" t="n"/>
       <c r="D158" s="43" t="n"/>
       <c r="P158">
-        <f>IF(B158="","",B158)</f>
+        <f>IF(OR(B158="",COUNTIF($B$6:$B158,B158)&gt;1),"",B158)</f>
         <v/>
       </c>
       <c r="Q158">
-        <f>IF(C158="","",C158)</f>
+        <f>IF(P158="","",C158)</f>
         <v/>
       </c>
       <c r="R158">
-        <f>IF(B158="","",SUMIF($B$6:$B$305,B158,$D$6:$D$305))</f>
+        <f>IF(P158="","",SUMIF($B$6:$B$305,B158,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S158">
-        <f>IF(OR(B158="",COUNTIF($B$6:$B158,B158)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R158)+(($R$6:$R$305=R158)*($B$6:$B$305&lt;B158)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P158="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R158,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R158,"="&amp;R158,$P$6:$P158,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21664,19 +21664,19 @@
       <c r="C159" s="56" t="n"/>
       <c r="D159" s="43" t="n"/>
       <c r="P159">
-        <f>IF(B159="","",B159)</f>
+        <f>IF(OR(B159="",COUNTIF($B$6:$B159,B159)&gt;1),"",B159)</f>
         <v/>
       </c>
       <c r="Q159">
-        <f>IF(C159="","",C159)</f>
+        <f>IF(P159="","",C159)</f>
         <v/>
       </c>
       <c r="R159">
-        <f>IF(B159="","",SUMIF($B$6:$B$305,B159,$D$6:$D$305))</f>
+        <f>IF(P159="","",SUMIF($B$6:$B$305,B159,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S159">
-        <f>IF(OR(B159="",COUNTIF($B$6:$B159,B159)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R159)+(($R$6:$R$305=R159)*($B$6:$B$305&lt;B159)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P159="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R159,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R159,"="&amp;R159,$P$6:$P159,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21686,19 +21686,19 @@
       <c r="C160" s="56" t="n"/>
       <c r="D160" s="43" t="n"/>
       <c r="P160">
-        <f>IF(B160="","",B160)</f>
+        <f>IF(OR(B160="",COUNTIF($B$6:$B160,B160)&gt;1),"",B160)</f>
         <v/>
       </c>
       <c r="Q160">
-        <f>IF(C160="","",C160)</f>
+        <f>IF(P160="","",C160)</f>
         <v/>
       </c>
       <c r="R160">
-        <f>IF(B160="","",SUMIF($B$6:$B$305,B160,$D$6:$D$305))</f>
+        <f>IF(P160="","",SUMIF($B$6:$B$305,B160,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S160">
-        <f>IF(OR(B160="",COUNTIF($B$6:$B160,B160)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R160)+(($R$6:$R$305=R160)*($B$6:$B$305&lt;B160)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P160="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R160,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R160,"="&amp;R160,$P$6:$P160,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21708,19 +21708,19 @@
       <c r="C161" s="56" t="n"/>
       <c r="D161" s="43" t="n"/>
       <c r="P161">
-        <f>IF(B161="","",B161)</f>
+        <f>IF(OR(B161="",COUNTIF($B$6:$B161,B161)&gt;1),"",B161)</f>
         <v/>
       </c>
       <c r="Q161">
-        <f>IF(C161="","",C161)</f>
+        <f>IF(P161="","",C161)</f>
         <v/>
       </c>
       <c r="R161">
-        <f>IF(B161="","",SUMIF($B$6:$B$305,B161,$D$6:$D$305))</f>
+        <f>IF(P161="","",SUMIF($B$6:$B$305,B161,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S161">
-        <f>IF(OR(B161="",COUNTIF($B$6:$B161,B161)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R161)+(($R$6:$R$305=R161)*($B$6:$B$305&lt;B161)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P161="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R161,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R161,"="&amp;R161,$P$6:$P161,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21730,19 +21730,19 @@
       <c r="C162" s="56" t="n"/>
       <c r="D162" s="43" t="n"/>
       <c r="P162">
-        <f>IF(B162="","",B162)</f>
+        <f>IF(OR(B162="",COUNTIF($B$6:$B162,B162)&gt;1),"",B162)</f>
         <v/>
       </c>
       <c r="Q162">
-        <f>IF(C162="","",C162)</f>
+        <f>IF(P162="","",C162)</f>
         <v/>
       </c>
       <c r="R162">
-        <f>IF(B162="","",SUMIF($B$6:$B$305,B162,$D$6:$D$305))</f>
+        <f>IF(P162="","",SUMIF($B$6:$B$305,B162,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S162">
-        <f>IF(OR(B162="",COUNTIF($B$6:$B162,B162)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R162)+(($R$6:$R$305=R162)*($B$6:$B$305&lt;B162)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P162="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R162,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R162,"="&amp;R162,$P$6:$P162,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21752,19 +21752,19 @@
       <c r="C163" s="56" t="n"/>
       <c r="D163" s="43" t="n"/>
       <c r="P163">
-        <f>IF(B163="","",B163)</f>
+        <f>IF(OR(B163="",COUNTIF($B$6:$B163,B163)&gt;1),"",B163)</f>
         <v/>
       </c>
       <c r="Q163">
-        <f>IF(C163="","",C163)</f>
+        <f>IF(P163="","",C163)</f>
         <v/>
       </c>
       <c r="R163">
-        <f>IF(B163="","",SUMIF($B$6:$B$305,B163,$D$6:$D$305))</f>
+        <f>IF(P163="","",SUMIF($B$6:$B$305,B163,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S163">
-        <f>IF(OR(B163="",COUNTIF($B$6:$B163,B163)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R163)+(($R$6:$R$305=R163)*($B$6:$B$305&lt;B163)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P163="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R163,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R163,"="&amp;R163,$P$6:$P163,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21774,19 +21774,19 @@
       <c r="C164" s="56" t="n"/>
       <c r="D164" s="43" t="n"/>
       <c r="P164">
-        <f>IF(B164="","",B164)</f>
+        <f>IF(OR(B164="",COUNTIF($B$6:$B164,B164)&gt;1),"",B164)</f>
         <v/>
       </c>
       <c r="Q164">
-        <f>IF(C164="","",C164)</f>
+        <f>IF(P164="","",C164)</f>
         <v/>
       </c>
       <c r="R164">
-        <f>IF(B164="","",SUMIF($B$6:$B$305,B164,$D$6:$D$305))</f>
+        <f>IF(P164="","",SUMIF($B$6:$B$305,B164,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S164">
-        <f>IF(OR(B164="",COUNTIF($B$6:$B164,B164)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R164)+(($R$6:$R$305=R164)*($B$6:$B$305&lt;B164)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P164="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R164,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R164,"="&amp;R164,$P$6:$P164,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21796,19 +21796,19 @@
       <c r="C165" s="56" t="n"/>
       <c r="D165" s="43" t="n"/>
       <c r="P165">
-        <f>IF(B165="","",B165)</f>
+        <f>IF(OR(B165="",COUNTIF($B$6:$B165,B165)&gt;1),"",B165)</f>
         <v/>
       </c>
       <c r="Q165">
-        <f>IF(C165="","",C165)</f>
+        <f>IF(P165="","",C165)</f>
         <v/>
       </c>
       <c r="R165">
-        <f>IF(B165="","",SUMIF($B$6:$B$305,B165,$D$6:$D$305))</f>
+        <f>IF(P165="","",SUMIF($B$6:$B$305,B165,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S165">
-        <f>IF(OR(B165="",COUNTIF($B$6:$B165,B165)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R165)+(($R$6:$R$305=R165)*($B$6:$B$305&lt;B165)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P165="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R165,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R165,"="&amp;R165,$P$6:$P165,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21818,19 +21818,19 @@
       <c r="C166" s="56" t="n"/>
       <c r="D166" s="43" t="n"/>
       <c r="P166">
-        <f>IF(B166="","",B166)</f>
+        <f>IF(OR(B166="",COUNTIF($B$6:$B166,B166)&gt;1),"",B166)</f>
         <v/>
       </c>
       <c r="Q166">
-        <f>IF(C166="","",C166)</f>
+        <f>IF(P166="","",C166)</f>
         <v/>
       </c>
       <c r="R166">
-        <f>IF(B166="","",SUMIF($B$6:$B$305,B166,$D$6:$D$305))</f>
+        <f>IF(P166="","",SUMIF($B$6:$B$305,B166,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S166">
-        <f>IF(OR(B166="",COUNTIF($B$6:$B166,B166)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R166)+(($R$6:$R$305=R166)*($B$6:$B$305&lt;B166)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P166="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R166,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R166,"="&amp;R166,$P$6:$P166,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21840,19 +21840,19 @@
       <c r="C167" s="56" t="n"/>
       <c r="D167" s="43" t="n"/>
       <c r="P167">
-        <f>IF(B167="","",B167)</f>
+        <f>IF(OR(B167="",COUNTIF($B$6:$B167,B167)&gt;1),"",B167)</f>
         <v/>
       </c>
       <c r="Q167">
-        <f>IF(C167="","",C167)</f>
+        <f>IF(P167="","",C167)</f>
         <v/>
       </c>
       <c r="R167">
-        <f>IF(B167="","",SUMIF($B$6:$B$305,B167,$D$6:$D$305))</f>
+        <f>IF(P167="","",SUMIF($B$6:$B$305,B167,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S167">
-        <f>IF(OR(B167="",COUNTIF($B$6:$B167,B167)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R167)+(($R$6:$R$305=R167)*($B$6:$B$305&lt;B167)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P167="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R167,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R167,"="&amp;R167,$P$6:$P167,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21862,19 +21862,19 @@
       <c r="C168" s="56" t="n"/>
       <c r="D168" s="43" t="n"/>
       <c r="P168">
-        <f>IF(B168="","",B168)</f>
+        <f>IF(OR(B168="",COUNTIF($B$6:$B168,B168)&gt;1),"",B168)</f>
         <v/>
       </c>
       <c r="Q168">
-        <f>IF(C168="","",C168)</f>
+        <f>IF(P168="","",C168)</f>
         <v/>
       </c>
       <c r="R168">
-        <f>IF(B168="","",SUMIF($B$6:$B$305,B168,$D$6:$D$305))</f>
+        <f>IF(P168="","",SUMIF($B$6:$B$305,B168,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S168">
-        <f>IF(OR(B168="",COUNTIF($B$6:$B168,B168)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R168)+(($R$6:$R$305=R168)*($B$6:$B$305&lt;B168)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P168="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R168,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R168,"="&amp;R168,$P$6:$P168,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21884,19 +21884,19 @@
       <c r="C169" s="56" t="n"/>
       <c r="D169" s="43" t="n"/>
       <c r="P169">
-        <f>IF(B169="","",B169)</f>
+        <f>IF(OR(B169="",COUNTIF($B$6:$B169,B169)&gt;1),"",B169)</f>
         <v/>
       </c>
       <c r="Q169">
-        <f>IF(C169="","",C169)</f>
+        <f>IF(P169="","",C169)</f>
         <v/>
       </c>
       <c r="R169">
-        <f>IF(B169="","",SUMIF($B$6:$B$305,B169,$D$6:$D$305))</f>
+        <f>IF(P169="","",SUMIF($B$6:$B$305,B169,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S169">
-        <f>IF(OR(B169="",COUNTIF($B$6:$B169,B169)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R169)+(($R$6:$R$305=R169)*($B$6:$B$305&lt;B169)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P169="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R169,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R169,"="&amp;R169,$P$6:$P169,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21906,19 +21906,19 @@
       <c r="C170" s="56" t="n"/>
       <c r="D170" s="43" t="n"/>
       <c r="P170">
-        <f>IF(B170="","",B170)</f>
+        <f>IF(OR(B170="",COUNTIF($B$6:$B170,B170)&gt;1),"",B170)</f>
         <v/>
       </c>
       <c r="Q170">
-        <f>IF(C170="","",C170)</f>
+        <f>IF(P170="","",C170)</f>
         <v/>
       </c>
       <c r="R170">
-        <f>IF(B170="","",SUMIF($B$6:$B$305,B170,$D$6:$D$305))</f>
+        <f>IF(P170="","",SUMIF($B$6:$B$305,B170,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S170">
-        <f>IF(OR(B170="",COUNTIF($B$6:$B170,B170)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R170)+(($R$6:$R$305=R170)*($B$6:$B$305&lt;B170)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P170="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R170,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R170,"="&amp;R170,$P$6:$P170,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21928,19 +21928,19 @@
       <c r="C171" s="56" t="n"/>
       <c r="D171" s="43" t="n"/>
       <c r="P171">
-        <f>IF(B171="","",B171)</f>
+        <f>IF(OR(B171="",COUNTIF($B$6:$B171,B171)&gt;1),"",B171)</f>
         <v/>
       </c>
       <c r="Q171">
-        <f>IF(C171="","",C171)</f>
+        <f>IF(P171="","",C171)</f>
         <v/>
       </c>
       <c r="R171">
-        <f>IF(B171="","",SUMIF($B$6:$B$305,B171,$D$6:$D$305))</f>
+        <f>IF(P171="","",SUMIF($B$6:$B$305,B171,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S171">
-        <f>IF(OR(B171="",COUNTIF($B$6:$B171,B171)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R171)+(($R$6:$R$305=R171)*($B$6:$B$305&lt;B171)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P171="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R171,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R171,"="&amp;R171,$P$6:$P171,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21950,19 +21950,19 @@
       <c r="C172" s="56" t="n"/>
       <c r="D172" s="43" t="n"/>
       <c r="P172">
-        <f>IF(B172="","",B172)</f>
+        <f>IF(OR(B172="",COUNTIF($B$6:$B172,B172)&gt;1),"",B172)</f>
         <v/>
       </c>
       <c r="Q172">
-        <f>IF(C172="","",C172)</f>
+        <f>IF(P172="","",C172)</f>
         <v/>
       </c>
       <c r="R172">
-        <f>IF(B172="","",SUMIF($B$6:$B$305,B172,$D$6:$D$305))</f>
+        <f>IF(P172="","",SUMIF($B$6:$B$305,B172,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S172">
-        <f>IF(OR(B172="",COUNTIF($B$6:$B172,B172)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R172)+(($R$6:$R$305=R172)*($B$6:$B$305&lt;B172)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P172="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R172,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R172,"="&amp;R172,$P$6:$P172,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21972,19 +21972,19 @@
       <c r="C173" s="56" t="n"/>
       <c r="D173" s="43" t="n"/>
       <c r="P173">
-        <f>IF(B173="","",B173)</f>
+        <f>IF(OR(B173="",COUNTIF($B$6:$B173,B173)&gt;1),"",B173)</f>
         <v/>
       </c>
       <c r="Q173">
-        <f>IF(C173="","",C173)</f>
+        <f>IF(P173="","",C173)</f>
         <v/>
       </c>
       <c r="R173">
-        <f>IF(B173="","",SUMIF($B$6:$B$305,B173,$D$6:$D$305))</f>
+        <f>IF(P173="","",SUMIF($B$6:$B$305,B173,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S173">
-        <f>IF(OR(B173="",COUNTIF($B$6:$B173,B173)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R173)+(($R$6:$R$305=R173)*($B$6:$B$305&lt;B173)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P173="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R173,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R173,"="&amp;R173,$P$6:$P173,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -21994,19 +21994,19 @@
       <c r="C174" s="56" t="n"/>
       <c r="D174" s="43" t="n"/>
       <c r="P174">
-        <f>IF(B174="","",B174)</f>
+        <f>IF(OR(B174="",COUNTIF($B$6:$B174,B174)&gt;1),"",B174)</f>
         <v/>
       </c>
       <c r="Q174">
-        <f>IF(C174="","",C174)</f>
+        <f>IF(P174="","",C174)</f>
         <v/>
       </c>
       <c r="R174">
-        <f>IF(B174="","",SUMIF($B$6:$B$305,B174,$D$6:$D$305))</f>
+        <f>IF(P174="","",SUMIF($B$6:$B$305,B174,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S174">
-        <f>IF(OR(B174="",COUNTIF($B$6:$B174,B174)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R174)+(($R$6:$R$305=R174)*($B$6:$B$305&lt;B174)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P174="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R174,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R174,"="&amp;R174,$P$6:$P174,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22016,19 +22016,19 @@
       <c r="C175" s="56" t="n"/>
       <c r="D175" s="43" t="n"/>
       <c r="P175">
-        <f>IF(B175="","",B175)</f>
+        <f>IF(OR(B175="",COUNTIF($B$6:$B175,B175)&gt;1),"",B175)</f>
         <v/>
       </c>
       <c r="Q175">
-        <f>IF(C175="","",C175)</f>
+        <f>IF(P175="","",C175)</f>
         <v/>
       </c>
       <c r="R175">
-        <f>IF(B175="","",SUMIF($B$6:$B$305,B175,$D$6:$D$305))</f>
+        <f>IF(P175="","",SUMIF($B$6:$B$305,B175,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S175">
-        <f>IF(OR(B175="",COUNTIF($B$6:$B175,B175)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R175)+(($R$6:$R$305=R175)*($B$6:$B$305&lt;B175)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P175="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R175,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R175,"="&amp;R175,$P$6:$P175,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22038,19 +22038,19 @@
       <c r="C176" s="56" t="n"/>
       <c r="D176" s="43" t="n"/>
       <c r="P176">
-        <f>IF(B176="","",B176)</f>
+        <f>IF(OR(B176="",COUNTIF($B$6:$B176,B176)&gt;1),"",B176)</f>
         <v/>
       </c>
       <c r="Q176">
-        <f>IF(C176="","",C176)</f>
+        <f>IF(P176="","",C176)</f>
         <v/>
       </c>
       <c r="R176">
-        <f>IF(B176="","",SUMIF($B$6:$B$305,B176,$D$6:$D$305))</f>
+        <f>IF(P176="","",SUMIF($B$6:$B$305,B176,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S176">
-        <f>IF(OR(B176="",COUNTIF($B$6:$B176,B176)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R176)+(($R$6:$R$305=R176)*($B$6:$B$305&lt;B176)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P176="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R176,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R176,"="&amp;R176,$P$6:$P176,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22060,19 +22060,19 @@
       <c r="C177" s="56" t="n"/>
       <c r="D177" s="43" t="n"/>
       <c r="P177">
-        <f>IF(B177="","",B177)</f>
+        <f>IF(OR(B177="",COUNTIF($B$6:$B177,B177)&gt;1),"",B177)</f>
         <v/>
       </c>
       <c r="Q177">
-        <f>IF(C177="","",C177)</f>
+        <f>IF(P177="","",C177)</f>
         <v/>
       </c>
       <c r="R177">
-        <f>IF(B177="","",SUMIF($B$6:$B$305,B177,$D$6:$D$305))</f>
+        <f>IF(P177="","",SUMIF($B$6:$B$305,B177,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S177">
-        <f>IF(OR(B177="",COUNTIF($B$6:$B177,B177)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R177)+(($R$6:$R$305=R177)*($B$6:$B$305&lt;B177)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P177="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R177,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R177,"="&amp;R177,$P$6:$P177,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22082,19 +22082,19 @@
       <c r="C178" s="56" t="n"/>
       <c r="D178" s="43" t="n"/>
       <c r="P178">
-        <f>IF(B178="","",B178)</f>
+        <f>IF(OR(B178="",COUNTIF($B$6:$B178,B178)&gt;1),"",B178)</f>
         <v/>
       </c>
       <c r="Q178">
-        <f>IF(C178="","",C178)</f>
+        <f>IF(P178="","",C178)</f>
         <v/>
       </c>
       <c r="R178">
-        <f>IF(B178="","",SUMIF($B$6:$B$305,B178,$D$6:$D$305))</f>
+        <f>IF(P178="","",SUMIF($B$6:$B$305,B178,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S178">
-        <f>IF(OR(B178="",COUNTIF($B$6:$B178,B178)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R178)+(($R$6:$R$305=R178)*($B$6:$B$305&lt;B178)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P178="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R178,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R178,"="&amp;R178,$P$6:$P178,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22104,19 +22104,19 @@
       <c r="C179" s="56" t="n"/>
       <c r="D179" s="43" t="n"/>
       <c r="P179">
-        <f>IF(B179="","",B179)</f>
+        <f>IF(OR(B179="",COUNTIF($B$6:$B179,B179)&gt;1),"",B179)</f>
         <v/>
       </c>
       <c r="Q179">
-        <f>IF(C179="","",C179)</f>
+        <f>IF(P179="","",C179)</f>
         <v/>
       </c>
       <c r="R179">
-        <f>IF(B179="","",SUMIF($B$6:$B$305,B179,$D$6:$D$305))</f>
+        <f>IF(P179="","",SUMIF($B$6:$B$305,B179,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S179">
-        <f>IF(OR(B179="",COUNTIF($B$6:$B179,B179)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R179)+(($R$6:$R$305=R179)*($B$6:$B$305&lt;B179)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P179="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R179,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R179,"="&amp;R179,$P$6:$P179,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22126,19 +22126,19 @@
       <c r="C180" s="56" t="n"/>
       <c r="D180" s="43" t="n"/>
       <c r="P180">
-        <f>IF(B180="","",B180)</f>
+        <f>IF(OR(B180="",COUNTIF($B$6:$B180,B180)&gt;1),"",B180)</f>
         <v/>
       </c>
       <c r="Q180">
-        <f>IF(C180="","",C180)</f>
+        <f>IF(P180="","",C180)</f>
         <v/>
       </c>
       <c r="R180">
-        <f>IF(B180="","",SUMIF($B$6:$B$305,B180,$D$6:$D$305))</f>
+        <f>IF(P180="","",SUMIF($B$6:$B$305,B180,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S180">
-        <f>IF(OR(B180="",COUNTIF($B$6:$B180,B180)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R180)+(($R$6:$R$305=R180)*($B$6:$B$305&lt;B180)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P180="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R180,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R180,"="&amp;R180,$P$6:$P180,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22148,19 +22148,19 @@
       <c r="C181" s="56" t="n"/>
       <c r="D181" s="43" t="n"/>
       <c r="P181">
-        <f>IF(B181="","",B181)</f>
+        <f>IF(OR(B181="",COUNTIF($B$6:$B181,B181)&gt;1),"",B181)</f>
         <v/>
       </c>
       <c r="Q181">
-        <f>IF(C181="","",C181)</f>
+        <f>IF(P181="","",C181)</f>
         <v/>
       </c>
       <c r="R181">
-        <f>IF(B181="","",SUMIF($B$6:$B$305,B181,$D$6:$D$305))</f>
+        <f>IF(P181="","",SUMIF($B$6:$B$305,B181,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S181">
-        <f>IF(OR(B181="",COUNTIF($B$6:$B181,B181)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R181)+(($R$6:$R$305=R181)*($B$6:$B$305&lt;B181)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P181="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R181,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R181,"="&amp;R181,$P$6:$P181,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22170,19 +22170,19 @@
       <c r="C182" s="56" t="n"/>
       <c r="D182" s="43" t="n"/>
       <c r="P182">
-        <f>IF(B182="","",B182)</f>
+        <f>IF(OR(B182="",COUNTIF($B$6:$B182,B182)&gt;1),"",B182)</f>
         <v/>
       </c>
       <c r="Q182">
-        <f>IF(C182="","",C182)</f>
+        <f>IF(P182="","",C182)</f>
         <v/>
       </c>
       <c r="R182">
-        <f>IF(B182="","",SUMIF($B$6:$B$305,B182,$D$6:$D$305))</f>
+        <f>IF(P182="","",SUMIF($B$6:$B$305,B182,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S182">
-        <f>IF(OR(B182="",COUNTIF($B$6:$B182,B182)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R182)+(($R$6:$R$305=R182)*($B$6:$B$305&lt;B182)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P182="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R182,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R182,"="&amp;R182,$P$6:$P182,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22192,19 +22192,19 @@
       <c r="C183" s="56" t="n"/>
       <c r="D183" s="43" t="n"/>
       <c r="P183">
-        <f>IF(B183="","",B183)</f>
+        <f>IF(OR(B183="",COUNTIF($B$6:$B183,B183)&gt;1),"",B183)</f>
         <v/>
       </c>
       <c r="Q183">
-        <f>IF(C183="","",C183)</f>
+        <f>IF(P183="","",C183)</f>
         <v/>
       </c>
       <c r="R183">
-        <f>IF(B183="","",SUMIF($B$6:$B$305,B183,$D$6:$D$305))</f>
+        <f>IF(P183="","",SUMIF($B$6:$B$305,B183,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S183">
-        <f>IF(OR(B183="",COUNTIF($B$6:$B183,B183)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R183)+(($R$6:$R$305=R183)*($B$6:$B$305&lt;B183)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P183="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R183,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R183,"="&amp;R183,$P$6:$P183,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22214,19 +22214,19 @@
       <c r="C184" s="56" t="n"/>
       <c r="D184" s="43" t="n"/>
       <c r="P184">
-        <f>IF(B184="","",B184)</f>
+        <f>IF(OR(B184="",COUNTIF($B$6:$B184,B184)&gt;1),"",B184)</f>
         <v/>
       </c>
       <c r="Q184">
-        <f>IF(C184="","",C184)</f>
+        <f>IF(P184="","",C184)</f>
         <v/>
       </c>
       <c r="R184">
-        <f>IF(B184="","",SUMIF($B$6:$B$305,B184,$D$6:$D$305))</f>
+        <f>IF(P184="","",SUMIF($B$6:$B$305,B184,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S184">
-        <f>IF(OR(B184="",COUNTIF($B$6:$B184,B184)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R184)+(($R$6:$R$305=R184)*($B$6:$B$305&lt;B184)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P184="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R184,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R184,"="&amp;R184,$P$6:$P184,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22236,19 +22236,19 @@
       <c r="C185" s="56" t="n"/>
       <c r="D185" s="43" t="n"/>
       <c r="P185">
-        <f>IF(B185="","",B185)</f>
+        <f>IF(OR(B185="",COUNTIF($B$6:$B185,B185)&gt;1),"",B185)</f>
         <v/>
       </c>
       <c r="Q185">
-        <f>IF(C185="","",C185)</f>
+        <f>IF(P185="","",C185)</f>
         <v/>
       </c>
       <c r="R185">
-        <f>IF(B185="","",SUMIF($B$6:$B$305,B185,$D$6:$D$305))</f>
+        <f>IF(P185="","",SUMIF($B$6:$B$305,B185,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S185">
-        <f>IF(OR(B185="",COUNTIF($B$6:$B185,B185)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R185)+(($R$6:$R$305=R185)*($B$6:$B$305&lt;B185)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P185="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R185,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R185,"="&amp;R185,$P$6:$P185,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22258,19 +22258,19 @@
       <c r="C186" s="56" t="n"/>
       <c r="D186" s="43" t="n"/>
       <c r="P186">
-        <f>IF(B186="","",B186)</f>
+        <f>IF(OR(B186="",COUNTIF($B$6:$B186,B186)&gt;1),"",B186)</f>
         <v/>
       </c>
       <c r="Q186">
-        <f>IF(C186="","",C186)</f>
+        <f>IF(P186="","",C186)</f>
         <v/>
       </c>
       <c r="R186">
-        <f>IF(B186="","",SUMIF($B$6:$B$305,B186,$D$6:$D$305))</f>
+        <f>IF(P186="","",SUMIF($B$6:$B$305,B186,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S186">
-        <f>IF(OR(B186="",COUNTIF($B$6:$B186,B186)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R186)+(($R$6:$R$305=R186)*($B$6:$B$305&lt;B186)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P186="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R186,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R186,"="&amp;R186,$P$6:$P186,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22280,19 +22280,19 @@
       <c r="C187" s="56" t="n"/>
       <c r="D187" s="43" t="n"/>
       <c r="P187">
-        <f>IF(B187="","",B187)</f>
+        <f>IF(OR(B187="",COUNTIF($B$6:$B187,B187)&gt;1),"",B187)</f>
         <v/>
       </c>
       <c r="Q187">
-        <f>IF(C187="","",C187)</f>
+        <f>IF(P187="","",C187)</f>
         <v/>
       </c>
       <c r="R187">
-        <f>IF(B187="","",SUMIF($B$6:$B$305,B187,$D$6:$D$305))</f>
+        <f>IF(P187="","",SUMIF($B$6:$B$305,B187,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S187">
-        <f>IF(OR(B187="",COUNTIF($B$6:$B187,B187)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R187)+(($R$6:$R$305=R187)*($B$6:$B$305&lt;B187)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P187="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R187,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R187,"="&amp;R187,$P$6:$P187,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22302,19 +22302,19 @@
       <c r="C188" s="56" t="n"/>
       <c r="D188" s="43" t="n"/>
       <c r="P188">
-        <f>IF(B188="","",B188)</f>
+        <f>IF(OR(B188="",COUNTIF($B$6:$B188,B188)&gt;1),"",B188)</f>
         <v/>
       </c>
       <c r="Q188">
-        <f>IF(C188="","",C188)</f>
+        <f>IF(P188="","",C188)</f>
         <v/>
       </c>
       <c r="R188">
-        <f>IF(B188="","",SUMIF($B$6:$B$305,B188,$D$6:$D$305))</f>
+        <f>IF(P188="","",SUMIF($B$6:$B$305,B188,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S188">
-        <f>IF(OR(B188="",COUNTIF($B$6:$B188,B188)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R188)+(($R$6:$R$305=R188)*($B$6:$B$305&lt;B188)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P188="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R188,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R188,"="&amp;R188,$P$6:$P188,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22324,19 +22324,19 @@
       <c r="C189" s="56" t="n"/>
       <c r="D189" s="43" t="n"/>
       <c r="P189">
-        <f>IF(B189="","",B189)</f>
+        <f>IF(OR(B189="",COUNTIF($B$6:$B189,B189)&gt;1),"",B189)</f>
         <v/>
       </c>
       <c r="Q189">
-        <f>IF(C189="","",C189)</f>
+        <f>IF(P189="","",C189)</f>
         <v/>
       </c>
       <c r="R189">
-        <f>IF(B189="","",SUMIF($B$6:$B$305,B189,$D$6:$D$305))</f>
+        <f>IF(P189="","",SUMIF($B$6:$B$305,B189,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S189">
-        <f>IF(OR(B189="",COUNTIF($B$6:$B189,B189)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R189)+(($R$6:$R$305=R189)*($B$6:$B$305&lt;B189)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P189="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R189,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R189,"="&amp;R189,$P$6:$P189,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22346,19 +22346,19 @@
       <c r="C190" s="56" t="n"/>
       <c r="D190" s="43" t="n"/>
       <c r="P190">
-        <f>IF(B190="","",B190)</f>
+        <f>IF(OR(B190="",COUNTIF($B$6:$B190,B190)&gt;1),"",B190)</f>
         <v/>
       </c>
       <c r="Q190">
-        <f>IF(C190="","",C190)</f>
+        <f>IF(P190="","",C190)</f>
         <v/>
       </c>
       <c r="R190">
-        <f>IF(B190="","",SUMIF($B$6:$B$305,B190,$D$6:$D$305))</f>
+        <f>IF(P190="","",SUMIF($B$6:$B$305,B190,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S190">
-        <f>IF(OR(B190="",COUNTIF($B$6:$B190,B190)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R190)+(($R$6:$R$305=R190)*($B$6:$B$305&lt;B190)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P190="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R190,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R190,"="&amp;R190,$P$6:$P190,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22368,19 +22368,19 @@
       <c r="C191" s="56" t="n"/>
       <c r="D191" s="43" t="n"/>
       <c r="P191">
-        <f>IF(B191="","",B191)</f>
+        <f>IF(OR(B191="",COUNTIF($B$6:$B191,B191)&gt;1),"",B191)</f>
         <v/>
       </c>
       <c r="Q191">
-        <f>IF(C191="","",C191)</f>
+        <f>IF(P191="","",C191)</f>
         <v/>
       </c>
       <c r="R191">
-        <f>IF(B191="","",SUMIF($B$6:$B$305,B191,$D$6:$D$305))</f>
+        <f>IF(P191="","",SUMIF($B$6:$B$305,B191,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S191">
-        <f>IF(OR(B191="",COUNTIF($B$6:$B191,B191)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R191)+(($R$6:$R$305=R191)*($B$6:$B$305&lt;B191)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P191="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R191,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R191,"="&amp;R191,$P$6:$P191,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22390,19 +22390,19 @@
       <c r="C192" s="56" t="n"/>
       <c r="D192" s="43" t="n"/>
       <c r="P192">
-        <f>IF(B192="","",B192)</f>
+        <f>IF(OR(B192="",COUNTIF($B$6:$B192,B192)&gt;1),"",B192)</f>
         <v/>
       </c>
       <c r="Q192">
-        <f>IF(C192="","",C192)</f>
+        <f>IF(P192="","",C192)</f>
         <v/>
       </c>
       <c r="R192">
-        <f>IF(B192="","",SUMIF($B$6:$B$305,B192,$D$6:$D$305))</f>
+        <f>IF(P192="","",SUMIF($B$6:$B$305,B192,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S192">
-        <f>IF(OR(B192="",COUNTIF($B$6:$B192,B192)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R192)+(($R$6:$R$305=R192)*($B$6:$B$305&lt;B192)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P192="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R192,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R192,"="&amp;R192,$P$6:$P192,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22412,19 +22412,19 @@
       <c r="C193" s="56" t="n"/>
       <c r="D193" s="43" t="n"/>
       <c r="P193">
-        <f>IF(B193="","",B193)</f>
+        <f>IF(OR(B193="",COUNTIF($B$6:$B193,B193)&gt;1),"",B193)</f>
         <v/>
       </c>
       <c r="Q193">
-        <f>IF(C193="","",C193)</f>
+        <f>IF(P193="","",C193)</f>
         <v/>
       </c>
       <c r="R193">
-        <f>IF(B193="","",SUMIF($B$6:$B$305,B193,$D$6:$D$305))</f>
+        <f>IF(P193="","",SUMIF($B$6:$B$305,B193,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S193">
-        <f>IF(OR(B193="",COUNTIF($B$6:$B193,B193)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R193)+(($R$6:$R$305=R193)*($B$6:$B$305&lt;B193)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P193="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R193,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R193,"="&amp;R193,$P$6:$P193,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22434,19 +22434,19 @@
       <c r="C194" s="56" t="n"/>
       <c r="D194" s="43" t="n"/>
       <c r="P194">
-        <f>IF(B194="","",B194)</f>
+        <f>IF(OR(B194="",COUNTIF($B$6:$B194,B194)&gt;1),"",B194)</f>
         <v/>
       </c>
       <c r="Q194">
-        <f>IF(C194="","",C194)</f>
+        <f>IF(P194="","",C194)</f>
         <v/>
       </c>
       <c r="R194">
-        <f>IF(B194="","",SUMIF($B$6:$B$305,B194,$D$6:$D$305))</f>
+        <f>IF(P194="","",SUMIF($B$6:$B$305,B194,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S194">
-        <f>IF(OR(B194="",COUNTIF($B$6:$B194,B194)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R194)+(($R$6:$R$305=R194)*($B$6:$B$305&lt;B194)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P194="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R194,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R194,"="&amp;R194,$P$6:$P194,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22456,19 +22456,19 @@
       <c r="C195" s="56" t="n"/>
       <c r="D195" s="43" t="n"/>
       <c r="P195">
-        <f>IF(B195="","",B195)</f>
+        <f>IF(OR(B195="",COUNTIF($B$6:$B195,B195)&gt;1),"",B195)</f>
         <v/>
       </c>
       <c r="Q195">
-        <f>IF(C195="","",C195)</f>
+        <f>IF(P195="","",C195)</f>
         <v/>
       </c>
       <c r="R195">
-        <f>IF(B195="","",SUMIF($B$6:$B$305,B195,$D$6:$D$305))</f>
+        <f>IF(P195="","",SUMIF($B$6:$B$305,B195,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S195">
-        <f>IF(OR(B195="",COUNTIF($B$6:$B195,B195)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R195)+(($R$6:$R$305=R195)*($B$6:$B$305&lt;B195)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P195="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R195,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R195,"="&amp;R195,$P$6:$P195,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22478,19 +22478,19 @@
       <c r="C196" s="56" t="n"/>
       <c r="D196" s="43" t="n"/>
       <c r="P196">
-        <f>IF(B196="","",B196)</f>
+        <f>IF(OR(B196="",COUNTIF($B$6:$B196,B196)&gt;1),"",B196)</f>
         <v/>
       </c>
       <c r="Q196">
-        <f>IF(C196="","",C196)</f>
+        <f>IF(P196="","",C196)</f>
         <v/>
       </c>
       <c r="R196">
-        <f>IF(B196="","",SUMIF($B$6:$B$305,B196,$D$6:$D$305))</f>
+        <f>IF(P196="","",SUMIF($B$6:$B$305,B196,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S196">
-        <f>IF(OR(B196="",COUNTIF($B$6:$B196,B196)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R196)+(($R$6:$R$305=R196)*($B$6:$B$305&lt;B196)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P196="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R196,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R196,"="&amp;R196,$P$6:$P196,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22500,19 +22500,19 @@
       <c r="C197" s="56" t="n"/>
       <c r="D197" s="43" t="n"/>
       <c r="P197">
-        <f>IF(B197="","",B197)</f>
+        <f>IF(OR(B197="",COUNTIF($B$6:$B197,B197)&gt;1),"",B197)</f>
         <v/>
       </c>
       <c r="Q197">
-        <f>IF(C197="","",C197)</f>
+        <f>IF(P197="","",C197)</f>
         <v/>
       </c>
       <c r="R197">
-        <f>IF(B197="","",SUMIF($B$6:$B$305,B197,$D$6:$D$305))</f>
+        <f>IF(P197="","",SUMIF($B$6:$B$305,B197,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S197">
-        <f>IF(OR(B197="",COUNTIF($B$6:$B197,B197)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R197)+(($R$6:$R$305=R197)*($B$6:$B$305&lt;B197)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P197="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R197,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R197,"="&amp;R197,$P$6:$P197,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22522,19 +22522,19 @@
       <c r="C198" s="56" t="n"/>
       <c r="D198" s="43" t="n"/>
       <c r="P198">
-        <f>IF(B198="","",B198)</f>
+        <f>IF(OR(B198="",COUNTIF($B$6:$B198,B198)&gt;1),"",B198)</f>
         <v/>
       </c>
       <c r="Q198">
-        <f>IF(C198="","",C198)</f>
+        <f>IF(P198="","",C198)</f>
         <v/>
       </c>
       <c r="R198">
-        <f>IF(B198="","",SUMIF($B$6:$B$305,B198,$D$6:$D$305))</f>
+        <f>IF(P198="","",SUMIF($B$6:$B$305,B198,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S198">
-        <f>IF(OR(B198="",COUNTIF($B$6:$B198,B198)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R198)+(($R$6:$R$305=R198)*($B$6:$B$305&lt;B198)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P198="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R198,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R198,"="&amp;R198,$P$6:$P198,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22544,19 +22544,19 @@
       <c r="C199" s="56" t="n"/>
       <c r="D199" s="43" t="n"/>
       <c r="P199">
-        <f>IF(B199="","",B199)</f>
+        <f>IF(OR(B199="",COUNTIF($B$6:$B199,B199)&gt;1),"",B199)</f>
         <v/>
       </c>
       <c r="Q199">
-        <f>IF(C199="","",C199)</f>
+        <f>IF(P199="","",C199)</f>
         <v/>
       </c>
       <c r="R199">
-        <f>IF(B199="","",SUMIF($B$6:$B$305,B199,$D$6:$D$305))</f>
+        <f>IF(P199="","",SUMIF($B$6:$B$305,B199,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S199">
-        <f>IF(OR(B199="",COUNTIF($B$6:$B199,B199)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R199)+(($R$6:$R$305=R199)*($B$6:$B$305&lt;B199)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P199="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R199,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R199,"="&amp;R199,$P$6:$P199,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22566,19 +22566,19 @@
       <c r="C200" s="56" t="n"/>
       <c r="D200" s="43" t="n"/>
       <c r="P200">
-        <f>IF(B200="","",B200)</f>
+        <f>IF(OR(B200="",COUNTIF($B$6:$B200,B200)&gt;1),"",B200)</f>
         <v/>
       </c>
       <c r="Q200">
-        <f>IF(C200="","",C200)</f>
+        <f>IF(P200="","",C200)</f>
         <v/>
       </c>
       <c r="R200">
-        <f>IF(B200="","",SUMIF($B$6:$B$305,B200,$D$6:$D$305))</f>
+        <f>IF(P200="","",SUMIF($B$6:$B$305,B200,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S200">
-        <f>IF(OR(B200="",COUNTIF($B$6:$B200,B200)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R200)+(($R$6:$R$305=R200)*($B$6:$B$305&lt;B200)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P200="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R200,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R200,"="&amp;R200,$P$6:$P200,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22588,19 +22588,19 @@
       <c r="C201" s="56" t="n"/>
       <c r="D201" s="43" t="n"/>
       <c r="P201">
-        <f>IF(B201="","",B201)</f>
+        <f>IF(OR(B201="",COUNTIF($B$6:$B201,B201)&gt;1),"",B201)</f>
         <v/>
       </c>
       <c r="Q201">
-        <f>IF(C201="","",C201)</f>
+        <f>IF(P201="","",C201)</f>
         <v/>
       </c>
       <c r="R201">
-        <f>IF(B201="","",SUMIF($B$6:$B$305,B201,$D$6:$D$305))</f>
+        <f>IF(P201="","",SUMIF($B$6:$B$305,B201,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S201">
-        <f>IF(OR(B201="",COUNTIF($B$6:$B201,B201)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R201)+(($R$6:$R$305=R201)*($B$6:$B$305&lt;B201)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P201="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R201,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R201,"="&amp;R201,$P$6:$P201,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22610,19 +22610,19 @@
       <c r="C202" s="56" t="n"/>
       <c r="D202" s="43" t="n"/>
       <c r="P202">
-        <f>IF(B202="","",B202)</f>
+        <f>IF(OR(B202="",COUNTIF($B$6:$B202,B202)&gt;1),"",B202)</f>
         <v/>
       </c>
       <c r="Q202">
-        <f>IF(C202="","",C202)</f>
+        <f>IF(P202="","",C202)</f>
         <v/>
       </c>
       <c r="R202">
-        <f>IF(B202="","",SUMIF($B$6:$B$305,B202,$D$6:$D$305))</f>
+        <f>IF(P202="","",SUMIF($B$6:$B$305,B202,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S202">
-        <f>IF(OR(B202="",COUNTIF($B$6:$B202,B202)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R202)+(($R$6:$R$305=R202)*($B$6:$B$305&lt;B202)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P202="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R202,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R202,"="&amp;R202,$P$6:$P202,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22632,19 +22632,19 @@
       <c r="C203" s="56" t="n"/>
       <c r="D203" s="43" t="n"/>
       <c r="P203">
-        <f>IF(B203="","",B203)</f>
+        <f>IF(OR(B203="",COUNTIF($B$6:$B203,B203)&gt;1),"",B203)</f>
         <v/>
       </c>
       <c r="Q203">
-        <f>IF(C203="","",C203)</f>
+        <f>IF(P203="","",C203)</f>
         <v/>
       </c>
       <c r="R203">
-        <f>IF(B203="","",SUMIF($B$6:$B$305,B203,$D$6:$D$305))</f>
+        <f>IF(P203="","",SUMIF($B$6:$B$305,B203,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S203">
-        <f>IF(OR(B203="",COUNTIF($B$6:$B203,B203)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R203)+(($R$6:$R$305=R203)*($B$6:$B$305&lt;B203)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P203="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R203,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R203,"="&amp;R203,$P$6:$P203,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22654,19 +22654,19 @@
       <c r="C204" s="56" t="n"/>
       <c r="D204" s="43" t="n"/>
       <c r="P204">
-        <f>IF(B204="","",B204)</f>
+        <f>IF(OR(B204="",COUNTIF($B$6:$B204,B204)&gt;1),"",B204)</f>
         <v/>
       </c>
       <c r="Q204">
-        <f>IF(C204="","",C204)</f>
+        <f>IF(P204="","",C204)</f>
         <v/>
       </c>
       <c r="R204">
-        <f>IF(B204="","",SUMIF($B$6:$B$305,B204,$D$6:$D$305))</f>
+        <f>IF(P204="","",SUMIF($B$6:$B$305,B204,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S204">
-        <f>IF(OR(B204="",COUNTIF($B$6:$B204,B204)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R204)+(($R$6:$R$305=R204)*($B$6:$B$305&lt;B204)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P204="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R204,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R204,"="&amp;R204,$P$6:$P204,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22676,19 +22676,19 @@
       <c r="C205" s="56" t="n"/>
       <c r="D205" s="43" t="n"/>
       <c r="P205">
-        <f>IF(B205="","",B205)</f>
+        <f>IF(OR(B205="",COUNTIF($B$6:$B205,B205)&gt;1),"",B205)</f>
         <v/>
       </c>
       <c r="Q205">
-        <f>IF(C205="","",C205)</f>
+        <f>IF(P205="","",C205)</f>
         <v/>
       </c>
       <c r="R205">
-        <f>IF(B205="","",SUMIF($B$6:$B$305,B205,$D$6:$D$305))</f>
+        <f>IF(P205="","",SUMIF($B$6:$B$305,B205,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S205">
-        <f>IF(OR(B205="",COUNTIF($B$6:$B205,B205)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R205)+(($R$6:$R$305=R205)*($B$6:$B$305&lt;B205)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P205="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R205,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R205,"="&amp;R205,$P$6:$P205,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22698,19 +22698,19 @@
       <c r="C206" s="56" t="n"/>
       <c r="D206" s="43" t="n"/>
       <c r="P206">
-        <f>IF(B206="","",B206)</f>
+        <f>IF(OR(B206="",COUNTIF($B$6:$B206,B206)&gt;1),"",B206)</f>
         <v/>
       </c>
       <c r="Q206">
-        <f>IF(C206="","",C206)</f>
+        <f>IF(P206="","",C206)</f>
         <v/>
       </c>
       <c r="R206">
-        <f>IF(B206="","",SUMIF($B$6:$B$305,B206,$D$6:$D$305))</f>
+        <f>IF(P206="","",SUMIF($B$6:$B$305,B206,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S206">
-        <f>IF(OR(B206="",COUNTIF($B$6:$B206,B206)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R206)+(($R$6:$R$305=R206)*($B$6:$B$305&lt;B206)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P206="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R206,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R206,"="&amp;R206,$P$6:$P206,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22720,19 +22720,19 @@
       <c r="C207" s="56" t="n"/>
       <c r="D207" s="43" t="n"/>
       <c r="P207">
-        <f>IF(B207="","",B207)</f>
+        <f>IF(OR(B207="",COUNTIF($B$6:$B207,B207)&gt;1),"",B207)</f>
         <v/>
       </c>
       <c r="Q207">
-        <f>IF(C207="","",C207)</f>
+        <f>IF(P207="","",C207)</f>
         <v/>
       </c>
       <c r="R207">
-        <f>IF(B207="","",SUMIF($B$6:$B$305,B207,$D$6:$D$305))</f>
+        <f>IF(P207="","",SUMIF($B$6:$B$305,B207,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S207">
-        <f>IF(OR(B207="",COUNTIF($B$6:$B207,B207)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R207)+(($R$6:$R$305=R207)*($B$6:$B$305&lt;B207)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P207="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R207,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R207,"="&amp;R207,$P$6:$P207,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22742,19 +22742,19 @@
       <c r="C208" s="56" t="n"/>
       <c r="D208" s="43" t="n"/>
       <c r="P208">
-        <f>IF(B208="","",B208)</f>
+        <f>IF(OR(B208="",COUNTIF($B$6:$B208,B208)&gt;1),"",B208)</f>
         <v/>
       </c>
       <c r="Q208">
-        <f>IF(C208="","",C208)</f>
+        <f>IF(P208="","",C208)</f>
         <v/>
       </c>
       <c r="R208">
-        <f>IF(B208="","",SUMIF($B$6:$B$305,B208,$D$6:$D$305))</f>
+        <f>IF(P208="","",SUMIF($B$6:$B$305,B208,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S208">
-        <f>IF(OR(B208="",COUNTIF($B$6:$B208,B208)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R208)+(($R$6:$R$305=R208)*($B$6:$B$305&lt;B208)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P208="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R208,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R208,"="&amp;R208,$P$6:$P208,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22764,19 +22764,19 @@
       <c r="C209" s="56" t="n"/>
       <c r="D209" s="43" t="n"/>
       <c r="P209">
-        <f>IF(B209="","",B209)</f>
+        <f>IF(OR(B209="",COUNTIF($B$6:$B209,B209)&gt;1),"",B209)</f>
         <v/>
       </c>
       <c r="Q209">
-        <f>IF(C209="","",C209)</f>
+        <f>IF(P209="","",C209)</f>
         <v/>
       </c>
       <c r="R209">
-        <f>IF(B209="","",SUMIF($B$6:$B$305,B209,$D$6:$D$305))</f>
+        <f>IF(P209="","",SUMIF($B$6:$B$305,B209,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S209">
-        <f>IF(OR(B209="",COUNTIF($B$6:$B209,B209)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R209)+(($R$6:$R$305=R209)*($B$6:$B$305&lt;B209)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P209="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R209,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R209,"="&amp;R209,$P$6:$P209,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22786,19 +22786,19 @@
       <c r="C210" s="56" t="n"/>
       <c r="D210" s="43" t="n"/>
       <c r="P210">
-        <f>IF(B210="","",B210)</f>
+        <f>IF(OR(B210="",COUNTIF($B$6:$B210,B210)&gt;1),"",B210)</f>
         <v/>
       </c>
       <c r="Q210">
-        <f>IF(C210="","",C210)</f>
+        <f>IF(P210="","",C210)</f>
         <v/>
       </c>
       <c r="R210">
-        <f>IF(B210="","",SUMIF($B$6:$B$305,B210,$D$6:$D$305))</f>
+        <f>IF(P210="","",SUMIF($B$6:$B$305,B210,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S210">
-        <f>IF(OR(B210="",COUNTIF($B$6:$B210,B210)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R210)+(($R$6:$R$305=R210)*($B$6:$B$305&lt;B210)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P210="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R210,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R210,"="&amp;R210,$P$6:$P210,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22808,19 +22808,19 @@
       <c r="C211" s="56" t="n"/>
       <c r="D211" s="43" t="n"/>
       <c r="P211">
-        <f>IF(B211="","",B211)</f>
+        <f>IF(OR(B211="",COUNTIF($B$6:$B211,B211)&gt;1),"",B211)</f>
         <v/>
       </c>
       <c r="Q211">
-        <f>IF(C211="","",C211)</f>
+        <f>IF(P211="","",C211)</f>
         <v/>
       </c>
       <c r="R211">
-        <f>IF(B211="","",SUMIF($B$6:$B$305,B211,$D$6:$D$305))</f>
+        <f>IF(P211="","",SUMIF($B$6:$B$305,B211,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S211">
-        <f>IF(OR(B211="",COUNTIF($B$6:$B211,B211)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R211)+(($R$6:$R$305=R211)*($B$6:$B$305&lt;B211)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P211="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R211,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R211,"="&amp;R211,$P$6:$P211,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22830,19 +22830,19 @@
       <c r="C212" s="56" t="n"/>
       <c r="D212" s="43" t="n"/>
       <c r="P212">
-        <f>IF(B212="","",B212)</f>
+        <f>IF(OR(B212="",COUNTIF($B$6:$B212,B212)&gt;1),"",B212)</f>
         <v/>
       </c>
       <c r="Q212">
-        <f>IF(C212="","",C212)</f>
+        <f>IF(P212="","",C212)</f>
         <v/>
       </c>
       <c r="R212">
-        <f>IF(B212="","",SUMIF($B$6:$B$305,B212,$D$6:$D$305))</f>
+        <f>IF(P212="","",SUMIF($B$6:$B$305,B212,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S212">
-        <f>IF(OR(B212="",COUNTIF($B$6:$B212,B212)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R212)+(($R$6:$R$305=R212)*($B$6:$B$305&lt;B212)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P212="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R212,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R212,"="&amp;R212,$P$6:$P212,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22852,19 +22852,19 @@
       <c r="C213" s="56" t="n"/>
       <c r="D213" s="43" t="n"/>
       <c r="P213">
-        <f>IF(B213="","",B213)</f>
+        <f>IF(OR(B213="",COUNTIF($B$6:$B213,B213)&gt;1),"",B213)</f>
         <v/>
       </c>
       <c r="Q213">
-        <f>IF(C213="","",C213)</f>
+        <f>IF(P213="","",C213)</f>
         <v/>
       </c>
       <c r="R213">
-        <f>IF(B213="","",SUMIF($B$6:$B$305,B213,$D$6:$D$305))</f>
+        <f>IF(P213="","",SUMIF($B$6:$B$305,B213,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S213">
-        <f>IF(OR(B213="",COUNTIF($B$6:$B213,B213)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R213)+(($R$6:$R$305=R213)*($B$6:$B$305&lt;B213)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P213="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R213,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R213,"="&amp;R213,$P$6:$P213,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22874,19 +22874,19 @@
       <c r="C214" s="56" t="n"/>
       <c r="D214" s="43" t="n"/>
       <c r="P214">
-        <f>IF(B214="","",B214)</f>
+        <f>IF(OR(B214="",COUNTIF($B$6:$B214,B214)&gt;1),"",B214)</f>
         <v/>
       </c>
       <c r="Q214">
-        <f>IF(C214="","",C214)</f>
+        <f>IF(P214="","",C214)</f>
         <v/>
       </c>
       <c r="R214">
-        <f>IF(B214="","",SUMIF($B$6:$B$305,B214,$D$6:$D$305))</f>
+        <f>IF(P214="","",SUMIF($B$6:$B$305,B214,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S214">
-        <f>IF(OR(B214="",COUNTIF($B$6:$B214,B214)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R214)+(($R$6:$R$305=R214)*($B$6:$B$305&lt;B214)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P214="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R214,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R214,"="&amp;R214,$P$6:$P214,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22896,19 +22896,19 @@
       <c r="C215" s="56" t="n"/>
       <c r="D215" s="43" t="n"/>
       <c r="P215">
-        <f>IF(B215="","",B215)</f>
+        <f>IF(OR(B215="",COUNTIF($B$6:$B215,B215)&gt;1),"",B215)</f>
         <v/>
       </c>
       <c r="Q215">
-        <f>IF(C215="","",C215)</f>
+        <f>IF(P215="","",C215)</f>
         <v/>
       </c>
       <c r="R215">
-        <f>IF(B215="","",SUMIF($B$6:$B$305,B215,$D$6:$D$305))</f>
+        <f>IF(P215="","",SUMIF($B$6:$B$305,B215,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S215">
-        <f>IF(OR(B215="",COUNTIF($B$6:$B215,B215)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R215)+(($R$6:$R$305=R215)*($B$6:$B$305&lt;B215)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P215="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R215,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R215,"="&amp;R215,$P$6:$P215,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22918,19 +22918,19 @@
       <c r="C216" s="56" t="n"/>
       <c r="D216" s="43" t="n"/>
       <c r="P216">
-        <f>IF(B216="","",B216)</f>
+        <f>IF(OR(B216="",COUNTIF($B$6:$B216,B216)&gt;1),"",B216)</f>
         <v/>
       </c>
       <c r="Q216">
-        <f>IF(C216="","",C216)</f>
+        <f>IF(P216="","",C216)</f>
         <v/>
       </c>
       <c r="R216">
-        <f>IF(B216="","",SUMIF($B$6:$B$305,B216,$D$6:$D$305))</f>
+        <f>IF(P216="","",SUMIF($B$6:$B$305,B216,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S216">
-        <f>IF(OR(B216="",COUNTIF($B$6:$B216,B216)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R216)+(($R$6:$R$305=R216)*($B$6:$B$305&lt;B216)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P216="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R216,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R216,"="&amp;R216,$P$6:$P216,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22940,19 +22940,19 @@
       <c r="C217" s="56" t="n"/>
       <c r="D217" s="43" t="n"/>
       <c r="P217">
-        <f>IF(B217="","",B217)</f>
+        <f>IF(OR(B217="",COUNTIF($B$6:$B217,B217)&gt;1),"",B217)</f>
         <v/>
       </c>
       <c r="Q217">
-        <f>IF(C217="","",C217)</f>
+        <f>IF(P217="","",C217)</f>
         <v/>
       </c>
       <c r="R217">
-        <f>IF(B217="","",SUMIF($B$6:$B$305,B217,$D$6:$D$305))</f>
+        <f>IF(P217="","",SUMIF($B$6:$B$305,B217,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S217">
-        <f>IF(OR(B217="",COUNTIF($B$6:$B217,B217)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R217)+(($R$6:$R$305=R217)*($B$6:$B$305&lt;B217)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P217="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R217,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R217,"="&amp;R217,$P$6:$P217,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22962,19 +22962,19 @@
       <c r="C218" s="56" t="n"/>
       <c r="D218" s="43" t="n"/>
       <c r="P218">
-        <f>IF(B218="","",B218)</f>
+        <f>IF(OR(B218="",COUNTIF($B$6:$B218,B218)&gt;1),"",B218)</f>
         <v/>
       </c>
       <c r="Q218">
-        <f>IF(C218="","",C218)</f>
+        <f>IF(P218="","",C218)</f>
         <v/>
       </c>
       <c r="R218">
-        <f>IF(B218="","",SUMIF($B$6:$B$305,B218,$D$6:$D$305))</f>
+        <f>IF(P218="","",SUMIF($B$6:$B$305,B218,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S218">
-        <f>IF(OR(B218="",COUNTIF($B$6:$B218,B218)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R218)+(($R$6:$R$305=R218)*($B$6:$B$305&lt;B218)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P218="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R218,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R218,"="&amp;R218,$P$6:$P218,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -22984,19 +22984,19 @@
       <c r="C219" s="56" t="n"/>
       <c r="D219" s="43" t="n"/>
       <c r="P219">
-        <f>IF(B219="","",B219)</f>
+        <f>IF(OR(B219="",COUNTIF($B$6:$B219,B219)&gt;1),"",B219)</f>
         <v/>
       </c>
       <c r="Q219">
-        <f>IF(C219="","",C219)</f>
+        <f>IF(P219="","",C219)</f>
         <v/>
       </c>
       <c r="R219">
-        <f>IF(B219="","",SUMIF($B$6:$B$305,B219,$D$6:$D$305))</f>
+        <f>IF(P219="","",SUMIF($B$6:$B$305,B219,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S219">
-        <f>IF(OR(B219="",COUNTIF($B$6:$B219,B219)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R219)+(($R$6:$R$305=R219)*($B$6:$B$305&lt;B219)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P219="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R219,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R219,"="&amp;R219,$P$6:$P219,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23006,19 +23006,19 @@
       <c r="C220" s="56" t="n"/>
       <c r="D220" s="43" t="n"/>
       <c r="P220">
-        <f>IF(B220="","",B220)</f>
+        <f>IF(OR(B220="",COUNTIF($B$6:$B220,B220)&gt;1),"",B220)</f>
         <v/>
       </c>
       <c r="Q220">
-        <f>IF(C220="","",C220)</f>
+        <f>IF(P220="","",C220)</f>
         <v/>
       </c>
       <c r="R220">
-        <f>IF(B220="","",SUMIF($B$6:$B$305,B220,$D$6:$D$305))</f>
+        <f>IF(P220="","",SUMIF($B$6:$B$305,B220,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S220">
-        <f>IF(OR(B220="",COUNTIF($B$6:$B220,B220)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R220)+(($R$6:$R$305=R220)*($B$6:$B$305&lt;B220)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P220="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R220,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R220,"="&amp;R220,$P$6:$P220,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23028,19 +23028,19 @@
       <c r="C221" s="56" t="n"/>
       <c r="D221" s="43" t="n"/>
       <c r="P221">
-        <f>IF(B221="","",B221)</f>
+        <f>IF(OR(B221="",COUNTIF($B$6:$B221,B221)&gt;1),"",B221)</f>
         <v/>
       </c>
       <c r="Q221">
-        <f>IF(C221="","",C221)</f>
+        <f>IF(P221="","",C221)</f>
         <v/>
       </c>
       <c r="R221">
-        <f>IF(B221="","",SUMIF($B$6:$B$305,B221,$D$6:$D$305))</f>
+        <f>IF(P221="","",SUMIF($B$6:$B$305,B221,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S221">
-        <f>IF(OR(B221="",COUNTIF($B$6:$B221,B221)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R221)+(($R$6:$R$305=R221)*($B$6:$B$305&lt;B221)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P221="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R221,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R221,"="&amp;R221,$P$6:$P221,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23050,19 +23050,19 @@
       <c r="C222" s="56" t="n"/>
       <c r="D222" s="43" t="n"/>
       <c r="P222">
-        <f>IF(B222="","",B222)</f>
+        <f>IF(OR(B222="",COUNTIF($B$6:$B222,B222)&gt;1),"",B222)</f>
         <v/>
       </c>
       <c r="Q222">
-        <f>IF(C222="","",C222)</f>
+        <f>IF(P222="","",C222)</f>
         <v/>
       </c>
       <c r="R222">
-        <f>IF(B222="","",SUMIF($B$6:$B$305,B222,$D$6:$D$305))</f>
+        <f>IF(P222="","",SUMIF($B$6:$B$305,B222,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S222">
-        <f>IF(OR(B222="",COUNTIF($B$6:$B222,B222)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R222)+(($R$6:$R$305=R222)*($B$6:$B$305&lt;B222)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P222="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R222,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R222,"="&amp;R222,$P$6:$P222,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23072,19 +23072,19 @@
       <c r="C223" s="56" t="n"/>
       <c r="D223" s="43" t="n"/>
       <c r="P223">
-        <f>IF(B223="","",B223)</f>
+        <f>IF(OR(B223="",COUNTIF($B$6:$B223,B223)&gt;1),"",B223)</f>
         <v/>
       </c>
       <c r="Q223">
-        <f>IF(C223="","",C223)</f>
+        <f>IF(P223="","",C223)</f>
         <v/>
       </c>
       <c r="R223">
-        <f>IF(B223="","",SUMIF($B$6:$B$305,B223,$D$6:$D$305))</f>
+        <f>IF(P223="","",SUMIF($B$6:$B$305,B223,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S223">
-        <f>IF(OR(B223="",COUNTIF($B$6:$B223,B223)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R223)+(($R$6:$R$305=R223)*($B$6:$B$305&lt;B223)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P223="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R223,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R223,"="&amp;R223,$P$6:$P223,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23094,19 +23094,19 @@
       <c r="C224" s="56" t="n"/>
       <c r="D224" s="43" t="n"/>
       <c r="P224">
-        <f>IF(B224="","",B224)</f>
+        <f>IF(OR(B224="",COUNTIF($B$6:$B224,B224)&gt;1),"",B224)</f>
         <v/>
       </c>
       <c r="Q224">
-        <f>IF(C224="","",C224)</f>
+        <f>IF(P224="","",C224)</f>
         <v/>
       </c>
       <c r="R224">
-        <f>IF(B224="","",SUMIF($B$6:$B$305,B224,$D$6:$D$305))</f>
+        <f>IF(P224="","",SUMIF($B$6:$B$305,B224,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S224">
-        <f>IF(OR(B224="",COUNTIF($B$6:$B224,B224)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R224)+(($R$6:$R$305=R224)*($B$6:$B$305&lt;B224)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P224="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R224,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R224,"="&amp;R224,$P$6:$P224,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23116,19 +23116,19 @@
       <c r="C225" s="56" t="n"/>
       <c r="D225" s="43" t="n"/>
       <c r="P225">
-        <f>IF(B225="","",B225)</f>
+        <f>IF(OR(B225="",COUNTIF($B$6:$B225,B225)&gt;1),"",B225)</f>
         <v/>
       </c>
       <c r="Q225">
-        <f>IF(C225="","",C225)</f>
+        <f>IF(P225="","",C225)</f>
         <v/>
       </c>
       <c r="R225">
-        <f>IF(B225="","",SUMIF($B$6:$B$305,B225,$D$6:$D$305))</f>
+        <f>IF(P225="","",SUMIF($B$6:$B$305,B225,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S225">
-        <f>IF(OR(B225="",COUNTIF($B$6:$B225,B225)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R225)+(($R$6:$R$305=R225)*($B$6:$B$305&lt;B225)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P225="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R225,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R225,"="&amp;R225,$P$6:$P225,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23138,19 +23138,19 @@
       <c r="C226" s="56" t="n"/>
       <c r="D226" s="43" t="n"/>
       <c r="P226">
-        <f>IF(B226="","",B226)</f>
+        <f>IF(OR(B226="",COUNTIF($B$6:$B226,B226)&gt;1),"",B226)</f>
         <v/>
       </c>
       <c r="Q226">
-        <f>IF(C226="","",C226)</f>
+        <f>IF(P226="","",C226)</f>
         <v/>
       </c>
       <c r="R226">
-        <f>IF(B226="","",SUMIF($B$6:$B$305,B226,$D$6:$D$305))</f>
+        <f>IF(P226="","",SUMIF($B$6:$B$305,B226,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S226">
-        <f>IF(OR(B226="",COUNTIF($B$6:$B226,B226)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R226)+(($R$6:$R$305=R226)*($B$6:$B$305&lt;B226)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P226="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R226,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R226,"="&amp;R226,$P$6:$P226,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23160,19 +23160,19 @@
       <c r="C227" s="56" t="n"/>
       <c r="D227" s="43" t="n"/>
       <c r="P227">
-        <f>IF(B227="","",B227)</f>
+        <f>IF(OR(B227="",COUNTIF($B$6:$B227,B227)&gt;1),"",B227)</f>
         <v/>
       </c>
       <c r="Q227">
-        <f>IF(C227="","",C227)</f>
+        <f>IF(P227="","",C227)</f>
         <v/>
       </c>
       <c r="R227">
-        <f>IF(B227="","",SUMIF($B$6:$B$305,B227,$D$6:$D$305))</f>
+        <f>IF(P227="","",SUMIF($B$6:$B$305,B227,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S227">
-        <f>IF(OR(B227="",COUNTIF($B$6:$B227,B227)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R227)+(($R$6:$R$305=R227)*($B$6:$B$305&lt;B227)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P227="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R227,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R227,"="&amp;R227,$P$6:$P227,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23182,19 +23182,19 @@
       <c r="C228" s="56" t="n"/>
       <c r="D228" s="43" t="n"/>
       <c r="P228">
-        <f>IF(B228="","",B228)</f>
+        <f>IF(OR(B228="",COUNTIF($B$6:$B228,B228)&gt;1),"",B228)</f>
         <v/>
       </c>
       <c r="Q228">
-        <f>IF(C228="","",C228)</f>
+        <f>IF(P228="","",C228)</f>
         <v/>
       </c>
       <c r="R228">
-        <f>IF(B228="","",SUMIF($B$6:$B$305,B228,$D$6:$D$305))</f>
+        <f>IF(P228="","",SUMIF($B$6:$B$305,B228,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S228">
-        <f>IF(OR(B228="",COUNTIF($B$6:$B228,B228)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R228)+(($R$6:$R$305=R228)*($B$6:$B$305&lt;B228)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P228="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R228,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R228,"="&amp;R228,$P$6:$P228,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23204,19 +23204,19 @@
       <c r="C229" s="56" t="n"/>
       <c r="D229" s="43" t="n"/>
       <c r="P229">
-        <f>IF(B229="","",B229)</f>
+        <f>IF(OR(B229="",COUNTIF($B$6:$B229,B229)&gt;1),"",B229)</f>
         <v/>
       </c>
       <c r="Q229">
-        <f>IF(C229="","",C229)</f>
+        <f>IF(P229="","",C229)</f>
         <v/>
       </c>
       <c r="R229">
-        <f>IF(B229="","",SUMIF($B$6:$B$305,B229,$D$6:$D$305))</f>
+        <f>IF(P229="","",SUMIF($B$6:$B$305,B229,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S229">
-        <f>IF(OR(B229="",COUNTIF($B$6:$B229,B229)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R229)+(($R$6:$R$305=R229)*($B$6:$B$305&lt;B229)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P229="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R229,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R229,"="&amp;R229,$P$6:$P229,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23226,19 +23226,19 @@
       <c r="C230" s="56" t="n"/>
       <c r="D230" s="43" t="n"/>
       <c r="P230">
-        <f>IF(B230="","",B230)</f>
+        <f>IF(OR(B230="",COUNTIF($B$6:$B230,B230)&gt;1),"",B230)</f>
         <v/>
       </c>
       <c r="Q230">
-        <f>IF(C230="","",C230)</f>
+        <f>IF(P230="","",C230)</f>
         <v/>
       </c>
       <c r="R230">
-        <f>IF(B230="","",SUMIF($B$6:$B$305,B230,$D$6:$D$305))</f>
+        <f>IF(P230="","",SUMIF($B$6:$B$305,B230,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S230">
-        <f>IF(OR(B230="",COUNTIF($B$6:$B230,B230)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R230)+(($R$6:$R$305=R230)*($B$6:$B$305&lt;B230)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P230="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R230,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R230,"="&amp;R230,$P$6:$P230,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23248,19 +23248,19 @@
       <c r="C231" s="56" t="n"/>
       <c r="D231" s="43" t="n"/>
       <c r="P231">
-        <f>IF(B231="","",B231)</f>
+        <f>IF(OR(B231="",COUNTIF($B$6:$B231,B231)&gt;1),"",B231)</f>
         <v/>
       </c>
       <c r="Q231">
-        <f>IF(C231="","",C231)</f>
+        <f>IF(P231="","",C231)</f>
         <v/>
       </c>
       <c r="R231">
-        <f>IF(B231="","",SUMIF($B$6:$B$305,B231,$D$6:$D$305))</f>
+        <f>IF(P231="","",SUMIF($B$6:$B$305,B231,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S231">
-        <f>IF(OR(B231="",COUNTIF($B$6:$B231,B231)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R231)+(($R$6:$R$305=R231)*($B$6:$B$305&lt;B231)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P231="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R231,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R231,"="&amp;R231,$P$6:$P231,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23270,19 +23270,19 @@
       <c r="C232" s="56" t="n"/>
       <c r="D232" s="43" t="n"/>
       <c r="P232">
-        <f>IF(B232="","",B232)</f>
+        <f>IF(OR(B232="",COUNTIF($B$6:$B232,B232)&gt;1),"",B232)</f>
         <v/>
       </c>
       <c r="Q232">
-        <f>IF(C232="","",C232)</f>
+        <f>IF(P232="","",C232)</f>
         <v/>
       </c>
       <c r="R232">
-        <f>IF(B232="","",SUMIF($B$6:$B$305,B232,$D$6:$D$305))</f>
+        <f>IF(P232="","",SUMIF($B$6:$B$305,B232,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S232">
-        <f>IF(OR(B232="",COUNTIF($B$6:$B232,B232)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R232)+(($R$6:$R$305=R232)*($B$6:$B$305&lt;B232)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P232="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R232,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R232,"="&amp;R232,$P$6:$P232,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23292,19 +23292,19 @@
       <c r="C233" s="56" t="n"/>
       <c r="D233" s="43" t="n"/>
       <c r="P233">
-        <f>IF(B233="","",B233)</f>
+        <f>IF(OR(B233="",COUNTIF($B$6:$B233,B233)&gt;1),"",B233)</f>
         <v/>
       </c>
       <c r="Q233">
-        <f>IF(C233="","",C233)</f>
+        <f>IF(P233="","",C233)</f>
         <v/>
       </c>
       <c r="R233">
-        <f>IF(B233="","",SUMIF($B$6:$B$305,B233,$D$6:$D$305))</f>
+        <f>IF(P233="","",SUMIF($B$6:$B$305,B233,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S233">
-        <f>IF(OR(B233="",COUNTIF($B$6:$B233,B233)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R233)+(($R$6:$R$305=R233)*($B$6:$B$305&lt;B233)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P233="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R233,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R233,"="&amp;R233,$P$6:$P233,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23314,19 +23314,19 @@
       <c r="C234" s="56" t="n"/>
       <c r="D234" s="43" t="n"/>
       <c r="P234">
-        <f>IF(B234="","",B234)</f>
+        <f>IF(OR(B234="",COUNTIF($B$6:$B234,B234)&gt;1),"",B234)</f>
         <v/>
       </c>
       <c r="Q234">
-        <f>IF(C234="","",C234)</f>
+        <f>IF(P234="","",C234)</f>
         <v/>
       </c>
       <c r="R234">
-        <f>IF(B234="","",SUMIF($B$6:$B$305,B234,$D$6:$D$305))</f>
+        <f>IF(P234="","",SUMIF($B$6:$B$305,B234,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S234">
-        <f>IF(OR(B234="",COUNTIF($B$6:$B234,B234)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R234)+(($R$6:$R$305=R234)*($B$6:$B$305&lt;B234)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P234="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R234,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R234,"="&amp;R234,$P$6:$P234,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23336,19 +23336,19 @@
       <c r="C235" s="56" t="n"/>
       <c r="D235" s="43" t="n"/>
       <c r="P235">
-        <f>IF(B235="","",B235)</f>
+        <f>IF(OR(B235="",COUNTIF($B$6:$B235,B235)&gt;1),"",B235)</f>
         <v/>
       </c>
       <c r="Q235">
-        <f>IF(C235="","",C235)</f>
+        <f>IF(P235="","",C235)</f>
         <v/>
       </c>
       <c r="R235">
-        <f>IF(B235="","",SUMIF($B$6:$B$305,B235,$D$6:$D$305))</f>
+        <f>IF(P235="","",SUMIF($B$6:$B$305,B235,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S235">
-        <f>IF(OR(B235="",COUNTIF($B$6:$B235,B235)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R235)+(($R$6:$R$305=R235)*($B$6:$B$305&lt;B235)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P235="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R235,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R235,"="&amp;R235,$P$6:$P235,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23358,19 +23358,19 @@
       <c r="C236" s="56" t="n"/>
       <c r="D236" s="43" t="n"/>
       <c r="P236">
-        <f>IF(B236="","",B236)</f>
+        <f>IF(OR(B236="",COUNTIF($B$6:$B236,B236)&gt;1),"",B236)</f>
         <v/>
       </c>
       <c r="Q236">
-        <f>IF(C236="","",C236)</f>
+        <f>IF(P236="","",C236)</f>
         <v/>
       </c>
       <c r="R236">
-        <f>IF(B236="","",SUMIF($B$6:$B$305,B236,$D$6:$D$305))</f>
+        <f>IF(P236="","",SUMIF($B$6:$B$305,B236,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S236">
-        <f>IF(OR(B236="",COUNTIF($B$6:$B236,B236)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R236)+(($R$6:$R$305=R236)*($B$6:$B$305&lt;B236)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P236="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R236,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R236,"="&amp;R236,$P$6:$P236,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23380,19 +23380,19 @@
       <c r="C237" s="56" t="n"/>
       <c r="D237" s="43" t="n"/>
       <c r="P237">
-        <f>IF(B237="","",B237)</f>
+        <f>IF(OR(B237="",COUNTIF($B$6:$B237,B237)&gt;1),"",B237)</f>
         <v/>
       </c>
       <c r="Q237">
-        <f>IF(C237="","",C237)</f>
+        <f>IF(P237="","",C237)</f>
         <v/>
       </c>
       <c r="R237">
-        <f>IF(B237="","",SUMIF($B$6:$B$305,B237,$D$6:$D$305))</f>
+        <f>IF(P237="","",SUMIF($B$6:$B$305,B237,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S237">
-        <f>IF(OR(B237="",COUNTIF($B$6:$B237,B237)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R237)+(($R$6:$R$305=R237)*($B$6:$B$305&lt;B237)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P237="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R237,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R237,"="&amp;R237,$P$6:$P237,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23402,19 +23402,19 @@
       <c r="C238" s="56" t="n"/>
       <c r="D238" s="43" t="n"/>
       <c r="P238">
-        <f>IF(B238="","",B238)</f>
+        <f>IF(OR(B238="",COUNTIF($B$6:$B238,B238)&gt;1),"",B238)</f>
         <v/>
       </c>
       <c r="Q238">
-        <f>IF(C238="","",C238)</f>
+        <f>IF(P238="","",C238)</f>
         <v/>
       </c>
       <c r="R238">
-        <f>IF(B238="","",SUMIF($B$6:$B$305,B238,$D$6:$D$305))</f>
+        <f>IF(P238="","",SUMIF($B$6:$B$305,B238,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S238">
-        <f>IF(OR(B238="",COUNTIF($B$6:$B238,B238)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R238)+(($R$6:$R$305=R238)*($B$6:$B$305&lt;B238)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P238="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R238,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R238,"="&amp;R238,$P$6:$P238,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23424,19 +23424,19 @@
       <c r="C239" s="56" t="n"/>
       <c r="D239" s="43" t="n"/>
       <c r="P239">
-        <f>IF(B239="","",B239)</f>
+        <f>IF(OR(B239="",COUNTIF($B$6:$B239,B239)&gt;1),"",B239)</f>
         <v/>
       </c>
       <c r="Q239">
-        <f>IF(C239="","",C239)</f>
+        <f>IF(P239="","",C239)</f>
         <v/>
       </c>
       <c r="R239">
-        <f>IF(B239="","",SUMIF($B$6:$B$305,B239,$D$6:$D$305))</f>
+        <f>IF(P239="","",SUMIF($B$6:$B$305,B239,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S239">
-        <f>IF(OR(B239="",COUNTIF($B$6:$B239,B239)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R239)+(($R$6:$R$305=R239)*($B$6:$B$305&lt;B239)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P239="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R239,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R239,"="&amp;R239,$P$6:$P239,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23446,19 +23446,19 @@
       <c r="C240" s="56" t="n"/>
       <c r="D240" s="43" t="n"/>
       <c r="P240">
-        <f>IF(B240="","",B240)</f>
+        <f>IF(OR(B240="",COUNTIF($B$6:$B240,B240)&gt;1),"",B240)</f>
         <v/>
       </c>
       <c r="Q240">
-        <f>IF(C240="","",C240)</f>
+        <f>IF(P240="","",C240)</f>
         <v/>
       </c>
       <c r="R240">
-        <f>IF(B240="","",SUMIF($B$6:$B$305,B240,$D$6:$D$305))</f>
+        <f>IF(P240="","",SUMIF($B$6:$B$305,B240,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S240">
-        <f>IF(OR(B240="",COUNTIF($B$6:$B240,B240)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R240)+(($R$6:$R$305=R240)*($B$6:$B$305&lt;B240)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P240="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R240,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R240,"="&amp;R240,$P$6:$P240,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23468,19 +23468,19 @@
       <c r="C241" s="56" t="n"/>
       <c r="D241" s="43" t="n"/>
       <c r="P241">
-        <f>IF(B241="","",B241)</f>
+        <f>IF(OR(B241="",COUNTIF($B$6:$B241,B241)&gt;1),"",B241)</f>
         <v/>
       </c>
       <c r="Q241">
-        <f>IF(C241="","",C241)</f>
+        <f>IF(P241="","",C241)</f>
         <v/>
       </c>
       <c r="R241">
-        <f>IF(B241="","",SUMIF($B$6:$B$305,B241,$D$6:$D$305))</f>
+        <f>IF(P241="","",SUMIF($B$6:$B$305,B241,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S241">
-        <f>IF(OR(B241="",COUNTIF($B$6:$B241,B241)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R241)+(($R$6:$R$305=R241)*($B$6:$B$305&lt;B241)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P241="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R241,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R241,"="&amp;R241,$P$6:$P241,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23490,19 +23490,19 @@
       <c r="C242" s="56" t="n"/>
       <c r="D242" s="43" t="n"/>
       <c r="P242">
-        <f>IF(B242="","",B242)</f>
+        <f>IF(OR(B242="",COUNTIF($B$6:$B242,B242)&gt;1),"",B242)</f>
         <v/>
       </c>
       <c r="Q242">
-        <f>IF(C242="","",C242)</f>
+        <f>IF(P242="","",C242)</f>
         <v/>
       </c>
       <c r="R242">
-        <f>IF(B242="","",SUMIF($B$6:$B$305,B242,$D$6:$D$305))</f>
+        <f>IF(P242="","",SUMIF($B$6:$B$305,B242,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S242">
-        <f>IF(OR(B242="",COUNTIF($B$6:$B242,B242)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R242)+(($R$6:$R$305=R242)*($B$6:$B$305&lt;B242)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P242="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R242,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R242,"="&amp;R242,$P$6:$P242,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23512,19 +23512,19 @@
       <c r="C243" s="56" t="n"/>
       <c r="D243" s="43" t="n"/>
       <c r="P243">
-        <f>IF(B243="","",B243)</f>
+        <f>IF(OR(B243="",COUNTIF($B$6:$B243,B243)&gt;1),"",B243)</f>
         <v/>
       </c>
       <c r="Q243">
-        <f>IF(C243="","",C243)</f>
+        <f>IF(P243="","",C243)</f>
         <v/>
       </c>
       <c r="R243">
-        <f>IF(B243="","",SUMIF($B$6:$B$305,B243,$D$6:$D$305))</f>
+        <f>IF(P243="","",SUMIF($B$6:$B$305,B243,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S243">
-        <f>IF(OR(B243="",COUNTIF($B$6:$B243,B243)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R243)+(($R$6:$R$305=R243)*($B$6:$B$305&lt;B243)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P243="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R243,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R243,"="&amp;R243,$P$6:$P243,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23534,19 +23534,19 @@
       <c r="C244" s="56" t="n"/>
       <c r="D244" s="43" t="n"/>
       <c r="P244">
-        <f>IF(B244="","",B244)</f>
+        <f>IF(OR(B244="",COUNTIF($B$6:$B244,B244)&gt;1),"",B244)</f>
         <v/>
       </c>
       <c r="Q244">
-        <f>IF(C244="","",C244)</f>
+        <f>IF(P244="","",C244)</f>
         <v/>
       </c>
       <c r="R244">
-        <f>IF(B244="","",SUMIF($B$6:$B$305,B244,$D$6:$D$305))</f>
+        <f>IF(P244="","",SUMIF($B$6:$B$305,B244,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S244">
-        <f>IF(OR(B244="",COUNTIF($B$6:$B244,B244)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R244)+(($R$6:$R$305=R244)*($B$6:$B$305&lt;B244)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P244="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R244,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R244,"="&amp;R244,$P$6:$P244,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23556,19 +23556,19 @@
       <c r="C245" s="56" t="n"/>
       <c r="D245" s="43" t="n"/>
       <c r="P245">
-        <f>IF(B245="","",B245)</f>
+        <f>IF(OR(B245="",COUNTIF($B$6:$B245,B245)&gt;1),"",B245)</f>
         <v/>
       </c>
       <c r="Q245">
-        <f>IF(C245="","",C245)</f>
+        <f>IF(P245="","",C245)</f>
         <v/>
       </c>
       <c r="R245">
-        <f>IF(B245="","",SUMIF($B$6:$B$305,B245,$D$6:$D$305))</f>
+        <f>IF(P245="","",SUMIF($B$6:$B$305,B245,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S245">
-        <f>IF(OR(B245="",COUNTIF($B$6:$B245,B245)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R245)+(($R$6:$R$305=R245)*($B$6:$B$305&lt;B245)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P245="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R245,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R245,"="&amp;R245,$P$6:$P245,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23578,19 +23578,19 @@
       <c r="C246" s="56" t="n"/>
       <c r="D246" s="43" t="n"/>
       <c r="P246">
-        <f>IF(B246="","",B246)</f>
+        <f>IF(OR(B246="",COUNTIF($B$6:$B246,B246)&gt;1),"",B246)</f>
         <v/>
       </c>
       <c r="Q246">
-        <f>IF(C246="","",C246)</f>
+        <f>IF(P246="","",C246)</f>
         <v/>
       </c>
       <c r="R246">
-        <f>IF(B246="","",SUMIF($B$6:$B$305,B246,$D$6:$D$305))</f>
+        <f>IF(P246="","",SUMIF($B$6:$B$305,B246,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S246">
-        <f>IF(OR(B246="",COUNTIF($B$6:$B246,B246)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R246)+(($R$6:$R$305=R246)*($B$6:$B$305&lt;B246)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P246="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R246,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R246,"="&amp;R246,$P$6:$P246,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23600,19 +23600,19 @@
       <c r="C247" s="56" t="n"/>
       <c r="D247" s="43" t="n"/>
       <c r="P247">
-        <f>IF(B247="","",B247)</f>
+        <f>IF(OR(B247="",COUNTIF($B$6:$B247,B247)&gt;1),"",B247)</f>
         <v/>
       </c>
       <c r="Q247">
-        <f>IF(C247="","",C247)</f>
+        <f>IF(P247="","",C247)</f>
         <v/>
       </c>
       <c r="R247">
-        <f>IF(B247="","",SUMIF($B$6:$B$305,B247,$D$6:$D$305))</f>
+        <f>IF(P247="","",SUMIF($B$6:$B$305,B247,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S247">
-        <f>IF(OR(B247="",COUNTIF($B$6:$B247,B247)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R247)+(($R$6:$R$305=R247)*($B$6:$B$305&lt;B247)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P247="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R247,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R247,"="&amp;R247,$P$6:$P247,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23622,19 +23622,19 @@
       <c r="C248" s="56" t="n"/>
       <c r="D248" s="43" t="n"/>
       <c r="P248">
-        <f>IF(B248="","",B248)</f>
+        <f>IF(OR(B248="",COUNTIF($B$6:$B248,B248)&gt;1),"",B248)</f>
         <v/>
       </c>
       <c r="Q248">
-        <f>IF(C248="","",C248)</f>
+        <f>IF(P248="","",C248)</f>
         <v/>
       </c>
       <c r="R248">
-        <f>IF(B248="","",SUMIF($B$6:$B$305,B248,$D$6:$D$305))</f>
+        <f>IF(P248="","",SUMIF($B$6:$B$305,B248,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S248">
-        <f>IF(OR(B248="",COUNTIF($B$6:$B248,B248)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R248)+(($R$6:$R$305=R248)*($B$6:$B$305&lt;B248)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P248="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R248,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R248,"="&amp;R248,$P$6:$P248,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23644,19 +23644,19 @@
       <c r="C249" s="56" t="n"/>
       <c r="D249" s="43" t="n"/>
       <c r="P249">
-        <f>IF(B249="","",B249)</f>
+        <f>IF(OR(B249="",COUNTIF($B$6:$B249,B249)&gt;1),"",B249)</f>
         <v/>
       </c>
       <c r="Q249">
-        <f>IF(C249="","",C249)</f>
+        <f>IF(P249="","",C249)</f>
         <v/>
       </c>
       <c r="R249">
-        <f>IF(B249="","",SUMIF($B$6:$B$305,B249,$D$6:$D$305))</f>
+        <f>IF(P249="","",SUMIF($B$6:$B$305,B249,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S249">
-        <f>IF(OR(B249="",COUNTIF($B$6:$B249,B249)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R249)+(($R$6:$R$305=R249)*($B$6:$B$305&lt;B249)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P249="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R249,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R249,"="&amp;R249,$P$6:$P249,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23666,19 +23666,19 @@
       <c r="C250" s="56" t="n"/>
       <c r="D250" s="43" t="n"/>
       <c r="P250">
-        <f>IF(B250="","",B250)</f>
+        <f>IF(OR(B250="",COUNTIF($B$6:$B250,B250)&gt;1),"",B250)</f>
         <v/>
       </c>
       <c r="Q250">
-        <f>IF(C250="","",C250)</f>
+        <f>IF(P250="","",C250)</f>
         <v/>
       </c>
       <c r="R250">
-        <f>IF(B250="","",SUMIF($B$6:$B$305,B250,$D$6:$D$305))</f>
+        <f>IF(P250="","",SUMIF($B$6:$B$305,B250,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S250">
-        <f>IF(OR(B250="",COUNTIF($B$6:$B250,B250)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R250)+(($R$6:$R$305=R250)*($B$6:$B$305&lt;B250)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P250="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R250,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R250,"="&amp;R250,$P$6:$P250,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23688,19 +23688,19 @@
       <c r="C251" s="56" t="n"/>
       <c r="D251" s="43" t="n"/>
       <c r="P251">
-        <f>IF(B251="","",B251)</f>
+        <f>IF(OR(B251="",COUNTIF($B$6:$B251,B251)&gt;1),"",B251)</f>
         <v/>
       </c>
       <c r="Q251">
-        <f>IF(C251="","",C251)</f>
+        <f>IF(P251="","",C251)</f>
         <v/>
       </c>
       <c r="R251">
-        <f>IF(B251="","",SUMIF($B$6:$B$305,B251,$D$6:$D$305))</f>
+        <f>IF(P251="","",SUMIF($B$6:$B$305,B251,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S251">
-        <f>IF(OR(B251="",COUNTIF($B$6:$B251,B251)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R251)+(($R$6:$R$305=R251)*($B$6:$B$305&lt;B251)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P251="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R251,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R251,"="&amp;R251,$P$6:$P251,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23710,19 +23710,19 @@
       <c r="C252" s="56" t="n"/>
       <c r="D252" s="43" t="n"/>
       <c r="P252">
-        <f>IF(B252="","",B252)</f>
+        <f>IF(OR(B252="",COUNTIF($B$6:$B252,B252)&gt;1),"",B252)</f>
         <v/>
       </c>
       <c r="Q252">
-        <f>IF(C252="","",C252)</f>
+        <f>IF(P252="","",C252)</f>
         <v/>
       </c>
       <c r="R252">
-        <f>IF(B252="","",SUMIF($B$6:$B$305,B252,$D$6:$D$305))</f>
+        <f>IF(P252="","",SUMIF($B$6:$B$305,B252,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S252">
-        <f>IF(OR(B252="",COUNTIF($B$6:$B252,B252)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R252)+(($R$6:$R$305=R252)*($B$6:$B$305&lt;B252)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P252="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R252,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R252,"="&amp;R252,$P$6:$P252,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23732,19 +23732,19 @@
       <c r="C253" s="56" t="n"/>
       <c r="D253" s="43" t="n"/>
       <c r="P253">
-        <f>IF(B253="","",B253)</f>
+        <f>IF(OR(B253="",COUNTIF($B$6:$B253,B253)&gt;1),"",B253)</f>
         <v/>
       </c>
       <c r="Q253">
-        <f>IF(C253="","",C253)</f>
+        <f>IF(P253="","",C253)</f>
         <v/>
       </c>
       <c r="R253">
-        <f>IF(B253="","",SUMIF($B$6:$B$305,B253,$D$6:$D$305))</f>
+        <f>IF(P253="","",SUMIF($B$6:$B$305,B253,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S253">
-        <f>IF(OR(B253="",COUNTIF($B$6:$B253,B253)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R253)+(($R$6:$R$305=R253)*($B$6:$B$305&lt;B253)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P253="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R253,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R253,"="&amp;R253,$P$6:$P253,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23754,19 +23754,19 @@
       <c r="C254" s="56" t="n"/>
       <c r="D254" s="43" t="n"/>
       <c r="P254">
-        <f>IF(B254="","",B254)</f>
+        <f>IF(OR(B254="",COUNTIF($B$6:$B254,B254)&gt;1),"",B254)</f>
         <v/>
       </c>
       <c r="Q254">
-        <f>IF(C254="","",C254)</f>
+        <f>IF(P254="","",C254)</f>
         <v/>
       </c>
       <c r="R254">
-        <f>IF(B254="","",SUMIF($B$6:$B$305,B254,$D$6:$D$305))</f>
+        <f>IF(P254="","",SUMIF($B$6:$B$305,B254,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S254">
-        <f>IF(OR(B254="",COUNTIF($B$6:$B254,B254)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R254)+(($R$6:$R$305=R254)*($B$6:$B$305&lt;B254)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P254="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R254,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R254,"="&amp;R254,$P$6:$P254,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23776,19 +23776,19 @@
       <c r="C255" s="56" t="n"/>
       <c r="D255" s="43" t="n"/>
       <c r="P255">
-        <f>IF(B255="","",B255)</f>
+        <f>IF(OR(B255="",COUNTIF($B$6:$B255,B255)&gt;1),"",B255)</f>
         <v/>
       </c>
       <c r="Q255">
-        <f>IF(C255="","",C255)</f>
+        <f>IF(P255="","",C255)</f>
         <v/>
       </c>
       <c r="R255">
-        <f>IF(B255="","",SUMIF($B$6:$B$305,B255,$D$6:$D$305))</f>
+        <f>IF(P255="","",SUMIF($B$6:$B$305,B255,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S255">
-        <f>IF(OR(B255="",COUNTIF($B$6:$B255,B255)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R255)+(($R$6:$R$305=R255)*($B$6:$B$305&lt;B255)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P255="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R255,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R255,"="&amp;R255,$P$6:$P255,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23798,19 +23798,19 @@
       <c r="C256" s="56" t="n"/>
       <c r="D256" s="43" t="n"/>
       <c r="P256">
-        <f>IF(B256="","",B256)</f>
+        <f>IF(OR(B256="",COUNTIF($B$6:$B256,B256)&gt;1),"",B256)</f>
         <v/>
       </c>
       <c r="Q256">
-        <f>IF(C256="","",C256)</f>
+        <f>IF(P256="","",C256)</f>
         <v/>
       </c>
       <c r="R256">
-        <f>IF(B256="","",SUMIF($B$6:$B$305,B256,$D$6:$D$305))</f>
+        <f>IF(P256="","",SUMIF($B$6:$B$305,B256,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S256">
-        <f>IF(OR(B256="",COUNTIF($B$6:$B256,B256)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R256)+(($R$6:$R$305=R256)*($B$6:$B$305&lt;B256)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P256="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R256,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R256,"="&amp;R256,$P$6:$P256,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23820,19 +23820,19 @@
       <c r="C257" s="56" t="n"/>
       <c r="D257" s="43" t="n"/>
       <c r="P257">
-        <f>IF(B257="","",B257)</f>
+        <f>IF(OR(B257="",COUNTIF($B$6:$B257,B257)&gt;1),"",B257)</f>
         <v/>
       </c>
       <c r="Q257">
-        <f>IF(C257="","",C257)</f>
+        <f>IF(P257="","",C257)</f>
         <v/>
       </c>
       <c r="R257">
-        <f>IF(B257="","",SUMIF($B$6:$B$305,B257,$D$6:$D$305))</f>
+        <f>IF(P257="","",SUMIF($B$6:$B$305,B257,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S257">
-        <f>IF(OR(B257="",COUNTIF($B$6:$B257,B257)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R257)+(($R$6:$R$305=R257)*($B$6:$B$305&lt;B257)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P257="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R257,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R257,"="&amp;R257,$P$6:$P257,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23842,19 +23842,19 @@
       <c r="C258" s="56" t="n"/>
       <c r="D258" s="43" t="n"/>
       <c r="P258">
-        <f>IF(B258="","",B258)</f>
+        <f>IF(OR(B258="",COUNTIF($B$6:$B258,B258)&gt;1),"",B258)</f>
         <v/>
       </c>
       <c r="Q258">
-        <f>IF(C258="","",C258)</f>
+        <f>IF(P258="","",C258)</f>
         <v/>
       </c>
       <c r="R258">
-        <f>IF(B258="","",SUMIF($B$6:$B$305,B258,$D$6:$D$305))</f>
+        <f>IF(P258="","",SUMIF($B$6:$B$305,B258,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S258">
-        <f>IF(OR(B258="",COUNTIF($B$6:$B258,B258)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R258)+(($R$6:$R$305=R258)*($B$6:$B$305&lt;B258)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P258="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R258,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R258,"="&amp;R258,$P$6:$P258,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23864,19 +23864,19 @@
       <c r="C259" s="56" t="n"/>
       <c r="D259" s="43" t="n"/>
       <c r="P259">
-        <f>IF(B259="","",B259)</f>
+        <f>IF(OR(B259="",COUNTIF($B$6:$B259,B259)&gt;1),"",B259)</f>
         <v/>
       </c>
       <c r="Q259">
-        <f>IF(C259="","",C259)</f>
+        <f>IF(P259="","",C259)</f>
         <v/>
       </c>
       <c r="R259">
-        <f>IF(B259="","",SUMIF($B$6:$B$305,B259,$D$6:$D$305))</f>
+        <f>IF(P259="","",SUMIF($B$6:$B$305,B259,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S259">
-        <f>IF(OR(B259="",COUNTIF($B$6:$B259,B259)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R259)+(($R$6:$R$305=R259)*($B$6:$B$305&lt;B259)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P259="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R259,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R259,"="&amp;R259,$P$6:$P259,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23886,19 +23886,19 @@
       <c r="C260" s="56" t="n"/>
       <c r="D260" s="43" t="n"/>
       <c r="P260">
-        <f>IF(B260="","",B260)</f>
+        <f>IF(OR(B260="",COUNTIF($B$6:$B260,B260)&gt;1),"",B260)</f>
         <v/>
       </c>
       <c r="Q260">
-        <f>IF(C260="","",C260)</f>
+        <f>IF(P260="","",C260)</f>
         <v/>
       </c>
       <c r="R260">
-        <f>IF(B260="","",SUMIF($B$6:$B$305,B260,$D$6:$D$305))</f>
+        <f>IF(P260="","",SUMIF($B$6:$B$305,B260,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S260">
-        <f>IF(OR(B260="",COUNTIF($B$6:$B260,B260)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R260)+(($R$6:$R$305=R260)*($B$6:$B$305&lt;B260)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P260="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R260,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R260,"="&amp;R260,$P$6:$P260,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23908,19 +23908,19 @@
       <c r="C261" s="56" t="n"/>
       <c r="D261" s="43" t="n"/>
       <c r="P261">
-        <f>IF(B261="","",B261)</f>
+        <f>IF(OR(B261="",COUNTIF($B$6:$B261,B261)&gt;1),"",B261)</f>
         <v/>
       </c>
       <c r="Q261">
-        <f>IF(C261="","",C261)</f>
+        <f>IF(P261="","",C261)</f>
         <v/>
       </c>
       <c r="R261">
-        <f>IF(B261="","",SUMIF($B$6:$B$305,B261,$D$6:$D$305))</f>
+        <f>IF(P261="","",SUMIF($B$6:$B$305,B261,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S261">
-        <f>IF(OR(B261="",COUNTIF($B$6:$B261,B261)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R261)+(($R$6:$R$305=R261)*($B$6:$B$305&lt;B261)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P261="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R261,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R261,"="&amp;R261,$P$6:$P261,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23930,19 +23930,19 @@
       <c r="C262" s="56" t="n"/>
       <c r="D262" s="43" t="n"/>
       <c r="P262">
-        <f>IF(B262="","",B262)</f>
+        <f>IF(OR(B262="",COUNTIF($B$6:$B262,B262)&gt;1),"",B262)</f>
         <v/>
       </c>
       <c r="Q262">
-        <f>IF(C262="","",C262)</f>
+        <f>IF(P262="","",C262)</f>
         <v/>
       </c>
       <c r="R262">
-        <f>IF(B262="","",SUMIF($B$6:$B$305,B262,$D$6:$D$305))</f>
+        <f>IF(P262="","",SUMIF($B$6:$B$305,B262,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S262">
-        <f>IF(OR(B262="",COUNTIF($B$6:$B262,B262)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R262)+(($R$6:$R$305=R262)*($B$6:$B$305&lt;B262)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P262="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R262,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R262,"="&amp;R262,$P$6:$P262,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23952,19 +23952,19 @@
       <c r="C263" s="56" t="n"/>
       <c r="D263" s="43" t="n"/>
       <c r="P263">
-        <f>IF(B263="","",B263)</f>
+        <f>IF(OR(B263="",COUNTIF($B$6:$B263,B263)&gt;1),"",B263)</f>
         <v/>
       </c>
       <c r="Q263">
-        <f>IF(C263="","",C263)</f>
+        <f>IF(P263="","",C263)</f>
         <v/>
       </c>
       <c r="R263">
-        <f>IF(B263="","",SUMIF($B$6:$B$305,B263,$D$6:$D$305))</f>
+        <f>IF(P263="","",SUMIF($B$6:$B$305,B263,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S263">
-        <f>IF(OR(B263="",COUNTIF($B$6:$B263,B263)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R263)+(($R$6:$R$305=R263)*($B$6:$B$305&lt;B263)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P263="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R263,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R263,"="&amp;R263,$P$6:$P263,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23974,19 +23974,19 @@
       <c r="C264" s="56" t="n"/>
       <c r="D264" s="43" t="n"/>
       <c r="P264">
-        <f>IF(B264="","",B264)</f>
+        <f>IF(OR(B264="",COUNTIF($B$6:$B264,B264)&gt;1),"",B264)</f>
         <v/>
       </c>
       <c r="Q264">
-        <f>IF(C264="","",C264)</f>
+        <f>IF(P264="","",C264)</f>
         <v/>
       </c>
       <c r="R264">
-        <f>IF(B264="","",SUMIF($B$6:$B$305,B264,$D$6:$D$305))</f>
+        <f>IF(P264="","",SUMIF($B$6:$B$305,B264,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S264">
-        <f>IF(OR(B264="",COUNTIF($B$6:$B264,B264)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R264)+(($R$6:$R$305=R264)*($B$6:$B$305&lt;B264)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P264="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R264,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R264,"="&amp;R264,$P$6:$P264,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -23996,19 +23996,19 @@
       <c r="C265" s="56" t="n"/>
       <c r="D265" s="43" t="n"/>
       <c r="P265">
-        <f>IF(B265="","",B265)</f>
+        <f>IF(OR(B265="",COUNTIF($B$6:$B265,B265)&gt;1),"",B265)</f>
         <v/>
       </c>
       <c r="Q265">
-        <f>IF(C265="","",C265)</f>
+        <f>IF(P265="","",C265)</f>
         <v/>
       </c>
       <c r="R265">
-        <f>IF(B265="","",SUMIF($B$6:$B$305,B265,$D$6:$D$305))</f>
+        <f>IF(P265="","",SUMIF($B$6:$B$305,B265,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S265">
-        <f>IF(OR(B265="",COUNTIF($B$6:$B265,B265)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R265)+(($R$6:$R$305=R265)*($B$6:$B$305&lt;B265)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P265="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R265,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R265,"="&amp;R265,$P$6:$P265,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24018,19 +24018,19 @@
       <c r="C266" s="56" t="n"/>
       <c r="D266" s="43" t="n"/>
       <c r="P266">
-        <f>IF(B266="","",B266)</f>
+        <f>IF(OR(B266="",COUNTIF($B$6:$B266,B266)&gt;1),"",B266)</f>
         <v/>
       </c>
       <c r="Q266">
-        <f>IF(C266="","",C266)</f>
+        <f>IF(P266="","",C266)</f>
         <v/>
       </c>
       <c r="R266">
-        <f>IF(B266="","",SUMIF($B$6:$B$305,B266,$D$6:$D$305))</f>
+        <f>IF(P266="","",SUMIF($B$6:$B$305,B266,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S266">
-        <f>IF(OR(B266="",COUNTIF($B$6:$B266,B266)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R266)+(($R$6:$R$305=R266)*($B$6:$B$305&lt;B266)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P266="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R266,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R266,"="&amp;R266,$P$6:$P266,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24040,19 +24040,19 @@
       <c r="C267" s="56" t="n"/>
       <c r="D267" s="43" t="n"/>
       <c r="P267">
-        <f>IF(B267="","",B267)</f>
+        <f>IF(OR(B267="",COUNTIF($B$6:$B267,B267)&gt;1),"",B267)</f>
         <v/>
       </c>
       <c r="Q267">
-        <f>IF(C267="","",C267)</f>
+        <f>IF(P267="","",C267)</f>
         <v/>
       </c>
       <c r="R267">
-        <f>IF(B267="","",SUMIF($B$6:$B$305,B267,$D$6:$D$305))</f>
+        <f>IF(P267="","",SUMIF($B$6:$B$305,B267,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S267">
-        <f>IF(OR(B267="",COUNTIF($B$6:$B267,B267)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R267)+(($R$6:$R$305=R267)*($B$6:$B$305&lt;B267)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P267="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R267,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R267,"="&amp;R267,$P$6:$P267,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24062,19 +24062,19 @@
       <c r="C268" s="56" t="n"/>
       <c r="D268" s="43" t="n"/>
       <c r="P268">
-        <f>IF(B268="","",B268)</f>
+        <f>IF(OR(B268="",COUNTIF($B$6:$B268,B268)&gt;1),"",B268)</f>
         <v/>
       </c>
       <c r="Q268">
-        <f>IF(C268="","",C268)</f>
+        <f>IF(P268="","",C268)</f>
         <v/>
       </c>
       <c r="R268">
-        <f>IF(B268="","",SUMIF($B$6:$B$305,B268,$D$6:$D$305))</f>
+        <f>IF(P268="","",SUMIF($B$6:$B$305,B268,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S268">
-        <f>IF(OR(B268="",COUNTIF($B$6:$B268,B268)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R268)+(($R$6:$R$305=R268)*($B$6:$B$305&lt;B268)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P268="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R268,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R268,"="&amp;R268,$P$6:$P268,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24084,19 +24084,19 @@
       <c r="C269" s="56" t="n"/>
       <c r="D269" s="43" t="n"/>
       <c r="P269">
-        <f>IF(B269="","",B269)</f>
+        <f>IF(OR(B269="",COUNTIF($B$6:$B269,B269)&gt;1),"",B269)</f>
         <v/>
       </c>
       <c r="Q269">
-        <f>IF(C269="","",C269)</f>
+        <f>IF(P269="","",C269)</f>
         <v/>
       </c>
       <c r="R269">
-        <f>IF(B269="","",SUMIF($B$6:$B$305,B269,$D$6:$D$305))</f>
+        <f>IF(P269="","",SUMIF($B$6:$B$305,B269,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S269">
-        <f>IF(OR(B269="",COUNTIF($B$6:$B269,B269)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R269)+(($R$6:$R$305=R269)*($B$6:$B$305&lt;B269)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P269="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R269,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R269,"="&amp;R269,$P$6:$P269,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24106,19 +24106,19 @@
       <c r="C270" s="56" t="n"/>
       <c r="D270" s="43" t="n"/>
       <c r="P270">
-        <f>IF(B270="","",B270)</f>
+        <f>IF(OR(B270="",COUNTIF($B$6:$B270,B270)&gt;1),"",B270)</f>
         <v/>
       </c>
       <c r="Q270">
-        <f>IF(C270="","",C270)</f>
+        <f>IF(P270="","",C270)</f>
         <v/>
       </c>
       <c r="R270">
-        <f>IF(B270="","",SUMIF($B$6:$B$305,B270,$D$6:$D$305))</f>
+        <f>IF(P270="","",SUMIF($B$6:$B$305,B270,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S270">
-        <f>IF(OR(B270="",COUNTIF($B$6:$B270,B270)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R270)+(($R$6:$R$305=R270)*($B$6:$B$305&lt;B270)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P270="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R270,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R270,"="&amp;R270,$P$6:$P270,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24128,19 +24128,19 @@
       <c r="C271" s="56" t="n"/>
       <c r="D271" s="43" t="n"/>
       <c r="P271">
-        <f>IF(B271="","",B271)</f>
+        <f>IF(OR(B271="",COUNTIF($B$6:$B271,B271)&gt;1),"",B271)</f>
         <v/>
       </c>
       <c r="Q271">
-        <f>IF(C271="","",C271)</f>
+        <f>IF(P271="","",C271)</f>
         <v/>
       </c>
       <c r="R271">
-        <f>IF(B271="","",SUMIF($B$6:$B$305,B271,$D$6:$D$305))</f>
+        <f>IF(P271="","",SUMIF($B$6:$B$305,B271,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S271">
-        <f>IF(OR(B271="",COUNTIF($B$6:$B271,B271)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R271)+(($R$6:$R$305=R271)*($B$6:$B$305&lt;B271)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P271="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R271,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R271,"="&amp;R271,$P$6:$P271,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24150,19 +24150,19 @@
       <c r="C272" s="56" t="n"/>
       <c r="D272" s="43" t="n"/>
       <c r="P272">
-        <f>IF(B272="","",B272)</f>
+        <f>IF(OR(B272="",COUNTIF($B$6:$B272,B272)&gt;1),"",B272)</f>
         <v/>
       </c>
       <c r="Q272">
-        <f>IF(C272="","",C272)</f>
+        <f>IF(P272="","",C272)</f>
         <v/>
       </c>
       <c r="R272">
-        <f>IF(B272="","",SUMIF($B$6:$B$305,B272,$D$6:$D$305))</f>
+        <f>IF(P272="","",SUMIF($B$6:$B$305,B272,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S272">
-        <f>IF(OR(B272="",COUNTIF($B$6:$B272,B272)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R272)+(($R$6:$R$305=R272)*($B$6:$B$305&lt;B272)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P272="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R272,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R272,"="&amp;R272,$P$6:$P272,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24172,19 +24172,19 @@
       <c r="C273" s="56" t="n"/>
       <c r="D273" s="43" t="n"/>
       <c r="P273">
-        <f>IF(B273="","",B273)</f>
+        <f>IF(OR(B273="",COUNTIF($B$6:$B273,B273)&gt;1),"",B273)</f>
         <v/>
       </c>
       <c r="Q273">
-        <f>IF(C273="","",C273)</f>
+        <f>IF(P273="","",C273)</f>
         <v/>
       </c>
       <c r="R273">
-        <f>IF(B273="","",SUMIF($B$6:$B$305,B273,$D$6:$D$305))</f>
+        <f>IF(P273="","",SUMIF($B$6:$B$305,B273,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S273">
-        <f>IF(OR(B273="",COUNTIF($B$6:$B273,B273)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R273)+(($R$6:$R$305=R273)*($B$6:$B$305&lt;B273)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P273="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R273,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R273,"="&amp;R273,$P$6:$P273,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24194,19 +24194,19 @@
       <c r="C274" s="56" t="n"/>
       <c r="D274" s="43" t="n"/>
       <c r="P274">
-        <f>IF(B274="","",B274)</f>
+        <f>IF(OR(B274="",COUNTIF($B$6:$B274,B274)&gt;1),"",B274)</f>
         <v/>
       </c>
       <c r="Q274">
-        <f>IF(C274="","",C274)</f>
+        <f>IF(P274="","",C274)</f>
         <v/>
       </c>
       <c r="R274">
-        <f>IF(B274="","",SUMIF($B$6:$B$305,B274,$D$6:$D$305))</f>
+        <f>IF(P274="","",SUMIF($B$6:$B$305,B274,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S274">
-        <f>IF(OR(B274="",COUNTIF($B$6:$B274,B274)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R274)+(($R$6:$R$305=R274)*($B$6:$B$305&lt;B274)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P274="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R274,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R274,"="&amp;R274,$P$6:$P274,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24216,19 +24216,19 @@
       <c r="C275" s="56" t="n"/>
       <c r="D275" s="43" t="n"/>
       <c r="P275">
-        <f>IF(B275="","",B275)</f>
+        <f>IF(OR(B275="",COUNTIF($B$6:$B275,B275)&gt;1),"",B275)</f>
         <v/>
       </c>
       <c r="Q275">
-        <f>IF(C275="","",C275)</f>
+        <f>IF(P275="","",C275)</f>
         <v/>
       </c>
       <c r="R275">
-        <f>IF(B275="","",SUMIF($B$6:$B$305,B275,$D$6:$D$305))</f>
+        <f>IF(P275="","",SUMIF($B$6:$B$305,B275,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S275">
-        <f>IF(OR(B275="",COUNTIF($B$6:$B275,B275)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R275)+(($R$6:$R$305=R275)*($B$6:$B$305&lt;B275)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P275="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R275,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R275,"="&amp;R275,$P$6:$P275,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24238,19 +24238,19 @@
       <c r="C276" s="56" t="n"/>
       <c r="D276" s="43" t="n"/>
       <c r="P276">
-        <f>IF(B276="","",B276)</f>
+        <f>IF(OR(B276="",COUNTIF($B$6:$B276,B276)&gt;1),"",B276)</f>
         <v/>
       </c>
       <c r="Q276">
-        <f>IF(C276="","",C276)</f>
+        <f>IF(P276="","",C276)</f>
         <v/>
       </c>
       <c r="R276">
-        <f>IF(B276="","",SUMIF($B$6:$B$305,B276,$D$6:$D$305))</f>
+        <f>IF(P276="","",SUMIF($B$6:$B$305,B276,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S276">
-        <f>IF(OR(B276="",COUNTIF($B$6:$B276,B276)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R276)+(($R$6:$R$305=R276)*($B$6:$B$305&lt;B276)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P276="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R276,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R276,"="&amp;R276,$P$6:$P276,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24260,19 +24260,19 @@
       <c r="C277" s="56" t="n"/>
       <c r="D277" s="43" t="n"/>
       <c r="P277">
-        <f>IF(B277="","",B277)</f>
+        <f>IF(OR(B277="",COUNTIF($B$6:$B277,B277)&gt;1),"",B277)</f>
         <v/>
       </c>
       <c r="Q277">
-        <f>IF(C277="","",C277)</f>
+        <f>IF(P277="","",C277)</f>
         <v/>
       </c>
       <c r="R277">
-        <f>IF(B277="","",SUMIF($B$6:$B$305,B277,$D$6:$D$305))</f>
+        <f>IF(P277="","",SUMIF($B$6:$B$305,B277,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S277">
-        <f>IF(OR(B277="",COUNTIF($B$6:$B277,B277)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R277)+(($R$6:$R$305=R277)*($B$6:$B$305&lt;B277)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P277="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R277,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R277,"="&amp;R277,$P$6:$P277,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24282,19 +24282,19 @@
       <c r="C278" s="56" t="n"/>
       <c r="D278" s="43" t="n"/>
       <c r="P278">
-        <f>IF(B278="","",B278)</f>
+        <f>IF(OR(B278="",COUNTIF($B$6:$B278,B278)&gt;1),"",B278)</f>
         <v/>
       </c>
       <c r="Q278">
-        <f>IF(C278="","",C278)</f>
+        <f>IF(P278="","",C278)</f>
         <v/>
       </c>
       <c r="R278">
-        <f>IF(B278="","",SUMIF($B$6:$B$305,B278,$D$6:$D$305))</f>
+        <f>IF(P278="","",SUMIF($B$6:$B$305,B278,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S278">
-        <f>IF(OR(B278="",COUNTIF($B$6:$B278,B278)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R278)+(($R$6:$R$305=R278)*($B$6:$B$305&lt;B278)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P278="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R278,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R278,"="&amp;R278,$P$6:$P278,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24304,19 +24304,19 @@
       <c r="C279" s="56" t="n"/>
       <c r="D279" s="43" t="n"/>
       <c r="P279">
-        <f>IF(B279="","",B279)</f>
+        <f>IF(OR(B279="",COUNTIF($B$6:$B279,B279)&gt;1),"",B279)</f>
         <v/>
       </c>
       <c r="Q279">
-        <f>IF(C279="","",C279)</f>
+        <f>IF(P279="","",C279)</f>
         <v/>
       </c>
       <c r="R279">
-        <f>IF(B279="","",SUMIF($B$6:$B$305,B279,$D$6:$D$305))</f>
+        <f>IF(P279="","",SUMIF($B$6:$B$305,B279,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S279">
-        <f>IF(OR(B279="",COUNTIF($B$6:$B279,B279)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R279)+(($R$6:$R$305=R279)*($B$6:$B$305&lt;B279)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P279="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R279,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R279,"="&amp;R279,$P$6:$P279,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24326,19 +24326,19 @@
       <c r="C280" s="56" t="n"/>
       <c r="D280" s="43" t="n"/>
       <c r="P280">
-        <f>IF(B280="","",B280)</f>
+        <f>IF(OR(B280="",COUNTIF($B$6:$B280,B280)&gt;1),"",B280)</f>
         <v/>
       </c>
       <c r="Q280">
-        <f>IF(C280="","",C280)</f>
+        <f>IF(P280="","",C280)</f>
         <v/>
       </c>
       <c r="R280">
-        <f>IF(B280="","",SUMIF($B$6:$B$305,B280,$D$6:$D$305))</f>
+        <f>IF(P280="","",SUMIF($B$6:$B$305,B280,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S280">
-        <f>IF(OR(B280="",COUNTIF($B$6:$B280,B280)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R280)+(($R$6:$R$305=R280)*($B$6:$B$305&lt;B280)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P280="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R280,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R280,"="&amp;R280,$P$6:$P280,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24348,19 +24348,19 @@
       <c r="C281" s="56" t="n"/>
       <c r="D281" s="43" t="n"/>
       <c r="P281">
-        <f>IF(B281="","",B281)</f>
+        <f>IF(OR(B281="",COUNTIF($B$6:$B281,B281)&gt;1),"",B281)</f>
         <v/>
       </c>
       <c r="Q281">
-        <f>IF(C281="","",C281)</f>
+        <f>IF(P281="","",C281)</f>
         <v/>
       </c>
       <c r="R281">
-        <f>IF(B281="","",SUMIF($B$6:$B$305,B281,$D$6:$D$305))</f>
+        <f>IF(P281="","",SUMIF($B$6:$B$305,B281,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S281">
-        <f>IF(OR(B281="",COUNTIF($B$6:$B281,B281)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R281)+(($R$6:$R$305=R281)*($B$6:$B$305&lt;B281)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P281="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R281,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R281,"="&amp;R281,$P$6:$P281,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24370,19 +24370,19 @@
       <c r="C282" s="56" t="n"/>
       <c r="D282" s="43" t="n"/>
       <c r="P282">
-        <f>IF(B282="","",B282)</f>
+        <f>IF(OR(B282="",COUNTIF($B$6:$B282,B282)&gt;1),"",B282)</f>
         <v/>
       </c>
       <c r="Q282">
-        <f>IF(C282="","",C282)</f>
+        <f>IF(P282="","",C282)</f>
         <v/>
       </c>
       <c r="R282">
-        <f>IF(B282="","",SUMIF($B$6:$B$305,B282,$D$6:$D$305))</f>
+        <f>IF(P282="","",SUMIF($B$6:$B$305,B282,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S282">
-        <f>IF(OR(B282="",COUNTIF($B$6:$B282,B282)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R282)+(($R$6:$R$305=R282)*($B$6:$B$305&lt;B282)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P282="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R282,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R282,"="&amp;R282,$P$6:$P282,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24392,19 +24392,19 @@
       <c r="C283" s="56" t="n"/>
       <c r="D283" s="43" t="n"/>
       <c r="P283">
-        <f>IF(B283="","",B283)</f>
+        <f>IF(OR(B283="",COUNTIF($B$6:$B283,B283)&gt;1),"",B283)</f>
         <v/>
       </c>
       <c r="Q283">
-        <f>IF(C283="","",C283)</f>
+        <f>IF(P283="","",C283)</f>
         <v/>
       </c>
       <c r="R283">
-        <f>IF(B283="","",SUMIF($B$6:$B$305,B283,$D$6:$D$305))</f>
+        <f>IF(P283="","",SUMIF($B$6:$B$305,B283,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S283">
-        <f>IF(OR(B283="",COUNTIF($B$6:$B283,B283)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R283)+(($R$6:$R$305=R283)*($B$6:$B$305&lt;B283)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P283="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R283,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R283,"="&amp;R283,$P$6:$P283,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24414,19 +24414,19 @@
       <c r="C284" s="56" t="n"/>
       <c r="D284" s="43" t="n"/>
       <c r="P284">
-        <f>IF(B284="","",B284)</f>
+        <f>IF(OR(B284="",COUNTIF($B$6:$B284,B284)&gt;1),"",B284)</f>
         <v/>
       </c>
       <c r="Q284">
-        <f>IF(C284="","",C284)</f>
+        <f>IF(P284="","",C284)</f>
         <v/>
       </c>
       <c r="R284">
-        <f>IF(B284="","",SUMIF($B$6:$B$305,B284,$D$6:$D$305))</f>
+        <f>IF(P284="","",SUMIF($B$6:$B$305,B284,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S284">
-        <f>IF(OR(B284="",COUNTIF($B$6:$B284,B284)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R284)+(($R$6:$R$305=R284)*($B$6:$B$305&lt;B284)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P284="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R284,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R284,"="&amp;R284,$P$6:$P284,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24436,19 +24436,19 @@
       <c r="C285" s="56" t="n"/>
       <c r="D285" s="43" t="n"/>
       <c r="P285">
-        <f>IF(B285="","",B285)</f>
+        <f>IF(OR(B285="",COUNTIF($B$6:$B285,B285)&gt;1),"",B285)</f>
         <v/>
       </c>
       <c r="Q285">
-        <f>IF(C285="","",C285)</f>
+        <f>IF(P285="","",C285)</f>
         <v/>
       </c>
       <c r="R285">
-        <f>IF(B285="","",SUMIF($B$6:$B$305,B285,$D$6:$D$305))</f>
+        <f>IF(P285="","",SUMIF($B$6:$B$305,B285,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S285">
-        <f>IF(OR(B285="",COUNTIF($B$6:$B285,B285)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R285)+(($R$6:$R$305=R285)*($B$6:$B$305&lt;B285)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P285="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R285,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R285,"="&amp;R285,$P$6:$P285,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24458,19 +24458,19 @@
       <c r="C286" s="56" t="n"/>
       <c r="D286" s="43" t="n"/>
       <c r="P286">
-        <f>IF(B286="","",B286)</f>
+        <f>IF(OR(B286="",COUNTIF($B$6:$B286,B286)&gt;1),"",B286)</f>
         <v/>
       </c>
       <c r="Q286">
-        <f>IF(C286="","",C286)</f>
+        <f>IF(P286="","",C286)</f>
         <v/>
       </c>
       <c r="R286">
-        <f>IF(B286="","",SUMIF($B$6:$B$305,B286,$D$6:$D$305))</f>
+        <f>IF(P286="","",SUMIF($B$6:$B$305,B286,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S286">
-        <f>IF(OR(B286="",COUNTIF($B$6:$B286,B286)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R286)+(($R$6:$R$305=R286)*($B$6:$B$305&lt;B286)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P286="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R286,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R286,"="&amp;R286,$P$6:$P286,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24480,19 +24480,19 @@
       <c r="C287" s="56" t="n"/>
       <c r="D287" s="43" t="n"/>
       <c r="P287">
-        <f>IF(B287="","",B287)</f>
+        <f>IF(OR(B287="",COUNTIF($B$6:$B287,B287)&gt;1),"",B287)</f>
         <v/>
       </c>
       <c r="Q287">
-        <f>IF(C287="","",C287)</f>
+        <f>IF(P287="","",C287)</f>
         <v/>
       </c>
       <c r="R287">
-        <f>IF(B287="","",SUMIF($B$6:$B$305,B287,$D$6:$D$305))</f>
+        <f>IF(P287="","",SUMIF($B$6:$B$305,B287,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S287">
-        <f>IF(OR(B287="",COUNTIF($B$6:$B287,B287)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R287)+(($R$6:$R$305=R287)*($B$6:$B$305&lt;B287)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P287="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R287,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R287,"="&amp;R287,$P$6:$P287,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24502,19 +24502,19 @@
       <c r="C288" s="56" t="n"/>
       <c r="D288" s="43" t="n"/>
       <c r="P288">
-        <f>IF(B288="","",B288)</f>
+        <f>IF(OR(B288="",COUNTIF($B$6:$B288,B288)&gt;1),"",B288)</f>
         <v/>
       </c>
       <c r="Q288">
-        <f>IF(C288="","",C288)</f>
+        <f>IF(P288="","",C288)</f>
         <v/>
       </c>
       <c r="R288">
-        <f>IF(B288="","",SUMIF($B$6:$B$305,B288,$D$6:$D$305))</f>
+        <f>IF(P288="","",SUMIF($B$6:$B$305,B288,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S288">
-        <f>IF(OR(B288="",COUNTIF($B$6:$B288,B288)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R288)+(($R$6:$R$305=R288)*($B$6:$B$305&lt;B288)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P288="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R288,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R288,"="&amp;R288,$P$6:$P288,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24524,19 +24524,19 @@
       <c r="C289" s="56" t="n"/>
       <c r="D289" s="43" t="n"/>
       <c r="P289">
-        <f>IF(B289="","",B289)</f>
+        <f>IF(OR(B289="",COUNTIF($B$6:$B289,B289)&gt;1),"",B289)</f>
         <v/>
       </c>
       <c r="Q289">
-        <f>IF(C289="","",C289)</f>
+        <f>IF(P289="","",C289)</f>
         <v/>
       </c>
       <c r="R289">
-        <f>IF(B289="","",SUMIF($B$6:$B$305,B289,$D$6:$D$305))</f>
+        <f>IF(P289="","",SUMIF($B$6:$B$305,B289,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S289">
-        <f>IF(OR(B289="",COUNTIF($B$6:$B289,B289)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R289)+(($R$6:$R$305=R289)*($B$6:$B$305&lt;B289)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P289="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R289,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R289,"="&amp;R289,$P$6:$P289,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24546,19 +24546,19 @@
       <c r="C290" s="56" t="n"/>
       <c r="D290" s="43" t="n"/>
       <c r="P290">
-        <f>IF(B290="","",B290)</f>
+        <f>IF(OR(B290="",COUNTIF($B$6:$B290,B290)&gt;1),"",B290)</f>
         <v/>
       </c>
       <c r="Q290">
-        <f>IF(C290="","",C290)</f>
+        <f>IF(P290="","",C290)</f>
         <v/>
       </c>
       <c r="R290">
-        <f>IF(B290="","",SUMIF($B$6:$B$305,B290,$D$6:$D$305))</f>
+        <f>IF(P290="","",SUMIF($B$6:$B$305,B290,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S290">
-        <f>IF(OR(B290="",COUNTIF($B$6:$B290,B290)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R290)+(($R$6:$R$305=R290)*($B$6:$B$305&lt;B290)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P290="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R290,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R290,"="&amp;R290,$P$6:$P290,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24568,19 +24568,19 @@
       <c r="C291" s="56" t="n"/>
       <c r="D291" s="43" t="n"/>
       <c r="P291">
-        <f>IF(B291="","",B291)</f>
+        <f>IF(OR(B291="",COUNTIF($B$6:$B291,B291)&gt;1),"",B291)</f>
         <v/>
       </c>
       <c r="Q291">
-        <f>IF(C291="","",C291)</f>
+        <f>IF(P291="","",C291)</f>
         <v/>
       </c>
       <c r="R291">
-        <f>IF(B291="","",SUMIF($B$6:$B$305,B291,$D$6:$D$305))</f>
+        <f>IF(P291="","",SUMIF($B$6:$B$305,B291,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S291">
-        <f>IF(OR(B291="",COUNTIF($B$6:$B291,B291)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R291)+(($R$6:$R$305=R291)*($B$6:$B$305&lt;B291)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P291="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R291,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R291,"="&amp;R291,$P$6:$P291,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24590,19 +24590,19 @@
       <c r="C292" s="56" t="n"/>
       <c r="D292" s="43" t="n"/>
       <c r="P292">
-        <f>IF(B292="","",B292)</f>
+        <f>IF(OR(B292="",COUNTIF($B$6:$B292,B292)&gt;1),"",B292)</f>
         <v/>
       </c>
       <c r="Q292">
-        <f>IF(C292="","",C292)</f>
+        <f>IF(P292="","",C292)</f>
         <v/>
       </c>
       <c r="R292">
-        <f>IF(B292="","",SUMIF($B$6:$B$305,B292,$D$6:$D$305))</f>
+        <f>IF(P292="","",SUMIF($B$6:$B$305,B292,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S292">
-        <f>IF(OR(B292="",COUNTIF($B$6:$B292,B292)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R292)+(($R$6:$R$305=R292)*($B$6:$B$305&lt;B292)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P292="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R292,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R292,"="&amp;R292,$P$6:$P292,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24612,19 +24612,19 @@
       <c r="C293" s="56" t="n"/>
       <c r="D293" s="43" t="n"/>
       <c r="P293">
-        <f>IF(B293="","",B293)</f>
+        <f>IF(OR(B293="",COUNTIF($B$6:$B293,B293)&gt;1),"",B293)</f>
         <v/>
       </c>
       <c r="Q293">
-        <f>IF(C293="","",C293)</f>
+        <f>IF(P293="","",C293)</f>
         <v/>
       </c>
       <c r="R293">
-        <f>IF(B293="","",SUMIF($B$6:$B$305,B293,$D$6:$D$305))</f>
+        <f>IF(P293="","",SUMIF($B$6:$B$305,B293,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S293">
-        <f>IF(OR(B293="",COUNTIF($B$6:$B293,B293)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R293)+(($R$6:$R$305=R293)*($B$6:$B$305&lt;B293)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P293="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R293,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R293,"="&amp;R293,$P$6:$P293,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24634,19 +24634,19 @@
       <c r="C294" s="56" t="n"/>
       <c r="D294" s="43" t="n"/>
       <c r="P294">
-        <f>IF(B294="","",B294)</f>
+        <f>IF(OR(B294="",COUNTIF($B$6:$B294,B294)&gt;1),"",B294)</f>
         <v/>
       </c>
       <c r="Q294">
-        <f>IF(C294="","",C294)</f>
+        <f>IF(P294="","",C294)</f>
         <v/>
       </c>
       <c r="R294">
-        <f>IF(B294="","",SUMIF($B$6:$B$305,B294,$D$6:$D$305))</f>
+        <f>IF(P294="","",SUMIF($B$6:$B$305,B294,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S294">
-        <f>IF(OR(B294="",COUNTIF($B$6:$B294,B294)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R294)+(($R$6:$R$305=R294)*($B$6:$B$305&lt;B294)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P294="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R294,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R294,"="&amp;R294,$P$6:$P294,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24656,19 +24656,19 @@
       <c r="C295" s="56" t="n"/>
       <c r="D295" s="43" t="n"/>
       <c r="P295">
-        <f>IF(B295="","",B295)</f>
+        <f>IF(OR(B295="",COUNTIF($B$6:$B295,B295)&gt;1),"",B295)</f>
         <v/>
       </c>
       <c r="Q295">
-        <f>IF(C295="","",C295)</f>
+        <f>IF(P295="","",C295)</f>
         <v/>
       </c>
       <c r="R295">
-        <f>IF(B295="","",SUMIF($B$6:$B$305,B295,$D$6:$D$305))</f>
+        <f>IF(P295="","",SUMIF($B$6:$B$305,B295,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S295">
-        <f>IF(OR(B295="",COUNTIF($B$6:$B295,B295)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R295)+(($R$6:$R$305=R295)*($B$6:$B$305&lt;B295)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P295="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R295,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R295,"="&amp;R295,$P$6:$P295,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24678,19 +24678,19 @@
       <c r="C296" s="56" t="n"/>
       <c r="D296" s="43" t="n"/>
       <c r="P296">
-        <f>IF(B296="","",B296)</f>
+        <f>IF(OR(B296="",COUNTIF($B$6:$B296,B296)&gt;1),"",B296)</f>
         <v/>
       </c>
       <c r="Q296">
-        <f>IF(C296="","",C296)</f>
+        <f>IF(P296="","",C296)</f>
         <v/>
       </c>
       <c r="R296">
-        <f>IF(B296="","",SUMIF($B$6:$B$305,B296,$D$6:$D$305))</f>
+        <f>IF(P296="","",SUMIF($B$6:$B$305,B296,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S296">
-        <f>IF(OR(B296="",COUNTIF($B$6:$B296,B296)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R296)+(($R$6:$R$305=R296)*($B$6:$B$305&lt;B296)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P296="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R296,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R296,"="&amp;R296,$P$6:$P296,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24700,19 +24700,19 @@
       <c r="C297" s="56" t="n"/>
       <c r="D297" s="43" t="n"/>
       <c r="P297">
-        <f>IF(B297="","",B297)</f>
+        <f>IF(OR(B297="",COUNTIF($B$6:$B297,B297)&gt;1),"",B297)</f>
         <v/>
       </c>
       <c r="Q297">
-        <f>IF(C297="","",C297)</f>
+        <f>IF(P297="","",C297)</f>
         <v/>
       </c>
       <c r="R297">
-        <f>IF(B297="","",SUMIF($B$6:$B$305,B297,$D$6:$D$305))</f>
+        <f>IF(P297="","",SUMIF($B$6:$B$305,B297,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S297">
-        <f>IF(OR(B297="",COUNTIF($B$6:$B297,B297)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R297)+(($R$6:$R$305=R297)*($B$6:$B$305&lt;B297)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P297="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R297,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R297,"="&amp;R297,$P$6:$P297,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24722,19 +24722,19 @@
       <c r="C298" s="56" t="n"/>
       <c r="D298" s="43" t="n"/>
       <c r="P298">
-        <f>IF(B298="","",B298)</f>
+        <f>IF(OR(B298="",COUNTIF($B$6:$B298,B298)&gt;1),"",B298)</f>
         <v/>
       </c>
       <c r="Q298">
-        <f>IF(C298="","",C298)</f>
+        <f>IF(P298="","",C298)</f>
         <v/>
       </c>
       <c r="R298">
-        <f>IF(B298="","",SUMIF($B$6:$B$305,B298,$D$6:$D$305))</f>
+        <f>IF(P298="","",SUMIF($B$6:$B$305,B298,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S298">
-        <f>IF(OR(B298="",COUNTIF($B$6:$B298,B298)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R298)+(($R$6:$R$305=R298)*($B$6:$B$305&lt;B298)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P298="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R298,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R298,"="&amp;R298,$P$6:$P298,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24744,19 +24744,19 @@
       <c r="C299" s="56" t="n"/>
       <c r="D299" s="43" t="n"/>
       <c r="P299">
-        <f>IF(B299="","",B299)</f>
+        <f>IF(OR(B299="",COUNTIF($B$6:$B299,B299)&gt;1),"",B299)</f>
         <v/>
       </c>
       <c r="Q299">
-        <f>IF(C299="","",C299)</f>
+        <f>IF(P299="","",C299)</f>
         <v/>
       </c>
       <c r="R299">
-        <f>IF(B299="","",SUMIF($B$6:$B$305,B299,$D$6:$D$305))</f>
+        <f>IF(P299="","",SUMIF($B$6:$B$305,B299,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S299">
-        <f>IF(OR(B299="",COUNTIF($B$6:$B299,B299)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R299)+(($R$6:$R$305=R299)*($B$6:$B$305&lt;B299)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P299="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R299,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R299,"="&amp;R299,$P$6:$P299,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24766,19 +24766,19 @@
       <c r="C300" s="56" t="n"/>
       <c r="D300" s="43" t="n"/>
       <c r="P300">
-        <f>IF(B300="","",B300)</f>
+        <f>IF(OR(B300="",COUNTIF($B$6:$B300,B300)&gt;1),"",B300)</f>
         <v/>
       </c>
       <c r="Q300">
-        <f>IF(C300="","",C300)</f>
+        <f>IF(P300="","",C300)</f>
         <v/>
       </c>
       <c r="R300">
-        <f>IF(B300="","",SUMIF($B$6:$B$305,B300,$D$6:$D$305))</f>
+        <f>IF(P300="","",SUMIF($B$6:$B$305,B300,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S300">
-        <f>IF(OR(B300="",COUNTIF($B$6:$B300,B300)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R300)+(($R$6:$R$305=R300)*($B$6:$B$305&lt;B300)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P300="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R300,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R300,"="&amp;R300,$P$6:$P300,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24788,19 +24788,19 @@
       <c r="C301" s="56" t="n"/>
       <c r="D301" s="43" t="n"/>
       <c r="P301">
-        <f>IF(B301="","",B301)</f>
+        <f>IF(OR(B301="",COUNTIF($B$6:$B301,B301)&gt;1),"",B301)</f>
         <v/>
       </c>
       <c r="Q301">
-        <f>IF(C301="","",C301)</f>
+        <f>IF(P301="","",C301)</f>
         <v/>
       </c>
       <c r="R301">
-        <f>IF(B301="","",SUMIF($B$6:$B$305,B301,$D$6:$D$305))</f>
+        <f>IF(P301="","",SUMIF($B$6:$B$305,B301,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S301">
-        <f>IF(OR(B301="",COUNTIF($B$6:$B301,B301)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R301)+(($R$6:$R$305=R301)*($B$6:$B$305&lt;B301)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P301="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R301,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R301,"="&amp;R301,$P$6:$P301,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24810,19 +24810,19 @@
       <c r="C302" s="56" t="n"/>
       <c r="D302" s="43" t="n"/>
       <c r="P302">
-        <f>IF(B302="","",B302)</f>
+        <f>IF(OR(B302="",COUNTIF($B$6:$B302,B302)&gt;1),"",B302)</f>
         <v/>
       </c>
       <c r="Q302">
-        <f>IF(C302="","",C302)</f>
+        <f>IF(P302="","",C302)</f>
         <v/>
       </c>
       <c r="R302">
-        <f>IF(B302="","",SUMIF($B$6:$B$305,B302,$D$6:$D$305))</f>
+        <f>IF(P302="","",SUMIF($B$6:$B$305,B302,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S302">
-        <f>IF(OR(B302="",COUNTIF($B$6:$B302,B302)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R302)+(($R$6:$R$305=R302)*($B$6:$B$305&lt;B302)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P302="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R302,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R302,"="&amp;R302,$P$6:$P302,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24832,19 +24832,19 @@
       <c r="C303" s="56" t="n"/>
       <c r="D303" s="43" t="n"/>
       <c r="P303">
-        <f>IF(B303="","",B303)</f>
+        <f>IF(OR(B303="",COUNTIF($B$6:$B303,B303)&gt;1),"",B303)</f>
         <v/>
       </c>
       <c r="Q303">
-        <f>IF(C303="","",C303)</f>
+        <f>IF(P303="","",C303)</f>
         <v/>
       </c>
       <c r="R303">
-        <f>IF(B303="","",SUMIF($B$6:$B$305,B303,$D$6:$D$305))</f>
+        <f>IF(P303="","",SUMIF($B$6:$B$305,B303,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S303">
-        <f>IF(OR(B303="",COUNTIF($B$6:$B303,B303)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R303)+(($R$6:$R$305=R303)*($B$6:$B$305&lt;B303)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P303="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R303,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R303,"="&amp;R303,$P$6:$P303,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24854,19 +24854,19 @@
       <c r="C304" s="56" t="n"/>
       <c r="D304" s="43" t="n"/>
       <c r="P304">
-        <f>IF(B304="","",B304)</f>
+        <f>IF(OR(B304="",COUNTIF($B$6:$B304,B304)&gt;1),"",B304)</f>
         <v/>
       </c>
       <c r="Q304">
-        <f>IF(C304="","",C304)</f>
+        <f>IF(P304="","",C304)</f>
         <v/>
       </c>
       <c r="R304">
-        <f>IF(B304="","",SUMIF($B$6:$B$305,B304,$D$6:$D$305))</f>
+        <f>IF(P304="","",SUMIF($B$6:$B$305,B304,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S304">
-        <f>IF(OR(B304="",COUNTIF($B$6:$B304,B304)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R304)+(($R$6:$R$305=R304)*($B$6:$B$305&lt;B304)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P304="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R304,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R304,"="&amp;R304,$P$6:$P304,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
@@ -24876,19 +24876,19 @@
       <c r="C305" s="56" t="n"/>
       <c r="D305" s="43" t="n"/>
       <c r="P305">
-        <f>IF(B305="","",B305)</f>
+        <f>IF(OR(B305="",COUNTIF($B$6:$B305,B305)&gt;1),"",B305)</f>
         <v/>
       </c>
       <c r="Q305">
-        <f>IF(C305="","",C305)</f>
+        <f>IF(P305="","",C305)</f>
         <v/>
       </c>
       <c r="R305">
-        <f>IF(B305="","",SUMIF($B$6:$B$305,B305,$D$6:$D$305))</f>
+        <f>IF(P305="","",SUMIF($B$6:$B$305,B305,$D$6:$D$305))</f>
         <v/>
       </c>
       <c r="S305">
-        <f>IF(OR(B305="",COUNTIF($B$6:$B305,B305)&gt;1),"",ROUND(SUMPRODUCT(($B$6:$B$305&lt;&gt;"")*(($R$6:$R$305&gt;R305)+(($R$6:$R$305=R305)*($B$6:$B$305&lt;B305)))/COUNTIF($B$6:$B$305,$B$6:$B$305)),0)+1)</f>
+        <f>IF(P305="","",COUNTIFS($R$6:$R$305,"&gt;"&amp;R305,$P$6:$P$305,"&lt;&gt;")+COUNTIFS($R$6:$R305,"="&amp;R305,$P$6:$P305,"&lt;&gt;"))</f>
         <v/>
       </c>
     </row>
